--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Artist Database" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Artist Database" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artist Database'!$A$1:$R$1</definedName>
@@ -741,9 +741,8 @@
       <c r="N2" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O2" s="6">
-        <f>AVERAGE(J2:N2)</f>
-        <v/>
+      <c r="O2" s="6" t="n">
+        <v>3</v>
       </c>
       <c r="P2" s="7" t="inlineStr">
         <is>
@@ -814,9 +813,8 @@
       <c r="N3" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O3" s="6">
-        <f>AVERAGE(J3:N3)</f>
-        <v/>
+      <c r="O3" s="6" t="n">
+        <v>5.6</v>
       </c>
       <c r="P3" s="7" t="inlineStr">
         <is>
@@ -887,9 +885,8 @@
       <c r="N4" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O4" s="6">
-        <f>AVERAGE(J4:N4)</f>
-        <v/>
+      <c r="O4" s="6" t="n">
+        <v>7.6</v>
       </c>
       <c r="P4" s="7" t="inlineStr">
         <is>
@@ -899,7 +896,7 @@
       <c r="Q4" s="2" t="inlineStr"/>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>'The Message' redefined what rap could say.</t>
+          <t>'The Message' — first truly serious rap lyric. Dark imagery of urban decay.</t>
         </is>
       </c>
     </row>
@@ -960,9 +957,8 @@
       <c r="N5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="O5" s="6">
-        <f>AVERAGE(J5:N5)</f>
-        <v/>
+      <c r="O5" s="6" t="n">
+        <v>3.2</v>
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
@@ -972,7 +968,7 @@
       <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>First commercial rap hit.</t>
+          <t>Brought hip-hop mainstream with 'Rapper's Delight'.</t>
         </is>
       </c>
     </row>
@@ -1033,9 +1029,8 @@
       <c r="N6" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="O6" s="6">
-        <f>AVERAGE(J6:N6)</f>
-        <v/>
+      <c r="O6" s="6" t="n">
+        <v>4.4</v>
       </c>
       <c r="P6" s="7" t="inlineStr">
         <is>
@@ -1045,7 +1040,7 @@
       <c r="Q6" s="2" t="inlineStr"/>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>Zulu Nation founder. Bridged hip-hop to electronic music.</t>
+          <t>'Planet Rock' visionary. Pan-African ideology in party form.</t>
         </is>
       </c>
     </row>
@@ -1106,9 +1101,8 @@
       <c r="N7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O7" s="6">
-        <f>AVERAGE(J7:N7)</f>
-        <v/>
+      <c r="O7" s="6" t="n">
+        <v>5.4</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1112,7 @@
       <c r="Q7" s="2" t="inlineStr"/>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>Defied rock and roll skeptics. First major Def Jam artist.</t>
+          <t>Def Jam's first star. Swagger as technique.</t>
         </is>
       </c>
     </row>
@@ -1179,9 +1173,8 @@
       <c r="N8" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O8" s="6">
-        <f>AVERAGE(J8:N8)</f>
-        <v/>
+      <c r="O8" s="6" t="n">
+        <v>5.2</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -1191,7 +1184,7 @@
       <c r="Q8" s="2" t="inlineStr"/>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>Integrated rock into rap. Made Adidas iconic.</t>
+          <t>Merged rock and rap. Iconic minimalism.</t>
         </is>
       </c>
     </row>
@@ -1252,9 +1245,8 @@
       <c r="N9" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O9" s="6">
-        <f>AVERAGE(J9:N9)</f>
-        <v/>
+      <c r="O9" s="6" t="n">
+        <v>5.8</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -1264,7 +1256,7 @@
       <c r="Q9" s="2" t="inlineStr"/>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>Crossover kings. Made rap acceptable to white rock audiences.</t>
+          <t>Frenetic cultural collage. Grew into genuine experimental sophistication.</t>
         </is>
       </c>
     </row>
@@ -1325,9 +1317,8 @@
       <c r="N10" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O10" s="6">
-        <f>AVERAGE(J10:N10)</f>
-        <v/>
+      <c r="O10" s="6" t="n">
+        <v>7.8</v>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
@@ -1337,7 +1328,7 @@
       <c r="Q10" s="2" t="inlineStr"/>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>The Teacha. 'South Bronx' battle classic.</t>
+          <t>'The Teacha.' Hip-hop philosopher-MC.</t>
         </is>
       </c>
     </row>
@@ -1398,9 +1389,8 @@
       <c r="N11" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="O11" s="6">
-        <f>AVERAGE(J11:N11)</f>
-        <v/>
+      <c r="O11" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
@@ -1410,7 +1400,7 @@
       <c r="Q11" s="2" t="inlineStr"/>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>Most politically explosive group in rap history.</t>
+          <t>Maximum political rage. Bomb Squad production as sonic warfare.</t>
         </is>
       </c>
     </row>
@@ -1471,9 +1461,8 @@
       <c r="N12" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="O12" s="6">
-        <f>AVERAGE(J12:N12)</f>
-        <v/>
+      <c r="O12" s="6" t="n">
+        <v>6.2</v>
       </c>
       <c r="P12" s="14" t="inlineStr">
         <is>
@@ -1487,7 +1476,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>First female voice in a rap beef. Battle rap pioneer.</t>
+          <t>Pioneer female MC. Battle rap legend at age 14. Foundational for women in hip-hop.</t>
         </is>
       </c>
     </row>
@@ -1548,9 +1537,8 @@
       <c r="N13" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O13" s="6">
-        <f>AVERAGE(J13:N13)</f>
-        <v/>
+      <c r="O13" s="6" t="n">
+        <v>6.8</v>
       </c>
       <c r="P13" s="14" t="inlineStr">
         <is>
@@ -1564,7 +1552,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>First female rapper to release a full solo album.</t>
+          <t>First solo female rapper to release a full album. Sharp, authoritative delivery.</t>
         </is>
       </c>
     </row>
@@ -1625,9 +1613,8 @@
       <c r="N14" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="O14" s="6">
-        <f>AVERAGE(J14:N14)</f>
-        <v/>
+      <c r="O14" s="6" t="n">
+        <v>5.4</v>
       </c>
       <c r="P14" s="14" t="inlineStr">
         <is>
@@ -1641,7 +1628,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>Godfather of gangsta rap. Influence often unacknowledged.</t>
+          <t>Philadelphia proto-gangsta rapper. Predates N.W.A's gangsta template.</t>
         </is>
       </c>
     </row>
@@ -1702,9 +1689,8 @@
       <c r="N15" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="O15" s="6">
-        <f>AVERAGE(J15:N15)</f>
-        <v/>
+      <c r="O15" s="6" t="n">
+        <v>3.6</v>
       </c>
       <c r="P15" s="15" t="inlineStr">
         <is>
@@ -1718,7 +1704,7 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>Supersonic. Early Ruthless Records female act.</t>
+          <t>First rap group Grammy-nominated. Female-fronted electro-hop novelty hit.</t>
         </is>
       </c>
     </row>
@@ -1779,9 +1765,8 @@
       <c r="N16" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O16" s="6">
-        <f>AVERAGE(J16:N16)</f>
-        <v/>
+      <c r="O16" s="6" t="n">
+        <v>4.6</v>
       </c>
       <c r="P16" s="14" t="inlineStr">
         <is>
@@ -1795,7 +1780,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>Crossover R&amp;B-rap. Smooth sophistication in Old School era.</t>
+          <t>Early electro-rap crossover. Bridged disco and hip-hop aesthetics.</t>
         </is>
       </c>
     </row>
@@ -1856,9 +1841,8 @@
       <c r="N17" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O17" s="6">
-        <f>AVERAGE(J17:N17)</f>
-        <v/>
+      <c r="O17" s="6" t="n">
+        <v>5.4</v>
       </c>
       <c r="P17" s="14" t="inlineStr">
         <is>
@@ -1872,7 +1856,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>Human beatbox originator. 'La Di Da Di' with Slick Rick.</t>
+          <t>Human beatbox pioneer. 'La Di Da Di' a canonical party rap text.</t>
         </is>
       </c>
     </row>
@@ -1933,9 +1917,8 @@
       <c r="N18" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="O18" s="6">
-        <f>AVERAGE(J18:N18)</f>
-        <v/>
+      <c r="O18" s="6" t="n">
+        <v>7.8</v>
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
@@ -1945,7 +1928,7 @@
       <c r="Q18" s="2" t="inlineStr"/>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>Master storyteller. 'Children's Story' is a narrative benchmark.</t>
+          <t>Master storyteller. Cockney-inflected delivery, vivid street fables.</t>
         </is>
       </c>
     </row>
@@ -2006,9 +1989,8 @@
       <c r="N19" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O19" s="6">
-        <f>AVERAGE(J19:N19)</f>
-        <v/>
+      <c r="O19" s="6" t="n">
+        <v>5.8</v>
       </c>
       <c r="P19" s="15" t="inlineStr">
         <is>
@@ -2022,7 +2004,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>Slick Rick adjacent storyteller. Underrated narrative voice.</t>
+          <t>Storytelling peer to Slick Rick. Underrated narrative rapper.</t>
         </is>
       </c>
     </row>
@@ -2083,9 +2065,8 @@
       <c r="N20" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O20" s="6">
-        <f>AVERAGE(J20:N20)</f>
-        <v/>
+      <c r="O20" s="6" t="n">
+        <v>7.8</v>
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
@@ -2095,7 +2076,7 @@
       <c r="Q20" s="2" t="inlineStr"/>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>Smoothed battle rap into an art form. Influenced Jay-Z directly.</t>
+          <t>Velvet-glove delivery hiding razor-sharp multisyllabic patterns.</t>
         </is>
       </c>
     </row>
@@ -2156,9 +2137,8 @@
       <c r="N21" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O21" s="6">
-        <f>AVERAGE(J21:N21)</f>
-        <v/>
+      <c r="O21" s="6" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
@@ -2168,7 +2148,7 @@
       <c r="Q21" s="2" t="inlineStr"/>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>Rewired how MCs thought about flow. The God MC.</t>
+          <t>Invented internal rhyme as default mode. The God MC.</t>
         </is>
       </c>
     </row>
@@ -2229,9 +2209,8 @@
       <c r="N22" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O22" s="6">
-        <f>AVERAGE(J22:N22)</f>
-        <v/>
+      <c r="O22" s="6" t="n">
+        <v>7.6</v>
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
@@ -2241,7 +2220,7 @@
       <c r="Q22" s="2" t="inlineStr"/>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>U.N.I.T.Y. feminist anthem. First lady of hip-hop royalty.</t>
+          <t>Regal feminist authority. Foundational for women in rap.</t>
         </is>
       </c>
     </row>
@@ -2302,9 +2281,8 @@
       <c r="N23" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O23" s="6">
-        <f>AVERAGE(J23:N23)</f>
-        <v/>
+      <c r="O23" s="6" t="n">
+        <v>7.2</v>
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
@@ -2314,7 +2292,7 @@
       <c r="Q23" s="2" t="inlineStr"/>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>Straight Outta Compton. Made the coasts speak different languages.</t>
+          <t>Invented gangsta rap. Vérité street journalism.</t>
         </is>
       </c>
     </row>
@@ -2375,9 +2353,8 @@
       <c r="N24" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O24" s="6">
-        <f>AVERAGE(J24:N24)</f>
-        <v/>
+      <c r="O24" s="6" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
@@ -2387,7 +2364,7 @@
       <c r="Q24" s="2" t="inlineStr"/>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>N.W.A pen. AmeriKKKa's Most Wanted is a lyrical high-water mark.</t>
+          <t>N.W.A's sharpest writer. Furious precision.</t>
         </is>
       </c>
     </row>
@@ -2448,9 +2425,8 @@
       <c r="N25" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O25" s="6">
-        <f>AVERAGE(J25:N25)</f>
-        <v/>
+      <c r="O25" s="6" t="n">
+        <v>7.6</v>
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
@@ -2460,7 +2436,7 @@
       <c r="Q25" s="2" t="inlineStr"/>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3 Feet High and Rising. Made sampling feel like art.</t>
+          <t>Playful polymaths. Vast vocabulary with absurdist wit.</t>
         </is>
       </c>
     </row>
@@ -2521,9 +2497,8 @@
       <c r="N26" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O26" s="6">
-        <f>AVERAGE(J26:N26)</f>
-        <v/>
+      <c r="O26" s="6" t="n">
+        <v>8.4</v>
       </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
@@ -2533,7 +2508,7 @@
       <c r="Q26" s="2" t="inlineStr"/>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>Married jazz and hip-hop elegantly. The Low End Theory is essential.</t>
+          <t>Q-Tip's conversational genius. Jazz improvisation in verse.</t>
         </is>
       </c>
     </row>
@@ -2594,9 +2569,8 @@
       <c r="N27" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O27" s="6">
-        <f>AVERAGE(J27:N27)</f>
-        <v/>
+      <c r="O27" s="6" t="n">
+        <v>9.4</v>
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
@@ -2606,7 +2580,7 @@
       <c r="Q27" s="2" t="inlineStr"/>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>Illmatic remains the most critically studied debut in rap.</t>
+          <t>'Illmatic' distilled Queensbridge into literary art.</t>
         </is>
       </c>
     </row>
@@ -2667,9 +2641,8 @@
       <c r="N28" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O28" s="6">
-        <f>AVERAGE(J28:N28)</f>
-        <v/>
+      <c r="O28" s="6" t="n">
+        <v>9</v>
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
@@ -2679,7 +2652,7 @@
       <c r="Q28" s="2" t="inlineStr"/>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>Lyrical density and narrative gift in equal measure.</t>
+          <t>Greatest natural storyteller. Cinematic scenes, effortless charisma.</t>
         </is>
       </c>
     </row>
@@ -2740,9 +2713,8 @@
       <c r="N29" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O29" s="6">
-        <f>AVERAGE(J29:N29)</f>
-        <v/>
+      <c r="O29" s="6" t="n">
+        <v>8.4</v>
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
@@ -2752,7 +2724,7 @@
       <c r="Q29" s="2" t="inlineStr"/>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>Enter the 36 Chambers. Martial arts mythology meets Shaolin New York.</t>
+          <t>Nine MCs, nine styles. Martial mythology meets grim NY street.</t>
         </is>
       </c>
     </row>
@@ -2813,9 +2785,8 @@
       <c r="N30" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O30" s="6">
-        <f>AVERAGE(J30:N30)</f>
-        <v/>
+      <c r="O30" s="6" t="n">
+        <v>6.6</v>
       </c>
       <c r="P30" s="7" t="inlineStr">
         <is>
@@ -2825,7 +2796,7 @@
       <c r="Q30" s="2" t="inlineStr"/>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>Iconic delivery over Dre's G-Funk. Doggystyle defined an era.</t>
+          <t>Flow as personality. Delivery transcends lyrical content.</t>
         </is>
       </c>
     </row>
@@ -2886,9 +2857,8 @@
       <c r="N31" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O31" s="6">
-        <f>AVERAGE(J31:N31)</f>
-        <v/>
+      <c r="O31" s="6" t="n">
+        <v>5.6</v>
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
@@ -2898,7 +2868,7 @@
       <c r="Q31" s="2" t="inlineStr"/>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>G-Funk architect. The Chronic changed West Coast sound globally.</t>
+          <t>Producer-first. Lyricism secondary to sonic architecture.</t>
         </is>
       </c>
     </row>
@@ -2959,9 +2929,8 @@
       <c r="N32" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="O32" s="6">
-        <f>AVERAGE(J32:N32)</f>
-        <v/>
+      <c r="O32" s="6" t="n">
+        <v>7.2</v>
       </c>
       <c r="P32" s="7" t="inlineStr">
         <is>
@@ -2971,7 +2940,7 @@
       <c r="Q32" s="2" t="inlineStr"/>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>Bizarre Ride II. Quirky alternative to gangsta dominance.</t>
+          <t>Acrobatic, joyful wordplay. LA's alternative answer to De La Soul.</t>
         </is>
       </c>
     </row>
@@ -3032,9 +3001,8 @@
       <c r="N33" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O33" s="6">
-        <f>AVERAGE(J33:N33)</f>
-        <v/>
+      <c r="O33" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
@@ -3044,7 +3012,7 @@
       <c r="Q33" s="2" t="inlineStr"/>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>The Infamous is peak Queens gothic menace.</t>
+          <t>Prodigy's paranoid poetry over Havoc's glacial loops.</t>
         </is>
       </c>
     </row>
@@ -3105,9 +3073,8 @@
       <c r="N34" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O34" s="6">
-        <f>AVERAGE(J34:N34)</f>
-        <v/>
+      <c r="O34" s="6" t="n">
+        <v>6.8</v>
       </c>
       <c r="P34" s="7" t="inlineStr">
         <is>
@@ -3117,7 +3084,7 @@
       <c r="Q34" s="2" t="inlineStr"/>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>Dictionary of Bay slang. Slanguistics pioneer.</t>
+          <t>Slang inventor. Vocabulary innovation as primary art form.</t>
         </is>
       </c>
     </row>
@@ -3178,9 +3145,8 @@
       <c r="N35" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O35" s="6">
-        <f>AVERAGE(J35:N35)</f>
-        <v/>
+      <c r="O35" s="6" t="n">
+        <v>7.4</v>
       </c>
       <c r="P35" s="14" t="inlineStr">
         <is>
@@ -3194,7 +3160,7 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>Mecca and the Soul Brother. CL Smooth's introspection over Pete's soul.</t>
+          <t>Pete Rock's jazz-inflected production plus CL Smooth's introspective flows.</t>
         </is>
       </c>
     </row>
@@ -3255,9 +3221,8 @@
       <c r="N36" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O36" s="6">
-        <f>AVERAGE(J36:N36)</f>
-        <v/>
+      <c r="O36" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="P36" s="7" t="inlineStr">
         <is>
@@ -3267,7 +3232,7 @@
       <c r="Q36" s="2" t="inlineStr"/>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>Guru's flat-affect wisdom over Primo's chopped jazz. Step In the Arena.</t>
+          <t>Guru's monotone wisdom over DJ Premier's crate-dug perfection.</t>
         </is>
       </c>
     </row>
@@ -3328,9 +3293,8 @@
       <c r="N37" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O37" s="6">
-        <f>AVERAGE(J37:N37)</f>
-        <v/>
+      <c r="O37" s="6" t="n">
+        <v>7.2</v>
       </c>
       <c r="P37" s="14" t="inlineStr">
         <is>
@@ -3344,7 +3308,7 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>5% Nation theology in hip-hop. One for All is a conscious landmark.</t>
+          <t>5 Percenter theology meets Afrocentric fury. Sadat X and Grand Puba.</t>
         </is>
       </c>
     </row>
@@ -3405,9 +3369,8 @@
       <c r="N38" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O38" s="6">
-        <f>AVERAGE(J38:N38)</f>
-        <v/>
+      <c r="O38" s="6" t="n">
+        <v>7</v>
       </c>
       <c r="P38" s="14" t="inlineStr">
         <is>
@@ -3421,7 +3384,7 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>To the East Blackwards. Black nationalist aesthetics in full bloom.</t>
+          <t>Black nationalist imagery and Afrocentric symbolism at maximum.</t>
         </is>
       </c>
     </row>
@@ -3482,9 +3445,8 @@
       <c r="N39" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O39" s="6">
-        <f>AVERAGE(J39:N39)</f>
-        <v/>
+      <c r="O39" s="6" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3456,7 @@
       <c r="Q39" s="2" t="inlineStr"/>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>Punchline king. Lifestylez ov da Poor &amp; Dangerous is criminally slept on.</t>
+          <t>Punchline architect. Harlem's greatest. Wordplay density rivals anyone.</t>
         </is>
       </c>
     </row>
@@ -3555,9 +3517,8 @@
       <c r="N40" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O40" s="6">
-        <f>AVERAGE(J40:N40)</f>
-        <v/>
+      <c r="O40" s="6" t="n">
+        <v>7.4</v>
       </c>
       <c r="P40" s="7" t="inlineStr">
         <is>
@@ -3567,7 +3528,7 @@
       <c r="Q40" s="2" t="inlineStr"/>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>My Mind Playing Tricks on Me. Southern rap's dark psychological turn.</t>
+          <t>Pioneered Southern horror-gangsta. Scarface's lyrical foundation.</t>
         </is>
       </c>
     </row>
@@ -3628,9 +3589,8 @@
       <c r="N41" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O41" s="6">
-        <f>AVERAGE(J41:N41)</f>
-        <v/>
+      <c r="O41" s="6" t="n">
+        <v>7.8</v>
       </c>
       <c r="P41" s="14" t="inlineStr">
         <is>
@@ -3644,7 +3604,7 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>Innercity Griots. Improvised lyricism from the Good Life Café scene.</t>
+          <t>LA's jazz-rap underground. Aceyalone among the most technically gifted MCs ever.</t>
         </is>
       </c>
     </row>
@@ -3705,9 +3665,8 @@
       <c r="N42" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O42" s="6">
-        <f>AVERAGE(J42:N42)</f>
-        <v/>
+      <c r="O42" s="6" t="n">
+        <v>7</v>
       </c>
       <c r="P42" s="14" t="inlineStr">
         <is>
@@ -3721,7 +3680,7 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>Reachin' (A New Refutation of Time and Space). Bohemian cool jazz.</t>
+          <t>Cool jazz-rap fusion. Ladybug Mecca one of the era's sharpest female voices.</t>
         </is>
       </c>
     </row>
@@ -3782,9 +3741,8 @@
       <c r="N43" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O43" s="6">
-        <f>AVERAGE(J43:N43)</f>
-        <v/>
+      <c r="O43" s="6" t="n">
+        <v>7.4</v>
       </c>
       <c r="P43" s="14" t="inlineStr">
         <is>
@@ -3798,7 +3756,7 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>A Future Without a Past. Busta Rhymes's stage before his solo explosions.</t>
+          <t>Launched Busta Rhymes. Charlie Brown and Dinco D also strong voices.</t>
         </is>
       </c>
     </row>
@@ -3859,9 +3817,8 @@
       <c r="N44" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O44" s="6">
-        <f>AVERAGE(J44:N44)</f>
-        <v/>
+      <c r="O44" s="6" t="n">
+        <v>7.8</v>
       </c>
       <c r="P44" s="7" t="inlineStr">
         <is>
@@ -3871,7 +3828,7 @@
       <c r="Q44" s="2" t="inlineStr"/>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>Hyperkinetic flow and energy. The Coming announced a superstar.</t>
+          <t>Hyper-kinetic delivery and flow complexity. One of the fastest MCs ever.</t>
         </is>
       </c>
     </row>
@@ -3932,9 +3889,8 @@
       <c r="N45" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O45" s="6">
-        <f>AVERAGE(J45:N45)</f>
-        <v/>
+      <c r="O45" s="6" t="n">
+        <v>8.4</v>
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
@@ -3944,7 +3900,7 @@
       <c r="Q45" s="2" t="inlineStr"/>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>Me Against the World / All Eyez on Me. Embodied generational pain.</t>
+          <t>Raw emotional intelligence. Political rage and personal vulnerability.</t>
         </is>
       </c>
     </row>
@@ -4005,9 +3961,8 @@
       <c r="N46" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O46" s="6">
-        <f>AVERAGE(J46:N46)</f>
-        <v/>
+      <c r="O46" s="6" t="n">
+        <v>8.6</v>
       </c>
       <c r="P46" s="7" t="inlineStr">
         <is>
@@ -4017,7 +3972,7 @@
       <c r="Q46" s="2" t="inlineStr"/>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>Reasonable Doubt to Blueprint. Business and artistry in concert.</t>
+          <t>Effortless mastery. Hustler's autobiography as album architecture.</t>
         </is>
       </c>
     </row>
@@ -4078,9 +4033,8 @@
       <c r="N47" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O47" s="6">
-        <f>AVERAGE(J47:N47)</f>
-        <v/>
+      <c r="O47" s="6" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
@@ -4090,7 +4044,7 @@
       <c r="Q47" s="2" t="inlineStr"/>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>Slim Shady LP. Technical rhyme density unchallenged in any era.</t>
+          <t>Most technically precise rapper. Internal rhyme density off the charts.</t>
         </is>
       </c>
     </row>
@@ -4151,9 +4105,8 @@
       <c r="N48" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="O48" s="6">
-        <f>AVERAGE(J48:N48)</f>
-        <v/>
+      <c r="O48" s="6" t="n">
+        <v>6.2</v>
       </c>
       <c r="P48" s="7" t="inlineStr">
         <is>
@@ -4163,7 +4116,7 @@
       <c r="Q48" s="2" t="inlineStr"/>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>Barking aggression as spiritual crisis. It's Dark and Hell Is Hot.</t>
+          <t>Primal confessional fury. Power through raw emotional delivery.</t>
         </is>
       </c>
     </row>
@@ -4224,9 +4177,8 @@
       <c r="N49" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O49" s="6">
-        <f>AVERAGE(J49:N49)</f>
-        <v/>
+      <c r="O49" s="6" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
@@ -4236,7 +4188,7 @@
       <c r="Q49" s="2" t="inlineStr"/>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>Miseducation is the high point of rap-soul fusion.</t>
+          <t>'Miseducation' — radical emotional honesty + technical precision.</t>
         </is>
       </c>
     </row>
@@ -4297,9 +4249,8 @@
       <c r="N50" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O50" s="6">
-        <f>AVERAGE(J50:N50)</f>
-        <v/>
+      <c r="O50" s="6" t="n">
+        <v>7.2</v>
       </c>
       <c r="P50" s="7" t="inlineStr">
         <is>
@@ -4309,7 +4260,7 @@
       <c r="Q50" s="2" t="inlineStr"/>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>Supa Dupa Fly. Avant-garde Southern vision over Timbaland.</t>
+          <t>Flow as futurist sculpture. Rhythm manipulation over traditional lyricism.</t>
         </is>
       </c>
     </row>
@@ -4370,9 +4321,8 @@
       <c r="N51" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O51" s="6">
-        <f>AVERAGE(J51:N51)</f>
-        <v/>
+      <c r="O51" s="6" t="n">
+        <v>8.6</v>
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
@@ -4382,7 +4332,7 @@
       <c r="Q51" s="2" t="inlineStr"/>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>Black on Both Sides. Renaissance man MC.</t>
+          <t>'Black on Both Sides' — blues, jazz, politics in one voice.</t>
         </is>
       </c>
     </row>
@@ -4443,9 +4393,8 @@
       <c r="N52" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O52" s="6">
-        <f>AVERAGE(J52:N52)</f>
-        <v/>
+      <c r="O52" s="6" t="n">
+        <v>8.4</v>
       </c>
       <c r="P52" s="7" t="inlineStr">
         <is>
@@ -4455,7 +4404,7 @@
       <c r="Q52" s="2" t="inlineStr"/>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>Reflection Eternal. Wordy, dense, deeply political.</t>
+          <t>Brooklyn's dense intellectual. Every bar packed with history.</t>
         </is>
       </c>
     </row>
@@ -4516,9 +4465,8 @@
       <c r="N53" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O53" s="6">
-        <f>AVERAGE(J53:N53)</f>
-        <v/>
+      <c r="O53" s="6" t="n">
+        <v>8.6</v>
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
@@ -4528,7 +4476,7 @@
       <c r="Q53" s="2" t="inlineStr"/>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>Aquemini. Andre 3000 is a singular artistic voice.</t>
+          <t>Andre 3000: genre-defying poet. Big Boi: underrated technical master.</t>
         </is>
       </c>
     </row>
@@ -4589,9 +4537,8 @@
       <c r="N54" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O54" s="6">
-        <f>AVERAGE(J54:N54)</f>
-        <v/>
+      <c r="O54" s="6" t="n">
+        <v>3.8</v>
       </c>
       <c r="P54" s="7" t="inlineStr">
         <is>
@@ -4601,7 +4548,7 @@
       <c r="Q54" s="2" t="inlineStr"/>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>Ghetto D. Cash Money architect. Business over lyricism.</t>
+          <t>Mogul over MC. Influence is business, not bars.</t>
         </is>
       </c>
     </row>
@@ -4662,9 +4609,8 @@
       <c r="N55" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="O55" s="6">
-        <f>AVERAGE(J55:N55)</f>
-        <v/>
+      <c r="O55" s="6" t="n">
+        <v>7</v>
       </c>
       <c r="P55" s="14" t="inlineStr">
         <is>
@@ -4678,7 +4624,7 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>Come Home with Me. Pink fur and oblique rap logic.</t>
+          <t>Pink fur and slant rhymes. Harlem's most stylistically eccentric MC.</t>
         </is>
       </c>
     </row>
@@ -4739,9 +4685,8 @@
       <c r="N56" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="O56" s="6">
-        <f>AVERAGE(J56:N56)</f>
-        <v/>
+      <c r="O56" s="6" t="n">
+        <v>6.8</v>
       </c>
       <c r="P56" s="14" t="inlineStr">
         <is>
@@ -4755,7 +4700,7 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>Ill Na Na. Mafioso rap via the female gaze.</t>
+          <t>Aggressive feminine sexuality as lyrical weapon. Def Jam's answer to Lil Kim.</t>
         </is>
       </c>
     </row>
@@ -4816,9 +4761,8 @@
       <c r="N57" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="O57" s="6">
-        <f>AVERAGE(J57:N57)</f>
-        <v/>
+      <c r="O57" s="6" t="n">
+        <v>7</v>
       </c>
       <c r="P57" s="7" t="inlineStr">
         <is>
@@ -4828,7 +4772,7 @@
       <c r="Q57" s="2" t="inlineStr"/>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>Hard Core. Explicit female sexuality as power and disruption.</t>
+          <t>Radical sexual candor. Graphic feminism that rewrote what women could say in rap.</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4797,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Late 99s</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -4889,9 +4833,8 @@
       <c r="N58" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O58" s="6">
-        <f>AVERAGE(J58:N58)</f>
-        <v/>
+      <c r="O58" s="6" t="n">
+        <v>5.8</v>
       </c>
       <c r="P58" s="14" t="inlineStr">
         <is>
@@ -4905,7 +4848,7 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>400 Degreez. Cash Money's breakout moment.</t>
+          <t>Cash Money's first star. New Orleans bounce meets street narrative.</t>
         </is>
       </c>
     </row>
@@ -4966,9 +4909,8 @@
       <c r="N59" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O59" s="6">
-        <f>AVERAGE(J59:N59)</f>
-        <v/>
+      <c r="O59" s="6" t="n">
+        <v>7</v>
       </c>
       <c r="P59" s="14" t="inlineStr">
         <is>
@@ -4982,7 +4924,7 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>Syllable count obsessive. Battle loss to LL never fully recovered from.</t>
+          <t>Battle rap legend. Technical skill occasionally undermined by ego.</t>
         </is>
       </c>
     </row>
@@ -5043,9 +4985,8 @@
       <c r="N60" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O60" s="6">
-        <f>AVERAGE(J60:N60)</f>
-        <v/>
+      <c r="O60" s="6" t="n">
+        <v>7.4</v>
       </c>
       <c r="P60" s="15" t="inlineStr">
         <is>
@@ -5059,7 +5000,7 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>Violent by Design. Horror-core meets political paranoia underground.</t>
+          <t>Philadelphia underground. Vinnie Paz's dense, conspiratorial lyricism.</t>
         </is>
       </c>
     </row>
@@ -5120,9 +5061,8 @@
       <c r="N61" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O61" s="6">
-        <f>AVERAGE(J61:N61)</f>
-        <v/>
+      <c r="O61" s="6" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
@@ -5132,7 +5072,7 @@
       <c r="Q61" s="2" t="inlineStr"/>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>Capital Punishment. First Latino rapper to go platinum solo.</t>
+          <t>First Latin rapper to go platinum solo. Multisyllabic rhyme virtuoso.</t>
         </is>
       </c>
     </row>
@@ -5193,9 +5133,8 @@
       <c r="N62" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O62" s="6">
-        <f>AVERAGE(J62:N62)</f>
-        <v/>
+      <c r="O62" s="6" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="P62" s="14" t="inlineStr">
         <is>
@@ -5209,7 +5148,7 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>Life's a Bitch collab. AZ's verse is among the finest in rap history.</t>
+          <t>AZ: One of the most underrated MCs of the era. 'Sugarhill' an all-time verse.</t>
         </is>
       </c>
     </row>
@@ -5270,9 +5209,8 @@
       <c r="N63" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="O63" s="6">
-        <f>AVERAGE(J63:N63)</f>
-        <v/>
+      <c r="O63" s="6" t="n">
+        <v>8.4</v>
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
@@ -5282,7 +5220,7 @@
       <c r="Q63" s="2" t="inlineStr"/>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>College Dropout to 808s. Artistic ambition reshapes each era.</t>
+          <t>Conceptual ambition as primary engine. Each album a reinvention.</t>
         </is>
       </c>
     </row>
@@ -5343,9 +5281,8 @@
       <c r="N64" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O64" s="6">
-        <f>AVERAGE(J64:N64)</f>
-        <v/>
+      <c r="O64" s="6" t="n">
+        <v>8.4</v>
       </c>
       <c r="P64" s="7" t="inlineStr">
         <is>
@@ -5355,7 +5292,7 @@
       <c r="Q64" s="2" t="inlineStr"/>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>Tha Carter III. Mixtape era Wayne is the definition of peak lyricism.</t>
+          <t>Simile machine at peak. Abstract metaphor-stacking as freestyle sport.</t>
         </is>
       </c>
     </row>
@@ -5416,9 +5353,8 @@
       <c r="N65" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O65" s="6">
-        <f>AVERAGE(J65:N65)</f>
-        <v/>
+      <c r="O65" s="6" t="n">
+        <v>7.2</v>
       </c>
       <c r="P65" s="7" t="inlineStr">
         <is>
@@ -5428,7 +5364,7 @@
       <c r="Q65" s="2" t="inlineStr"/>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>King. Claimed the ATL throne and the trap blueprint.</t>
+          <t>King of the South. Trap's emotional architect.</t>
         </is>
       </c>
     </row>
@@ -5489,9 +5425,8 @@
       <c r="N66" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O66" s="6">
-        <f>AVERAGE(J66:N66)</f>
-        <v/>
+      <c r="O66" s="6" t="n">
+        <v>4.8</v>
       </c>
       <c r="P66" s="7" t="inlineStr">
         <is>
@@ -5501,7 +5436,7 @@
       <c r="Q66" s="2" t="inlineStr"/>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>Trap God. Prolific mixtape movement godfather.</t>
+          <t>Vibe and charisma over craft. Trap music's spiritual godfather.</t>
         </is>
       </c>
     </row>
@@ -5562,9 +5497,8 @@
       <c r="N67" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O67" s="6">
-        <f>AVERAGE(J67:N67)</f>
-        <v/>
+      <c r="O67" s="6" t="n">
+        <v>8.4</v>
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
@@ -5574,7 +5508,7 @@
       <c r="Q67" s="2" t="inlineStr"/>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>Supreme Clientele. Dense, dazzling, associative.</t>
+          <t>Stream-of-consciousness genius. Dense slang, vivid scene-painting.</t>
         </is>
       </c>
     </row>
@@ -5635,9 +5569,8 @@
       <c r="N68" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O68" s="6">
-        <f>AVERAGE(J68:N68)</f>
-        <v/>
+      <c r="O68" s="6" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="P68" s="7" t="inlineStr">
         <is>
@@ -5647,7 +5580,7 @@
       <c r="Q68" s="2" t="inlineStr"/>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>Madvillainy. The mask, the myth, the syllable wizardry.</t>
+          <t>The supervillain. Labyrinths of internal rhyme no one has fully mapped.</t>
         </is>
       </c>
     </row>
@@ -5708,9 +5641,8 @@
       <c r="N69" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O69" s="6">
-        <f>AVERAGE(J69:N69)</f>
-        <v/>
+      <c r="O69" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
@@ -5720,7 +5652,7 @@
       <c r="Q69" s="2" t="inlineStr"/>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>Be. Elevated conscious rap into mainstream Grammy territory.</t>
+          <t>Chicago's philosopher-MC. Ernie Barnes paintings in verse form.</t>
         </is>
       </c>
     </row>
@@ -5781,9 +5713,8 @@
       <c r="N70" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O70" s="6">
-        <f>AVERAGE(J70:N70)</f>
-        <v/>
+      <c r="O70" s="6" t="n">
+        <v>6.6</v>
       </c>
       <c r="P70" s="7" t="inlineStr">
         <is>
@@ -5793,7 +5724,7 @@
       <c r="Q70" s="2" t="inlineStr"/>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>Word of Mouf. Playful Southern rapping with genuine lyrical edge.</t>
+          <t>Comic virtuosity. Punchline timing as precision instrument.</t>
         </is>
       </c>
     </row>
@@ -5854,9 +5785,8 @@
       <c r="N71" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="O71" s="6">
-        <f>AVERAGE(J71:N71)</f>
-        <v/>
+      <c r="O71" s="6" t="n">
+        <v>5.4</v>
       </c>
       <c r="P71" s="7" t="inlineStr">
         <is>
@@ -5866,7 +5796,7 @@
       <c r="Q71" s="2" t="inlineStr"/>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>Let's Get It: Thug Motivation 101. Trap's motivational speaker.</t>
+          <t>Trap's motivational orator. Delivery and charisma over craft.</t>
         </is>
       </c>
     </row>
@@ -5927,9 +5857,8 @@
       <c r="N72" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="O72" s="6">
-        <f>AVERAGE(J72:N72)</f>
-        <v/>
+      <c r="O72" s="6" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="P72" s="7" t="inlineStr">
         <is>
@@ -5939,7 +5868,7 @@
       <c r="Q72" s="2" t="inlineStr"/>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>Food &amp; Liquor. Skate kid from Chicago with dictionary flow.</t>
+          <t>Conceptually sui generis. 'Dumb It Down' a rebuke of simplicity.</t>
         </is>
       </c>
     </row>
@@ -6000,9 +5929,8 @@
       <c r="N73" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O73" s="6">
-        <f>AVERAGE(J73:N73)</f>
-        <v/>
+      <c r="O73" s="6" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
@@ -6012,7 +5940,7 @@
       <c r="Q73" s="2" t="inlineStr"/>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>The World Is Yours. Southern rap's great novelist.</t>
+          <t>Houston's great novelist. Psychological interior in gangsta rap.</t>
         </is>
       </c>
     </row>
@@ -6073,9 +6001,8 @@
       <c r="N74" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O74" s="6">
-        <f>AVERAGE(J74:N74)</f>
-        <v/>
+      <c r="O74" s="6" t="n">
+        <v>8.4</v>
       </c>
       <c r="P74" s="7" t="inlineStr">
         <is>
@@ -6085,7 +6012,7 @@
       <c r="Q74" s="2" t="inlineStr"/>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>None Shall Pass. Largest vocabulary in measured rap.</t>
+          <t>NLP-verified largest unique vocabulary in rap. Dense abstract imagery.</t>
         </is>
       </c>
     </row>
@@ -6146,9 +6073,8 @@
       <c r="N75" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O75" s="6">
-        <f>AVERAGE(J75:N75)</f>
-        <v/>
+      <c r="O75" s="6" t="n">
+        <v>8.6</v>
       </c>
       <c r="P75" s="14" t="inlineStr">
         <is>
@@ -6162,7 +6088,7 @@
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>Fishscale is Ghostface at peak: cinematic, dense, unmatched.</t>
+          <t>'Fishscale' is a 2000s apex. Singular stream-of-consciousness voice.</t>
         </is>
       </c>
     </row>
@@ -6223,9 +6149,8 @@
       <c r="N76" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="O76" s="6">
-        <f>AVERAGE(J76:N76)</f>
-        <v/>
+      <c r="O76" s="6" t="n">
+        <v>6.8</v>
       </c>
       <c r="P76" s="14" t="inlineStr">
         <is>
@@ -6239,7 +6164,7 @@
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>Why? punchline king. LOX member whose grimace became iconic.</t>
+          <t>Gravelly-voiced Yonkers MC. Punchline economy and street credibility.</t>
         </is>
       </c>
     </row>
@@ -6300,9 +6225,8 @@
       <c r="N77" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O77" s="6">
-        <f>AVERAGE(J77:N77)</f>
-        <v/>
+      <c r="O77" s="6" t="n">
+        <v>6</v>
       </c>
       <c r="P77" s="7" t="inlineStr">
         <is>
@@ -6312,7 +6236,7 @@
       <c r="Q77" s="2" t="inlineStr"/>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>Get Rich or Die Tryin'. Commercial domination built on street cred.</t>
+          <t>Bulletproof charisma. Street narrative over lyrical complexity.</t>
         </is>
       </c>
     </row>
@@ -6373,9 +6297,8 @@
       <c r="N78" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O78" s="6">
-        <f>AVERAGE(J78:N78)</f>
-        <v/>
+      <c r="O78" s="6" t="n">
+        <v>5.6</v>
       </c>
       <c r="P78" s="14" t="inlineStr">
         <is>
@@ -6389,7 +6312,7 @@
       </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>Tear da Club Up. Memphis horrorcore before trap existed.</t>
+          <t>Oscar-winning Southern horror-rap. Pioneered the dark triplet flow.</t>
         </is>
       </c>
     </row>
@@ -6450,9 +6373,8 @@
       <c r="N79" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O79" s="6">
-        <f>AVERAGE(J79:N79)</f>
-        <v/>
+      <c r="O79" s="6" t="n">
+        <v>7.4</v>
       </c>
       <c r="P79" s="7" t="inlineStr">
         <is>
@@ -6462,7 +6384,7 @@
       <c r="Q79" s="2" t="inlineStr"/>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>Ridin' Dirty. Bun B and Pimp C: Southern rap's purist duo.</t>
+          <t>Bun B and Pimp C. Texas's most complete rap duo.</t>
         </is>
       </c>
     </row>
@@ -6523,9 +6445,8 @@
       <c r="N80" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="O80" s="6">
-        <f>AVERAGE(J80:N80)</f>
-        <v/>
+      <c r="O80" s="6" t="n">
+        <v>6.4</v>
       </c>
       <c r="P80" s="15" t="inlineStr">
         <is>
@@ -6539,7 +6460,7 @@
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>Restless. Houston street reporting with slow, heavy flow.</t>
+          <t>Houston's street ambassador. Chopped-and-screwed delivery as identity.</t>
         </is>
       </c>
     </row>
@@ -6600,9 +6521,8 @@
       <c r="N81" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O81" s="6">
-        <f>AVERAGE(J81:N81)</f>
-        <v/>
+      <c r="O81" s="6" t="n">
+        <v>7.8</v>
       </c>
       <c r="P81" s="14" t="inlineStr">
         <is>
@@ -6616,7 +6536,7 @@
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>All Balls Don't Bounce. Project Blowed's academic underground MC.</t>
+          <t>LA underground legend. Freestyle Fellowship's most technically gifted MC.</t>
         </is>
       </c>
     </row>
@@ -6677,9 +6597,8 @@
       <c r="N82" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O82" s="6">
-        <f>AVERAGE(J82:N82)</f>
-        <v/>
+      <c r="O82" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="P82" s="7" t="inlineStr">
         <is>
@@ -6689,7 +6608,7 @@
       <c r="Q82" s="2" t="inlineStr"/>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>Only Built 4 Cuban Linx. Mafioso rap as cinematic epic.</t>
+          <t>'Only Built 4 Cuban Linx' — the Godfather Part II of rap albums.</t>
         </is>
       </c>
     </row>
@@ -6750,9 +6669,8 @@
       <c r="N83" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O83" s="6">
-        <f>AVERAGE(J83:N83)</f>
-        <v/>
+      <c r="O83" s="6" t="n">
+        <v>8.4</v>
       </c>
       <c r="P83" s="7" t="inlineStr">
         <is>
@@ -6762,7 +6680,7 @@
       <c r="Q83" s="2" t="inlineStr"/>
       <c r="R83" s="2" t="inlineStr">
         <is>
-          <t>Fantastic Damage. Dystopian industrial rap from the Def Jux era.</t>
+          <t>Company Flow / Run The Jewels architect. Dystopian sonic vision.</t>
         </is>
       </c>
     </row>
@@ -6823,9 +6741,8 @@
       <c r="N84" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O84" s="6">
-        <f>AVERAGE(J84:N84)</f>
-        <v/>
+      <c r="O84" s="6" t="n">
+        <v>7.4</v>
       </c>
       <c r="P84" s="14" t="inlineStr">
         <is>
@@ -6839,7 +6756,7 @@
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>Shadows on the Sun. Minneapolis underground social conscience.</t>
+          <t>Minneapolis conscious rapper. Raw emotional honesty over Ant's production.</t>
         </is>
       </c>
     </row>
@@ -6900,9 +6817,8 @@
       <c r="N85" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="O85" s="6">
-        <f>AVERAGE(J85:N85)</f>
-        <v/>
+      <c r="O85" s="6" t="n">
+        <v>7.8</v>
       </c>
       <c r="P85" s="14" t="inlineStr">
         <is>
@@ -6916,7 +6832,7 @@
       </c>
       <c r="R85" s="2" t="inlineStr">
         <is>
-          <t>Revolutionary Vol. 2. Conspiracy rap with genuine rhetorical force.</t>
+          <t>Most politically radical rapper in the genre. Conspiracy and revolution.</t>
         </is>
       </c>
     </row>
@@ -6977,9 +6893,8 @@
       <c r="N86" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="O86" s="6">
-        <f>AVERAGE(J86:N86)</f>
-        <v/>
+      <c r="O86" s="6" t="n">
+        <v>10</v>
       </c>
       <c r="P86" s="7" t="inlineStr">
         <is>
@@ -6989,7 +6904,7 @@
       <c r="Q86" s="2" t="inlineStr"/>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>good kid m.A.A.d city / TPAB. The most complete MC since Nas.</t>
+          <t>The complete package. Every dimension at peak. Pulitzer Prize.</t>
         </is>
       </c>
     </row>
@@ -7050,9 +6965,8 @@
       <c r="N87" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O87" s="6">
-        <f>AVERAGE(J87:N87)</f>
-        <v/>
+      <c r="O87" s="6" t="n">
+        <v>6.4</v>
       </c>
       <c r="P87" s="7" t="inlineStr">
         <is>
@@ -7062,7 +6976,7 @@
       <c r="Q87" s="2" t="inlineStr"/>
       <c r="R87" s="2" t="inlineStr">
         <is>
-          <t>Take Care. Emotional rap at massive commercial scale.</t>
+          <t>Emotional candor and commercial dominance. Lyricism secondary to feeling.</t>
         </is>
       </c>
     </row>
@@ -7123,9 +7037,8 @@
       <c r="N88" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O88" s="6">
-        <f>AVERAGE(J88:N88)</f>
-        <v/>
+      <c r="O88" s="6" t="n">
+        <v>8.4</v>
       </c>
       <c r="P88" s="7" t="inlineStr">
         <is>
@@ -7135,7 +7048,7 @@
       <c r="Q88" s="2" t="inlineStr"/>
       <c r="R88" s="2" t="inlineStr">
         <is>
-          <t>2014 Forest Hills Drive. Self-produced introspection at scale.</t>
+          <t>Working-class emotional intelligence. Deep narrative craft.</t>
         </is>
       </c>
     </row>
@@ -7196,9 +7109,8 @@
       <c r="N89" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O89" s="6">
-        <f>AVERAGE(J89:N89)</f>
-        <v/>
+      <c r="O89" s="6" t="n">
+        <v>5.2</v>
       </c>
       <c r="P89" s="7" t="inlineStr">
         <is>
@@ -7208,7 +7120,7 @@
       <c r="Q89" s="2" t="inlineStr"/>
       <c r="R89" s="2" t="inlineStr">
         <is>
-          <t>Barter 6. Recontextualized flow as melodic instrument.</t>
+          <t>Melody over meaning. Vocal texture as primary instrument.</t>
         </is>
       </c>
     </row>
@@ -7269,9 +7181,8 @@
       <c r="N90" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O90" s="6">
-        <f>AVERAGE(J90:N90)</f>
-        <v/>
+      <c r="O90" s="6" t="n">
+        <v>5.2</v>
       </c>
       <c r="P90" s="7" t="inlineStr">
         <is>
@@ -7281,7 +7192,7 @@
       <c r="Q90" s="2" t="inlineStr"/>
       <c r="R90" s="2" t="inlineStr">
         <is>
-          <t>DS2. Emotional ambivalence as trap subgenre.</t>
+          <t>Emotional auto-tune as confession. Vibe over lyrical architecture.</t>
         </is>
       </c>
     </row>
@@ -7342,9 +7253,8 @@
       <c r="N91" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O91" s="6">
-        <f>AVERAGE(J91:N91)</f>
-        <v/>
+      <c r="O91" s="6" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="P91" s="7" t="inlineStr">
         <is>
@@ -7354,7 +7264,7 @@
       <c r="Q91" s="2" t="inlineStr"/>
       <c r="R91" s="2" t="inlineStr">
         <is>
-          <t>Coloring Book. Gospel rap from Chicago's south side.</t>
+          <t>Joyful complexity. Gospel cadences and Chicago love letters.</t>
         </is>
       </c>
     </row>
@@ -7415,9 +7325,8 @@
       <c r="N92" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O92" s="6">
-        <f>AVERAGE(J92:N92)</f>
-        <v/>
+      <c r="O92" s="6" t="n">
+        <v>8.4</v>
       </c>
       <c r="P92" s="7" t="inlineStr">
         <is>
@@ -7427,7 +7336,7 @@
       <c r="Q92" s="2" t="inlineStr"/>
       <c r="R92" s="2" t="inlineStr">
         <is>
-          <t>I Don't Like Shit. Dense, interior, self-lacerating.</t>
+          <t>Compression and grief as poetics. Dense abstract imagery.</t>
         </is>
       </c>
     </row>
@@ -7488,9 +7397,8 @@
       <c r="N93" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="O93" s="6">
-        <f>AVERAGE(J93:N93)</f>
-        <v/>
+      <c r="O93" s="6" t="n">
+        <v>6.2</v>
       </c>
       <c r="P93" s="7" t="inlineStr">
         <is>
@@ -7500,7 +7408,7 @@
       <c r="Q93" s="2" t="inlineStr"/>
       <c r="R93" s="2" t="inlineStr">
         <is>
-          <t>Dreams and Nightmares. Philly grit at arena scale.</t>
+          <t>Visceral urgency. Philadelphia streets in raw kinetic delivery.</t>
         </is>
       </c>
     </row>
@@ -7561,9 +7469,8 @@
       <c r="N94" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O94" s="6">
-        <f>AVERAGE(J94:N94)</f>
-        <v/>
+      <c r="O94" s="6" t="n">
+        <v>6</v>
       </c>
       <c r="P94" s="7" t="inlineStr">
         <is>
@@ -7573,7 +7480,7 @@
       <c r="Q94" s="2" t="inlineStr"/>
       <c r="R94" s="2" t="inlineStr">
         <is>
-          <t>Long.Live.ASAP. Harlem avant-garde aesthetics in rap form.</t>
+          <t>Aesthetic as content. Flow and texture over lyrical substance.</t>
         </is>
       </c>
     </row>
@@ -7634,9 +7541,8 @@
       <c r="N95" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O95" s="6">
-        <f>AVERAGE(J95:N95)</f>
-        <v/>
+      <c r="O95" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="P95" s="7" t="inlineStr">
         <is>
@@ -7646,7 +7552,7 @@
       <c r="Q95" s="2" t="inlineStr"/>
       <c r="R95" s="2" t="inlineStr">
         <is>
-          <t>Pink Friday. Technical bars meet pop domination.</t>
+          <t>Technical precision and alter-ego theatrics. 'Monster' verse.</t>
         </is>
       </c>
     </row>
@@ -7707,9 +7613,8 @@
       <c r="N96" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O96" s="6">
-        <f>AVERAGE(J96:N96)</f>
-        <v/>
+      <c r="O96" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="P96" s="7" t="inlineStr">
         <is>
@@ -7719,7 +7624,7 @@
       <c r="Q96" s="2" t="inlineStr"/>
       <c r="R96" s="2" t="inlineStr">
         <is>
-          <t>Summertime '06. Long Beach noir, economical and bleak.</t>
+          <t>Deadpan sociologist. Minimalist language doing maximum structural work.</t>
         </is>
       </c>
     </row>
@@ -7780,9 +7685,8 @@
       <c r="N97" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O97" s="6">
-        <f>AVERAGE(J97:N97)</f>
-        <v/>
+      <c r="O97" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="P97" s="7" t="inlineStr">
         <is>
@@ -7792,7 +7696,7 @@
       <c r="Q97" s="2" t="inlineStr"/>
       <c r="R97" s="2" t="inlineStr">
         <is>
-          <t>Live from the Underground. Southern rap's self-produced soul heir.</t>
+          <t>Mississippi throwback futurist. Southern soul and lyrical ambition fused.</t>
         </is>
       </c>
     </row>
@@ -7853,9 +7757,8 @@
       <c r="N98" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O98" s="6">
-        <f>AVERAGE(J98:N98)</f>
-        <v/>
+      <c r="O98" s="6" t="n">
+        <v>8.4</v>
       </c>
       <c r="P98" s="7" t="inlineStr">
         <is>
@@ -7865,7 +7768,7 @@
       <c r="Q98" s="2" t="inlineStr"/>
       <c r="R98" s="2" t="inlineStr">
         <is>
-          <t>RTJ2. El-P + Killer Mike = relentless political rap.</t>
+          <t>El-P and Killer Mike. Most politically urgent rap duo since PE.</t>
         </is>
       </c>
     </row>
@@ -7926,9 +7829,8 @@
       <c r="N99" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O99" s="6">
-        <f>AVERAGE(J99:N99)</f>
-        <v/>
+      <c r="O99" s="6" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="P99" s="7" t="inlineStr">
         <is>
@@ -7938,7 +7840,7 @@
       <c r="Q99" s="2" t="inlineStr"/>
       <c r="R99" s="2" t="inlineStr">
         <is>
-          <t>R.A.P. Music. Atlanta social critique at its angriest best.</t>
+          <t>RTJ's political conscience. Atlanta's most morally serious MC.</t>
         </is>
       </c>
     </row>
@@ -7999,9 +7901,8 @@
       <c r="N100" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="O100" s="6">
-        <f>AVERAGE(J100:N100)</f>
-        <v/>
+      <c r="O100" s="6" t="n">
+        <v>3.8</v>
       </c>
       <c r="P100" s="7" t="inlineStr">
         <is>
@@ -8011,7 +7912,7 @@
       <c r="Q100" s="2" t="inlineStr"/>
       <c r="R100" s="2" t="inlineStr">
         <is>
-          <t>Fancy. Commercial peak; authenticity debates dominated reception.</t>
+          <t>Commercial success masking thin lyrical foundation. Accent controversy.</t>
         </is>
       </c>
     </row>
@@ -8072,9 +7973,8 @@
       <c r="N101" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O101" s="6">
-        <f>AVERAGE(J101:N101)</f>
-        <v/>
+      <c r="O101" s="6" t="n">
+        <v>7.8</v>
       </c>
       <c r="P101" s="7" t="inlineStr">
         <is>
@@ -8084,7 +7984,7 @@
       <c r="Q101" s="2" t="inlineStr"/>
       <c r="R101" s="2" t="inlineStr">
         <is>
-          <t>Piñata. Madlib collab reinvented his career and the genre.</t>
+          <t>Gary Indiana's finest. Technical gangsta rap with jazz-rap production.</t>
         </is>
       </c>
     </row>
@@ -8145,9 +8045,8 @@
       <c r="N102" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="O102" s="6">
-        <f>AVERAGE(J102:N102)</f>
-        <v/>
+      <c r="O102" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="P102" s="7" t="inlineStr">
         <is>
@@ -8157,7 +8056,7 @@
       <c r="Q102" s="2" t="inlineStr"/>
       <c r="R102" s="2" t="inlineStr">
         <is>
-          <t>Culture. Triplet flow codified an era; lyricism secondary.</t>
+          <t>Triplet flow inventors. Cultural influence far exceeds lyrical complexity.</t>
         </is>
       </c>
     </row>
@@ -8218,9 +8117,8 @@
       <c r="N103" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O103" s="6">
-        <f>AVERAGE(J103:N103)</f>
-        <v/>
+      <c r="O103" s="6" t="n">
+        <v>5.8</v>
       </c>
       <c r="P103" s="14" t="inlineStr">
         <is>
@@ -8234,7 +8132,7 @@
       </c>
       <c r="R103" s="2" t="inlineStr">
         <is>
-          <t>I Decided. Catchy rap with occasional lyrical ambition.</t>
+          <t>Detroit MC. Punchlines over conceptual depth. 'One Man Can Change The World'.</t>
         </is>
       </c>
     </row>
@@ -8295,9 +8193,8 @@
       <c r="N104" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O104" s="6">
-        <f>AVERAGE(J104:N104)</f>
-        <v/>
+      <c r="O104" s="6" t="n">
+        <v>7.6</v>
       </c>
       <c r="P104" s="14" t="inlineStr">
         <is>
@@ -8311,7 +8208,7 @@
       </c>
       <c r="R104" s="2" t="inlineStr">
         <is>
-          <t>Whack World. 15 one-minute songs as conceptual art project.</t>
+          <t>'Whack World' — 15 one-minute songs as unified concept. Wholly original.</t>
         </is>
       </c>
     </row>
@@ -8372,9 +8269,8 @@
       <c r="N105" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O105" s="6">
-        <f>AVERAGE(J105:N105)</f>
-        <v/>
+      <c r="O105" s="6" t="n">
+        <v>8.4</v>
       </c>
       <c r="P105" s="7" t="inlineStr">
         <is>
@@ -8384,7 +8280,7 @@
       <c r="Q105" s="2" t="inlineStr"/>
       <c r="R105" s="2" t="inlineStr">
         <is>
-          <t>Room 25. Quiet devastation over jazz loops.</t>
+          <t>Chicago's most literary voice. Jazz cadences and political awakening.</t>
         </is>
       </c>
     </row>
@@ -8445,9 +8341,8 @@
       <c r="N106" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O106" s="6">
-        <f>AVERAGE(J106:N106)</f>
-        <v/>
+      <c r="O106" s="6" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="P106" s="7" t="inlineStr">
         <is>
@@ -8457,7 +8352,7 @@
       <c r="Q106" s="2" t="inlineStr"/>
       <c r="R106" s="2" t="inlineStr">
         <is>
-          <t>CARE FOR ME. Grief album as Chicago hip-hop masterpiece.</t>
+          <t>'CARE FOR ME' — grief and Chicago violence as devastating concept album.</t>
         </is>
       </c>
     </row>
@@ -8518,9 +8413,8 @@
       <c r="N107" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O107" s="6">
-        <f>AVERAGE(J107:N107)</f>
-        <v/>
+      <c r="O107" s="6" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="P107" s="7" t="inlineStr">
         <is>
@@ -8530,7 +8424,7 @@
       <c r="Q107" s="2" t="inlineStr"/>
       <c r="R107" s="2" t="inlineStr">
         <is>
-          <t>Atrocity Exhibition. Detroit's answer to post-punk sonic chaos.</t>
+          <t>Detroit's avant-garde MC. Schizophrenic flows and surreal imagery.</t>
         </is>
       </c>
     </row>
@@ -8591,9 +8485,8 @@
       <c r="N108" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O108" s="6">
-        <f>AVERAGE(J108:N108)</f>
-        <v/>
+      <c r="O108" s="6" t="n">
+        <v>7.4</v>
       </c>
       <c r="P108" s="7" t="inlineStr">
         <is>
@@ -8603,7 +8496,7 @@
       <c r="Q108" s="2" t="inlineStr"/>
       <c r="R108" s="2" t="inlineStr">
         <is>
-          <t>Swimming. Self-medication turned into heartbreaking art.</t>
+          <t>Arc from frat-rap to deeply personal jazz introspection. 'Swimming' a peak.</t>
         </is>
       </c>
     </row>
@@ -8664,9 +8557,8 @@
       <c r="N109" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O109" s="6">
-        <f>AVERAGE(J109:N109)</f>
-        <v/>
+      <c r="O109" s="6" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="P109" s="14" t="inlineStr">
         <is>
@@ -8680,7 +8572,7 @@
       </c>
       <c r="R109" s="2" t="inlineStr">
         <is>
-          <t>DiCaprio 2. Switchable flow at a pace few can match.</t>
+          <t>Atlanta's most technically gifted rapper. 'DiCaprio 2' showed full potential.</t>
         </is>
       </c>
     </row>
@@ -8741,9 +8633,8 @@
       <c r="N110" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O110" s="6">
-        <f>AVERAGE(J110:N110)</f>
-        <v/>
+      <c r="O110" s="6" t="n">
+        <v>5.6</v>
       </c>
       <c r="P110" s="7" t="inlineStr">
         <is>
@@ -8753,7 +8644,7 @@
       <c r="Q110" s="2" t="inlineStr"/>
       <c r="R110" s="2" t="inlineStr">
         <is>
-          <t>Invasion of Privacy. Bronx bravado at Grammys level.</t>
+          <t>Unfiltered Bronx personality. Cultural force exceeds lyrical architecture.</t>
         </is>
       </c>
     </row>
@@ -8814,9 +8705,8 @@
       <c r="N111" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O111" s="6">
-        <f>AVERAGE(J111:N111)</f>
-        <v/>
+      <c r="O111" s="6" t="n">
+        <v>7.2</v>
       </c>
       <c r="P111" s="14" t="inlineStr">
         <is>
@@ -8830,7 +8720,7 @@
       </c>
       <c r="R111" s="2" t="inlineStr">
         <is>
-          <t>Pop Out. Melancholy Chicago trap with genuine lyrical care.</t>
+          <t>Chicago's introspective melodic trap voice. Melancholy street memoir.</t>
         </is>
       </c>
     </row>
@@ -8891,9 +8781,8 @@
       <c r="N112" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O112" s="6">
-        <f>AVERAGE(J112:N112)</f>
-        <v/>
+      <c r="O112" s="6" t="n">
+        <v>5.6</v>
       </c>
       <c r="P112" s="14" t="inlineStr">
         <is>
@@ -8907,7 +8796,7 @@
       </c>
       <c r="R112" s="2" t="inlineStr">
         <is>
-          <t>SoulFly. Florida's emotional trap meets gospel music.</t>
+          <t>Emotional vulnerability over technical precision. Florida pain made universal.</t>
         </is>
       </c>
     </row>
@@ -8968,9 +8857,8 @@
       <c r="N113" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O113" s="6">
-        <f>AVERAGE(J113:N113)</f>
-        <v/>
+      <c r="O113" s="6" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="P113" s="14" t="inlineStr">
         <is>
@@ -8984,7 +8872,7 @@
       </c>
       <c r="R113" s="2" t="inlineStr">
         <is>
-          <t>Alligator Bites Never Heal. Tampa avant-garde challenging rap norms.</t>
+          <t>Tampa's theatrical polymath. Technical fire meets conceptual daring.</t>
         </is>
       </c>
     </row>
@@ -9045,9 +8933,8 @@
       <c r="N114" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O114" s="6">
-        <f>AVERAGE(J114:N114)</f>
-        <v/>
+      <c r="O114" s="6" t="n">
+        <v>4.8</v>
       </c>
       <c r="P114" s="15" t="inlineStr">
         <is>
@@ -9061,7 +8948,7 @@
       </c>
       <c r="R114" s="2" t="inlineStr">
         <is>
-          <t>FNF. Memphis energy with instant cultural resonance.</t>
+          <t>Memphis energy, unfiltered personality. New Southern feminism in party form.</t>
         </is>
       </c>
     </row>
@@ -9122,9 +9009,8 @@
       <c r="N115" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="O115" s="6">
-        <f>AVERAGE(J115:N115)</f>
-        <v/>
+      <c r="O115" s="6" t="n">
+        <v>4.2</v>
       </c>
       <c r="P115" s="14" t="inlineStr">
         <is>
@@ -9138,7 +9024,7 @@
       </c>
       <c r="R115" s="2" t="inlineStr">
         <is>
-          <t>DS4EVER. Melodic trap comfort zone never pushed.</t>
+          <t>Melodic luxury trap. Vibe and aesthetic are the art.</t>
         </is>
       </c>
     </row>
@@ -9199,9 +9085,8 @@
       <c r="N116" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O116" s="6">
-        <f>AVERAGE(J116:N116)</f>
-        <v/>
+      <c r="O116" s="6" t="n">
+        <v>5.2</v>
       </c>
       <c r="P116" s="14" t="inlineStr">
         <is>
@@ -9215,7 +9100,7 @@
       </c>
       <c r="R116" s="2" t="inlineStr">
         <is>
-          <t>My Turn. Effortless commercial dominance; artistry developing.</t>
+          <t>Authentic street narrator. Storytelling grounded in lived experience.</t>
         </is>
       </c>
     </row>
@@ -9276,9 +9161,8 @@
       <c r="N117" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O117" s="6">
-        <f>AVERAGE(J117:N117)</f>
-        <v/>
+      <c r="O117" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="P117" s="7" t="inlineStr">
         <is>
@@ -9288,7 +9172,7 @@
       <c r="Q117" s="2" t="inlineStr"/>
       <c r="R117" s="2" t="inlineStr">
         <is>
-          <t>Burden of Proof. Griselda's street pulpit.</t>
+          <t>Griselda's lyrical backbone. Buffalo street narratives with East Coast precision.</t>
         </is>
       </c>
     </row>
@@ -9349,9 +9233,8 @@
       <c r="N118" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O118" s="6">
-        <f>AVERAGE(J118:N118)</f>
-        <v/>
+      <c r="O118" s="6" t="n">
+        <v>7.2</v>
       </c>
       <c r="P118" s="7" t="inlineStr">
         <is>
@@ -9361,7 +9244,7 @@
       <c r="Q118" s="2" t="inlineStr"/>
       <c r="R118" s="2" t="inlineStr">
         <is>
-          <t>Heavy Is the Head. UK grime at Glastonbury scale.</t>
+          <t>UK grime's political conscience. Authenticity and ambition fused.</t>
         </is>
       </c>
     </row>
@@ -9422,9 +9305,8 @@
       <c r="N119" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="O119" s="6">
-        <f>AVERAGE(J119:N119)</f>
-        <v/>
+      <c r="O119" s="6" t="n">
+        <v>5.8</v>
       </c>
       <c r="P119" s="14" t="inlineStr">
         <is>
@@ -9438,7 +9320,7 @@
       </c>
       <c r="R119" s="2" t="inlineStr">
         <is>
-          <t>Un Verano Sin Ti. Latin trap global domination.</t>
+          <t>Global Latin trap superstar. Reframed what non-English rap could achieve commercially.</t>
         </is>
       </c>
     </row>
@@ -9499,9 +9381,8 @@
       <c r="N120" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O120" s="6">
-        <f>AVERAGE(J120:N120)</f>
-        <v/>
+      <c r="O120" s="6" t="n">
+        <v>4.4</v>
       </c>
       <c r="P120" s="15" t="inlineStr">
         <is>
@@ -9515,7 +9396,7 @@
       </c>
       <c r="R120" s="2" t="inlineStr">
         <is>
-          <t>Colores. Reggaeton popstar with rap adjacency.</t>
+          <t>Reggaeton crossover king. Melody and production far exceed lyrical content.</t>
         </is>
       </c>
     </row>
@@ -9576,9 +9457,8 @@
       <c r="N121" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O121" s="6">
-        <f>AVERAGE(J121:N121)</f>
-        <v/>
+      <c r="O121" s="6" t="n">
+        <v>5</v>
       </c>
       <c r="P121" s="14" t="inlineStr">
         <is>
@@ -9592,7 +9472,7 @@
       </c>
       <c r="R121" s="2" t="inlineStr">
         <is>
-          <t>Set It Off. Post-Migos identity search ongoing.</t>
+          <t>Migos' most lyrical member. Flow variation and delivery standout in trap context.</t>
         </is>
       </c>
     </row>
@@ -9653,9 +9533,8 @@
       <c r="N122" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O122" s="6">
-        <f>AVERAGE(J122:N122)</f>
-        <v/>
+      <c r="O122" s="6" t="n">
+        <v>7</v>
       </c>
       <c r="P122" s="15" t="inlineStr">
         <is>
@@ -9669,7 +9548,7 @@
       </c>
       <c r="R122" s="2" t="inlineStr">
         <is>
-          <t>Angelic Hoodrat. Atlanta experimental underground at its weirdest.</t>
+          <t>Atlanta's punk-rap hybrid. Unconventional tonal range.</t>
         </is>
       </c>
     </row>
@@ -9730,9 +9609,8 @@
       <c r="N123" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O123" s="6">
-        <f>AVERAGE(J123:N123)</f>
-        <v/>
+      <c r="O123" s="6" t="n">
+        <v>5.8</v>
       </c>
       <c r="P123" s="14" t="inlineStr">
         <is>
@@ -9746,7 +9624,7 @@
       </c>
       <c r="R123" s="2" t="inlineStr">
         <is>
-          <t>777. Southern female rap following Cardi and Nicki's path.</t>
+          <t>Atlanta's female trap voice. Technical skill often underestimated.</t>
         </is>
       </c>
     </row>
@@ -9807,9 +9685,8 @@
       <c r="N124" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O124" s="6">
-        <f>AVERAGE(J124:N124)</f>
-        <v/>
+      <c r="O124" s="6" t="n">
+        <v>7.4</v>
       </c>
       <c r="P124" s="14" t="inlineStr">
         <is>
@@ -9823,7 +9700,7 @@
       </c>
       <c r="R124" s="2" t="inlineStr">
         <is>
-          <t>blkswn. Jazz-rap from St. Louis with melodic depth.</t>
+          <t>St. Louis's jazz-rap hybrid. Melodic and rhythmic sophistication.</t>
         </is>
       </c>
     </row>
@@ -9884,9 +9761,8 @@
       <c r="N125" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O125" s="6">
-        <f>AVERAGE(J125:N125)</f>
-        <v/>
+      <c r="O125" s="6" t="n">
+        <v>7.4</v>
       </c>
       <c r="P125" s="7" t="inlineStr">
         <is>
@@ -9896,7 +9772,7 @@
       <c r="Q125" s="2" t="inlineStr"/>
       <c r="R125" s="2" t="inlineStr">
         <is>
-          <t>It's Almost Dry. Coke rap as high art. Pharrell and Kanye dual production.</t>
+          <t>Cocaine rap's Rembrandt. 'Daytona' — maximum density, minimum waste.</t>
         </is>
       </c>
     </row>
@@ -9957,9 +9833,8 @@
       <c r="N126" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O126" s="6">
-        <f>AVERAGE(J126:N126)</f>
-        <v/>
+      <c r="O126" s="6" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="P126" s="14" t="inlineStr">
         <is>
@@ -9973,7 +9848,7 @@
       </c>
       <c r="R126" s="2" t="inlineStr">
         <is>
-          <t>The Never Story / Pandemonium!. Technical rapper escaping Atlanta tropes.</t>
+          <t>Atlanta's most technically gifted. 'The Never Story' showed generational talent.</t>
         </is>
       </c>
     </row>
@@ -10034,9 +9909,8 @@
       <c r="N127" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O127" s="6">
-        <f>AVERAGE(J127:N127)</f>
-        <v/>
+      <c r="O127" s="6" t="n">
+        <v>8.4</v>
       </c>
       <c r="P127" s="7" t="inlineStr">
         <is>
@@ -10046,7 +9920,7 @@
       <c r="Q127" s="2" t="inlineStr"/>
       <c r="R127" s="2" t="inlineStr">
         <is>
-          <t>Igor / Call Me If You Get Lost. Conceptual album art as rap.</t>
+          <t>'Igor' and 'Call Me If You Get Lost' — producer-auteur. Concept album mastery.</t>
         </is>
       </c>
     </row>
@@ -10107,9 +9981,8 @@
       <c r="N128" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O128" s="6">
-        <f>AVERAGE(J128:N128)</f>
-        <v/>
+      <c r="O128" s="6" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="P128" s="14" t="inlineStr">
         <is>
@@ -10123,7 +9996,7 @@
       </c>
       <c r="R128" s="2" t="inlineStr">
         <is>
-          <t>Haram. billy woods + ELUCID: dense, allusive, uncompromising.</t>
+          <t>billy woods + ELUCID. The most demanding abstract rap being made today.</t>
         </is>
       </c>
     </row>
@@ -10184,9 +10057,8 @@
       <c r="N129" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="O129" s="6">
-        <f>AVERAGE(J129:N129)</f>
-        <v/>
+      <c r="O129" s="6" t="n">
+        <v>6.4</v>
       </c>
       <c r="P129" s="15" t="inlineStr">
         <is>
@@ -10200,7 +10072,7 @@
       </c>
       <c r="R129" s="2" t="inlineStr">
         <is>
-          <t>Bussin. Internet-native absurdist rapper with genuine lyrical wit.</t>
+          <t>Comedy-meets-rap. Formally interesting but body of work too small to score confidently.</t>
         </is>
       </c>
     </row>
@@ -10261,9 +10133,8 @@
       <c r="N130" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O130" s="6">
-        <f>AVERAGE(J130:N130)</f>
-        <v/>
+      <c r="O130" s="6" t="n">
+        <v>5.2</v>
       </c>
       <c r="P130" s="14" t="inlineStr">
         <is>
@@ -10277,7 +10148,7 @@
       </c>
       <c r="R130" s="2" t="inlineStr">
         <is>
-          <t>The Voice. Chicago melodic trap emotional authenticity at scale.</t>
+          <t>Chicago drill's most commercially consistent voice.</t>
         </is>
       </c>
     </row>
@@ -10338,9 +10209,8 @@
       <c r="N131" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O131" s="6">
-        <f>AVERAGE(J131:N131)</f>
-        <v/>
+      <c r="O131" s="6" t="n">
+        <v>5</v>
       </c>
       <c r="P131" s="14" t="inlineStr">
         <is>
@@ -10354,7 +10224,7 @@
       </c>
       <c r="R131" s="2" t="inlineStr">
         <is>
-          <t>Project Baby. Florida trap originality clouded by off-mic controversies.</t>
+          <t>Florida trap's most distinctive voice. Rough-edged regional authenticity.</t>
         </is>
       </c>
     </row>
@@ -10415,9 +10285,8 @@
       <c r="N132" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O132" s="6">
-        <f>AVERAGE(J132:N132)</f>
-        <v/>
+      <c r="O132" s="6" t="n">
+        <v>6.6</v>
       </c>
       <c r="P132" s="15" t="inlineStr">
         <is>
@@ -10431,7 +10300,7 @@
       </c>
       <c r="R132" s="2" t="inlineStr">
         <is>
-          <t>Por Vida. Colombian-American bilingual artistry; rap adjacent.</t>
+          <t>Colombian-American crossover. When rapping, brings genuine bilingual lyricism.</t>
         </is>
       </c>
     </row>
@@ -10492,9 +10361,8 @@
       <c r="N133" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O133" s="6">
-        <f>AVERAGE(J133:N133)</f>
-        <v/>
+      <c r="O133" s="6" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="P133" s="7" t="inlineStr">
         <is>
@@ -10504,7 +10372,7 @@
       <c r="Q133" s="2" t="inlineStr"/>
       <c r="R133" s="2" t="inlineStr">
         <is>
-          <t>Eve. Named every track after a Black woman. Precision and purpose.</t>
+          <t>North Carolina's most complete female MC. Lyrical depth rivals any peer.</t>
         </is>
       </c>
     </row>
@@ -10565,9 +10433,8 @@
       <c r="N134" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="O134" s="6">
-        <f>AVERAGE(J134:N134)</f>
-        <v/>
+      <c r="O134" s="6" t="n">
+        <v>8.6</v>
       </c>
       <c r="P134" s="14" t="inlineStr">
         <is>
@@ -10581,7 +10448,7 @@
       </c>
       <c r="R134" s="2" t="inlineStr">
         <is>
-          <t>Factory Baby. Post-Room 25 political radicalization era.</t>
+          <t>Noname's political radicalization phase. Most conceptually ambitious output.</t>
         </is>
       </c>
     </row>
@@ -10642,9 +10509,8 @@
       <c r="N135" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O135" s="6">
-        <f>AVERAGE(J135:N135)</f>
-        <v/>
+      <c r="O135" s="6" t="n">
+        <v>7.2</v>
       </c>
       <c r="P135" s="15" t="inlineStr">
         <is>
@@ -10658,7 +10524,7 @@
       </c>
       <c r="R135" s="2" t="inlineStr">
         <is>
-          <t>Let the Sun Talk. Introspective underground debut with cultish following.</t>
+          <t>Charlotte underground. Dense introspective abstract rap. Watch this space.</t>
         </is>
       </c>
     </row>
@@ -10719,9 +10585,8 @@
       <c r="N136" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="O136" s="6">
-        <f>AVERAGE(J136:N136)</f>
-        <v/>
+      <c r="O136" s="6" t="n">
+        <v>6.8</v>
       </c>
       <c r="P136" s="14" t="inlineStr">
         <is>
@@ -10735,7 +10600,7 @@
       </c>
       <c r="R136" s="2" t="inlineStr">
         <is>
-          <t>At the Speed of Life. West Coast boom bap craftsman.</t>
+          <t>West Coast boom bap craftsman. More respected by peers than critics.</t>
         </is>
       </c>
     </row>
@@ -10796,9 +10661,8 @@
       <c r="N137" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O137" s="6">
-        <f>AVERAGE(J137:N137)</f>
-        <v/>
+      <c r="O137" s="6" t="n">
+        <v>4.8</v>
       </c>
       <c r="P137" s="14" t="inlineStr">
         <is>
@@ -10812,7 +10676,7 @@
       </c>
       <c r="R137" s="2" t="inlineStr">
         <is>
-          <t>Pretty Summer Playlist. Bay Area trap-pop aesthetic.</t>
+          <t>Bay Area trap-pop. Ice Princess persona over lyrical substance.</t>
         </is>
       </c>
     </row>
@@ -10873,9 +10737,8 @@
       <c r="N138" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O138" s="6">
-        <f>AVERAGE(J138:N138)</f>
-        <v/>
+      <c r="O138" s="6" t="n">
+        <v>4.6</v>
       </c>
       <c r="P138" s="15" t="inlineStr">
         <is>
@@ -10889,7 +10752,7 @@
       </c>
       <c r="R138" s="2" t="inlineStr">
         <is>
-          <t>Period. Miami hedonistic party rap duo.</t>
+          <t>Miami's hedonistic party rap duo. Energy over craft.</t>
         </is>
       </c>
     </row>
@@ -10950,9 +10813,8 @@
       <c r="N139" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O139" s="6">
-        <f>AVERAGE(J139:N139)</f>
-        <v/>
+      <c r="O139" s="6" t="n">
+        <v>7.4</v>
       </c>
       <c r="P139" s="14" t="inlineStr">
         <is>
@@ -10966,7 +10828,7 @@
       </c>
       <c r="R139" s="2" t="inlineStr">
         <is>
-          <t>Weight of the World. Houston storytelling tradition continued.</t>
+          <t>Houston storytelling tradition continued. 'Weight of the World' deeply affecting.</t>
         </is>
       </c>
     </row>
@@ -11027,9 +10889,8 @@
       <c r="N140" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O140" s="6">
-        <f>AVERAGE(J140:N140)</f>
-        <v/>
+      <c r="O140" s="6" t="n">
+        <v>7.6</v>
       </c>
       <c r="P140" s="15" t="inlineStr">
         <is>

--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Artist Database" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Confidence Guide" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artist Database'!$A$1:$R$1</definedName>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,6 +71,9 @@
       <b val="1"/>
       <color rgb="009C0006"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="15">
@@ -157,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -203,6 +207,13 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10912,4 +10923,161 @@
   <autoFilter ref="A1:R1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>Scoring Confidence Flag Guide</t>
+        </is>
+      </c>
+      <c r="C1" s="17" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Flag</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+      <c r="C2" s="18" t="inlineStr">
+        <is>
+          <t>Criteria for assignment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>H — High</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Extensive critical record</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>Artist has: (1) sustained critical and/or academic attention, (2) multiple long-form critical analyses of their lyrical craft, (3) consistent reception across multiple sources, (4) enough body of work that scores are stable across albums. Examples: Rakim, Nas, Eminem, Kendrick, Biggie, Jay-Z.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>M — Medium</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Moderate documentation</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>Artist meets 1–2 of the High criteria but not all. May be: historically significant but under-analyzed (e.g. MC Lyte), recently emergent with promising but incomplete body of work (e.g. J.I.D, Doechii), subject to contested or shifting critical reception, or significant in regional/underground circles without mainstream scholarly attention. Scores should be treated as provisional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>L — Low</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Thin or contested record</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>Artist has: limited formal critical analysis, very recent emergence (insufficient time for consensus), scores that rely heavily on a single source or thin evidence base, reception clouded by non-lyrical controversy, or requires critical frameworks not well-developed in English-language sources (e.g. Latin rap, non-English artists). Scores marked L should be treated as initial estimates requiring verification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" s="17" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>METHODOLOGICAL NOTES</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Scoring basis</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>Critical consensus synthesis</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>All scores are derived from synthesis of published music criticism, academic hip-hop scholarship (Bradley, Chang, Kajikawa, Rabaka), and documented critical consensus. They are NOT computational — no NLP analysis was run. Aesop Rock is used as the Vocab Breadth=10 anchor based on published NLP studies of unique vocabulary in rap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Known biases</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Prestige / gender / language</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>The dataset over-represents: critically acclaimed artists vs commercially dominant ones; male artists (correcting); Golden Age NYC; English-language rap. Latin, African, and non-Anglophone rap are significantly underrepresented and scores for international artists should be treated with extra caution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Recommended verification</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>For each L- and M-flagged artist</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>Cross-reference against: RateYourMusic critical consensus scores, Pitchfork / The Wire artist discography reviews, academic sources via Google Scholar ('artist name' + 'lyricism' or 'hip-hop'), genre-specific publications (The Source, XXL retrospectives, Passion of the Weiss).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -5093,12 +5093,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Nas feat. AZ</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>AZ's solo career less documented than Nas; scored as AZ</t>
+          <t>Solo career less documented than Nas; scored on his own body of work.</t>
         </is>
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>AZ: One of the most underrated MCs of the era. 'Sugarhill' an all-time verse.</t>
+          <t>One of the era's most underrated lyricists. 'Doe or Die' (1995) a classic; his 'Life's a Bitch' verse is all-time.</t>
         </is>
       </c>
     </row>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Ghostface / Fishscale era</t>
+          <t>Ghostface Killah</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>'Fishscale' is a 2000s apex. Singular stream-of-consciousness voice.</t>
+          <t>Wu-Tang's vivid storyteller; 'Fishscale' (2006) a stream-of-consciousness apex.</t>
         </is>
       </c>
     </row>
@@ -10854,7 +10854,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Yvonne (Yaya Bey)</t>
+          <t>Yaya Bey</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">

--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R140"/>
+  <dimension ref="A1:R135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>J.I.D</t>
+          <t>JID</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -9265,17 +9265,17 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Bad Bunny</t>
+          <t>Offset</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -9285,39 +9285,39 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Party/Pop</t>
+          <t>Trap/Drill</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Reggaeton/Latin Trap</t>
+          <t>Migos Solo Trap</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Rimas</t>
+          <t>Quality Control</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="J119" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="K119" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L119" s="9" t="n">
-        <v>6</v>
+      <c r="K119" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L119" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="M119" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="N119" s="9" t="n">
-        <v>6</v>
+      <c r="N119" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="O119" s="6" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="P119" s="14" t="inlineStr">
         <is>
@@ -9326,12 +9326,12 @@
       </c>
       <c r="Q119" s="2" t="inlineStr">
         <is>
-          <t>Massive influence on global rap; Spanish-language scoring requires different critical frame</t>
+          <t>Solo career emerging post-Migos; scoring tentative</t>
         </is>
       </c>
       <c r="R119" s="2" t="inlineStr">
         <is>
-          <t>Global Latin trap superstar. Reframed what non-English rap could achieve commercially.</t>
+          <t>Migos' most lyrical member. Flow variation and delivery standout in trap context.</t>
         </is>
       </c>
     </row>
@@ -9341,17 +9341,17 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>JB</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>J Balvin</t>
+          <t>Kenny Mason</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -9361,39 +9361,39 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Party/Pop</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Reggaeton</t>
+          <t>Atlanta Punk Rap</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Capitol</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>2007</v>
-      </c>
-      <c r="J120" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K120" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L120" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M120" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N120" s="5" t="n">
-        <v>4</v>
+        <v>2019</v>
+      </c>
+      <c r="J120" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K120" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L120" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M120" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N120" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="O120" s="6" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="P120" s="15" t="inlineStr">
         <is>
@@ -9402,12 +9402,12 @@
       </c>
       <c r="Q120" s="2" t="inlineStr">
         <is>
-          <t>Minimal lyrical critical record; scored on available Spanish-language criticism</t>
+          <t>Limited documentation; critical buzz building in underground circles</t>
         </is>
       </c>
       <c r="R120" s="2" t="inlineStr">
         <is>
-          <t>Reggaeton crossover king. Melody and production far exceed lyrical content.</t>
+          <t>Atlanta's punk-rap hybrid. Unconventional tonal range.</t>
         </is>
       </c>
     </row>
@@ -9417,12 +9417,12 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>OM</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Offset</t>
+          <t>Latto</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -9437,39 +9437,39 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Trap/Drill</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Migos Solo Trap</t>
+          <t>Atlanta Female Trap</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>RCA</t>
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="J121" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K121" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L121" s="8" t="n">
-        <v>5</v>
+        <v>2019</v>
+      </c>
+      <c r="J121" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K121" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L121" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="M121" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="N121" s="5" t="n">
-        <v>4</v>
+      <c r="N121" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="O121" s="6" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="P121" s="14" t="inlineStr">
         <is>
@@ -9478,12 +9478,12 @@
       </c>
       <c r="Q121" s="2" t="inlineStr">
         <is>
-          <t>Solo career emerging post-Migos; scoring tentative</t>
+          <t>Recent; commercial trajectory clearer than critical consensus</t>
         </is>
       </c>
       <c r="R121" s="2" t="inlineStr">
         <is>
-          <t>Migos' most lyrical member. Flow variation and delivery standout in trap context.</t>
+          <t>Atlanta's female trap voice. Technical skill often underestimated.</t>
         </is>
       </c>
     </row>
@@ -9493,17 +9493,17 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>SR</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Kenny Mason</t>
+          <t>Smino</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -9518,48 +9518,48 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Punk Rap</t>
+          <t>St. Louis Jazz Rap</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Zero Fatigue</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="J122" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="K122" s="10" t="n">
-        <v>7</v>
+      <c r="K122" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="L122" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="M122" s="10" t="n">
-        <v>7</v>
+      <c r="M122" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="N122" s="10" t="n">
         <v>7</v>
       </c>
       <c r="O122" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="P122" s="15" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>7.4</v>
+      </c>
+      <c r="P122" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
         <is>
-          <t>Limited documentation; critical buzz building in underground circles</t>
+          <t>Critical darling in jazz-rap circles; broader recognition still forming</t>
         </is>
       </c>
       <c r="R122" s="2" t="inlineStr">
         <is>
-          <t>Atlanta's punk-rap hybrid. Unconventional tonal range.</t>
+          <t>St. Louis's jazz-rap hybrid. Melodic and rhythmic sophistication.</t>
         </is>
       </c>
     </row>
@@ -9569,17 +9569,17 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>PZ</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Latto</t>
+          <t>Pusha T</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>NYC</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -9594,48 +9594,44 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Female Trap</t>
+          <t>Coke Rap Boom Bap</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>RCA</t>
+          <t>G.O.O.D.</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>2019</v>
-      </c>
-      <c r="J123" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K123" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L123" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M123" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N123" s="8" t="n">
-        <v>5</v>
+        <v>2002</v>
+      </c>
+      <c r="J123" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K123" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L123" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M123" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N123" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="O123" s="6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="P123" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q123" s="2" t="inlineStr">
-        <is>
-          <t>Recent; commercial trajectory clearer than critical consensus</t>
-        </is>
-      </c>
+        <v>7.4</v>
+      </c>
+      <c r="P123" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q123" s="2" t="inlineStr"/>
       <c r="R123" s="2" t="inlineStr">
         <is>
-          <t>Atlanta's female trap voice. Technical skill often underestimated.</t>
+          <t>Cocaine rap's Rembrandt. 'Daytona' — maximum density, minimum waste.</t>
         </is>
       </c>
     </row>
@@ -9645,17 +9641,17 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Smino</t>
+          <t>Tyler the Creator</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -9670,48 +9666,44 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>St. Louis Jazz Rap</t>
+          <t>Odd Future/Orchestral</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Zero Fatigue</t>
+          <t>Columbia</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>2017</v>
+        <v>2009</v>
       </c>
       <c r="J124" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="K124" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L124" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M124" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N124" s="10" t="n">
-        <v>7</v>
+      <c r="K124" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L124" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M124" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="N124" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="O124" s="6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="P124" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q124" s="2" t="inlineStr">
-        <is>
-          <t>Critical darling in jazz-rap circles; broader recognition still forming</t>
-        </is>
-      </c>
+        <v>8.4</v>
+      </c>
+      <c r="P124" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q124" s="2" t="inlineStr"/>
       <c r="R124" s="2" t="inlineStr">
         <is>
-          <t>St. Louis's jazz-rap hybrid. Melodic and rhythmic sophistication.</t>
+          <t>'Igor' and 'Call Me If You Get Lost' — producer-auteur. Concept album mastery.</t>
         </is>
       </c>
     </row>
@@ -9721,12 +9713,12 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>PZ</t>
+          <t>AB2</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Pusha T</t>
+          <t>Armand Hammer</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -9741,49 +9733,53 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Abstract</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Coke Rap Boom Bap</t>
+          <t>Abstract Boom Bap</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>G.O.O.D.</t>
+          <t>Backwoodz</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>2002</v>
+        <v>2012</v>
       </c>
       <c r="J125" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="K125" s="10" t="n">
-        <v>7</v>
+      <c r="K125" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="L125" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="M125" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N125" s="10" t="n">
-        <v>7</v>
+      <c r="M125" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="N125" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="O125" s="6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="P125" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q125" s="2" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="P125" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q125" s="2" t="inlineStr">
+        <is>
+          <t>Critical underground darling; thin mainstream documentation</t>
+        </is>
+      </c>
       <c r="R125" s="2" t="inlineStr">
         <is>
-          <t>Cocaine rap's Rembrandt. 'Daytona' — maximum density, minimum waste.</t>
+          <t>billy woods + ELUCID. The most demanding abstract rap being made today.</t>
         </is>
       </c>
     </row>
@@ -9793,17 +9789,17 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>ZE</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>JID</t>
+          <t>Zach Fox</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>NYC</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -9813,53 +9809,53 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Abstract</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Technical Rap</t>
+          <t>Comedy-Abstract Rap</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Dreamville</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="J126" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="K126" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L126" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M126" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N126" s="11" t="n">
-        <v>8</v>
+        <v>2020</v>
+      </c>
+      <c r="J126" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K126" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L126" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M126" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N126" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="O126" s="6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="P126" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
+        <v>6.4</v>
+      </c>
+      <c r="P126" s="15" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t>Recent; scoring likely conservative; upward trajectory clear</t>
+          <t>Very recent; extremely limited critical record</t>
         </is>
       </c>
       <c r="R126" s="2" t="inlineStr">
         <is>
-          <t>Atlanta's most technically gifted. 'The Never Story' showed generational talent.</t>
+          <t>Comedy-meets-rap. Formally interesting but body of work too small to score confidently.</t>
         </is>
       </c>
     </row>
@@ -9869,17 +9865,17 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Tyler the Creator</t>
+          <t>Lil Durk</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -9889,49 +9885,53 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Odd Future/Orchestral</t>
+          <t>Chicago Melodic Trap</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>Columbia</t>
+          <t>Only the Family</t>
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>2009</v>
-      </c>
-      <c r="J127" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K127" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L127" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M127" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="N127" s="12" t="n">
-        <v>9</v>
+        <v>2013</v>
+      </c>
+      <c r="J127" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K127" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L127" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M127" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N127" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="O127" s="6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="P127" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q127" s="2" t="inlineStr"/>
+        <v>5.2</v>
+      </c>
+      <c r="P127" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q127" s="2" t="inlineStr">
+        <is>
+          <t>Commercial dominance clear; critical depth limited</t>
+        </is>
+      </c>
       <c r="R127" s="2" t="inlineStr">
         <is>
-          <t>'Igor' and 'Call Me If You Get Lost' — producer-auteur. Concept album mastery.</t>
+          <t>Chicago drill's most commercially consistent voice.</t>
         </is>
       </c>
     </row>
@@ -9941,17 +9941,17 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>AB2</t>
+          <t>KS2</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Armand Hammer</t>
+          <t>Kodak Black</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -9961,39 +9961,39 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Abstract</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Abstract Boom Bap</t>
+          <t>Florida Trap</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Backwoodz</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>2012</v>
-      </c>
-      <c r="J128" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K128" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L128" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M128" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="N128" s="11" t="n">
-        <v>8</v>
+        <v>2014</v>
+      </c>
+      <c r="J128" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K128" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L128" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M128" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N128" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="O128" s="6" t="n">
-        <v>8.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="P128" s="14" t="inlineStr">
         <is>
@@ -10002,12 +10002,12 @@
       </c>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>Critical underground darling; thin mainstream documentation</t>
+          <t>Commercial success; thin critical framework; behavior clouds reception</t>
         </is>
       </c>
       <c r="R128" s="2" t="inlineStr">
         <is>
-          <t>billy woods + ELUCID. The most demanding abstract rap being made today.</t>
+          <t>Florida trap's most distinctive voice. Rough-edged regional authenticity.</t>
         </is>
       </c>
     </row>
@@ -10017,17 +10017,17 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>ZE</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Zach Fox</t>
+          <t>Rapsody</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -10037,53 +10037,49 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>Abstract</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Comedy-Abstract Rap</t>
+          <t>North Carolina Soul Rap</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Jamla</t>
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="J129" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K129" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L129" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M129" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N129" s="9" t="n">
-        <v>6</v>
+        <v>2010</v>
+      </c>
+      <c r="J129" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K129" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L129" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M129" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N129" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="O129" s="6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="P129" s="15" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="Q129" s="2" t="inlineStr">
-        <is>
-          <t>Very recent; extremely limited critical record</t>
-        </is>
-      </c>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="P129" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q129" s="2" t="inlineStr"/>
       <c r="R129" s="2" t="inlineStr">
         <is>
-          <t>Comedy-meets-rap. Formally interesting but body of work too small to score confidently.</t>
+          <t>North Carolina's most complete female MC. Lyrical depth rivals any peer.</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10089,12 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>MF2</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Lil Durk</t>
+          <t>Mavi</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -10113,53 +10109,53 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Abstract</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Chicago Melodic Trap</t>
+          <t>Underground Abstract</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Only the Family</t>
+          <t>Mutant Academy</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>2013</v>
-      </c>
-      <c r="J130" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K130" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L130" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M130" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N130" s="8" t="n">
-        <v>5</v>
+        <v>2019</v>
+      </c>
+      <c r="J130" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K130" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L130" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M130" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N130" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="O130" s="6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="P130" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
+        <v>7.2</v>
+      </c>
+      <c r="P130" s="15" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
         <is>
-          <t>Commercial dominance clear; critical depth limited</t>
+          <t>Very limited critical documentation; underground following only</t>
         </is>
       </c>
       <c r="R130" s="2" t="inlineStr">
         <is>
-          <t>Chicago drill's most commercially consistent voice.</t>
+          <t>Charlotte underground. Dense introspective abstract rap. Watch this space.</t>
         </is>
       </c>
     </row>
@@ -10169,22 +10165,22 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>KS2</t>
+          <t>XP</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Kodak Black</t>
+          <t>Xzibit</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2000s</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -10194,34 +10190,34 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Florida Trap</t>
+          <t>Hard West Coast</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Loud/Columbia</t>
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>2014</v>
-      </c>
-      <c r="J131" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K131" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L131" s="9" t="n">
+        <v>1996</v>
+      </c>
+      <c r="J131" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K131" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L131" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M131" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N131" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="M131" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N131" s="5" t="n">
-        <v>4</v>
-      </c>
       <c r="O131" s="6" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="P131" s="14" t="inlineStr">
         <is>
@@ -10230,12 +10226,12 @@
       </c>
       <c r="Q131" s="2" t="inlineStr">
         <is>
-          <t>Commercial success; thin critical framework; behavior clouds reception</t>
+          <t>Well-known but limited formal critical analysis</t>
         </is>
       </c>
       <c r="R131" s="2" t="inlineStr">
         <is>
-          <t>Florida trap's most distinctive voice. Rough-edged regional authenticity.</t>
+          <t>West Coast boom bap craftsman. More respected by peers than critics.</t>
         </is>
       </c>
     </row>
@@ -10245,17 +10241,17 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>LA2</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Lana (Kali Uchis rap)</t>
+          <t>Saweetie</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -10265,53 +10261,53 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Party/Pop</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R&amp;B/Latin Rap Hybrid</t>
+          <t>Trap Pop</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Virgin</t>
+          <t>Warner</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
         <v>2018</v>
       </c>
-      <c r="J132" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K132" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L132" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M132" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N132" s="10" t="n">
-        <v>7</v>
+      <c r="J132" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K132" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L132" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M132" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N132" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="O132" s="6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="P132" s="15" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>4.8</v>
+      </c>
+      <c r="P132" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
         <is>
-          <t>Primarily R&amp;B artist; rap output limited and under-analyzed</t>
+          <t>Recent commercial success; limited critical depth</t>
         </is>
       </c>
       <c r="R132" s="2" t="inlineStr">
         <is>
-          <t>Colombian-American crossover. When rapping, brings genuine bilingual lyricism.</t>
+          <t>Bay Area trap-pop. Ice Princess persona over lyrical substance.</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10317,12 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Rapsody</t>
+          <t>City Girls</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -10341,49 +10337,53 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Party/Pop</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>North Carolina Soul Rap</t>
+          <t>Miami Trap</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>Jamla</t>
+          <t>Quality Control/Motown</t>
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>2010</v>
-      </c>
-      <c r="J133" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K133" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L133" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M133" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N133" s="12" t="n">
-        <v>9</v>
+        <v>2018</v>
+      </c>
+      <c r="J133" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K133" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L133" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M133" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N133" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="O133" s="6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="P133" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q133" s="2" t="inlineStr"/>
+        <v>4.6</v>
+      </c>
+      <c r="P133" s="15" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q133" s="2" t="inlineStr">
+        <is>
+          <t>Limited critical record; cultural impact clearer than lyrical analysis</t>
+        </is>
+      </c>
       <c r="R133" s="2" t="inlineStr">
         <is>
-          <t>North Carolina's most complete female MC. Lyrical depth rivals any peer.</t>
+          <t>Miami's hedonistic party rap duo. Energy over craft.</t>
         </is>
       </c>
     </row>
@@ -10393,17 +10393,17 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Noname (Ghetto Sage)</t>
+          <t>Maxo Kream</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -10413,39 +10413,39 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>Political</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Political Jazz Rap</t>
+          <t>Houston Narrative Trap</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>2019</v>
-      </c>
-      <c r="J134" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K134" s="12" t="n">
+        <v>2017</v>
+      </c>
+      <c r="J134" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K134" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L134" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L134" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M134" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N134" s="13" t="n">
-        <v>10</v>
+      <c r="M134" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N134" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="O134" s="6" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="P134" s="14" t="inlineStr">
         <is>
@@ -10454,12 +10454,12 @@
       </c>
       <c r="Q134" s="2" t="inlineStr">
         <is>
-          <t>Political evolution post-Room 25; scoring for this phase specifically</t>
+          <t>Critical acclaim in narrative rap circles; limited mainstream documentation</t>
         </is>
       </c>
       <c r="R134" s="2" t="inlineStr">
         <is>
-          <t>Noname's political radicalization phase. Most conceptually ambitious output.</t>
+          <t>Houston storytelling tradition continued. 'Weight of the World' deeply affecting.</t>
         </is>
       </c>
     </row>
@@ -10469,17 +10469,17 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>MF2</t>
+          <t>YN</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Mavi</t>
+          <t>Yaya Bey</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>NYC</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -10489,21 +10489,21 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>Abstract</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Underground Abstract</t>
+          <t>Neo-Soul Jazz Rap</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>Mutant Academy</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="J135" s="10" t="n">
         <v>7</v>
@@ -10514,14 +10514,14 @@
       <c r="L135" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="M135" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N135" s="10" t="n">
-        <v>7</v>
+      <c r="M135" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N135" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="O135" s="6" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="P135" s="15" t="inlineStr">
         <is>
@@ -10530,390 +10530,10 @@
       </c>
       <c r="Q135" s="2" t="inlineStr">
         <is>
-          <t>Very limited critical documentation; underground following only</t>
+          <t>Very recent and limited documentation; genre straddles rap and R&amp;B</t>
         </is>
       </c>
       <c r="R135" s="2" t="inlineStr">
-        <is>
-          <t>Charlotte underground. Dense introspective abstract rap. Watch this space.</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="n">
-        <v>135</v>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>XP</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>Xzibit</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>LA</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>Gangsta/Street</t>
-        </is>
-      </c>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t>Hard West Coast</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>Loud/Columbia</t>
-        </is>
-      </c>
-      <c r="I136" s="2" t="n">
-        <v>1996</v>
-      </c>
-      <c r="J136" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K136" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L136" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M136" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N136" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="O136" s="6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="P136" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q136" s="2" t="inlineStr">
-        <is>
-          <t>Well-known but limited formal critical analysis</t>
-        </is>
-      </c>
-      <c r="R136" s="2" t="inlineStr">
-        <is>
-          <t>West Coast boom bap craftsman. More respected by peers than critics.</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="n">
-        <v>136</v>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>Saweetie</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>LA</t>
-        </is>
-      </c>
-      <c r="E137" s="2" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="inlineStr">
-        <is>
-          <t>Party/Pop</t>
-        </is>
-      </c>
-      <c r="G137" s="2" t="inlineStr">
-        <is>
-          <t>Trap Pop</t>
-        </is>
-      </c>
-      <c r="H137" s="2" t="inlineStr">
-        <is>
-          <t>Warner</t>
-        </is>
-      </c>
-      <c r="I137" s="2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="J137" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K137" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L137" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="M137" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N137" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="O137" s="6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P137" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q137" s="2" t="inlineStr">
-        <is>
-          <t>Recent commercial success; limited critical depth</t>
-        </is>
-      </c>
-      <c r="R137" s="2" t="inlineStr">
-        <is>
-          <t>Bay Area trap-pop. Ice Princess persona over lyrical substance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="n">
-        <v>137</v>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>CI</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>City Girls</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr">
-        <is>
-          <t>Party/Pop</t>
-        </is>
-      </c>
-      <c r="G138" s="2" t="inlineStr">
-        <is>
-          <t>Miami Trap</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>Quality Control/Motown</t>
-        </is>
-      </c>
-      <c r="I138" s="2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="J138" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K138" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L138" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="M138" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N138" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="O138" s="6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P138" s="15" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="Q138" s="2" t="inlineStr">
-        <is>
-          <t>Limited critical record; cultural impact clearer than lyrical analysis</t>
-        </is>
-      </c>
-      <c r="R138" s="2" t="inlineStr">
-        <is>
-          <t>Miami's hedonistic party rap duo. Energy over craft.</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="n">
-        <v>138</v>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>MX</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>Maxo Kream</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="E139" s="2" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>Gangsta/Street</t>
-        </is>
-      </c>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t>Houston Narrative Trap</t>
-        </is>
-      </c>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t>EMPIRE</t>
-        </is>
-      </c>
-      <c r="I139" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="J139" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K139" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L139" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M139" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N139" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="O139" s="6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="P139" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q139" s="2" t="inlineStr">
-        <is>
-          <t>Critical acclaim in narrative rap circles; limited mainstream documentation</t>
-        </is>
-      </c>
-      <c r="R139" s="2" t="inlineStr">
-        <is>
-          <t>Houston storytelling tradition continued. 'Weight of the World' deeply affecting.</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="n">
-        <v>139</v>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>YN</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>Yaya Bey</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>NYC</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>Experimental</t>
-        </is>
-      </c>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t>Neo-Soul Jazz Rap</t>
-        </is>
-      </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>Independent</t>
-        </is>
-      </c>
-      <c r="I140" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="J140" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K140" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L140" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M140" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N140" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="O140" s="6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="P140" s="15" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="Q140" s="2" t="inlineStr">
-        <is>
-          <t>Very recent and limited documentation; genre straddles rap and R&amp;B</t>
-        </is>
-      </c>
-      <c r="R140" s="2" t="inlineStr">
         <is>
           <t>Brooklyn experimental R&amp;B-rap hybrid. Underrecognized artistic depth.</t>
         </is>

--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -1583,7 +1583,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>NYC</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>RCA Records</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Zach Fox</t>
+          <t>Zack Fox</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -10119,7 +10119,7 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Mutant Academy</t>
+          <t>Secretly Canadian</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Big Dada</t>
         </is>
       </c>
       <c r="I135" s="2" t="n">

--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R135"/>
+  <dimension ref="A1:R134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>Philly</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>Philly</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -10460,82 +10460,6 @@
       <c r="R134" s="2" t="inlineStr">
         <is>
           <t>Houston storytelling tradition continued. 'Weight of the World' deeply affecting.</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="n">
-        <v>134</v>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>YN</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>Yaya Bey</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>NYC</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
-      <c r="F135" s="2" t="inlineStr">
-        <is>
-          <t>Experimental</t>
-        </is>
-      </c>
-      <c r="G135" s="2" t="inlineStr">
-        <is>
-          <t>Neo-Soul Jazz Rap</t>
-        </is>
-      </c>
-      <c r="H135" s="2" t="inlineStr">
-        <is>
-          <t>Big Dada</t>
-        </is>
-      </c>
-      <c r="I135" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="J135" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K135" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L135" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M135" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N135" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="O135" s="6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="P135" s="15" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="Q135" s="2" t="inlineStr">
-        <is>
-          <t>Very recent and limited documentation; genre straddles rap and R&amp;B</t>
-        </is>
-      </c>
-      <c r="R135" s="2" t="inlineStr">
-        <is>
-          <t>Brooklyn experimental R&amp;B-rap hybrid. Underrecognized artistic depth.</t>
         </is>
       </c>
     </row>

--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -8163,7 +8163,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>Philly</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -9875,7 +9875,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>Bay Area</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">

--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -3579,7 +3579,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Acacia</t>
+          <t>Sun Music</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
@@ -6146,7 +6146,7 @@
         <v>2001</v>
       </c>
       <c r="J76" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K76" s="10" t="n">
         <v>7</v>
@@ -6155,13 +6155,13 @@
         <v>7</v>
       </c>
       <c r="M76" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N76" s="9" t="n">
         <v>6</v>
       </c>
       <c r="O76" s="6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="P76" s="14" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Sony</t>
+          <t>Hypnotize Minds</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
@@ -9747,7 +9747,7 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="J125" s="11" t="n">
         <v>8</v>
@@ -10180,7 +10180,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">

--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R134"/>
+  <dimension ref="A1:R133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6033,12 +6033,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>JE</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Ghostface Killah</t>
+          <t>Jadakiss</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -6053,39 +6053,39 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Wu-Tang/Soul</t>
+          <t>East Coast Grit</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Def Jam</t>
+          <t>Ruff Ryders</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>2006</v>
-      </c>
-      <c r="J75" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="K75" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L75" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M75" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="N75" s="10" t="n">
-        <v>7</v>
+        <v>2001</v>
+      </c>
+      <c r="J75" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="K75" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L75" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M75" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N75" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="O75" s="6" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="P75" s="14" t="inlineStr">
         <is>
@@ -6094,12 +6094,12 @@
       </c>
       <c r="Q75" s="2" t="inlineStr">
         <is>
-          <t>Scored specifically for Fishscale-era peak; earlier work variable</t>
+          <t>Well-regarded but limited scholarly analysis</t>
         </is>
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>Wu-Tang's vivid storyteller; 'Fishscale' (2006) a stream-of-consciousness apex.</t>
+          <t>Gravelly-voiced Yonkers MC. Punchline economy and street credibility.</t>
         </is>
       </c>
     </row>
@@ -6109,12 +6109,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>JE</t>
+          <t>FK2</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Jadakiss</t>
+          <t>50 Cent</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -6134,48 +6134,44 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>East Coast Grit</t>
+          <t>G-Unit Boom Bap</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Ruff Ryders</t>
+          <t>Shady/Aftermath</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>2001</v>
-      </c>
-      <c r="J76" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="K76" s="10" t="n">
-        <v>7</v>
+        <v>2003</v>
+      </c>
+      <c r="J76" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K76" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="L76" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="M76" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="N76" s="9" t="n">
+      <c r="M76" s="9" t="n">
         <v>6</v>
       </c>
+      <c r="N76" s="8" t="n">
+        <v>5</v>
+      </c>
       <c r="O76" s="6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="P76" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q76" s="2" t="inlineStr">
-        <is>
-          <t>Well-regarded but limited scholarly analysis</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="P76" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>Gravelly-voiced Yonkers MC. Punchline economy and street credibility.</t>
+          <t>Bulletproof charisma. Street narrative over lyrical complexity.</t>
         </is>
       </c>
     </row>
@@ -6185,17 +6181,17 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>FK2</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>50 Cent</t>
+          <t>Three 6 Mafia</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -6210,25 +6206,25 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>G-Unit Boom Bap</t>
+          <t>Memphis Horrorcore</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Shady/Aftermath</t>
+          <t>Hypnotize Minds</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>2003</v>
-      </c>
-      <c r="J77" s="9" t="n">
-        <v>6</v>
+        <v>1995</v>
+      </c>
+      <c r="J77" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="K77" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="L77" s="10" t="n">
-        <v>7</v>
+      <c r="L77" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="M77" s="9" t="n">
         <v>6</v>
@@ -6237,17 +6233,21 @@
         <v>5</v>
       </c>
       <c r="O77" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="P77" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q77" s="2" t="inlineStr"/>
+        <v>5.6</v>
+      </c>
+      <c r="P77" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>Oscar win elevated profile; lyrical analysis limited</t>
+        </is>
+      </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>Bulletproof charisma. Street narrative over lyrical complexity.</t>
+          <t>Oscar-winning Southern horror-rap. Pioneered the dark triplet flow.</t>
         </is>
       </c>
     </row>
@@ -6257,12 +6257,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>UG</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Three 6 Mafia</t>
+          <t>UGK</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -6282,48 +6282,44 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Memphis Horrorcore</t>
+          <t>Texas Funk Rap</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Hypnotize Minds</t>
+          <t>Jive</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>1995</v>
-      </c>
-      <c r="J78" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K78" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L78" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M78" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N78" s="8" t="n">
-        <v>5</v>
+        <v>1992</v>
+      </c>
+      <c r="J78" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K78" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L78" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M78" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N78" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="O78" s="6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="P78" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q78" s="2" t="inlineStr">
-        <is>
-          <t>Oscar win elevated profile; lyrical analysis limited</t>
-        </is>
-      </c>
+        <v>7.4</v>
+      </c>
+      <c r="P78" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>Oscar-winning Southern horror-rap. Pioneered the dark triplet flow.</t>
+          <t>Bun B and Pimp C. Texas's most complete rap duo.</t>
         </is>
       </c>
     </row>
@@ -6333,12 +6329,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>TL2</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>UGK</t>
+          <t>Trae Tha Truth</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -6358,44 +6354,48 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Texas Funk Rap</t>
+          <t>Houston Chopped</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Jive</t>
+          <t>Asylum</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>1992</v>
-      </c>
-      <c r="J79" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K79" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L79" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M79" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N79" s="10" t="n">
-        <v>7</v>
+        <v>2003</v>
+      </c>
+      <c r="J79" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K79" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L79" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M79" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N79" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="O79" s="6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="P79" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q79" s="2" t="inlineStr"/>
+        <v>6.4</v>
+      </c>
+      <c r="P79" s="15" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>Regional significance; limited national critical record</t>
+        </is>
+      </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>Bun B and Pimp C. Texas's most complete rap duo.</t>
+          <t>Houston's street ambassador. Chopped-and-screwed delivery as identity.</t>
         </is>
       </c>
     </row>
@@ -6405,17 +6405,17 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>TL2</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Trae Tha Truth</t>
+          <t>Aceyalone</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -6425,53 +6425,53 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Abstract</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Houston Chopped</t>
+          <t>LA Free Jazz Rap</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Asylum</t>
+          <t>Project Blowed</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>2003</v>
-      </c>
-      <c r="J80" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K80" s="10" t="n">
-        <v>7</v>
+        <v>1993</v>
+      </c>
+      <c r="J80" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K80" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="L80" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="M80" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N80" s="9" t="n">
-        <v>6</v>
+      <c r="M80" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N80" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="O80" s="6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="P80" s="15" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>7.8</v>
+      </c>
+      <c r="P80" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>Regional significance; limited national critical record</t>
+          <t>Highly regarded in underground circles; thin mainstream documentation</t>
         </is>
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>Houston's street ambassador. Chopped-and-screwed delivery as identity.</t>
+          <t>LA underground legend. Freestyle Fellowship's most technically gifted MC.</t>
         </is>
       </c>
     </row>
@@ -6481,17 +6481,17 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>RA2</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Aceyalone</t>
+          <t>Raekwon</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>NYC</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -6501,31 +6501,31 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Abstract</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>LA Free Jazz Rap</t>
+          <t>Wu-Tang/Mafioso</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Project Blowed</t>
+          <t>Loud</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="J81" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="K81" s="12" t="n">
+      <c r="K81" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L81" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L81" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="M81" s="11" t="n">
         <v>8</v>
       </c>
@@ -6533,21 +6533,17 @@
         <v>7</v>
       </c>
       <c r="O81" s="6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="P81" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q81" s="2" t="inlineStr">
-        <is>
-          <t>Highly regarded in underground circles; thin mainstream documentation</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="P81" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>LA underground legend. Freestyle Fellowship's most technically gifted MC.</t>
+          <t>'Only Built 4 Cuban Linx' — the Godfather Part II of rap albums.</t>
         </is>
       </c>
     </row>
@@ -6557,12 +6553,12 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>RA2</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Raekwon</t>
+          <t>El-P</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -6577,39 +6573,39 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Wu-Tang/Mafioso</t>
+          <t>Industrial Boom Bap</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Loud</t>
+          <t>Def Jux</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>1995</v>
+        <v>2002</v>
       </c>
       <c r="J82" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="K82" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L82" s="12" t="n">
+      <c r="K82" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="M82" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N82" s="10" t="n">
-        <v>7</v>
+      <c r="L82" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M82" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="N82" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="O82" s="6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="P82" s="7" t="inlineStr">
         <is>
@@ -6619,7 +6615,7 @@
       <c r="Q82" s="2" t="inlineStr"/>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>'Only Built 4 Cuban Linx' — the Godfather Part II of rap albums.</t>
+          <t>Company Flow / Run The Jewels architect. Dystopian sonic vision.</t>
         </is>
       </c>
     </row>
@@ -6629,17 +6625,17 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>BU</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>El-P</t>
+          <t>Brother Ali</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -6649,49 +6645,53 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Industrial Boom Bap</t>
+          <t>Boom Bap/Soul</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Def Jux</t>
+          <t>Rhymesayers</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>2002</v>
-      </c>
-      <c r="J83" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K83" s="12" t="n">
-        <v>9</v>
+        <v>2000</v>
+      </c>
+      <c r="J83" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K83" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="L83" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="M83" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="N83" s="12" t="n">
-        <v>9</v>
+      <c r="M83" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N83" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="O83" s="6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="P83" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q83" s="2" t="inlineStr"/>
+        <v>7.4</v>
+      </c>
+      <c r="P83" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>Well-regarded in conscious rap; limited broader academic attention</t>
+        </is>
+      </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
-          <t>Company Flow / Run The Jewels architect. Dystopian sonic vision.</t>
+          <t>Minneapolis conscious rapper. Raw emotional honesty over Ant's production.</t>
         </is>
       </c>
     </row>
@@ -6701,17 +6701,17 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>BU</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Brother Ali</t>
+          <t>Immortal Technique</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>NYC</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -6721,21 +6721,21 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Political</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Boom Bap/Soul</t>
+          <t>Underground Agit-Rap</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Rhymesayers</t>
+          <t>Viper</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="J84" s="10" t="n">
         <v>7</v>
@@ -6749,11 +6749,11 @@
       <c r="M84" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="N84" s="11" t="n">
-        <v>8</v>
+      <c r="N84" s="13" t="n">
+        <v>9</v>
       </c>
       <c r="O84" s="6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="P84" s="14" t="inlineStr">
         <is>
@@ -6762,12 +6762,12 @@
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>Well-regarded in conscious rap; limited broader academic attention</t>
+          <t>Heavy political reputation; thin formal lyrical analysis</t>
         </is>
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>Minneapolis conscious rapper. Raw emotional honesty over Ant's production.</t>
+          <t>Most politically radical rapper in the genre. Conspiracy and revolution.</t>
         </is>
       </c>
     </row>
@@ -6777,73 +6777,69 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>KL</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Immortal Technique</t>
+          <t>Kendrick Lamar</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Political</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Underground Agit-Rap</t>
+          <t>Compton Concept</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Viper</t>
+          <t>Top Dawg</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>2001</v>
-      </c>
-      <c r="J85" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K85" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L85" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M85" s="10" t="n">
-        <v>7</v>
+        <v>2011</v>
+      </c>
+      <c r="J85" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="K85" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="L85" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="M85" s="13" t="n">
+        <v>10</v>
       </c>
       <c r="N85" s="13" t="n">
         <v>10</v>
       </c>
       <c r="O85" s="6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="P85" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q85" s="2" t="inlineStr">
-        <is>
-          <t>Heavy political reputation; thin formal lyrical analysis</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="P85" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
       <c r="R85" s="2" t="inlineStr">
         <is>
-          <t>Most politically radical rapper in the genre. Conspiracy and revolution.</t>
+          <t>The complete package. Every dimension at peak. Pulitzer Prize.</t>
         </is>
       </c>
     </row>
@@ -6853,17 +6849,17 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>KL</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Kendrick Lamar</t>
+          <t>Drake</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>International</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -6873,39 +6869,39 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Party/Pop</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Compton Concept</t>
+          <t>Melodic Rap</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Top Dawg</t>
+          <t>OVO/Young Money</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>2011</v>
-      </c>
-      <c r="J86" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="K86" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="L86" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="M86" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="N86" s="13" t="n">
-        <v>10</v>
+        <v>2006</v>
+      </c>
+      <c r="J86" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K86" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L86" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M86" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N86" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="O86" s="6" t="n">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="P86" s="7" t="inlineStr">
         <is>
@@ -6915,7 +6911,7 @@
       <c r="Q86" s="2" t="inlineStr"/>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>The complete package. Every dimension at peak. Pulitzer Prize.</t>
+          <t>Emotional candor and commercial dominance. Lyricism secondary to feeling.</t>
         </is>
       </c>
     </row>
@@ -6925,17 +6921,17 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>JC</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Drake</t>
+          <t>J. Cole</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -6945,39 +6941,39 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Party/Pop</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Melodic Rap</t>
+          <t>Soulful Boom Bap</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>OVO/Young Money</t>
+          <t>Dreamville</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>2006</v>
-      </c>
-      <c r="J87" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K87" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L87" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M87" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N87" s="8" t="n">
-        <v>5</v>
+        <v>2011</v>
+      </c>
+      <c r="J87" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K87" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L87" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M87" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N87" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="O87" s="6" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="P87" s="7" t="inlineStr">
         <is>
@@ -6987,7 +6983,7 @@
       <c r="Q87" s="2" t="inlineStr"/>
       <c r="R87" s="2" t="inlineStr">
         <is>
-          <t>Emotional candor and commercial dominance. Lyricism secondary to feeling.</t>
+          <t>Working-class emotional intelligence. Deep narrative craft.</t>
         </is>
       </c>
     </row>
@@ -6997,12 +6993,12 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>JC</t>
+          <t>YT</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>J. Cole</t>
+          <t>Young Thug</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -7017,39 +7013,39 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Soulful Boom Bap</t>
+          <t>Melodic Trap</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Dreamville</t>
+          <t>300 Entertainment</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
         <v>2011</v>
       </c>
-      <c r="J88" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K88" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L88" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M88" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N88" s="12" t="n">
-        <v>9</v>
+      <c r="J88" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K88" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M88" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N88" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="O88" s="6" t="n">
-        <v>8.4</v>
+        <v>5.2</v>
       </c>
       <c r="P88" s="7" t="inlineStr">
         <is>
@@ -7059,7 +7055,7 @@
       <c r="Q88" s="2" t="inlineStr"/>
       <c r="R88" s="2" t="inlineStr">
         <is>
-          <t>Working-class emotional intelligence. Deep narrative craft.</t>
+          <t>Melody over meaning. Vocal texture as primary instrument.</t>
         </is>
       </c>
     </row>
@@ -7069,12 +7065,12 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>YT</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Young Thug</t>
+          <t>Future</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -7089,30 +7085,30 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Trap/Drill</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Melodic Trap</t>
+          <t>Auto-Tune Trap</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>300 Entertainment</t>
+          <t>A1/Epic</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="J89" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="K89" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L89" s="5" t="n">
-        <v>4</v>
+      <c r="K89" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L89" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="M89" s="9" t="n">
         <v>6</v>
@@ -7131,7 +7127,7 @@
       <c r="Q89" s="2" t="inlineStr"/>
       <c r="R89" s="2" t="inlineStr">
         <is>
-          <t>Melody over meaning. Vocal texture as primary instrument.</t>
+          <t>Emotional auto-tune as confession. Vibe over lyrical architecture.</t>
         </is>
       </c>
     </row>
@@ -7141,17 +7137,17 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Future</t>
+          <t>Chance the Rapper</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -7161,39 +7157,39 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Trap/Drill</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Auto-Tune Trap</t>
+          <t>Chicago Gospel Rap</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>A1/Epic</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>2012</v>
-      </c>
-      <c r="J90" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K90" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L90" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="M90" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N90" s="8" t="n">
-        <v>5</v>
+        <v>2013</v>
+      </c>
+      <c r="J90" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K90" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L90" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M90" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N90" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="O90" s="6" t="n">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P90" s="7" t="inlineStr">
         <is>
@@ -7203,7 +7199,7 @@
       <c r="Q90" s="2" t="inlineStr"/>
       <c r="R90" s="2" t="inlineStr">
         <is>
-          <t>Emotional auto-tune as confession. Vibe over lyrical architecture.</t>
+          <t>Joyful complexity. Gospel cadences and Chicago love letters.</t>
         </is>
       </c>
     </row>
@@ -7213,17 +7209,17 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Chance the Rapper</t>
+          <t>Earl Sweatshirt</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -7233,39 +7229,39 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Abstract</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Chicago Gospel Rap</t>
+          <t>Odd Future/Boom Bap</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Tan Cressida</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>2013</v>
-      </c>
-      <c r="J91" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K91" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L91" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M91" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N91" s="12" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J91" s="12" t="n">
         <v>9</v>
       </c>
+      <c r="K91" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L91" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M91" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="N91" s="11" t="n">
+        <v>8</v>
+      </c>
       <c r="O91" s="6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="P91" s="7" t="inlineStr">
         <is>
@@ -7275,7 +7271,7 @@
       <c r="Q91" s="2" t="inlineStr"/>
       <c r="R91" s="2" t="inlineStr">
         <is>
-          <t>Joyful complexity. Gospel cadences and Chicago love letters.</t>
+          <t>Compression and grief as poetics. Dense abstract imagery.</t>
         </is>
       </c>
     </row>
@@ -7285,17 +7281,17 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>MM</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Earl Sweatshirt</t>
+          <t>Meek Mill</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>Philly</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -7305,39 +7301,39 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Abstract</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Odd Future/Boom Bap</t>
+          <t>Philly Trap</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Tan Cressida</t>
+          <t>Maybach Music</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>2010</v>
-      </c>
-      <c r="J92" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="K92" s="12" t="n">
-        <v>9</v>
+        <v>2012</v>
+      </c>
+      <c r="J92" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K92" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="L92" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="M92" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="N92" s="11" t="n">
-        <v>8</v>
+      <c r="M92" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N92" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="O92" s="6" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="P92" s="7" t="inlineStr">
         <is>
@@ -7347,7 +7343,7 @@
       <c r="Q92" s="2" t="inlineStr"/>
       <c r="R92" s="2" t="inlineStr">
         <is>
-          <t>Compression and grief as poetics. Dense abstract imagery.</t>
+          <t>Visceral urgency. Philadelphia streets in raw kinetic delivery.</t>
         </is>
       </c>
     </row>
@@ -7357,17 +7353,17 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>MM</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Meek Mill</t>
+          <t>A$AP Rocky</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>NYC</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -7377,39 +7373,39 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Philly Trap</t>
+          <t>Cloud Rap/Fashion</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Maybach Music</t>
+          <t>A$AP/RCA</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="J93" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="K93" s="9" t="n">
+      <c r="K93" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L93" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M93" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N93" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="O93" s="6" t="n">
         <v>6</v>
-      </c>
-      <c r="L93" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M93" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N93" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="O93" s="6" t="n">
-        <v>6.2</v>
       </c>
       <c r="P93" s="7" t="inlineStr">
         <is>
@@ -7419,7 +7415,7 @@
       <c r="Q93" s="2" t="inlineStr"/>
       <c r="R93" s="2" t="inlineStr">
         <is>
-          <t>Visceral urgency. Philadelphia streets in raw kinetic delivery.</t>
+          <t>Aesthetic as content. Flow and texture over lyrical substance.</t>
         </is>
       </c>
     </row>
@@ -7429,12 +7425,12 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>NM</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>A$AP Rocky</t>
+          <t>Nicki Minaj</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -7449,39 +7445,39 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Cloud Rap/Fashion</t>
+          <t>Pop Rap/Dancehall</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>A$AP/RCA</t>
+          <t>Young Money</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>2011</v>
-      </c>
-      <c r="J94" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K94" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L94" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="M94" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N94" s="8" t="n">
-        <v>5</v>
+        <v>2010</v>
+      </c>
+      <c r="J94" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K94" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L94" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M94" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N94" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="O94" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P94" s="7" t="inlineStr">
         <is>
@@ -7491,7 +7487,7 @@
       <c r="Q94" s="2" t="inlineStr"/>
       <c r="R94" s="2" t="inlineStr">
         <is>
-          <t>Aesthetic as content. Flow and texture over lyrical substance.</t>
+          <t>Technical precision and alter-ego theatrics. 'Monster' verse.</t>
         </is>
       </c>
     </row>
@@ -7501,17 +7497,17 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>NM</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Nicki Minaj</t>
+          <t>Vince Staples</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -7521,36 +7517,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Political</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Pop Rap/Dancehall</t>
+          <t>West Coast Minimalism</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Young Money</t>
+          <t>Def Jam</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>2010</v>
-      </c>
-      <c r="J95" s="12" t="n">
+        <v>2012</v>
+      </c>
+      <c r="J95" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K95" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L95" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M95" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N95" s="12" t="n">
         <v>9</v>
-      </c>
-      <c r="K95" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L95" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M95" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N95" s="10" t="n">
-        <v>7</v>
       </c>
       <c r="O95" s="6" t="n">
         <v>8</v>
@@ -7563,7 +7559,7 @@
       <c r="Q95" s="2" t="inlineStr"/>
       <c r="R95" s="2" t="inlineStr">
         <is>
-          <t>Technical precision and alter-ego theatrics. 'Monster' verse.</t>
+          <t>Deadpan sociologist. Minimalist language doing maximum structural work.</t>
         </is>
       </c>
     </row>
@@ -7573,17 +7569,17 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>BK2</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Vince Staples</t>
+          <t>Big K.R.I.T.</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -7593,12 +7589,12 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Political</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>West Coast Minimalism</t>
+          <t>Mississippi Soul Rap</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7607,10 +7603,10 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>2012</v>
-      </c>
-      <c r="J96" s="10" t="n">
-        <v>7</v>
+        <v>2010</v>
+      </c>
+      <c r="J96" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="K96" s="11" t="n">
         <v>8</v>
@@ -7621,8 +7617,8 @@
       <c r="M96" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="N96" s="12" t="n">
-        <v>9</v>
+      <c r="N96" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="O96" s="6" t="n">
         <v>8</v>
@@ -7635,7 +7631,7 @@
       <c r="Q96" s="2" t="inlineStr"/>
       <c r="R96" s="2" t="inlineStr">
         <is>
-          <t>Deadpan sociologist. Minimalist language doing maximum structural work.</t>
+          <t>Mississippi throwback futurist. Southern soul and lyrical ambition fused.</t>
         </is>
       </c>
     </row>
@@ -7645,17 +7641,17 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>BK2</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Big K.R.I.T.</t>
+          <t>Run The Jewels</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -7665,39 +7661,39 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Political</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Mississippi Soul Rap</t>
+          <t>Industrial Boom Bap</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Def Jam</t>
+          <t>Mass Appeal</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="J97" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="K97" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L97" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M97" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N97" s="11" t="n">
-        <v>8</v>
+      <c r="K97" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L97" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M97" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="N97" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="O97" s="6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="P97" s="7" t="inlineStr">
         <is>
@@ -7707,7 +7703,7 @@
       <c r="Q97" s="2" t="inlineStr"/>
       <c r="R97" s="2" t="inlineStr">
         <is>
-          <t>Mississippi throwback futurist. Southern soul and lyrical ambition fused.</t>
+          <t>El-P and Killer Mike. Most politically urgent rap duo since PE.</t>
         </is>
       </c>
     </row>
@@ -7717,17 +7713,17 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>KM</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Run The Jewels</t>
+          <t>Killer Mike</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -7742,34 +7738,34 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Industrial Boom Bap</t>
+          <t>Atlanta Boom Bap</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Mass Appeal</t>
+          <t>SMC Recordings</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>2013</v>
+        <v>2003</v>
       </c>
       <c r="J98" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="K98" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L98" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M98" s="12" t="n">
-        <v>9</v>
+      <c r="K98" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L98" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M98" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="N98" s="12" t="n">
         <v>9</v>
       </c>
       <c r="O98" s="6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P98" s="7" t="inlineStr">
         <is>
@@ -7779,7 +7775,7 @@
       <c r="Q98" s="2" t="inlineStr"/>
       <c r="R98" s="2" t="inlineStr">
         <is>
-          <t>El-P and Killer Mike. Most politically urgent rap duo since PE.</t>
+          <t>RTJ's political conscience. Atlanta's most morally serious MC.</t>
         </is>
       </c>
     </row>
@@ -7789,17 +7785,17 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>KM</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Killer Mike</t>
+          <t>Iggy Azalea</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>International</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -7809,39 +7805,39 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Political</t>
+          <t>Party/Pop</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Boom Bap</t>
+          <t>Southern Trap Pop</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>SMC Recordings</t>
+          <t>Grand Hustle</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>2003</v>
-      </c>
-      <c r="J99" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K99" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L99" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M99" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N99" s="12" t="n">
-        <v>9</v>
+        <v>2014</v>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M99" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="N99" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="O99" s="6" t="n">
-        <v>8.199999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="P99" s="7" t="inlineStr">
         <is>
@@ -7851,7 +7847,7 @@
       <c r="Q99" s="2" t="inlineStr"/>
       <c r="R99" s="2" t="inlineStr">
         <is>
-          <t>RTJ's political conscience. Atlanta's most morally serious MC.</t>
+          <t>Commercial success masking thin lyrical foundation. Accent controversy.</t>
         </is>
       </c>
     </row>
@@ -7861,17 +7857,17 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Iggy Azalea</t>
+          <t>Freddie Gibbs</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -7881,39 +7877,39 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Party/Pop</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Southern Trap Pop</t>
+          <t>Gangsta Boom Bap</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Grand Hustle</t>
+          <t>ESGN</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>2014</v>
-      </c>
-      <c r="J100" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K100" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="L100" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M100" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="N100" s="3" t="n">
-        <v>3</v>
+        <v>2004</v>
+      </c>
+      <c r="J100" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K100" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L100" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M100" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N100" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="O100" s="6" t="n">
-        <v>3.8</v>
+        <v>7.8</v>
       </c>
       <c r="P100" s="7" t="inlineStr">
         <is>
@@ -7923,7 +7919,7 @@
       <c r="Q100" s="2" t="inlineStr"/>
       <c r="R100" s="2" t="inlineStr">
         <is>
-          <t>Commercial success masking thin lyrical foundation. Accent controversy.</t>
+          <t>Gary Indiana's finest. Technical gangsta rap with jazz-rap production.</t>
         </is>
       </c>
     </row>
@@ -7933,17 +7929,17 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Freddie Gibbs</t>
+          <t>Migos</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -7953,39 +7949,39 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Trap/Drill</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Gangsta Boom Bap</t>
+          <t>Atlanta Triplet Trap</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>ESGN</t>
+          <t>Quality Control</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>2004</v>
-      </c>
-      <c r="J101" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K101" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L101" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M101" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N101" s="10" t="n">
-        <v>7</v>
+        <v>2013</v>
+      </c>
+      <c r="J101" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M101" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N101" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="O101" s="6" t="n">
-        <v>7.8</v>
+        <v>4</v>
       </c>
       <c r="P101" s="7" t="inlineStr">
         <is>
@@ -7995,7 +7991,7 @@
       <c r="Q101" s="2" t="inlineStr"/>
       <c r="R101" s="2" t="inlineStr">
         <is>
-          <t>Gary Indiana's finest. Technical gangsta rap with jazz-rap production.</t>
+          <t>Triplet flow inventors. Cultural influence far exceeds lyrical complexity.</t>
         </is>
       </c>
     </row>
@@ -8005,17 +8001,17 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>BI2</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Migos</t>
+          <t>Big Sean</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -8025,49 +8021,53 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Trap/Drill</t>
+          <t>Party/Pop</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Triplet Trap</t>
+          <t>Detroit Pop Rap</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>G.O.O.D.</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>2013</v>
-      </c>
-      <c r="J102" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K102" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="L102" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M102" s="8" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J102" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K102" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L102" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M102" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N102" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N102" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="O102" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="P102" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q102" s="2" t="inlineStr"/>
+        <v>5.8</v>
+      </c>
+      <c r="P102" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>Commercial success; critical reception mixed; thin formal analysis</t>
+        </is>
+      </c>
       <c r="R102" s="2" t="inlineStr">
         <is>
-          <t>Triplet flow inventors. Cultural influence far exceeds lyrical complexity.</t>
+          <t>Detroit MC. Punchlines over conceptual depth. 'One Man Can Change The World'.</t>
         </is>
       </c>
     </row>
@@ -8077,17 +8077,17 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>BI2</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Big Sean</t>
+          <t>Tierra Whack</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>Philly</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -8097,39 +8097,39 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Party/Pop</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Detroit Pop Rap</t>
+          <t>Experimental Pop Rap</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>G.O.O.D.</t>
+          <t>Interscope</t>
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>2011</v>
-      </c>
-      <c r="J103" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K103" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L103" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M103" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N103" s="8" t="n">
-        <v>5</v>
+        <v>2018</v>
+      </c>
+      <c r="J103" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K103" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L103" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M103" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N103" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="O103" s="6" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="P103" s="14" t="inlineStr">
         <is>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="Q103" s="2" t="inlineStr">
         <is>
-          <t>Commercial success; critical reception mixed; thin formal analysis</t>
+          <t>Breakout 2018; critical buzz high but career short; scoring may shift</t>
         </is>
       </c>
       <c r="R103" s="2" t="inlineStr">
         <is>
-          <t>Detroit MC. Punchlines over conceptual depth. 'One Man Can Change The World'.</t>
+          <t>'Whack World' — 15 one-minute songs as unified concept. Wholly original.</t>
         </is>
       </c>
     </row>
@@ -8153,17 +8153,17 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Tierra Whack</t>
+          <t>Noname</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Philly</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -8173,53 +8173,49 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Experimental Pop Rap</t>
+          <t>Chicago Jazz Rap</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Interscope</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="J104" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K104" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L104" s="10" t="n">
-        <v>7</v>
+        <v>2016</v>
+      </c>
+      <c r="J104" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K104" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L104" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="M104" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="N104" s="11" t="n">
-        <v>8</v>
+      <c r="N104" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="O104" s="6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="P104" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q104" s="2" t="inlineStr">
-        <is>
-          <t>Breakout 2018; critical buzz high but career short; scoring may shift</t>
-        </is>
-      </c>
+        <v>8.4</v>
+      </c>
+      <c r="P104" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
       <c r="R104" s="2" t="inlineStr">
         <is>
-          <t>'Whack World' — 15 one-minute songs as unified concept. Wholly original.</t>
+          <t>Chicago's most literary voice. Jazz cadences and political awakening.</t>
         </is>
       </c>
     </row>
@@ -8229,12 +8225,12 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>SZ</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Noname</t>
+          <t>Saba</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -8254,34 +8250,34 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Chicago Jazz Rap</t>
+          <t>Chicago Boom Bap</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Pivot Gang</t>
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="J105" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="K105" s="12" t="n">
+      <c r="K105" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L105" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L105" s="11" t="n">
-        <v>8</v>
-      </c>
       <c r="M105" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="N105" s="12" t="n">
-        <v>9</v>
+      <c r="N105" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="O105" s="6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P105" s="7" t="inlineStr">
         <is>
@@ -8291,7 +8287,7 @@
       <c r="Q105" s="2" t="inlineStr"/>
       <c r="R105" s="2" t="inlineStr">
         <is>
-          <t>Chicago's most literary voice. Jazz cadences and political awakening.</t>
+          <t>'CARE FOR ME' — grief and Chicago violence as devastating concept album.</t>
         </is>
       </c>
     </row>
@@ -8301,12 +8297,12 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>SZ</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Saba</t>
+          <t>Danny Brown</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -8321,33 +8317,33 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Chicago Boom Bap</t>
+          <t>Detroit Noise Rap</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Pivot Gang</t>
+          <t>Fool's Gold</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="J106" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="K106" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L106" s="12" t="n">
+      <c r="K106" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="M106" s="11" t="n">
-        <v>8</v>
+      <c r="L106" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M106" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="N106" s="11" t="n">
         <v>8</v>
@@ -8363,7 +8359,7 @@
       <c r="Q106" s="2" t="inlineStr"/>
       <c r="R106" s="2" t="inlineStr">
         <is>
-          <t>'CARE FOR ME' — grief and Chicago violence as devastating concept album.</t>
+          <t>Detroit's avant-garde MC. Schizophrenic flows and surreal imagery.</t>
         </is>
       </c>
     </row>
@@ -8373,12 +8369,12 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Danny Brown</t>
+          <t>Mac Miller</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -8393,39 +8389,39 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Detroit Noise Rap</t>
+          <t>Pittsburgh Soul Rap</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Fool's Gold</t>
+          <t>Rostrum</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
         <v>2010</v>
       </c>
-      <c r="J107" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K107" s="12" t="n">
-        <v>9</v>
+      <c r="J107" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K107" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="L107" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="M107" s="12" t="n">
-        <v>9</v>
+      <c r="M107" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="N107" s="11" t="n">
         <v>8</v>
       </c>
       <c r="O107" s="6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="P107" s="7" t="inlineStr">
         <is>
@@ -8435,7 +8431,7 @@
       <c r="Q107" s="2" t="inlineStr"/>
       <c r="R107" s="2" t="inlineStr">
         <is>
-          <t>Detroit's avant-garde MC. Schizophrenic flows and surreal imagery.</t>
+          <t>Arc from frat-rap to deeply personal jazz introspection. 'Swimming' a peak.</t>
         </is>
       </c>
     </row>
@@ -8445,17 +8441,17 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>JD2</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Mac Miller</t>
+          <t>JID</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -8470,44 +8466,48 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Pittsburgh Soul Rap</t>
+          <t>Atlanta Jazz Rap</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Rostrum</t>
+          <t>Dreamville</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>2010</v>
-      </c>
-      <c r="J108" s="10" t="n">
-        <v>7</v>
+        <v>2017</v>
+      </c>
+      <c r="J108" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="K108" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L108" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M108" s="10" t="n">
-        <v>7</v>
+      <c r="L108" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M108" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="N108" s="11" t="n">
         <v>8</v>
       </c>
       <c r="O108" s="6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="P108" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q108" s="2" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="P108" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>Late-decade emergence; critical acclaim building; may rescore upward</t>
+        </is>
+      </c>
       <c r="R108" s="2" t="inlineStr">
         <is>
-          <t>Arc from frat-rap to deeply personal jazz introspection. 'Swimming' a peak.</t>
+          <t>Atlanta's most technically gifted rapper. 'DiCaprio 2' showed full potential.</t>
         </is>
       </c>
     </row>
@@ -8517,17 +8517,17 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>JD2</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>JID</t>
+          <t>Cardi B</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>NYC</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -8537,53 +8537,49 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Party/Pop</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Jazz Rap</t>
+          <t>Bronx Trap Pop</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Dreamville</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="J109" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="K109" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L109" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M109" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N109" s="11" t="n">
-        <v>8</v>
+        <v>2018</v>
+      </c>
+      <c r="J109" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K109" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L109" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M109" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N109" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="O109" s="6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="P109" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q109" s="2" t="inlineStr">
-        <is>
-          <t>Late-decade emergence; critical acclaim building; may rescore upward</t>
-        </is>
-      </c>
+        <v>5.6</v>
+      </c>
+      <c r="P109" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="inlineStr"/>
       <c r="R109" s="2" t="inlineStr">
         <is>
-          <t>Atlanta's most technically gifted rapper. 'DiCaprio 2' showed full potential.</t>
+          <t>Unfiltered Bronx personality. Cultural force exceeds lyrical architecture.</t>
         </is>
       </c>
     </row>
@@ -8593,69 +8589,73 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Cardi B</t>
+          <t>Polo G</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Party/Pop</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Bronx Trap Pop</t>
+          <t>Chicago Melodic Trap</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Columbia</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="J110" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K110" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L110" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M110" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N110" s="5" t="n">
-        <v>4</v>
+        <v>2019</v>
+      </c>
+      <c r="J110" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K110" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L110" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M110" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N110" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="O110" s="6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="P110" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q110" s="2" t="inlineStr"/>
+        <v>7.2</v>
+      </c>
+      <c r="P110" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q110" s="2" t="inlineStr">
+        <is>
+          <t>Recent emergence; trajectory still forming</t>
+        </is>
+      </c>
       <c r="R110" s="2" t="inlineStr">
         <is>
-          <t>Unfiltered Bronx personality. Cultural force exceeds lyrical architecture.</t>
+          <t>Chicago's introspective melodic trap voice. Melancholy street memoir.</t>
         </is>
       </c>
     </row>
@@ -8665,17 +8665,17 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>RW</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Polo G</t>
+          <t>Rod Wave</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -8685,39 +8685,39 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Chicago Melodic Trap</t>
+          <t>Florida Soul Trap</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Columbia</t>
+          <t>Alamo</t>
         </is>
       </c>
       <c r="I111" s="2" t="n">
         <v>2019</v>
       </c>
-      <c r="J111" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K111" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L111" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M111" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N111" s="10" t="n">
-        <v>7</v>
+      <c r="J111" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K111" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L111" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M111" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N111" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="O111" s="6" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="P111" s="14" t="inlineStr">
         <is>
@@ -8726,12 +8726,12 @@
       </c>
       <c r="Q111" s="2" t="inlineStr">
         <is>
-          <t>Recent emergence; trajectory still forming</t>
+          <t>Recent; critical consensus not yet settled</t>
         </is>
       </c>
       <c r="R111" s="2" t="inlineStr">
         <is>
-          <t>Chicago's introspective melodic trap voice. Melancholy street memoir.</t>
+          <t>Emotional vulnerability over technical precision. Florida pain made universal.</t>
         </is>
       </c>
     </row>
@@ -8741,12 +8741,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Rod Wave</t>
+          <t>Doechii</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -8766,34 +8766,34 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Florida Soul Trap</t>
+          <t>Tampa Art Rap</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Alamo</t>
+          <t>Capitol</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>2019</v>
-      </c>
-      <c r="J112" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K112" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L112" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M112" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N112" s="8" t="n">
-        <v>5</v>
+        <v>2021</v>
+      </c>
+      <c r="J112" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K112" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L112" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M112" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N112" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="O112" s="6" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P112" s="14" t="inlineStr">
         <is>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="Q112" s="2" t="inlineStr">
         <is>
-          <t>Recent; critical consensus not yet settled</t>
+          <t>Breakout recent; scoring may shift upward as body of work grows</t>
         </is>
       </c>
       <c r="R112" s="2" t="inlineStr">
         <is>
-          <t>Emotional vulnerability over technical precision. Florida pain made universal.</t>
+          <t>Tampa's theatrical polymath. Technical fire meets conceptual daring.</t>
         </is>
       </c>
     </row>
@@ -8817,12 +8817,12 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>GG2</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Doechii</t>
+          <t>GloRilla</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -8837,53 +8837,53 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Party/Pop</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Tampa Art Rap</t>
+          <t>Memphis Trap</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Capitol</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>2021</v>
-      </c>
-      <c r="J113" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K113" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L113" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M113" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N113" s="12" t="n">
-        <v>9</v>
+        <v>2022</v>
+      </c>
+      <c r="J113" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K113" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L113" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M113" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N113" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="O113" s="6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="P113" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
+        <v>4.8</v>
+      </c>
+      <c r="P113" s="15" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
         <is>
-          <t>Breakout recent; scoring may shift upward as body of work grows</t>
+          <t>Very recent; limited critical record; commercial impact clear</t>
         </is>
       </c>
       <c r="R113" s="2" t="inlineStr">
         <is>
-          <t>Tampa's theatrical polymath. Technical fire meets conceptual daring.</t>
+          <t>Memphis energy, unfiltered personality. New Southern feminism in party form.</t>
         </is>
       </c>
     </row>
@@ -8893,12 +8893,12 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>GG2</t>
+          <t>GN</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>GloRilla</t>
+          <t>Gunna</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -8913,53 +8913,53 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Party/Pop</t>
+          <t>Trap/Drill</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Memphis Trap</t>
+          <t>Atlanta Melodic Trap</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>Young Stoner Life</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>2022</v>
-      </c>
-      <c r="J114" s="8" t="n">
-        <v>5</v>
+        <v>2018</v>
+      </c>
+      <c r="J114" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="K114" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="L114" s="8" t="n">
-        <v>5</v>
+      <c r="L114" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="M114" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N114" s="5" t="n">
-        <v>4</v>
+      <c r="N114" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="O114" s="6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P114" s="15" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>4.2</v>
+      </c>
+      <c r="P114" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
         <is>
-          <t>Very recent; limited critical record; commercial impact clear</t>
+          <t>Significant commercial presence; thin critical analysis</t>
         </is>
       </c>
       <c r="R114" s="2" t="inlineStr">
         <is>
-          <t>Memphis energy, unfiltered personality. New Southern feminism in party form.</t>
+          <t>Melodic luxury trap. Vibe and aesthetic are the art.</t>
         </is>
       </c>
     </row>
@@ -8969,12 +8969,12 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>GN</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Gunna</t>
+          <t>Lil Baby</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -8989,39 +8989,39 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Trap/Drill</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Melodic Trap</t>
+          <t>Atlanta Slime Trap</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Young Stoner Life</t>
+          <t>Quality Control</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="J115" s="5" t="n">
-        <v>4</v>
+        <v>2017</v>
+      </c>
+      <c r="J115" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="K115" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="L115" s="5" t="n">
-        <v>4</v>
+      <c r="L115" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="M115" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N115" s="3" t="n">
-        <v>3</v>
+      <c r="N115" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="O115" s="6" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="P115" s="14" t="inlineStr">
         <is>
@@ -9030,12 +9030,12 @@
       </c>
       <c r="Q115" s="2" t="inlineStr">
         <is>
-          <t>Significant commercial presence; thin critical analysis</t>
+          <t>Recent; commercial dominance clear; critical depth forming</t>
         </is>
       </c>
       <c r="R115" s="2" t="inlineStr">
         <is>
-          <t>Melodic luxury trap. Vibe and aesthetic are the art.</t>
+          <t>Authentic street narrator. Storytelling grounded in lived experience.</t>
         </is>
       </c>
     </row>
@@ -9045,17 +9045,17 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>BT</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Lil Baby</t>
+          <t>Benny the Butcher</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>NYC</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -9070,48 +9070,44 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Slime Trap</t>
+          <t>Buffalo Boom Bap</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>Griselda</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="J116" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K116" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L116" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M116" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N116" s="8" t="n">
-        <v>5</v>
+        <v>2012</v>
+      </c>
+      <c r="J116" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K116" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L116" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M116" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N116" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="O116" s="6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="P116" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q116" s="2" t="inlineStr">
-        <is>
-          <t>Recent; commercial dominance clear; critical depth forming</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="P116" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q116" s="2" t="inlineStr"/>
       <c r="R116" s="2" t="inlineStr">
         <is>
-          <t>Authentic street narrator. Storytelling grounded in lived experience.</t>
+          <t>Griselda's lyrical backbone. Buffalo street narratives with East Coast precision.</t>
         </is>
       </c>
     </row>
@@ -9121,17 +9117,17 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Benny the Butcher</t>
+          <t>Stormzy</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -9141,39 +9137,39 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Political</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Buffalo Boom Bap</t>
+          <t>UK Grime/Gospel</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Griselda</t>
+          <t>#Merky</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>2012</v>
-      </c>
-      <c r="J117" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K117" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L117" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M117" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N117" s="10" t="n">
-        <v>7</v>
+        <v>2015</v>
+      </c>
+      <c r="J117" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K117" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L117" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M117" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N117" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="O117" s="6" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="P117" s="7" t="inlineStr">
         <is>
@@ -9183,7 +9179,7 @@
       <c r="Q117" s="2" t="inlineStr"/>
       <c r="R117" s="2" t="inlineStr">
         <is>
-          <t>Griselda's lyrical backbone. Buffalo street narratives with East Coast precision.</t>
+          <t>UK grime's political conscience. Authenticity and ambition fused.</t>
         </is>
       </c>
     </row>
@@ -9193,17 +9189,17 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Stormzy</t>
+          <t>Offset</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -9213,49 +9209,53 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Political</t>
+          <t>Trap/Drill</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>UK Grime/Gospel</t>
+          <t>Migos Solo Trap</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>#Merky</t>
+          <t>Quality Control</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>2015</v>
-      </c>
-      <c r="J118" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K118" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L118" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M118" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N118" s="11" t="n">
-        <v>8</v>
+        <v>2017</v>
+      </c>
+      <c r="J118" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K118" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L118" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M118" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N118" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="O118" s="6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="P118" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q118" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="P118" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q118" s="2" t="inlineStr">
+        <is>
+          <t>Solo career emerging post-Migos; scoring tentative</t>
+        </is>
+      </c>
       <c r="R118" s="2" t="inlineStr">
         <is>
-          <t>UK grime's political conscience. Authenticity and ambition fused.</t>
+          <t>Migos' most lyrical member. Flow variation and delivery standout in trap context.</t>
         </is>
       </c>
     </row>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>OM</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Offset</t>
+          <t>Kenny Mason</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -9285,53 +9285,53 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Trap/Drill</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Migos Solo Trap</t>
+          <t>Atlanta Punk Rap</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>RCA Records</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="J119" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K119" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L119" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="M119" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N119" s="5" t="n">
-        <v>4</v>
+        <v>2019</v>
+      </c>
+      <c r="J119" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K119" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L119" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M119" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N119" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="O119" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="P119" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
+        <v>7</v>
+      </c>
+      <c r="P119" s="15" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
         <is>
-          <t>Solo career emerging post-Migos; scoring tentative</t>
+          <t>Limited documentation; critical buzz building in underground circles</t>
         </is>
       </c>
       <c r="R119" s="2" t="inlineStr">
         <is>
-          <t>Migos' most lyrical member. Flow variation and delivery standout in trap context.</t>
+          <t>Atlanta's punk-rap hybrid. Unconventional tonal range.</t>
         </is>
       </c>
     </row>
@@ -9341,12 +9341,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Kenny Mason</t>
+          <t>Latto</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -9361,53 +9361,53 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Punk Rap</t>
+          <t>Atlanta Female Trap</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>RCA Records</t>
+          <t>RCA</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
         <v>2019</v>
       </c>
-      <c r="J120" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K120" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L120" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M120" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N120" s="10" t="n">
-        <v>7</v>
+      <c r="J120" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K120" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L120" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M120" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N120" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="O120" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="P120" s="15" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>5.8</v>
+      </c>
+      <c r="P120" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
         <is>
-          <t>Limited documentation; critical buzz building in underground circles</t>
+          <t>Recent; commercial trajectory clearer than critical consensus</t>
         </is>
       </c>
       <c r="R120" s="2" t="inlineStr">
         <is>
-          <t>Atlanta's punk-rap hybrid. Unconventional tonal range.</t>
+          <t>Atlanta's female trap voice. Technical skill often underestimated.</t>
         </is>
       </c>
     </row>
@@ -9417,17 +9417,17 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>SR</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Latto</t>
+          <t>Smino</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -9437,39 +9437,39 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Female Trap</t>
+          <t>St. Louis Jazz Rap</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>RCA</t>
+          <t>Zero Fatigue</t>
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>2019</v>
-      </c>
-      <c r="J121" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K121" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L121" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M121" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N121" s="8" t="n">
-        <v>5</v>
+        <v>2017</v>
+      </c>
+      <c r="J121" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K121" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L121" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M121" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N121" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="O121" s="6" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="P121" s="14" t="inlineStr">
         <is>
@@ -9478,12 +9478,12 @@
       </c>
       <c r="Q121" s="2" t="inlineStr">
         <is>
-          <t>Recent; commercial trajectory clearer than critical consensus</t>
+          <t>Critical darling in jazz-rap circles; broader recognition still forming</t>
         </is>
       </c>
       <c r="R121" s="2" t="inlineStr">
         <is>
-          <t>Atlanta's female trap voice. Technical skill often underestimated.</t>
+          <t>St. Louis's jazz-rap hybrid. Melodic and rhythmic sophistication.</t>
         </is>
       </c>
     </row>
@@ -9493,17 +9493,17 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>PZ</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Smino</t>
+          <t>Pusha T</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>NYC</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -9513,27 +9513,27 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>St. Louis Jazz Rap</t>
+          <t>Coke Rap Boom Bap</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Zero Fatigue</t>
+          <t>G.O.O.D.</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="J122" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K122" s="11" t="n">
-        <v>8</v>
+        <v>2002</v>
+      </c>
+      <c r="J122" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K122" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="L122" s="10" t="n">
         <v>7</v>
@@ -9547,19 +9547,15 @@
       <c r="O122" s="6" t="n">
         <v>7.4</v>
       </c>
-      <c r="P122" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q122" s="2" t="inlineStr">
-        <is>
-          <t>Critical darling in jazz-rap circles; broader recognition still forming</t>
-        </is>
-      </c>
+      <c r="P122" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q122" s="2" t="inlineStr"/>
       <c r="R122" s="2" t="inlineStr">
         <is>
-          <t>St. Louis's jazz-rap hybrid. Melodic and rhythmic sophistication.</t>
+          <t>Cocaine rap's Rembrandt. 'Daytona' — maximum density, minimum waste.</t>
         </is>
       </c>
     </row>
@@ -9569,17 +9565,17 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>PZ</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Pusha T</t>
+          <t>Tyler the Creator</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -9589,39 +9585,39 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Coke Rap Boom Bap</t>
+          <t>Odd Future/Orchestral</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>G.O.O.D.</t>
+          <t>Columbia</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>2002</v>
-      </c>
-      <c r="J123" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K123" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L123" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M123" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N123" s="10" t="n">
-        <v>7</v>
+        <v>2009</v>
+      </c>
+      <c r="J123" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K123" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L123" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M123" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="N123" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="O123" s="6" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="P123" s="7" t="inlineStr">
         <is>
@@ -9631,7 +9627,7 @@
       <c r="Q123" s="2" t="inlineStr"/>
       <c r="R123" s="2" t="inlineStr">
         <is>
-          <t>Cocaine rap's Rembrandt. 'Daytona' — maximum density, minimum waste.</t>
+          <t>'Igor' and 'Call Me If You Get Lost' — producer-auteur. Concept album mastery.</t>
         </is>
       </c>
     </row>
@@ -9641,17 +9637,17 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>AB2</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Tyler the Creator</t>
+          <t>Armand Hammer</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>NYC</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -9661,49 +9657,53 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Abstract</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Odd Future/Orchestral</t>
+          <t>Abstract Boom Bap</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Columbia</t>
+          <t>Backwoodz</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>2009</v>
-      </c>
-      <c r="J124" s="10" t="n">
-        <v>7</v>
+        <v>2013</v>
+      </c>
+      <c r="J124" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="K124" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L124" s="11" t="n">
-        <v>8</v>
+      <c r="L124" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="M124" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="N124" s="12" t="n">
-        <v>9</v>
+      <c r="N124" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="O124" s="6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="P124" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q124" s="2" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="P124" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q124" s="2" t="inlineStr">
+        <is>
+          <t>Critical underground darling; thin mainstream documentation</t>
+        </is>
+      </c>
       <c r="R124" s="2" t="inlineStr">
         <is>
-          <t>'Igor' and 'Call Me If You Get Lost' — producer-auteur. Concept album mastery.</t>
+          <t>billy woods + ELUCID. The most demanding abstract rap being made today.</t>
         </is>
       </c>
     </row>
@@ -9713,17 +9713,17 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>AB2</t>
+          <t>ZE</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Armand Hammer</t>
+          <t>Zack Fox</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -9738,48 +9738,48 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Abstract Boom Bap</t>
+          <t>Comedy-Abstract Rap</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>Backwoodz</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>2013</v>
-      </c>
-      <c r="J125" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K125" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L125" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M125" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="N125" s="11" t="n">
-        <v>8</v>
+        <v>2020</v>
+      </c>
+      <c r="J125" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K125" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L125" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M125" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N125" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="O125" s="6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="P125" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
+        <v>6.4</v>
+      </c>
+      <c r="P125" s="15" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
         <is>
-          <t>Critical underground darling; thin mainstream documentation</t>
+          <t>Very recent; extremely limited critical record</t>
         </is>
       </c>
       <c r="R125" s="2" t="inlineStr">
         <is>
-          <t>billy woods + ELUCID. The most demanding abstract rap being made today.</t>
+          <t>Comedy-meets-rap. Formally interesting but body of work too small to score confidently.</t>
         </is>
       </c>
     </row>
@@ -9789,17 +9789,17 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>ZE</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Zack Fox</t>
+          <t>Lil Durk</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -9809,53 +9809,53 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Abstract</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Comedy-Abstract Rap</t>
+          <t>Chicago Melodic Trap</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Only the Family</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="J126" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K126" s="10" t="n">
-        <v>7</v>
+        <v>2013</v>
+      </c>
+      <c r="J126" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K126" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="L126" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="M126" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N126" s="9" t="n">
-        <v>6</v>
+      <c r="M126" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N126" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="O126" s="6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="P126" s="15" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>5.2</v>
+      </c>
+      <c r="P126" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t>Very recent; extremely limited critical record</t>
+          <t>Commercial dominance clear; critical depth limited</t>
         </is>
       </c>
       <c r="R126" s="2" t="inlineStr">
         <is>
-          <t>Comedy-meets-rap. Formally interesting but body of work too small to score confidently.</t>
+          <t>Chicago drill's most commercially consistent voice.</t>
         </is>
       </c>
     </row>
@@ -9865,17 +9865,17 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>KS2</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Lil Durk</t>
+          <t>Kodak Black</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -9890,16 +9890,16 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Chicago Melodic Trap</t>
+          <t>Florida Trap</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>Only the Family</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="J127" s="8" t="n">
         <v>5</v>
@@ -9913,12 +9913,12 @@
       <c r="M127" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N127" s="8" t="n">
+      <c r="N127" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O127" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="O127" s="6" t="n">
-        <v>5.2</v>
-      </c>
       <c r="P127" s="14" t="inlineStr">
         <is>
           <t>M</t>
@@ -9926,12 +9926,12 @@
       </c>
       <c r="Q127" s="2" t="inlineStr">
         <is>
-          <t>Commercial dominance clear; critical depth limited</t>
+          <t>Commercial success; thin critical framework; behavior clouds reception</t>
         </is>
       </c>
       <c r="R127" s="2" t="inlineStr">
         <is>
-          <t>Chicago drill's most commercially consistent voice.</t>
+          <t>Florida trap's most distinctive voice. Rough-edged regional authenticity.</t>
         </is>
       </c>
     </row>
@@ -9941,12 +9941,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>KS2</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Kodak Black</t>
+          <t>Rapsody</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -9961,53 +9961,49 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Florida Trap</t>
+          <t>North Carolina Soul Rap</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Jamla</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>2014</v>
-      </c>
-      <c r="J128" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K128" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L128" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M128" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N128" s="5" t="n">
-        <v>4</v>
+        <v>2010</v>
+      </c>
+      <c r="J128" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K128" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L128" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M128" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N128" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="O128" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="P128" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q128" s="2" t="inlineStr">
-        <is>
-          <t>Commercial success; thin critical framework; behavior clouds reception</t>
-        </is>
-      </c>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="P128" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q128" s="2" t="inlineStr"/>
       <c r="R128" s="2" t="inlineStr">
         <is>
-          <t>Florida trap's most distinctive voice. Rough-edged regional authenticity.</t>
+          <t>North Carolina's most complete female MC. Lyrical depth rivals any peer.</t>
         </is>
       </c>
     </row>
@@ -10017,12 +10013,12 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>MF2</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Rapsody</t>
+          <t>Mavi</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -10037,49 +10033,53 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Abstract</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>North Carolina Soul Rap</t>
+          <t>Underground Abstract</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Jamla</t>
+          <t>Secretly Canadian</t>
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>2010</v>
-      </c>
-      <c r="J129" s="11" t="n">
-        <v>8</v>
+        <v>2019</v>
+      </c>
+      <c r="J129" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="K129" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L129" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M129" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N129" s="12" t="n">
-        <v>9</v>
+      <c r="L129" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M129" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N129" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="O129" s="6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="P129" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q129" s="2" t="inlineStr"/>
+        <v>7.2</v>
+      </c>
+      <c r="P129" s="15" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q129" s="2" t="inlineStr">
+        <is>
+          <t>Very limited critical documentation; underground following only</t>
+        </is>
+      </c>
       <c r="R129" s="2" t="inlineStr">
         <is>
-          <t>North Carolina's most complete female MC. Lyrical depth rivals any peer.</t>
+          <t>Charlotte underground. Dense introspective abstract rap. Watch this space.</t>
         </is>
       </c>
     </row>
@@ -10089,47 +10089,47 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>MF2</t>
+          <t>XP</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Mavi</t>
+          <t>Xzibit</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>Abstract</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Underground Abstract</t>
+          <t>Hard West Coast</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Secretly Canadian</t>
+          <t>Loud/Columbia</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>2019</v>
+        <v>1996</v>
       </c>
       <c r="J130" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="K130" s="11" t="n">
-        <v>8</v>
+      <c r="K130" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="L130" s="10" t="n">
         <v>7</v>
@@ -10137,25 +10137,25 @@
       <c r="M130" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="N130" s="10" t="n">
-        <v>7</v>
+      <c r="N130" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="O130" s="6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="P130" s="15" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>6.8</v>
+      </c>
+      <c r="P130" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
         <is>
-          <t>Very limited critical documentation; underground following only</t>
+          <t>Well-known but limited formal critical analysis</t>
         </is>
       </c>
       <c r="R130" s="2" t="inlineStr">
         <is>
-          <t>Charlotte underground. Dense introspective abstract rap. Watch this space.</t>
+          <t>West Coast boom bap craftsman. More respected by peers than critics.</t>
         </is>
       </c>
     </row>
@@ -10165,59 +10165,59 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>XP</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Xzibit</t>
+          <t>Saweetie</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>Bay Area</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Late 90s</t>
+          <t>2020s</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Party/Pop</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Hard West Coast</t>
+          <t>Trap Pop</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>Loud/Columbia</t>
+          <t>Warner</t>
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>1996</v>
-      </c>
-      <c r="J131" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K131" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L131" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M131" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N131" s="9" t="n">
-        <v>6</v>
+        <v>2018</v>
+      </c>
+      <c r="J131" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K131" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L131" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M131" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N131" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="O131" s="6" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="P131" s="14" t="inlineStr">
         <is>
@@ -10226,12 +10226,12 @@
       </c>
       <c r="Q131" s="2" t="inlineStr">
         <is>
-          <t>Well-known but limited formal critical analysis</t>
+          <t>Recent commercial success; limited critical depth</t>
         </is>
       </c>
       <c r="R131" s="2" t="inlineStr">
         <is>
-          <t>West Coast boom bap craftsman. More respected by peers than critics.</t>
+          <t>Bay Area trap-pop. Ice Princess persona over lyrical substance.</t>
         </is>
       </c>
     </row>
@@ -10241,17 +10241,17 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Saweetie</t>
+          <t>City Girls</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -10266,19 +10266,19 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Trap Pop</t>
+          <t>Miami Trap</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Warner</t>
+          <t>Quality Control/Motown</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
         <v>2018</v>
       </c>
-      <c r="J132" s="8" t="n">
-        <v>5</v>
+      <c r="J132" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="K132" s="8" t="n">
         <v>5</v>
@@ -10293,21 +10293,21 @@
         <v>4</v>
       </c>
       <c r="O132" s="6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P132" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
+        <v>4.6</v>
+      </c>
+      <c r="P132" s="15" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
         <is>
-          <t>Recent commercial success; limited critical depth</t>
+          <t>Limited critical record; cultural impact clearer than lyrical analysis</t>
         </is>
       </c>
       <c r="R132" s="2" t="inlineStr">
         <is>
-          <t>Bay Area trap-pop. Ice Princess persona over lyrical substance.</t>
+          <t>Miami's hedonistic party rap duo. Energy over craft.</t>
         </is>
       </c>
     </row>
@@ -10317,12 +10317,12 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>City Girls</t>
+          <t>Maxo Kream</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -10337,127 +10337,51 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>Party/Pop</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Miami Trap</t>
+          <t>Houston Narrative Trap</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>Quality Control/Motown</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="J133" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K133" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L133" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="M133" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N133" s="5" t="n">
-        <v>4</v>
+        <v>2017</v>
+      </c>
+      <c r="J133" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K133" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L133" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M133" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N133" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="O133" s="6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P133" s="15" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>7.4</v>
+      </c>
+      <c r="P133" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
         <is>
-          <t>Limited critical record; cultural impact clearer than lyrical analysis</t>
+          <t>Critical acclaim in narrative rap circles; limited mainstream documentation</t>
         </is>
       </c>
       <c r="R133" s="2" t="inlineStr">
-        <is>
-          <t>Miami's hedonistic party rap duo. Energy over craft.</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="n">
-        <v>133</v>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>MX</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>Maxo Kream</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="inlineStr">
-        <is>
-          <t>Gangsta/Street</t>
-        </is>
-      </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>Houston Narrative Trap</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>EMPIRE</t>
-        </is>
-      </c>
-      <c r="I134" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="J134" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K134" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L134" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M134" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N134" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="O134" s="6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="P134" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q134" s="2" t="inlineStr">
-        <is>
-          <t>Critical acclaim in narrative rap circles; limited mainstream documentation</t>
-        </is>
-      </c>
-      <c r="R134" s="2" t="inlineStr">
         <is>
           <t>Houston storytelling tradition continued. 'Weight of the World' deeply affecting.</t>
         </is>

--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R133"/>
+  <dimension ref="A1:R151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -10387,6 +10387,1364 @@
         </is>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>BT3</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Black Thought</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Philly</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Golden Age</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Conscious/Lyrical</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Live-Band Boom Bap</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Geffen/MCA</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>1993</v>
+      </c>
+      <c r="J134" t="n">
+        <v>10</v>
+      </c>
+      <c r="K134" t="n">
+        <v>9</v>
+      </c>
+      <c r="L134" t="n">
+        <v>8</v>
+      </c>
+      <c r="M134" t="n">
+        <v>9</v>
+      </c>
+      <c r="N134" t="n">
+        <v>8</v>
+      </c>
+      <c r="O134" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>The Roots' engine and a consensus top-tier technician. Relentless breath control and rhyme density.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Beanie Sigel</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Philly</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Gangsta/Street</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Soul Boom Bap</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Roc-A-Fella</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J135" t="n">
+        <v>8</v>
+      </c>
+      <c r="K135" t="n">
+        <v>7</v>
+      </c>
+      <c r="L135" t="n">
+        <v>8</v>
+      </c>
+      <c r="M135" t="n">
+        <v>7</v>
+      </c>
+      <c r="N135" t="n">
+        <v>7</v>
+      </c>
+      <c r="O135" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>Critically respected but thinly documented outside the Roc-A-Fella context.</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>Philadelphia's hardest pen. Street narratives carried with weight and conviction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>UV</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Lil Uzi Vert</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Philly</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Rage/Trap</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Generation Now/Atlantic</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>2016</v>
+      </c>
+      <c r="J136" t="n">
+        <v>6</v>
+      </c>
+      <c r="K136" t="n">
+        <v>6</v>
+      </c>
+      <c r="L136" t="n">
+        <v>5</v>
+      </c>
+      <c r="M136" t="n">
+        <v>6</v>
+      </c>
+      <c r="N136" t="n">
+        <v>6</v>
+      </c>
+      <c r="O136" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>Melodic rage star; influence on sound outweighs lyrical scholarship.</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>Genre-bending rage pioneer. Melody and energy over lyrical density.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Freeway</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Philly</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Gangsta/Street</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Soul Boom Bap</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Roc-A-Fella</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>2003</v>
+      </c>
+      <c r="J137" t="n">
+        <v>7</v>
+      </c>
+      <c r="K137" t="n">
+        <v>6</v>
+      </c>
+      <c r="L137" t="n">
+        <v>6</v>
+      </c>
+      <c r="M137" t="n">
+        <v>6</v>
+      </c>
+      <c r="N137" t="n">
+        <v>5</v>
+      </c>
+      <c r="O137" t="n">
+        <v>6</v>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>Limited critical record; respected within State Property/Roc-A-Fella circles.</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>Distinctive raspy urgency and Philly grit. State Property standout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Eve</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Philly</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Party/Pop</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Ruff Ryders</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Ruff Ryders/Interscope</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>1999</v>
+      </c>
+      <c r="J138" t="n">
+        <v>6</v>
+      </c>
+      <c r="K138" t="n">
+        <v>6</v>
+      </c>
+      <c r="L138" t="n">
+        <v>6</v>
+      </c>
+      <c r="M138" t="n">
+        <v>6</v>
+      </c>
+      <c r="N138" t="n">
+        <v>5</v>
+      </c>
+      <c r="O138" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>Commercial success clearer than lyrical analysis.</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>Ruff Ryders' First Lady. Charismatic crossover with Philly roots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Da Brat</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Golden Age</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Party/Pop</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>So So Def Bass</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>So So Def</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>1994</v>
+      </c>
+      <c r="J139" t="n">
+        <v>6</v>
+      </c>
+      <c r="K139" t="n">
+        <v>6</v>
+      </c>
+      <c r="L139" t="n">
+        <v>6</v>
+      </c>
+      <c r="M139" t="n">
+        <v>6</v>
+      </c>
+      <c r="N139" t="n">
+        <v>5</v>
+      </c>
+      <c r="O139" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>First female solo rapper to go platinum; under-analyzed lyrically.</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>So So Def's breakout. First female solo rapper to go platinum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>TS2</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Too $hort</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Old School</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Gangsta/Street</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Funk/Bass</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Jive/Dangerous Music</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>1987</v>
+      </c>
+      <c r="J140" t="n">
+        <v>6</v>
+      </c>
+      <c r="K140" t="n">
+        <v>5</v>
+      </c>
+      <c r="L140" t="n">
+        <v>6</v>
+      </c>
+      <c r="M140" t="n">
+        <v>5</v>
+      </c>
+      <c r="N140" t="n">
+        <v>5</v>
+      </c>
+      <c r="O140" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>Pioneer status outweighs lyrical-craft documentation.</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>Oakland pioneer and pimp-rap archetype. Influence over intricacy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Del the Funky Homosapien</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Golden Age</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Hieroglyphics</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Elektra/Hiero Imperium</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>1991</v>
+      </c>
+      <c r="J141" t="n">
+        <v>7</v>
+      </c>
+      <c r="K141" t="n">
+        <v>8</v>
+      </c>
+      <c r="L141" t="n">
+        <v>6</v>
+      </c>
+      <c r="M141" t="n">
+        <v>7</v>
+      </c>
+      <c r="N141" t="n">
+        <v>7</v>
+      </c>
+      <c r="O141" t="n">
+        <v>7</v>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>Underground Hieroglyphics following; specialist critical attention.</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>Hieroglyphics wordsmith. Quirky vocabulary and abstract wit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>MD3</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Mac Dre</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Party/Pop</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Hyphy</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Thizz Entertainment</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J142" t="n">
+        <v>6</v>
+      </c>
+      <c r="K142" t="n">
+        <v>6</v>
+      </c>
+      <c r="L142" t="n">
+        <v>6</v>
+      </c>
+      <c r="M142" t="n">
+        <v>5</v>
+      </c>
+      <c r="N142" t="n">
+        <v>5</v>
+      </c>
+      <c r="O142" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>Regional hyphy icon; limited national critical record.</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>Hyphy movement godfather. Enduring Bay Area cult legend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Royce da 5'9"</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Conscious/Lyrical</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Detroit Boom Bap</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Shady/Independent</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>2002</v>
+      </c>
+      <c r="J143" t="n">
+        <v>9</v>
+      </c>
+      <c r="K143" t="n">
+        <v>8</v>
+      </c>
+      <c r="L143" t="n">
+        <v>7</v>
+      </c>
+      <c r="M143" t="n">
+        <v>8</v>
+      </c>
+      <c r="N143" t="n">
+        <v>7</v>
+      </c>
+      <c r="O143" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>Elite technician; documentation grew via Slaughterhouse and PRhyme.</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>Detroit technician. Slaughterhouse and PRhyme cornerstone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Kool G Rap</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Golden Age</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Gangsta/Street</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Boom Bap</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Cold Chillin'</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J144" t="n">
+        <v>9</v>
+      </c>
+      <c r="K144" t="n">
+        <v>8</v>
+      </c>
+      <c r="L144" t="n">
+        <v>9</v>
+      </c>
+      <c r="M144" t="n">
+        <v>8</v>
+      </c>
+      <c r="N144" t="n">
+        <v>7</v>
+      </c>
+      <c r="O144" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>Mafioso-rap forefather. The multisyllabic blueprint for Nas, Biggie and Jay-Z.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>RM</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Redman</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Golden Age</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Conscious/Lyrical</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Funk Boom Bap</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Def Jam</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>1992</v>
+      </c>
+      <c r="J145" t="n">
+        <v>8</v>
+      </c>
+      <c r="K145" t="n">
+        <v>7</v>
+      </c>
+      <c r="L145" t="n">
+        <v>7</v>
+      </c>
+      <c r="M145" t="n">
+        <v>7</v>
+      </c>
+      <c r="N145" t="n">
+        <v>6</v>
+      </c>
+      <c r="O145" t="n">
+        <v>7</v>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>Beloved and skilled; lyrical scholarship modest relative to peers.</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>Newark's funkiest. Effortless flow with comedic menace.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Method Man</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Late 90s</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Conscious/Lyrical</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Wu-Tang</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Def Jam</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>1994</v>
+      </c>
+      <c r="J146" t="n">
+        <v>7</v>
+      </c>
+      <c r="K146" t="n">
+        <v>7</v>
+      </c>
+      <c r="L146" t="n">
+        <v>6</v>
+      </c>
+      <c r="M146" t="n">
+        <v>7</v>
+      </c>
+      <c r="N146" t="n">
+        <v>6</v>
+      </c>
+      <c r="O146" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>Scored solo; Wu-Tang charisma vs pure-lyric metrics.</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>Wu-Tang's charismatic star. Gravel-voiced hooks and grit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>EP</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>EPMD</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Golden Age</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Conscious/Lyrical</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Funk Boom Bap</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Def Jam</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>1988</v>
+      </c>
+      <c r="J147" t="n">
+        <v>7</v>
+      </c>
+      <c r="K147" t="n">
+        <v>6</v>
+      </c>
+      <c r="L147" t="n">
+        <v>6</v>
+      </c>
+      <c r="M147" t="n">
+        <v>6</v>
+      </c>
+      <c r="N147" t="n">
+        <v>6</v>
+      </c>
+      <c r="O147" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>Influential funk-rap duo; understated lyrical documentation.</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>Strictly Business. Laid-back funk and durable chemistry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>TG</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>The Game</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Gangsta/Street</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>West Coast</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Aftermath/G-Unit</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>2005</v>
+      </c>
+      <c r="J148" t="n">
+        <v>7</v>
+      </c>
+      <c r="K148" t="n">
+        <v>7</v>
+      </c>
+      <c r="L148" t="n">
+        <v>7</v>
+      </c>
+      <c r="M148" t="n">
+        <v>7</v>
+      </c>
+      <c r="N148" t="n">
+        <v>6</v>
+      </c>
+      <c r="O148" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>Commercially dominant; reference-heavy bars, mixed critical view.</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>Compton revivalist. The Documentary-era West Coast resurgence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Ice-T</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Old School</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Gangsta/Street</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Electro/Funk</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Sire/Rhyme Syndicate</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>1987</v>
+      </c>
+      <c r="J149" t="n">
+        <v>6</v>
+      </c>
+      <c r="K149" t="n">
+        <v>6</v>
+      </c>
+      <c r="L149" t="n">
+        <v>7</v>
+      </c>
+      <c r="M149" t="n">
+        <v>6</v>
+      </c>
+      <c r="N149" t="n">
+        <v>7</v>
+      </c>
+      <c r="O149" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>Gangsta-rap pioneer; influence and narrative over technical metrics.</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>Gangsta-rap originator. Street reportage before the template existed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Nipsey Hussle</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Conscious/Street</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>West Coast</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>All Money In/Atlantic</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J150" t="n">
+        <v>7</v>
+      </c>
+      <c r="K150" t="n">
+        <v>7</v>
+      </c>
+      <c r="L150" t="n">
+        <v>7</v>
+      </c>
+      <c r="M150" t="n">
+        <v>7</v>
+      </c>
+      <c r="N150" t="n">
+        <v>7</v>
+      </c>
+      <c r="O150" t="n">
+        <v>7</v>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>Posthumous reappraisal ongoing; entrepreneurial legacy prominent.</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>Crenshaw's marathon. Street wisdom and self-determination.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>DQ</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>DJ Quik</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Golden Age</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Gangsta/Street</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>G-Funk</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>1991</v>
+      </c>
+      <c r="J151" t="n">
+        <v>7</v>
+      </c>
+      <c r="K151" t="n">
+        <v>6</v>
+      </c>
+      <c r="L151" t="n">
+        <v>6</v>
+      </c>
+      <c r="M151" t="n">
+        <v>6</v>
+      </c>
+      <c r="N151" t="n">
+        <v>6</v>
+      </c>
+      <c r="O151" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>Revered as a producer; underrated as a lyricist.</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>G-funk auteur. Producer-rapper with effortless West Coast bounce.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:R1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R151"/>
+  <dimension ref="A1:R149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7785,17 +7785,17 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Iggy Azalea</t>
+          <t>Freddie Gibbs</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -7805,39 +7805,39 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Party/Pop</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Southern Trap Pop</t>
+          <t>Gangsta Boom Bap</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Grand Hustle</t>
+          <t>ESGN</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>2014</v>
-      </c>
-      <c r="J99" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K99" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="L99" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M99" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="N99" s="3" t="n">
-        <v>3</v>
+        <v>2004</v>
+      </c>
+      <c r="J99" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K99" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L99" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M99" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N99" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="O99" s="6" t="n">
-        <v>3.8</v>
+        <v>7.8</v>
       </c>
       <c r="P99" s="7" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
       <c r="Q99" s="2" t="inlineStr"/>
       <c r="R99" s="2" t="inlineStr">
         <is>
-          <t>Commercial success masking thin lyrical foundation. Accent controversy.</t>
+          <t>Gary Indiana's finest. Technical gangsta rap with jazz-rap production.</t>
         </is>
       </c>
     </row>
@@ -7857,17 +7857,17 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Freddie Gibbs</t>
+          <t>Migos</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -7877,39 +7877,39 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Trap/Drill</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Gangsta Boom Bap</t>
+          <t>Atlanta Triplet Trap</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>ESGN</t>
+          <t>Quality Control</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>2004</v>
-      </c>
-      <c r="J100" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K100" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L100" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M100" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N100" s="10" t="n">
-        <v>7</v>
+        <v>2013</v>
+      </c>
+      <c r="J100" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M100" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N100" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="O100" s="6" t="n">
-        <v>7.8</v>
+        <v>4</v>
       </c>
       <c r="P100" s="7" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
       <c r="Q100" s="2" t="inlineStr"/>
       <c r="R100" s="2" t="inlineStr">
         <is>
-          <t>Gary Indiana's finest. Technical gangsta rap with jazz-rap production.</t>
+          <t>Triplet flow inventors. Cultural influence far exceeds lyrical complexity.</t>
         </is>
       </c>
     </row>
@@ -7929,17 +7929,17 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>BI2</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Migos</t>
+          <t>Big Sean</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -7949,49 +7949,53 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Trap/Drill</t>
+          <t>Party/Pop</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Triplet Trap</t>
+          <t>Detroit Pop Rap</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>G.O.O.D.</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>2013</v>
-      </c>
-      <c r="J101" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K101" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="L101" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M101" s="8" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J101" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K101" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L101" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M101" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N101" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N101" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="O101" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="P101" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q101" s="2" t="inlineStr"/>
+        <v>5.8</v>
+      </c>
+      <c r="P101" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>Commercial success; critical reception mixed; thin formal analysis</t>
+        </is>
+      </c>
       <c r="R101" s="2" t="inlineStr">
         <is>
-          <t>Triplet flow inventors. Cultural influence far exceeds lyrical complexity.</t>
+          <t>Detroit MC. Punchlines over conceptual depth. 'One Man Can Change The World'.</t>
         </is>
       </c>
     </row>
@@ -8001,17 +8005,17 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>BI2</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Big Sean</t>
+          <t>Tierra Whack</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>Philly</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -8021,39 +8025,39 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Party/Pop</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Detroit Pop Rap</t>
+          <t>Experimental Pop Rap</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>G.O.O.D.</t>
+          <t>Interscope</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>2011</v>
-      </c>
-      <c r="J102" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K102" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L102" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M102" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N102" s="8" t="n">
-        <v>5</v>
+        <v>2018</v>
+      </c>
+      <c r="J102" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K102" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L102" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M102" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N102" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="O102" s="6" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="P102" s="14" t="inlineStr">
         <is>
@@ -8062,12 +8066,12 @@
       </c>
       <c r="Q102" s="2" t="inlineStr">
         <is>
-          <t>Commercial success; critical reception mixed; thin formal analysis</t>
+          <t>Breakout 2018; critical buzz high but career short; scoring may shift</t>
         </is>
       </c>
       <c r="R102" s="2" t="inlineStr">
         <is>
-          <t>Detroit MC. Punchlines over conceptual depth. 'One Man Can Change The World'.</t>
+          <t>'Whack World' — 15 one-minute songs as unified concept. Wholly original.</t>
         </is>
       </c>
     </row>
@@ -8077,17 +8081,17 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Tierra Whack</t>
+          <t>Noname</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Philly</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -8097,53 +8101,49 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Experimental Pop Rap</t>
+          <t>Chicago Jazz Rap</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Interscope</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="J103" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K103" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L103" s="10" t="n">
-        <v>7</v>
+        <v>2016</v>
+      </c>
+      <c r="J103" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K103" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L103" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="M103" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="N103" s="11" t="n">
-        <v>8</v>
+      <c r="N103" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="O103" s="6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="P103" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q103" s="2" t="inlineStr">
-        <is>
-          <t>Breakout 2018; critical buzz high but career short; scoring may shift</t>
-        </is>
-      </c>
+        <v>8.4</v>
+      </c>
+      <c r="P103" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
       <c r="R103" s="2" t="inlineStr">
         <is>
-          <t>'Whack World' — 15 one-minute songs as unified concept. Wholly original.</t>
+          <t>Chicago's most literary voice. Jazz cadences and political awakening.</t>
         </is>
       </c>
     </row>
@@ -8153,12 +8153,12 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>SZ</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Noname</t>
+          <t>Saba</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -8178,34 +8178,34 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Chicago Jazz Rap</t>
+          <t>Chicago Boom Bap</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Pivot Gang</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="J104" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="K104" s="12" t="n">
+      <c r="K104" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L104" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L104" s="11" t="n">
-        <v>8</v>
-      </c>
       <c r="M104" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="N104" s="12" t="n">
-        <v>9</v>
+      <c r="N104" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="O104" s="6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P104" s="7" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
       <c r="Q104" s="2" t="inlineStr"/>
       <c r="R104" s="2" t="inlineStr">
         <is>
-          <t>Chicago's most literary voice. Jazz cadences and political awakening.</t>
+          <t>'CARE FOR ME' — grief and Chicago violence as devastating concept album.</t>
         </is>
       </c>
     </row>
@@ -8225,12 +8225,12 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>SZ</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Saba</t>
+          <t>Danny Brown</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -8245,33 +8245,33 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Chicago Boom Bap</t>
+          <t>Detroit Noise Rap</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Pivot Gang</t>
+          <t>Fool's Gold</t>
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="J105" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="K105" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L105" s="12" t="n">
+      <c r="K105" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="M105" s="11" t="n">
-        <v>8</v>
+      <c r="L105" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M105" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="N105" s="11" t="n">
         <v>8</v>
@@ -8287,7 +8287,7 @@
       <c r="Q105" s="2" t="inlineStr"/>
       <c r="R105" s="2" t="inlineStr">
         <is>
-          <t>'CARE FOR ME' — grief and Chicago violence as devastating concept album.</t>
+          <t>Detroit's avant-garde MC. Schizophrenic flows and surreal imagery.</t>
         </is>
       </c>
     </row>
@@ -8297,12 +8297,12 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Danny Brown</t>
+          <t>Mac Miller</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -8317,39 +8317,39 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Detroit Noise Rap</t>
+          <t>Pittsburgh Soul Rap</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Fool's Gold</t>
+          <t>Rostrum</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
         <v>2010</v>
       </c>
-      <c r="J106" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K106" s="12" t="n">
-        <v>9</v>
+      <c r="J106" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K106" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="L106" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="M106" s="12" t="n">
-        <v>9</v>
+      <c r="M106" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="N106" s="11" t="n">
         <v>8</v>
       </c>
       <c r="O106" s="6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="P106" s="7" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
       <c r="Q106" s="2" t="inlineStr"/>
       <c r="R106" s="2" t="inlineStr">
         <is>
-          <t>Detroit's avant-garde MC. Schizophrenic flows and surreal imagery.</t>
+          <t>Arc from frat-rap to deeply personal jazz introspection. 'Swimming' a peak.</t>
         </is>
       </c>
     </row>
@@ -8369,17 +8369,17 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>JD2</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Mac Miller</t>
+          <t>JID</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -8394,44 +8394,48 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Pittsburgh Soul Rap</t>
+          <t>Atlanta Jazz Rap</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Rostrum</t>
+          <t>Dreamville</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>2010</v>
-      </c>
-      <c r="J107" s="10" t="n">
-        <v>7</v>
+        <v>2017</v>
+      </c>
+      <c r="J107" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="K107" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L107" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M107" s="10" t="n">
-        <v>7</v>
+      <c r="L107" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M107" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="N107" s="11" t="n">
         <v>8</v>
       </c>
       <c r="O107" s="6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="P107" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q107" s="2" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="P107" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr">
+        <is>
+          <t>Late-decade emergence; critical acclaim building; may rescore upward</t>
+        </is>
+      </c>
       <c r="R107" s="2" t="inlineStr">
         <is>
-          <t>Arc from frat-rap to deeply personal jazz introspection. 'Swimming' a peak.</t>
+          <t>Atlanta's most technically gifted rapper. 'DiCaprio 2' showed full potential.</t>
         </is>
       </c>
     </row>
@@ -8441,17 +8445,17 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>JD2</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>JID</t>
+          <t>Cardi B</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>NYC</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -8461,53 +8465,49 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Party/Pop</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Jazz Rap</t>
+          <t>Bronx Trap Pop</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Dreamville</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="J108" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="K108" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L108" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M108" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N108" s="11" t="n">
-        <v>8</v>
+        <v>2018</v>
+      </c>
+      <c r="J108" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K108" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L108" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M108" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N108" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="O108" s="6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="P108" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q108" s="2" t="inlineStr">
-        <is>
-          <t>Late-decade emergence; critical acclaim building; may rescore upward</t>
-        </is>
-      </c>
+        <v>5.6</v>
+      </c>
+      <c r="P108" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr"/>
       <c r="R108" s="2" t="inlineStr">
         <is>
-          <t>Atlanta's most technically gifted rapper. 'DiCaprio 2' showed full potential.</t>
+          <t>Unfiltered Bronx personality. Cultural force exceeds lyrical architecture.</t>
         </is>
       </c>
     </row>
@@ -8517,69 +8517,73 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Cardi B</t>
+          <t>Polo G</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Party/Pop</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Bronx Trap Pop</t>
+          <t>Chicago Melodic Trap</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Columbia</t>
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="J109" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K109" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L109" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M109" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N109" s="5" t="n">
-        <v>4</v>
+        <v>2019</v>
+      </c>
+      <c r="J109" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K109" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L109" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M109" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N109" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="O109" s="6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="P109" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q109" s="2" t="inlineStr"/>
+        <v>7.2</v>
+      </c>
+      <c r="P109" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="inlineStr">
+        <is>
+          <t>Recent emergence; trajectory still forming</t>
+        </is>
+      </c>
       <c r="R109" s="2" t="inlineStr">
         <is>
-          <t>Unfiltered Bronx personality. Cultural force exceeds lyrical architecture.</t>
+          <t>Chicago's introspective melodic trap voice. Melancholy street memoir.</t>
         </is>
       </c>
     </row>
@@ -8589,17 +8593,17 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>RW</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Polo G</t>
+          <t>Rod Wave</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -8609,39 +8613,39 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Chicago Melodic Trap</t>
+          <t>Florida Soul Trap</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Columbia</t>
+          <t>Alamo</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
         <v>2019</v>
       </c>
-      <c r="J110" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K110" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L110" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M110" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N110" s="10" t="n">
-        <v>7</v>
+      <c r="J110" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K110" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L110" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M110" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N110" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="O110" s="6" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="P110" s="14" t="inlineStr">
         <is>
@@ -8650,12 +8654,12 @@
       </c>
       <c r="Q110" s="2" t="inlineStr">
         <is>
-          <t>Recent emergence; trajectory still forming</t>
+          <t>Recent; critical consensus not yet settled</t>
         </is>
       </c>
       <c r="R110" s="2" t="inlineStr">
         <is>
-          <t>Chicago's introspective melodic trap voice. Melancholy street memoir.</t>
+          <t>Emotional vulnerability over technical precision. Florida pain made universal.</t>
         </is>
       </c>
     </row>
@@ -8665,12 +8669,12 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Rod Wave</t>
+          <t>Doechii</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -8690,34 +8694,34 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Florida Soul Trap</t>
+          <t>Tampa Art Rap</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Alamo</t>
+          <t>Capitol</t>
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>2019</v>
-      </c>
-      <c r="J111" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K111" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L111" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M111" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N111" s="8" t="n">
-        <v>5</v>
+        <v>2021</v>
+      </c>
+      <c r="J111" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K111" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L111" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M111" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N111" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="O111" s="6" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P111" s="14" t="inlineStr">
         <is>
@@ -8726,12 +8730,12 @@
       </c>
       <c r="Q111" s="2" t="inlineStr">
         <is>
-          <t>Recent; critical consensus not yet settled</t>
+          <t>Breakout recent; scoring may shift upward as body of work grows</t>
         </is>
       </c>
       <c r="R111" s="2" t="inlineStr">
         <is>
-          <t>Emotional vulnerability over technical precision. Florida pain made universal.</t>
+          <t>Tampa's theatrical polymath. Technical fire meets conceptual daring.</t>
         </is>
       </c>
     </row>
@@ -8741,12 +8745,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>GG2</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Doechii</t>
+          <t>GloRilla</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -8761,53 +8765,53 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Party/Pop</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Tampa Art Rap</t>
+          <t>Memphis Trap</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Capitol</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>2021</v>
-      </c>
-      <c r="J112" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K112" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L112" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M112" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N112" s="12" t="n">
-        <v>9</v>
+        <v>2022</v>
+      </c>
+      <c r="J112" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K112" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L112" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M112" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N112" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="O112" s="6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="P112" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
+        <v>4.8</v>
+      </c>
+      <c r="P112" s="15" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
         <is>
-          <t>Breakout recent; scoring may shift upward as body of work grows</t>
+          <t>Very recent; limited critical record; commercial impact clear</t>
         </is>
       </c>
       <c r="R112" s="2" t="inlineStr">
         <is>
-          <t>Tampa's theatrical polymath. Technical fire meets conceptual daring.</t>
+          <t>Memphis energy, unfiltered personality. New Southern feminism in party form.</t>
         </is>
       </c>
     </row>
@@ -8817,12 +8821,12 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>GG2</t>
+          <t>GN</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>GloRilla</t>
+          <t>Gunna</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -8837,53 +8841,53 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Party/Pop</t>
+          <t>Trap/Drill</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Memphis Trap</t>
+          <t>Atlanta Melodic Trap</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>Young Stoner Life</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>2022</v>
-      </c>
-      <c r="J113" s="8" t="n">
-        <v>5</v>
+        <v>2018</v>
+      </c>
+      <c r="J113" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="K113" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="L113" s="8" t="n">
-        <v>5</v>
+      <c r="L113" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="M113" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N113" s="5" t="n">
-        <v>4</v>
+      <c r="N113" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="O113" s="6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P113" s="15" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>4.2</v>
+      </c>
+      <c r="P113" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
         <is>
-          <t>Very recent; limited critical record; commercial impact clear</t>
+          <t>Significant commercial presence; thin critical analysis</t>
         </is>
       </c>
       <c r="R113" s="2" t="inlineStr">
         <is>
-          <t>Memphis energy, unfiltered personality. New Southern feminism in party form.</t>
+          <t>Melodic luxury trap. Vibe and aesthetic are the art.</t>
         </is>
       </c>
     </row>
@@ -8893,12 +8897,12 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>GN</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Gunna</t>
+          <t>Lil Baby</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -8913,39 +8917,39 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Trap/Drill</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Melodic Trap</t>
+          <t>Atlanta Slime Trap</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Young Stoner Life</t>
+          <t>Quality Control</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="J114" s="5" t="n">
-        <v>4</v>
+        <v>2017</v>
+      </c>
+      <c r="J114" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="K114" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="L114" s="5" t="n">
-        <v>4</v>
+      <c r="L114" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="M114" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N114" s="3" t="n">
-        <v>3</v>
+      <c r="N114" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="O114" s="6" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="P114" s="14" t="inlineStr">
         <is>
@@ -8954,12 +8958,12 @@
       </c>
       <c r="Q114" s="2" t="inlineStr">
         <is>
-          <t>Significant commercial presence; thin critical analysis</t>
+          <t>Recent; commercial dominance clear; critical depth forming</t>
         </is>
       </c>
       <c r="R114" s="2" t="inlineStr">
         <is>
-          <t>Melodic luxury trap. Vibe and aesthetic are the art.</t>
+          <t>Authentic street narrator. Storytelling grounded in lived experience.</t>
         </is>
       </c>
     </row>
@@ -8969,17 +8973,17 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>BT</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Lil Baby</t>
+          <t>Benny the Butcher</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>NYC</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -8994,48 +8998,44 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Slime Trap</t>
+          <t>Buffalo Boom Bap</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>Griselda</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="J115" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K115" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L115" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M115" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N115" s="8" t="n">
-        <v>5</v>
+        <v>2012</v>
+      </c>
+      <c r="J115" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K115" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L115" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M115" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N115" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="O115" s="6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="P115" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q115" s="2" t="inlineStr">
-        <is>
-          <t>Recent; commercial dominance clear; critical depth forming</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="P115" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q115" s="2" t="inlineStr"/>
       <c r="R115" s="2" t="inlineStr">
         <is>
-          <t>Authentic street narrator. Storytelling grounded in lived experience.</t>
+          <t>Griselda's lyrical backbone. Buffalo street narratives with East Coast precision.</t>
         </is>
       </c>
     </row>
@@ -9045,17 +9045,17 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Benny the Butcher</t>
+          <t>Offset</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -9065,49 +9065,53 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Trap/Drill</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Buffalo Boom Bap</t>
+          <t>Migos Solo Trap</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Griselda</t>
+          <t>Quality Control</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>2012</v>
-      </c>
-      <c r="J116" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K116" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L116" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M116" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N116" s="10" t="n">
-        <v>7</v>
+        <v>2017</v>
+      </c>
+      <c r="J116" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K116" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L116" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M116" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N116" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="O116" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="P116" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q116" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="P116" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q116" s="2" t="inlineStr">
+        <is>
+          <t>Solo career emerging post-Migos; scoring tentative</t>
+        </is>
+      </c>
       <c r="R116" s="2" t="inlineStr">
         <is>
-          <t>Griselda's lyrical backbone. Buffalo street narratives with East Coast precision.</t>
+          <t>Migos' most lyrical member. Flow variation and delivery standout in trap context.</t>
         </is>
       </c>
     </row>
@@ -9117,17 +9121,17 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Stormzy</t>
+          <t>Kenny Mason</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -9137,21 +9141,21 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Political</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>UK Grime/Gospel</t>
+          <t>Atlanta Punk Rap</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>#Merky</t>
+          <t>RCA Records</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="J117" s="10" t="n">
         <v>7</v>
@@ -9165,21 +9169,25 @@
       <c r="M117" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="N117" s="11" t="n">
-        <v>8</v>
+      <c r="N117" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="O117" s="6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="P117" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q117" s="2" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="P117" s="15" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q117" s="2" t="inlineStr">
+        <is>
+          <t>Limited documentation; critical buzz building in underground circles</t>
+        </is>
+      </c>
       <c r="R117" s="2" t="inlineStr">
         <is>
-          <t>UK grime's political conscience. Authenticity and ambition fused.</t>
+          <t>Atlanta's punk-rap hybrid. Unconventional tonal range.</t>
         </is>
       </c>
     </row>
@@ -9189,12 +9197,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>OM</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Offset</t>
+          <t>Latto</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -9209,39 +9217,39 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Trap/Drill</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Migos Solo Trap</t>
+          <t>Atlanta Female Trap</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>RCA</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="J118" s="8" t="n">
+        <v>2019</v>
+      </c>
+      <c r="J118" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K118" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L118" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M118" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N118" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="K118" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L118" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="M118" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N118" s="5" t="n">
-        <v>4</v>
-      </c>
       <c r="O118" s="6" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="P118" s="14" t="inlineStr">
         <is>
@@ -9250,12 +9258,12 @@
       </c>
       <c r="Q118" s="2" t="inlineStr">
         <is>
-          <t>Solo career emerging post-Migos; scoring tentative</t>
+          <t>Recent; commercial trajectory clearer than critical consensus</t>
         </is>
       </c>
       <c r="R118" s="2" t="inlineStr">
         <is>
-          <t>Migos' most lyrical member. Flow variation and delivery standout in trap context.</t>
+          <t>Atlanta's female trap voice. Technical skill often underestimated.</t>
         </is>
       </c>
     </row>
@@ -9265,17 +9273,17 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>SR</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Kenny Mason</t>
+          <t>Smino</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -9290,48 +9298,48 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Punk Rap</t>
+          <t>St. Louis Jazz Rap</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>RCA Records</t>
+          <t>Zero Fatigue</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="J119" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="K119" s="10" t="n">
-        <v>7</v>
+      <c r="K119" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="L119" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="M119" s="10" t="n">
-        <v>7</v>
+      <c r="M119" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="N119" s="10" t="n">
         <v>7</v>
       </c>
       <c r="O119" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="P119" s="15" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>7.4</v>
+      </c>
+      <c r="P119" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
         <is>
-          <t>Limited documentation; critical buzz building in underground circles</t>
+          <t>Critical darling in jazz-rap circles; broader recognition still forming</t>
         </is>
       </c>
       <c r="R119" s="2" t="inlineStr">
         <is>
-          <t>Atlanta's punk-rap hybrid. Unconventional tonal range.</t>
+          <t>St. Louis's jazz-rap hybrid. Melodic and rhythmic sophistication.</t>
         </is>
       </c>
     </row>
@@ -9341,17 +9349,17 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>PZ</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Latto</t>
+          <t>Pusha T</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>NYC</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -9366,48 +9374,44 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Female Trap</t>
+          <t>Coke Rap Boom Bap</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>RCA</t>
+          <t>G.O.O.D.</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>2019</v>
-      </c>
-      <c r="J120" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K120" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L120" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M120" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N120" s="8" t="n">
-        <v>5</v>
+        <v>2002</v>
+      </c>
+      <c r="J120" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K120" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L120" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M120" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N120" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="O120" s="6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="P120" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q120" s="2" t="inlineStr">
-        <is>
-          <t>Recent; commercial trajectory clearer than critical consensus</t>
-        </is>
-      </c>
+        <v>7.4</v>
+      </c>
+      <c r="P120" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q120" s="2" t="inlineStr"/>
       <c r="R120" s="2" t="inlineStr">
         <is>
-          <t>Atlanta's female trap voice. Technical skill often underestimated.</t>
+          <t>Cocaine rap's Rembrandt. 'Daytona' — maximum density, minimum waste.</t>
         </is>
       </c>
     </row>
@@ -9417,17 +9421,17 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Smino</t>
+          <t>Tyler the Creator</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -9442,48 +9446,44 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>St. Louis Jazz Rap</t>
+          <t>Odd Future/Orchestral</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>Zero Fatigue</t>
+          <t>Columbia</t>
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>2017</v>
+        <v>2009</v>
       </c>
       <c r="J121" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="K121" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L121" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M121" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N121" s="10" t="n">
-        <v>7</v>
+      <c r="K121" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L121" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M121" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="N121" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="O121" s="6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="P121" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q121" s="2" t="inlineStr">
-        <is>
-          <t>Critical darling in jazz-rap circles; broader recognition still forming</t>
-        </is>
-      </c>
+        <v>8.4</v>
+      </c>
+      <c r="P121" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q121" s="2" t="inlineStr"/>
       <c r="R121" s="2" t="inlineStr">
         <is>
-          <t>St. Louis's jazz-rap hybrid. Melodic and rhythmic sophistication.</t>
+          <t>'Igor' and 'Call Me If You Get Lost' — producer-auteur. Concept album mastery.</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>PZ</t>
+          <t>AB2</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Pusha T</t>
+          <t>Armand Hammer</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -9513,49 +9513,53 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Abstract</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Coke Rap Boom Bap</t>
+          <t>Abstract Boom Bap</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>G.O.O.D.</t>
+          <t>Backwoodz</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>2002</v>
+        <v>2013</v>
       </c>
       <c r="J122" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="K122" s="10" t="n">
-        <v>7</v>
+      <c r="K122" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="L122" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="M122" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N122" s="10" t="n">
-        <v>7</v>
+      <c r="M122" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="N122" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="O122" s="6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="P122" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q122" s="2" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="P122" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q122" s="2" t="inlineStr">
+        <is>
+          <t>Critical underground darling; thin mainstream documentation</t>
+        </is>
+      </c>
       <c r="R122" s="2" t="inlineStr">
         <is>
-          <t>Cocaine rap's Rembrandt. 'Daytona' — maximum density, minimum waste.</t>
+          <t>billy woods + ELUCID. The most demanding abstract rap being made today.</t>
         </is>
       </c>
     </row>
@@ -9565,17 +9569,17 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>ZE</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Tyler the Creator</t>
+          <t>Zack Fox</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -9585,49 +9589,53 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Abstract</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Odd Future/Orchestral</t>
+          <t>Comedy-Abstract Rap</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>Columbia</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>2009</v>
-      </c>
-      <c r="J123" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K123" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L123" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M123" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="N123" s="12" t="n">
-        <v>9</v>
+        <v>2020</v>
+      </c>
+      <c r="J123" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K123" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L123" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M123" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N123" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="O123" s="6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="P123" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q123" s="2" t="inlineStr"/>
+        <v>6.4</v>
+      </c>
+      <c r="P123" s="15" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q123" s="2" t="inlineStr">
+        <is>
+          <t>Very recent; extremely limited critical record</t>
+        </is>
+      </c>
       <c r="R123" s="2" t="inlineStr">
         <is>
-          <t>'Igor' and 'Call Me If You Get Lost' — producer-auteur. Concept album mastery.</t>
+          <t>Comedy-meets-rap. Formally interesting but body of work too small to score confidently.</t>
         </is>
       </c>
     </row>
@@ -9637,17 +9645,17 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>AB2</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Armand Hammer</t>
+          <t>Lil Durk</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -9657,39 +9665,39 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>Abstract</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Abstract Boom Bap</t>
+          <t>Chicago Melodic Trap</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Backwoodz</t>
+          <t>Only the Family</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
         <v>2013</v>
       </c>
-      <c r="J124" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K124" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L124" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M124" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="N124" s="11" t="n">
-        <v>8</v>
+      <c r="J124" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K124" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L124" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M124" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N124" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="O124" s="6" t="n">
-        <v>8.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="P124" s="14" t="inlineStr">
         <is>
@@ -9698,12 +9706,12 @@
       </c>
       <c r="Q124" s="2" t="inlineStr">
         <is>
-          <t>Critical underground darling; thin mainstream documentation</t>
+          <t>Commercial dominance clear; critical depth limited</t>
         </is>
       </c>
       <c r="R124" s="2" t="inlineStr">
         <is>
-          <t>billy woods + ELUCID. The most demanding abstract rap being made today.</t>
+          <t>Chicago drill's most commercially consistent voice.</t>
         </is>
       </c>
     </row>
@@ -9713,12 +9721,12 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>ZE</t>
+          <t>KS2</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Zack Fox</t>
+          <t>Kodak Black</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -9733,53 +9741,53 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Abstract</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Comedy-Abstract Rap</t>
+          <t>Florida Trap</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="J125" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K125" s="10" t="n">
-        <v>7</v>
+        <v>2014</v>
+      </c>
+      <c r="J125" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K125" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="L125" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="M125" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N125" s="9" t="n">
-        <v>6</v>
+      <c r="M125" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N125" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="O125" s="6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="P125" s="15" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>5</v>
+      </c>
+      <c r="P125" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
         <is>
-          <t>Very recent; extremely limited critical record</t>
+          <t>Commercial success; thin critical framework; behavior clouds reception</t>
         </is>
       </c>
       <c r="R125" s="2" t="inlineStr">
         <is>
-          <t>Comedy-meets-rap. Formally interesting but body of work too small to score confidently.</t>
+          <t>Florida trap's most distinctive voice. Rough-edged regional authenticity.</t>
         </is>
       </c>
     </row>
@@ -9789,17 +9797,17 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Lil Durk</t>
+          <t>Rapsody</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -9809,53 +9817,49 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Chicago Melodic Trap</t>
+          <t>North Carolina Soul Rap</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Only the Family</t>
+          <t>Jamla</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>2013</v>
-      </c>
-      <c r="J126" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K126" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L126" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M126" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N126" s="8" t="n">
-        <v>5</v>
+        <v>2010</v>
+      </c>
+      <c r="J126" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K126" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L126" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M126" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N126" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="O126" s="6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="P126" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q126" s="2" t="inlineStr">
-        <is>
-          <t>Commercial dominance clear; critical depth limited</t>
-        </is>
-      </c>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="P126" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q126" s="2" t="inlineStr"/>
       <c r="R126" s="2" t="inlineStr">
         <is>
-          <t>Chicago drill's most commercially consistent voice.</t>
+          <t>North Carolina's most complete female MC. Lyrical depth rivals any peer.</t>
         </is>
       </c>
     </row>
@@ -9865,12 +9869,12 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>KS2</t>
+          <t>MF2</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Kodak Black</t>
+          <t>Mavi</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -9885,53 +9889,53 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Abstract</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Florida Trap</t>
+          <t>Underground Abstract</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Secretly Canadian</t>
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>2014</v>
-      </c>
-      <c r="J127" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K127" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L127" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M127" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N127" s="5" t="n">
-        <v>4</v>
+        <v>2019</v>
+      </c>
+      <c r="J127" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K127" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L127" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M127" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N127" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="O127" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="P127" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
+        <v>7.2</v>
+      </c>
+      <c r="P127" s="15" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
         <is>
-          <t>Commercial success; thin critical framework; behavior clouds reception</t>
+          <t>Very limited critical documentation; underground following only</t>
         </is>
       </c>
       <c r="R127" s="2" t="inlineStr">
         <is>
-          <t>Florida trap's most distinctive voice. Rough-edged regional authenticity.</t>
+          <t>Charlotte underground. Dense introspective abstract rap. Watch this space.</t>
         </is>
       </c>
     </row>
@@ -9941,69 +9945,73 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>XP</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Rapsody</t>
+          <t>Xzibit</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>North Carolina Soul Rap</t>
+          <t>Hard West Coast</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Jamla</t>
+          <t>Loud/Columbia</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>2010</v>
-      </c>
-      <c r="J128" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K128" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L128" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M128" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N128" s="12" t="n">
-        <v>9</v>
+        <v>1996</v>
+      </c>
+      <c r="J128" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K128" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L128" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M128" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N128" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="O128" s="6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="P128" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q128" s="2" t="inlineStr"/>
+        <v>6.8</v>
+      </c>
+      <c r="P128" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q128" s="2" t="inlineStr">
+        <is>
+          <t>Well-known but limited formal critical analysis</t>
+        </is>
+      </c>
       <c r="R128" s="2" t="inlineStr">
         <is>
-          <t>North Carolina's most complete female MC. Lyrical depth rivals any peer.</t>
+          <t>West Coast boom bap craftsman. More respected by peers than critics.</t>
         </is>
       </c>
     </row>
@@ -10013,17 +10021,17 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>MF2</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Mavi</t>
+          <t>Saweetie</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Bay Area</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -10033,53 +10041,53 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>Abstract</t>
+          <t>Party/Pop</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Underground Abstract</t>
+          <t>Trap Pop</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Secretly Canadian</t>
+          <t>Warner</t>
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>2019</v>
-      </c>
-      <c r="J129" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K129" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L129" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M129" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N129" s="10" t="n">
-        <v>7</v>
+        <v>2018</v>
+      </c>
+      <c r="J129" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K129" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L129" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M129" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N129" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="O129" s="6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="P129" s="15" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>4.8</v>
+      </c>
+      <c r="P129" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
         <is>
-          <t>Very limited critical documentation; underground following only</t>
+          <t>Recent commercial success; limited critical depth</t>
         </is>
       </c>
       <c r="R129" s="2" t="inlineStr">
         <is>
-          <t>Charlotte underground. Dense introspective abstract rap. Watch this space.</t>
+          <t>Bay Area trap-pop. Ice Princess persona over lyrical substance.</t>
         </is>
       </c>
     </row>
@@ -10089,73 +10097,73 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>XP</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Xzibit</t>
+          <t>City Girls</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Late 90s</t>
+          <t>2020s</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Party/Pop</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Hard West Coast</t>
+          <t>Miami Trap</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Loud/Columbia</t>
+          <t>Quality Control/Motown</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>1996</v>
-      </c>
-      <c r="J130" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K130" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L130" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M130" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N130" s="9" t="n">
-        <v>6</v>
+        <v>2018</v>
+      </c>
+      <c r="J130" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K130" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L130" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M130" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N130" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="O130" s="6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="P130" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
+        <v>4.6</v>
+      </c>
+      <c r="P130" s="15" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
         <is>
-          <t>Well-known but limited formal critical analysis</t>
+          <t>Limited critical record; cultural impact clearer than lyrical analysis</t>
         </is>
       </c>
       <c r="R130" s="2" t="inlineStr">
         <is>
-          <t>West Coast boom bap craftsman. More respected by peers than critics.</t>
+          <t>Miami's hedonistic party rap duo. Energy over craft.</t>
         </is>
       </c>
     </row>
@@ -10165,17 +10173,17 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Saweetie</t>
+          <t>Maxo Kream</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -10185,39 +10193,39 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>Party/Pop</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>Trap Pop</t>
+          <t>Houston Narrative Trap</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>Warner</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="J131" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K131" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L131" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="M131" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N131" s="5" t="n">
-        <v>4</v>
+        <v>2017</v>
+      </c>
+      <c r="J131" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K131" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L131" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M131" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N131" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="O131" s="6" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="P131" s="14" t="inlineStr">
         <is>
@@ -10226,164 +10234,159 @@
       </c>
       <c r="Q131" s="2" t="inlineStr">
         <is>
-          <t>Recent commercial success; limited critical depth</t>
+          <t>Critical acclaim in narrative rap circles; limited mainstream documentation</t>
         </is>
       </c>
       <c r="R131" s="2" t="inlineStr">
         <is>
-          <t>Bay Area trap-pop. Ice Princess persona over lyrical substance.</t>
+          <t>Houston storytelling tradition continued. 'Weight of the World' deeply affecting.</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" t="n">
         <v>131</v>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>CI</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>City Girls</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>Party/Pop</t>
-        </is>
-      </c>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>Miami Trap</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>Quality Control/Motown</t>
-        </is>
-      </c>
-      <c r="I132" s="2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="J132" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K132" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L132" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="M132" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N132" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="O132" s="6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P132" s="15" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="Q132" s="2" t="inlineStr">
-        <is>
-          <t>Limited critical record; cultural impact clearer than lyrical analysis</t>
-        </is>
-      </c>
-      <c r="R132" s="2" t="inlineStr">
-        <is>
-          <t>Miami's hedonistic party rap duo. Energy over craft.</t>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>The Roots</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Philly</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Golden Age</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Conscious/Lyrical</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Live-Band Boom Bap</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Geffen/MCA</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>1993</v>
+      </c>
+      <c r="J132" t="n">
+        <v>10</v>
+      </c>
+      <c r="K132" t="n">
+        <v>9</v>
+      </c>
+      <c r="L132" t="n">
+        <v>8</v>
+      </c>
+      <c r="M132" t="n">
+        <v>9</v>
+      </c>
+      <c r="N132" t="n">
+        <v>8</v>
+      </c>
+      <c r="O132" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>Philadelphia's live-band institution; Black Thought's relentless technique anchors a peerless catalog.</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" t="n">
         <v>132</v>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>MX</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>Maxo Kream</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="E133" s="2" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Beanie Sigel</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Philly</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
         <is>
           <t>Gangsta/Street</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
-        <is>
-          <t>Houston Narrative Trap</t>
-        </is>
-      </c>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t>EMPIRE</t>
-        </is>
-      </c>
-      <c r="I133" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="J133" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K133" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L133" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M133" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N133" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="O133" s="6" t="n">
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Soul Boom Bap</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Roc-A-Fella</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J133" t="n">
+        <v>8</v>
+      </c>
+      <c r="K133" t="n">
+        <v>7</v>
+      </c>
+      <c r="L133" t="n">
+        <v>8</v>
+      </c>
+      <c r="M133" t="n">
+        <v>7</v>
+      </c>
+      <c r="N133" t="n">
+        <v>7</v>
+      </c>
+      <c r="O133" t="n">
         <v>7.4</v>
       </c>
-      <c r="P133" s="14" t="inlineStr">
+      <c r="P133" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="Q133" s="2" t="inlineStr">
-        <is>
-          <t>Critical acclaim in narrative rap circles; limited mainstream documentation</t>
-        </is>
-      </c>
-      <c r="R133" s="2" t="inlineStr">
-        <is>
-          <t>Houston storytelling tradition continued. 'Weight of the World' deeply affecting.</t>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>Critically respected but thinly documented outside the Roc-A-Fella context.</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>Philadelphia's hardest pen. Street narratives carried with weight and conviction.</t>
         </is>
       </c>
     </row>
@@ -10393,12 +10396,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>BT3</t>
+          <t>UV</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Black Thought</t>
+          <t>Lil Uzi Vert</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -10408,53 +10411,58 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Golden Age</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Live-Band Boom Bap</t>
+          <t>Rage/Trap</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Geffen/MCA</t>
+          <t>Generation Now/Atlantic</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1993</v>
+        <v>2016</v>
       </c>
       <c r="J134" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K134" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L134" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M134" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N134" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O134" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>Melodic rage star; influence on sound outweighs lyrical scholarship.</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>The Roots' engine and a consensus top-tier technician. Relentless breath control and rhyme density.</t>
+          <t>Genre-bending rage pioneer. Melody and energy over lyrical density.</t>
         </is>
       </c>
     </row>
@@ -10464,12 +10472,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>BS</t>
+          <t>FW</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Beanie Sigel</t>
+          <t>Freeway</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -10498,39 +10506,39 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2000</v>
+        <v>2003</v>
       </c>
       <c r="J135" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K135" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L135" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M135" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N135" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O135" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>Critically respected but thinly documented outside the Roc-A-Fella context.</t>
+          <t>Limited critical record; respected within State Property/Roc-A-Fella circles.</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>Philadelphia's hardest pen. Street narratives carried with weight and conviction.</t>
+          <t>Distinctive raspy urgency and Philly grit. State Property standout.</t>
         </is>
       </c>
     </row>
@@ -10540,12 +10548,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>UV</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Lil Uzi Vert</t>
+          <t>Eve</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -10555,26 +10563,26 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Party/Pop</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Rage/Trap</t>
+          <t>Ruff Ryders</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Generation Now/Atlantic</t>
+          <t>Ruff Ryders/Interscope</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2016</v>
+        <v>1999</v>
       </c>
       <c r="J136" t="n">
         <v>6</v>
@@ -10583,30 +10591,30 @@
         <v>6</v>
       </c>
       <c r="L136" t="n">
+        <v>6</v>
+      </c>
+      <c r="M136" t="n">
+        <v>6</v>
+      </c>
+      <c r="N136" t="n">
         <v>5</v>
-      </c>
-      <c r="M136" t="n">
-        <v>6</v>
-      </c>
-      <c r="N136" t="n">
-        <v>6</v>
       </c>
       <c r="O136" t="n">
         <v>5.8</v>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>Melodic rage star; influence on sound outweighs lyrical scholarship.</t>
+          <t>Commercial success clearer than lyrical analysis.</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>Genre-bending rage pioneer. Melody and energy over lyrical density.</t>
+          <t>Ruff Ryders' First Lady. Charismatic crossover with Philly roots.</t>
         </is>
       </c>
     </row>
@@ -10616,44 +10624,44 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Freeway</t>
+          <t>Da Brat</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Philly</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Party/Pop</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Soul Boom Bap</t>
+          <t>So So Def Bass</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Roc-A-Fella</t>
+          <t>So So Def</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2003</v>
+        <v>1994</v>
       </c>
       <c r="J137" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K137" t="n">
         <v>6</v>
@@ -10668,21 +10676,21 @@
         <v>5</v>
       </c>
       <c r="O137" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>Limited critical record; respected within State Property/Roc-A-Fella circles.</t>
+          <t>First female solo rapper to go platinum; under-analyzed lyrically.</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>Distinctive raspy urgency and Philly grit. State Property standout.</t>
+          <t>So So Def's breakout. First female solo rapper to go platinum.</t>
         </is>
       </c>
     </row>
@@ -10692,73 +10700,73 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>TS2</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Eve</t>
+          <t>Too $hort</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Philly</t>
+          <t>Bay Area</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>Old School</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Party/Pop</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ruff Ryders</t>
+          <t>Funk/Bass</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Ruff Ryders/Interscope</t>
+          <t>Jive/Dangerous Music</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1999</v>
+        <v>1987</v>
       </c>
       <c r="J138" t="n">
         <v>6</v>
       </c>
       <c r="K138" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L138" t="n">
         <v>6</v>
       </c>
       <c r="M138" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N138" t="n">
         <v>5</v>
       </c>
       <c r="O138" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>Commercial success clearer than lyrical analysis.</t>
+          <t>Pioneer status outweighs lyrical-craft documentation.</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>Ruff Ryders' First Lady. Charismatic crossover with Philly roots.</t>
+          <t>Oakland pioneer and pimp-rap archetype. Influence over intricacy.</t>
         </is>
       </c>
     </row>
@@ -10768,17 +10776,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Da Brat</t>
+          <t>Del the Funky Homosapien</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Bay Area</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -10788,39 +10796,39 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Party/Pop</t>
+          <t>Abstract</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>So So Def Bass</t>
+          <t>Hieroglyphics</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>So So Def</t>
+          <t>Elektra/Hiero Imperium</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1994</v>
+        <v>1991</v>
       </c>
       <c r="J139" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K139" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L139" t="n">
         <v>6</v>
       </c>
       <c r="M139" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N139" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O139" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="P139" t="inlineStr">
         <is>
@@ -10829,12 +10837,12 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>First female solo rapper to go platinum; under-analyzed lyrically.</t>
+          <t>Underground Hieroglyphics following; specialist critical attention.</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>So So Def's breakout. First female solo rapper to go platinum.</t>
+          <t>Hieroglyphics wordsmith. Quirky vocabulary and abstract wit.</t>
         </is>
       </c>
     </row>
@@ -10844,12 +10852,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>TS2</t>
+          <t>MD3</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Too $hort</t>
+          <t>Mac Dre</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -10859,32 +10867,32 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Old School</t>
+          <t>2000s</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Party/Pop</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Funk/Bass</t>
+          <t>Hyphy</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Jive/Dangerous Music</t>
+          <t>Thizz Entertainment</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="J140" t="n">
         <v>6</v>
       </c>
       <c r="K140" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L140" t="n">
         <v>6</v>
@@ -10896,21 +10904,21 @@
         <v>5</v>
       </c>
       <c r="O140" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>Pioneer status outweighs lyrical-craft documentation.</t>
+          <t>Regional hyphy icon; limited national critical record.</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>Oakland pioneer and pimp-rap archetype. Influence over intricacy.</t>
+          <t>Hyphy movement godfather. Enduring Bay Area cult legend.</t>
         </is>
       </c>
     </row>
@@ -10920,59 +10928,59 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Del the Funky Homosapien</t>
+          <t>Royce da 5'9"</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Golden Age</t>
+          <t>2000s</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Abstract</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hieroglyphics</t>
+          <t>Detroit Boom Bap</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Elektra/Hiero Imperium</t>
+          <t>Shady/Independent</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1991</v>
+        <v>2002</v>
       </c>
       <c r="J141" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K141" t="n">
         <v>8</v>
       </c>
       <c r="L141" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M141" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N141" t="n">
         <v>7</v>
       </c>
       <c r="O141" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="P141" t="inlineStr">
         <is>
@@ -10981,12 +10989,12 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>Underground Hieroglyphics following; specialist critical attention.</t>
+          <t>Elite technician; documentation grew via Slaughterhouse and PRhyme.</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>Hieroglyphics wordsmith. Quirky vocabulary and abstract wit.</t>
+          <t>Detroit technician. Slaughterhouse and PRhyme cornerstone.</t>
         </is>
       </c>
     </row>
@@ -10996,73 +11004,68 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MD3</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Mac Dre</t>
+          <t>Kool G Rap</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>NYC</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Party/Pop</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hyphy</t>
+          <t>Boom Bap</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Thizz Entertainment</t>
+          <t>Cold Chillin'</t>
         </is>
       </c>
       <c r="I142" t="n">
         <v>1989</v>
       </c>
       <c r="J142" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K142" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L142" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M142" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N142" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O142" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="Q142" t="inlineStr">
-        <is>
-          <t>Regional hyphy icon; limited national critical record.</t>
+          <t>H</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>Hyphy movement godfather. Enduring Bay Area cult legend.</t>
+          <t>Mafioso-rap forefather. The multisyllabic blueprint for Nas, Biggie and Jay-Z.</t>
         </is>
       </c>
     </row>
@@ -11072,22 +11075,22 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Royce da 5'9"</t>
+          <t>Redman</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>NYC</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -11097,34 +11100,34 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Detroit Boom Bap</t>
+          <t>Funk Boom Bap</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Shady/Independent</t>
+          <t>Def Jam</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2002</v>
+        <v>1992</v>
       </c>
       <c r="J143" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K143" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L143" t="n">
         <v>7</v>
       </c>
       <c r="M143" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N143" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O143" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="P143" t="inlineStr">
         <is>
@@ -11133,12 +11136,12 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>Elite technician; documentation grew via Slaughterhouse and PRhyme.</t>
+          <t>Beloved and skilled; lyrical scholarship modest relative to peers.</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>Detroit technician. Slaughterhouse and PRhyme cornerstone.</t>
+          <t>Newark's funkiest. Effortless flow with comedic menace.</t>
         </is>
       </c>
     </row>
@@ -11148,12 +11151,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Kool G Rap</t>
+          <t>Method Man</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -11163,53 +11166,58 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Golden Age</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Boom Bap</t>
+          <t>Wu-Tang</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Cold Chillin'</t>
+          <t>Def Jam</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1989</v>
+        <v>1994</v>
       </c>
       <c r="J144" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K144" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L144" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M144" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N144" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O144" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>Scored solo; Wu-Tang charisma vs pure-lyric metrics.</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>Mafioso-rap forefather. The multisyllabic blueprint for Nas, Biggie and Jay-Z.</t>
+          <t>Wu-Tang's charismatic star. Gravel-voiced hooks and grit.</t>
         </is>
       </c>
     </row>
@@ -11219,12 +11227,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>EP</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Redman</t>
+          <t>EPMD</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -11253,25 +11261,25 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1992</v>
+        <v>1988</v>
       </c>
       <c r="J145" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K145" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L145" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M145" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N145" t="n">
         <v>6</v>
       </c>
       <c r="O145" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="P145" t="inlineStr">
         <is>
@@ -11280,12 +11288,12 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>Beloved and skilled; lyrical scholarship modest relative to peers.</t>
+          <t>Influential funk-rap duo; understated lyrical documentation.</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>Newark's funkiest. Effortless flow with comedic menace.</t>
+          <t>Strictly Business. Laid-back funk and durable chemistry.</t>
         </is>
       </c>
     </row>
@@ -11295,41 +11303,41 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ME</t>
+          <t>TG</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Method Man</t>
+          <t>The Game</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Late 90s</t>
+          <t>2000s</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Wu-Tang</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Def Jam</t>
+          <t>Aftermath/G-Unit</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1994</v>
+        <v>2005</v>
       </c>
       <c r="J146" t="n">
         <v>7</v>
@@ -11338,7 +11346,7 @@
         <v>7</v>
       </c>
       <c r="L146" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M146" t="n">
         <v>7</v>
@@ -11347,7 +11355,7 @@
         <v>6</v>
       </c>
       <c r="O146" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="P146" t="inlineStr">
         <is>
@@ -11356,12 +11364,12 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>Scored solo; Wu-Tang charisma vs pure-lyric metrics.</t>
+          <t>Commercially dominant; reference-heavy bars, mixed critical view.</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>Wu-Tang's charismatic star. Gravel-voiced hooks and grit.</t>
+          <t>Compton revivalist. The Documentary-era West Coast resurgence.</t>
         </is>
       </c>
     </row>
@@ -11371,59 +11379,59 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>EP</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>EPMD</t>
+          <t>Ice-T</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Golden Age</t>
+          <t>Old School</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Funk Boom Bap</t>
+          <t>Electro/Funk</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Def Jam</t>
+          <t>Sire/Rhyme Syndicate</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="J147" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K147" t="n">
         <v>6</v>
       </c>
       <c r="L147" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M147" t="n">
         <v>6</v>
       </c>
       <c r="N147" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O147" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="P147" t="inlineStr">
         <is>
@@ -11432,12 +11440,12 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>Influential funk-rap duo; understated lyrical documentation.</t>
+          <t>Gangsta-rap pioneer; influence and narrative over technical metrics.</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>Strictly Business. Laid-back funk and durable chemistry.</t>
+          <t>Gangsta-rap originator. Street reportage before the template existed.</t>
         </is>
       </c>
     </row>
@@ -11447,12 +11455,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>TG</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>The Game</t>
+          <t>Nipsey Hussle</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -11462,12 +11470,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Conscious/Street</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -11477,11 +11485,11 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Aftermath/G-Unit</t>
+          <t>All Money In/Atlantic</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2005</v>
+        <v>2010</v>
       </c>
       <c r="J148" t="n">
         <v>7</v>
@@ -11496,10 +11504,10 @@
         <v>7</v>
       </c>
       <c r="N148" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O148" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="P148" t="inlineStr">
         <is>
@@ -11508,12 +11516,12 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>Commercially dominant; reference-heavy bars, mixed critical view.</t>
+          <t>Posthumous reappraisal ongoing; entrepreneurial legacy prominent.</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>Compton revivalist. The Documentary-era West Coast resurgence.</t>
+          <t>Crenshaw's marathon. Street wisdom and self-determination.</t>
         </is>
       </c>
     </row>
@@ -11523,12 +11531,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DQ</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Ice-T</t>
+          <t>DJ Quik</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -11538,7 +11546,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Old School</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -11548,34 +11556,34 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Electro/Funk</t>
+          <t>G-Funk</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Sire/Rhyme Syndicate</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1987</v>
+        <v>1991</v>
       </c>
       <c r="J149" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K149" t="n">
         <v>6</v>
       </c>
       <c r="L149" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M149" t="n">
         <v>6</v>
       </c>
       <c r="N149" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O149" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="P149" t="inlineStr">
         <is>
@@ -11584,162 +11592,10 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>Gangsta-rap pioneer; influence and narrative over technical metrics.</t>
+          <t>Revered as a producer; underrated as a lyricist.</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
-        <is>
-          <t>Gangsta-rap originator. Street reportage before the template existed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="n">
-        <v>149</v>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>NH</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Nipsey Hussle</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>LA</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>2010s</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>Conscious/Street</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>West Coast</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>All Money In/Atlantic</t>
-        </is>
-      </c>
-      <c r="I150" t="n">
-        <v>2010</v>
-      </c>
-      <c r="J150" t="n">
-        <v>7</v>
-      </c>
-      <c r="K150" t="n">
-        <v>7</v>
-      </c>
-      <c r="L150" t="n">
-        <v>7</v>
-      </c>
-      <c r="M150" t="n">
-        <v>7</v>
-      </c>
-      <c r="N150" t="n">
-        <v>7</v>
-      </c>
-      <c r="O150" t="n">
-        <v>7</v>
-      </c>
-      <c r="P150" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q150" t="inlineStr">
-        <is>
-          <t>Posthumous reappraisal ongoing; entrepreneurial legacy prominent.</t>
-        </is>
-      </c>
-      <c r="R150" t="inlineStr">
-        <is>
-          <t>Crenshaw's marathon. Street wisdom and self-determination.</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="n">
-        <v>150</v>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>DQ</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>DJ Quik</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>LA</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Golden Age</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>Gangsta/Street</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>G-Funk</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Profile</t>
-        </is>
-      </c>
-      <c r="I151" t="n">
-        <v>1991</v>
-      </c>
-      <c r="J151" t="n">
-        <v>7</v>
-      </c>
-      <c r="K151" t="n">
-        <v>6</v>
-      </c>
-      <c r="L151" t="n">
-        <v>6</v>
-      </c>
-      <c r="M151" t="n">
-        <v>6</v>
-      </c>
-      <c r="N151" t="n">
-        <v>6</v>
-      </c>
-      <c r="O151" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="P151" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q151" t="inlineStr">
-        <is>
-          <t>Revered as a producer; underrated as a lyricist.</t>
-        </is>
-      </c>
-      <c r="R151" t="inlineStr">
         <is>
           <t>G-funk auteur. Producer-rapper with effortless West Coast bounce.</t>
         </is>

--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R149"/>
+  <dimension ref="A1:R148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6849,17 +6849,17 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>JC</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Drake</t>
+          <t>J. Cole</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -6869,39 +6869,39 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Party/Pop</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Melodic Rap</t>
+          <t>Soulful Boom Bap</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>OVO/Young Money</t>
+          <t>Dreamville</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>2006</v>
-      </c>
-      <c r="J86" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K86" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L86" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M86" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N86" s="8" t="n">
-        <v>5</v>
+        <v>2011</v>
+      </c>
+      <c r="J86" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K86" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L86" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M86" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N86" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="O86" s="6" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="P86" s="7" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
       <c r="Q86" s="2" t="inlineStr"/>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>Emotional candor and commercial dominance. Lyricism secondary to feeling.</t>
+          <t>Working-class emotional intelligence. Deep narrative craft.</t>
         </is>
       </c>
     </row>
@@ -6921,12 +6921,12 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>JC</t>
+          <t>YT</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>J. Cole</t>
+          <t>Young Thug</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -6941,39 +6941,39 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Soulful Boom Bap</t>
+          <t>Melodic Trap</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Dreamville</t>
+          <t>300 Entertainment</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
         <v>2011</v>
       </c>
-      <c r="J87" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K87" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L87" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M87" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N87" s="12" t="n">
-        <v>9</v>
+      <c r="J87" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K87" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M87" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N87" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="O87" s="6" t="n">
-        <v>8.4</v>
+        <v>5.2</v>
       </c>
       <c r="P87" s="7" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
       <c r="Q87" s="2" t="inlineStr"/>
       <c r="R87" s="2" t="inlineStr">
         <is>
-          <t>Working-class emotional intelligence. Deep narrative craft.</t>
+          <t>Melody over meaning. Vocal texture as primary instrument.</t>
         </is>
       </c>
     </row>
@@ -6993,12 +6993,12 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>YT</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Young Thug</t>
+          <t>Future</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -7013,30 +7013,30 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Trap/Drill</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Melodic Trap</t>
+          <t>Auto-Tune Trap</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>300 Entertainment</t>
+          <t>A1/Epic</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="J88" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="K88" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L88" s="5" t="n">
-        <v>4</v>
+      <c r="K88" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L88" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="M88" s="9" t="n">
         <v>6</v>
@@ -7055,7 +7055,7 @@
       <c r="Q88" s="2" t="inlineStr"/>
       <c r="R88" s="2" t="inlineStr">
         <is>
-          <t>Melody over meaning. Vocal texture as primary instrument.</t>
+          <t>Emotional auto-tune as confession. Vibe over lyrical architecture.</t>
         </is>
       </c>
     </row>
@@ -7065,17 +7065,17 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Future</t>
+          <t>Chance the Rapper</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -7085,39 +7085,39 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Trap/Drill</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Auto-Tune Trap</t>
+          <t>Chicago Gospel Rap</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>A1/Epic</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>2012</v>
-      </c>
-      <c r="J89" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K89" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L89" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="M89" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N89" s="8" t="n">
-        <v>5</v>
+        <v>2013</v>
+      </c>
+      <c r="J89" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K89" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L89" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M89" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N89" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="O89" s="6" t="n">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P89" s="7" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
       <c r="Q89" s="2" t="inlineStr"/>
       <c r="R89" s="2" t="inlineStr">
         <is>
-          <t>Emotional auto-tune as confession. Vibe over lyrical architecture.</t>
+          <t>Joyful complexity. Gospel cadences and Chicago love letters.</t>
         </is>
       </c>
     </row>
@@ -7137,17 +7137,17 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Chance the Rapper</t>
+          <t>Earl Sweatshirt</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -7157,39 +7157,39 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Abstract</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Chicago Gospel Rap</t>
+          <t>Odd Future/Boom Bap</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Tan Cressida</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>2013</v>
-      </c>
-      <c r="J90" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K90" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L90" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M90" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N90" s="12" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J90" s="12" t="n">
         <v>9</v>
       </c>
+      <c r="K90" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L90" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M90" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="N90" s="11" t="n">
+        <v>8</v>
+      </c>
       <c r="O90" s="6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="P90" s="7" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
       <c r="Q90" s="2" t="inlineStr"/>
       <c r="R90" s="2" t="inlineStr">
         <is>
-          <t>Joyful complexity. Gospel cadences and Chicago love letters.</t>
+          <t>Compression and grief as poetics. Dense abstract imagery.</t>
         </is>
       </c>
     </row>
@@ -7209,17 +7209,17 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>MM</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Earl Sweatshirt</t>
+          <t>Meek Mill</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>Philly</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -7229,39 +7229,39 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Abstract</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Odd Future/Boom Bap</t>
+          <t>Philly Trap</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Tan Cressida</t>
+          <t>Maybach Music</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>2010</v>
-      </c>
-      <c r="J91" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="K91" s="12" t="n">
-        <v>9</v>
+        <v>2012</v>
+      </c>
+      <c r="J91" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K91" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="L91" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="M91" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="N91" s="11" t="n">
-        <v>8</v>
+      <c r="M91" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N91" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="O91" s="6" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="P91" s="7" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
       <c r="Q91" s="2" t="inlineStr"/>
       <c r="R91" s="2" t="inlineStr">
         <is>
-          <t>Compression and grief as poetics. Dense abstract imagery.</t>
+          <t>Visceral urgency. Philadelphia streets in raw kinetic delivery.</t>
         </is>
       </c>
     </row>
@@ -7281,17 +7281,17 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>MM</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Meek Mill</t>
+          <t>A$AP Rocky</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Philly</t>
+          <t>NYC</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -7301,39 +7301,39 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Philly Trap</t>
+          <t>Cloud Rap/Fashion</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Maybach Music</t>
+          <t>A$AP/RCA</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="J92" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="K92" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L92" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M92" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N92" s="9" t="n">
-        <v>6</v>
+      <c r="K92" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L92" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M92" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N92" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="O92" s="6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="P92" s="7" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
       <c r="Q92" s="2" t="inlineStr"/>
       <c r="R92" s="2" t="inlineStr">
         <is>
-          <t>Visceral urgency. Philadelphia streets in raw kinetic delivery.</t>
+          <t>Aesthetic as content. Flow and texture over lyrical substance.</t>
         </is>
       </c>
     </row>
@@ -7353,12 +7353,12 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>NM</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>A$AP Rocky</t>
+          <t>Nicki Minaj</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -7373,39 +7373,39 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Cloud Rap/Fashion</t>
+          <t>Pop Rap/Dancehall</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>A$AP/RCA</t>
+          <t>Young Money</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>2011</v>
-      </c>
-      <c r="J93" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K93" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L93" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="M93" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N93" s="8" t="n">
-        <v>5</v>
+        <v>2010</v>
+      </c>
+      <c r="J93" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K93" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L93" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M93" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N93" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="O93" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P93" s="7" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
       <c r="Q93" s="2" t="inlineStr"/>
       <c r="R93" s="2" t="inlineStr">
         <is>
-          <t>Aesthetic as content. Flow and texture over lyrical substance.</t>
+          <t>Technical precision and alter-ego theatrics. 'Monster' verse.</t>
         </is>
       </c>
     </row>
@@ -7425,17 +7425,17 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>NM</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Nicki Minaj</t>
+          <t>Vince Staples</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -7445,36 +7445,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Political</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Pop Rap/Dancehall</t>
+          <t>West Coast Minimalism</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Young Money</t>
+          <t>Def Jam</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>2010</v>
-      </c>
-      <c r="J94" s="12" t="n">
+        <v>2012</v>
+      </c>
+      <c r="J94" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K94" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L94" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M94" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N94" s="12" t="n">
         <v>9</v>
-      </c>
-      <c r="K94" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L94" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M94" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N94" s="10" t="n">
-        <v>7</v>
       </c>
       <c r="O94" s="6" t="n">
         <v>8</v>
@@ -7487,7 +7487,7 @@
       <c r="Q94" s="2" t="inlineStr"/>
       <c r="R94" s="2" t="inlineStr">
         <is>
-          <t>Technical precision and alter-ego theatrics. 'Monster' verse.</t>
+          <t>Deadpan sociologist. Minimalist language doing maximum structural work.</t>
         </is>
       </c>
     </row>
@@ -7497,17 +7497,17 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>BK2</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Vince Staples</t>
+          <t>Big K.R.I.T.</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Political</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>West Coast Minimalism</t>
+          <t>Mississippi Soul Rap</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7531,10 +7531,10 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>2012</v>
-      </c>
-      <c r="J95" s="10" t="n">
-        <v>7</v>
+        <v>2010</v>
+      </c>
+      <c r="J95" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="K95" s="11" t="n">
         <v>8</v>
@@ -7545,8 +7545,8 @@
       <c r="M95" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="N95" s="12" t="n">
-        <v>9</v>
+      <c r="N95" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="O95" s="6" t="n">
         <v>8</v>
@@ -7559,7 +7559,7 @@
       <c r="Q95" s="2" t="inlineStr"/>
       <c r="R95" s="2" t="inlineStr">
         <is>
-          <t>Deadpan sociologist. Minimalist language doing maximum structural work.</t>
+          <t>Mississippi throwback futurist. Southern soul and lyrical ambition fused.</t>
         </is>
       </c>
     </row>
@@ -7569,17 +7569,17 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>BK2</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Big K.R.I.T.</t>
+          <t>Run The Jewels</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -7589,39 +7589,39 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Political</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Mississippi Soul Rap</t>
+          <t>Industrial Boom Bap</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Def Jam</t>
+          <t>Mass Appeal</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="J96" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="K96" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L96" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M96" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N96" s="11" t="n">
-        <v>8</v>
+      <c r="K96" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L96" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M96" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="N96" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="O96" s="6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="P96" s="7" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
       <c r="Q96" s="2" t="inlineStr"/>
       <c r="R96" s="2" t="inlineStr">
         <is>
-          <t>Mississippi throwback futurist. Southern soul and lyrical ambition fused.</t>
+          <t>El-P and Killer Mike. Most politically urgent rap duo since PE.</t>
         </is>
       </c>
     </row>
@@ -7641,17 +7641,17 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>KM</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Run The Jewels</t>
+          <t>Killer Mike</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -7666,34 +7666,34 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Industrial Boom Bap</t>
+          <t>Atlanta Boom Bap</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Mass Appeal</t>
+          <t>SMC Recordings</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>2013</v>
+        <v>2003</v>
       </c>
       <c r="J97" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="K97" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L97" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M97" s="12" t="n">
-        <v>9</v>
+      <c r="K97" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L97" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M97" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="N97" s="12" t="n">
         <v>9</v>
       </c>
       <c r="O97" s="6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P97" s="7" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
       <c r="Q97" s="2" t="inlineStr"/>
       <c r="R97" s="2" t="inlineStr">
         <is>
-          <t>El-P and Killer Mike. Most politically urgent rap duo since PE.</t>
+          <t>RTJ's political conscience. Atlanta's most morally serious MC.</t>
         </is>
       </c>
     </row>
@@ -7713,17 +7713,17 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>KM</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Killer Mike</t>
+          <t>Freddie Gibbs</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -7733,21 +7733,21 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Political</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Boom Bap</t>
+          <t>Gangsta Boom Bap</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>SMC Recordings</t>
+          <t>ESGN</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="J98" s="11" t="n">
         <v>8</v>
@@ -7755,17 +7755,17 @@
       <c r="K98" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L98" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M98" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N98" s="12" t="n">
+      <c r="L98" s="12" t="n">
         <v>9</v>
       </c>
+      <c r="M98" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N98" s="10" t="n">
+        <v>7</v>
+      </c>
       <c r="O98" s="6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="P98" s="7" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
       <c r="Q98" s="2" t="inlineStr"/>
       <c r="R98" s="2" t="inlineStr">
         <is>
-          <t>RTJ's political conscience. Atlanta's most morally serious MC.</t>
+          <t>Gary Indiana's finest. Technical gangsta rap with jazz-rap production.</t>
         </is>
       </c>
     </row>
@@ -7785,17 +7785,17 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Freddie Gibbs</t>
+          <t>Migos</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -7805,39 +7805,39 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Trap/Drill</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Gangsta Boom Bap</t>
+          <t>Atlanta Triplet Trap</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>ESGN</t>
+          <t>Quality Control</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>2004</v>
-      </c>
-      <c r="J99" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K99" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L99" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M99" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N99" s="10" t="n">
-        <v>7</v>
+        <v>2013</v>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M99" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N99" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="O99" s="6" t="n">
-        <v>7.8</v>
+        <v>4</v>
       </c>
       <c r="P99" s="7" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
       <c r="Q99" s="2" t="inlineStr"/>
       <c r="R99" s="2" t="inlineStr">
         <is>
-          <t>Gary Indiana's finest. Technical gangsta rap with jazz-rap production.</t>
+          <t>Triplet flow inventors. Cultural influence far exceeds lyrical complexity.</t>
         </is>
       </c>
     </row>
@@ -7857,17 +7857,17 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>BI2</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Migos</t>
+          <t>Big Sean</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -7877,49 +7877,53 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Trap/Drill</t>
+          <t>Party/Pop</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Triplet Trap</t>
+          <t>Detroit Pop Rap</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>G.O.O.D.</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>2013</v>
-      </c>
-      <c r="J100" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K100" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="L100" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M100" s="8" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J100" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K100" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L100" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M100" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N100" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N100" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="O100" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="P100" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q100" s="2" t="inlineStr"/>
+        <v>5.8</v>
+      </c>
+      <c r="P100" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>Commercial success; critical reception mixed; thin formal analysis</t>
+        </is>
+      </c>
       <c r="R100" s="2" t="inlineStr">
         <is>
-          <t>Triplet flow inventors. Cultural influence far exceeds lyrical complexity.</t>
+          <t>Detroit MC. Punchlines over conceptual depth. 'One Man Can Change The World'.</t>
         </is>
       </c>
     </row>
@@ -7929,17 +7933,17 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>BI2</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Big Sean</t>
+          <t>Tierra Whack</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>Philly</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -7949,39 +7953,39 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Party/Pop</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Detroit Pop Rap</t>
+          <t>Experimental Pop Rap</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>G.O.O.D.</t>
+          <t>Interscope</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>2011</v>
-      </c>
-      <c r="J101" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K101" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L101" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M101" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N101" s="8" t="n">
-        <v>5</v>
+        <v>2018</v>
+      </c>
+      <c r="J101" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K101" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L101" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M101" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N101" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="O101" s="6" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="P101" s="14" t="inlineStr">
         <is>
@@ -7990,12 +7994,12 @@
       </c>
       <c r="Q101" s="2" t="inlineStr">
         <is>
-          <t>Commercial success; critical reception mixed; thin formal analysis</t>
+          <t>Breakout 2018; critical buzz high but career short; scoring may shift</t>
         </is>
       </c>
       <c r="R101" s="2" t="inlineStr">
         <is>
-          <t>Detroit MC. Punchlines over conceptual depth. 'One Man Can Change The World'.</t>
+          <t>'Whack World' — 15 one-minute songs as unified concept. Wholly original.</t>
         </is>
       </c>
     </row>
@@ -8005,17 +8009,17 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Tierra Whack</t>
+          <t>Noname</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Philly</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -8025,53 +8029,49 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Experimental Pop Rap</t>
+          <t>Chicago Jazz Rap</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Interscope</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="J102" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K102" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L102" s="10" t="n">
-        <v>7</v>
+        <v>2016</v>
+      </c>
+      <c r="J102" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K102" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L102" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="M102" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="N102" s="11" t="n">
-        <v>8</v>
+      <c r="N102" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="O102" s="6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="P102" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q102" s="2" t="inlineStr">
-        <is>
-          <t>Breakout 2018; critical buzz high but career short; scoring may shift</t>
-        </is>
-      </c>
+        <v>8.4</v>
+      </c>
+      <c r="P102" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
       <c r="R102" s="2" t="inlineStr">
         <is>
-          <t>'Whack World' — 15 one-minute songs as unified concept. Wholly original.</t>
+          <t>Chicago's most literary voice. Jazz cadences and political awakening.</t>
         </is>
       </c>
     </row>
@@ -8081,12 +8081,12 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>SZ</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Noname</t>
+          <t>Saba</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -8106,34 +8106,34 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Chicago Jazz Rap</t>
+          <t>Chicago Boom Bap</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Pivot Gang</t>
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="J103" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="K103" s="12" t="n">
+      <c r="K103" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L103" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L103" s="11" t="n">
-        <v>8</v>
-      </c>
       <c r="M103" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="N103" s="12" t="n">
-        <v>9</v>
+      <c r="N103" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="O103" s="6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P103" s="7" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
       <c r="Q103" s="2" t="inlineStr"/>
       <c r="R103" s="2" t="inlineStr">
         <is>
-          <t>Chicago's most literary voice. Jazz cadences and political awakening.</t>
+          <t>'CARE FOR ME' — grief and Chicago violence as devastating concept album.</t>
         </is>
       </c>
     </row>
@@ -8153,12 +8153,12 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>SZ</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Saba</t>
+          <t>Danny Brown</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -8173,33 +8173,33 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Chicago Boom Bap</t>
+          <t>Detroit Noise Rap</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Pivot Gang</t>
+          <t>Fool's Gold</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="J104" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="K104" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L104" s="12" t="n">
+      <c r="K104" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="M104" s="11" t="n">
-        <v>8</v>
+      <c r="L104" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M104" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="N104" s="11" t="n">
         <v>8</v>
@@ -8215,7 +8215,7 @@
       <c r="Q104" s="2" t="inlineStr"/>
       <c r="R104" s="2" t="inlineStr">
         <is>
-          <t>'CARE FOR ME' — grief and Chicago violence as devastating concept album.</t>
+          <t>Detroit's avant-garde MC. Schizophrenic flows and surreal imagery.</t>
         </is>
       </c>
     </row>
@@ -8225,12 +8225,12 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Danny Brown</t>
+          <t>Mac Miller</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -8245,39 +8245,39 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Detroit Noise Rap</t>
+          <t>Pittsburgh Soul Rap</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Fool's Gold</t>
+          <t>Rostrum</t>
         </is>
       </c>
       <c r="I105" s="2" t="n">
         <v>2010</v>
       </c>
-      <c r="J105" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K105" s="12" t="n">
-        <v>9</v>
+      <c r="J105" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K105" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="L105" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="M105" s="12" t="n">
-        <v>9</v>
+      <c r="M105" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="N105" s="11" t="n">
         <v>8</v>
       </c>
       <c r="O105" s="6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="P105" s="7" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
       <c r="Q105" s="2" t="inlineStr"/>
       <c r="R105" s="2" t="inlineStr">
         <is>
-          <t>Detroit's avant-garde MC. Schizophrenic flows and surreal imagery.</t>
+          <t>Arc from frat-rap to deeply personal jazz introspection. 'Swimming' a peak.</t>
         </is>
       </c>
     </row>
@@ -8297,17 +8297,17 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>JD2</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Mac Miller</t>
+          <t>JID</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -8322,44 +8322,48 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Pittsburgh Soul Rap</t>
+          <t>Atlanta Jazz Rap</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Rostrum</t>
+          <t>Dreamville</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>2010</v>
-      </c>
-      <c r="J106" s="10" t="n">
-        <v>7</v>
+        <v>2017</v>
+      </c>
+      <c r="J106" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="K106" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L106" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M106" s="10" t="n">
-        <v>7</v>
+      <c r="L106" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M106" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="N106" s="11" t="n">
         <v>8</v>
       </c>
       <c r="O106" s="6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="P106" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q106" s="2" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="P106" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr">
+        <is>
+          <t>Late-decade emergence; critical acclaim building; may rescore upward</t>
+        </is>
+      </c>
       <c r="R106" s="2" t="inlineStr">
         <is>
-          <t>Arc from frat-rap to deeply personal jazz introspection. 'Swimming' a peak.</t>
+          <t>Atlanta's most technically gifted rapper. 'DiCaprio 2' showed full potential.</t>
         </is>
       </c>
     </row>
@@ -8369,17 +8373,17 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>JD2</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>JID</t>
+          <t>Cardi B</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>NYC</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -8389,53 +8393,49 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Party/Pop</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Jazz Rap</t>
+          <t>Bronx Trap Pop</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Dreamville</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="J107" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="K107" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L107" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M107" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N107" s="11" t="n">
-        <v>8</v>
+        <v>2018</v>
+      </c>
+      <c r="J107" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K107" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L107" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M107" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N107" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="O107" s="6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="P107" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q107" s="2" t="inlineStr">
-        <is>
-          <t>Late-decade emergence; critical acclaim building; may rescore upward</t>
-        </is>
-      </c>
+        <v>5.6</v>
+      </c>
+      <c r="P107" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
       <c r="R107" s="2" t="inlineStr">
         <is>
-          <t>Atlanta's most technically gifted rapper. 'DiCaprio 2' showed full potential.</t>
+          <t>Unfiltered Bronx personality. Cultural force exceeds lyrical architecture.</t>
         </is>
       </c>
     </row>
@@ -8445,69 +8445,73 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Cardi B</t>
+          <t>Polo G</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Party/Pop</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Bronx Trap Pop</t>
+          <t>Chicago Melodic Trap</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Columbia</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="J108" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K108" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L108" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M108" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N108" s="5" t="n">
-        <v>4</v>
+        <v>2019</v>
+      </c>
+      <c r="J108" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K108" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L108" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M108" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N108" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="O108" s="6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="P108" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q108" s="2" t="inlineStr"/>
+        <v>7.2</v>
+      </c>
+      <c r="P108" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>Recent emergence; trajectory still forming</t>
+        </is>
+      </c>
       <c r="R108" s="2" t="inlineStr">
         <is>
-          <t>Unfiltered Bronx personality. Cultural force exceeds lyrical architecture.</t>
+          <t>Chicago's introspective melodic trap voice. Melancholy street memoir.</t>
         </is>
       </c>
     </row>
@@ -8517,17 +8521,17 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>RW</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Polo G</t>
+          <t>Rod Wave</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -8537,39 +8541,39 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Chicago Melodic Trap</t>
+          <t>Florida Soul Trap</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Columbia</t>
+          <t>Alamo</t>
         </is>
       </c>
       <c r="I109" s="2" t="n">
         <v>2019</v>
       </c>
-      <c r="J109" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K109" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L109" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M109" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N109" s="10" t="n">
-        <v>7</v>
+      <c r="J109" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K109" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L109" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M109" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N109" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="O109" s="6" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="P109" s="14" t="inlineStr">
         <is>
@@ -8578,12 +8582,12 @@
       </c>
       <c r="Q109" s="2" t="inlineStr">
         <is>
-          <t>Recent emergence; trajectory still forming</t>
+          <t>Recent; critical consensus not yet settled</t>
         </is>
       </c>
       <c r="R109" s="2" t="inlineStr">
         <is>
-          <t>Chicago's introspective melodic trap voice. Melancholy street memoir.</t>
+          <t>Emotional vulnerability over technical precision. Florida pain made universal.</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8597,12 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Rod Wave</t>
+          <t>Doechii</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -8618,34 +8622,34 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Florida Soul Trap</t>
+          <t>Tampa Art Rap</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Alamo</t>
+          <t>Capitol</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>2019</v>
-      </c>
-      <c r="J110" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K110" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L110" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M110" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N110" s="8" t="n">
-        <v>5</v>
+        <v>2021</v>
+      </c>
+      <c r="J110" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K110" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L110" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M110" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N110" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="O110" s="6" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P110" s="14" t="inlineStr">
         <is>
@@ -8654,12 +8658,12 @@
       </c>
       <c r="Q110" s="2" t="inlineStr">
         <is>
-          <t>Recent; critical consensus not yet settled</t>
+          <t>Breakout recent; scoring may shift upward as body of work grows</t>
         </is>
       </c>
       <c r="R110" s="2" t="inlineStr">
         <is>
-          <t>Emotional vulnerability over technical precision. Florida pain made universal.</t>
+          <t>Tampa's theatrical polymath. Technical fire meets conceptual daring.</t>
         </is>
       </c>
     </row>
@@ -8669,12 +8673,12 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>GG2</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Doechii</t>
+          <t>GloRilla</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -8689,53 +8693,53 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Party/Pop</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Tampa Art Rap</t>
+          <t>Memphis Trap</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Capitol</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>2021</v>
-      </c>
-      <c r="J111" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K111" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L111" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M111" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N111" s="12" t="n">
-        <v>9</v>
+        <v>2022</v>
+      </c>
+      <c r="J111" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K111" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L111" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M111" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N111" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="O111" s="6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="P111" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
+        <v>4.8</v>
+      </c>
+      <c r="P111" s="15" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
         <is>
-          <t>Breakout recent; scoring may shift upward as body of work grows</t>
+          <t>Very recent; limited critical record; commercial impact clear</t>
         </is>
       </c>
       <c r="R111" s="2" t="inlineStr">
         <is>
-          <t>Tampa's theatrical polymath. Technical fire meets conceptual daring.</t>
+          <t>Memphis energy, unfiltered personality. New Southern feminism in party form.</t>
         </is>
       </c>
     </row>
@@ -8745,12 +8749,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>GG2</t>
+          <t>GN</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>GloRilla</t>
+          <t>Gunna</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -8765,53 +8769,53 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Party/Pop</t>
+          <t>Trap/Drill</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Memphis Trap</t>
+          <t>Atlanta Melodic Trap</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>Young Stoner Life</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>2022</v>
-      </c>
-      <c r="J112" s="8" t="n">
-        <v>5</v>
+        <v>2018</v>
+      </c>
+      <c r="J112" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="K112" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="L112" s="8" t="n">
-        <v>5</v>
+      <c r="L112" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="M112" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N112" s="5" t="n">
-        <v>4</v>
+      <c r="N112" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="O112" s="6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P112" s="15" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>4.2</v>
+      </c>
+      <c r="P112" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
         <is>
-          <t>Very recent; limited critical record; commercial impact clear</t>
+          <t>Significant commercial presence; thin critical analysis</t>
         </is>
       </c>
       <c r="R112" s="2" t="inlineStr">
         <is>
-          <t>Memphis energy, unfiltered personality. New Southern feminism in party form.</t>
+          <t>Melodic luxury trap. Vibe and aesthetic are the art.</t>
         </is>
       </c>
     </row>
@@ -8821,12 +8825,12 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>GN</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Gunna</t>
+          <t>Lil Baby</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -8841,39 +8845,39 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Trap/Drill</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Melodic Trap</t>
+          <t>Atlanta Slime Trap</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Young Stoner Life</t>
+          <t>Quality Control</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="J113" s="5" t="n">
-        <v>4</v>
+        <v>2017</v>
+      </c>
+      <c r="J113" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="K113" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="L113" s="5" t="n">
-        <v>4</v>
+      <c r="L113" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="M113" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N113" s="3" t="n">
-        <v>3</v>
+      <c r="N113" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="O113" s="6" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="P113" s="14" t="inlineStr">
         <is>
@@ -8882,12 +8886,12 @@
       </c>
       <c r="Q113" s="2" t="inlineStr">
         <is>
-          <t>Significant commercial presence; thin critical analysis</t>
+          <t>Recent; commercial dominance clear; critical depth forming</t>
         </is>
       </c>
       <c r="R113" s="2" t="inlineStr">
         <is>
-          <t>Melodic luxury trap. Vibe and aesthetic are the art.</t>
+          <t>Authentic street narrator. Storytelling grounded in lived experience.</t>
         </is>
       </c>
     </row>
@@ -8897,17 +8901,17 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>BT</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Lil Baby</t>
+          <t>Benny the Butcher</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>NYC</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -8922,48 +8926,44 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Slime Trap</t>
+          <t>Buffalo Boom Bap</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>Griselda</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="J114" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K114" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L114" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M114" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N114" s="8" t="n">
-        <v>5</v>
+        <v>2012</v>
+      </c>
+      <c r="J114" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K114" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L114" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M114" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N114" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="O114" s="6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="P114" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q114" s="2" t="inlineStr">
-        <is>
-          <t>Recent; commercial dominance clear; critical depth forming</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="P114" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q114" s="2" t="inlineStr"/>
       <c r="R114" s="2" t="inlineStr">
         <is>
-          <t>Authentic street narrator. Storytelling grounded in lived experience.</t>
+          <t>Griselda's lyrical backbone. Buffalo street narratives with East Coast precision.</t>
         </is>
       </c>
     </row>
@@ -8973,17 +8973,17 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Benny the Butcher</t>
+          <t>Offset</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -8993,49 +8993,53 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Trap/Drill</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Buffalo Boom Bap</t>
+          <t>Migos Solo Trap</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Griselda</t>
+          <t>Quality Control</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>2012</v>
-      </c>
-      <c r="J115" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K115" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L115" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M115" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N115" s="10" t="n">
-        <v>7</v>
+        <v>2017</v>
+      </c>
+      <c r="J115" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K115" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L115" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M115" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N115" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="O115" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="P115" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q115" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="P115" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q115" s="2" t="inlineStr">
+        <is>
+          <t>Solo career emerging post-Migos; scoring tentative</t>
+        </is>
+      </c>
       <c r="R115" s="2" t="inlineStr">
         <is>
-          <t>Griselda's lyrical backbone. Buffalo street narratives with East Coast precision.</t>
+          <t>Migos' most lyrical member. Flow variation and delivery standout in trap context.</t>
         </is>
       </c>
     </row>
@@ -9045,12 +9049,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>OM</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Offset</t>
+          <t>Kenny Mason</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -9065,53 +9069,53 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>Trap/Drill</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Migos Solo Trap</t>
+          <t>Atlanta Punk Rap</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>RCA Records</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="J116" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K116" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L116" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="M116" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N116" s="5" t="n">
-        <v>4</v>
+        <v>2019</v>
+      </c>
+      <c r="J116" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K116" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L116" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M116" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N116" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="O116" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="P116" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
+        <v>7</v>
+      </c>
+      <c r="P116" s="15" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
         <is>
-          <t>Solo career emerging post-Migos; scoring tentative</t>
+          <t>Limited documentation; critical buzz building in underground circles</t>
         </is>
       </c>
       <c r="R116" s="2" t="inlineStr">
         <is>
-          <t>Migos' most lyrical member. Flow variation and delivery standout in trap context.</t>
+          <t>Atlanta's punk-rap hybrid. Unconventional tonal range.</t>
         </is>
       </c>
     </row>
@@ -9121,12 +9125,12 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Kenny Mason</t>
+          <t>Latto</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -9141,53 +9145,53 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Punk Rap</t>
+          <t>Atlanta Female Trap</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>RCA Records</t>
+          <t>RCA</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
         <v>2019</v>
       </c>
-      <c r="J117" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K117" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L117" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M117" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N117" s="10" t="n">
-        <v>7</v>
+      <c r="J117" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K117" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L117" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M117" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N117" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="O117" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="P117" s="15" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>5.8</v>
+      </c>
+      <c r="P117" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
         <is>
-          <t>Limited documentation; critical buzz building in underground circles</t>
+          <t>Recent; commercial trajectory clearer than critical consensus</t>
         </is>
       </c>
       <c r="R117" s="2" t="inlineStr">
         <is>
-          <t>Atlanta's punk-rap hybrid. Unconventional tonal range.</t>
+          <t>Atlanta's female trap voice. Technical skill often underestimated.</t>
         </is>
       </c>
     </row>
@@ -9197,17 +9201,17 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>SR</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Latto</t>
+          <t>Smino</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -9217,39 +9221,39 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Female Trap</t>
+          <t>St. Louis Jazz Rap</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>RCA</t>
+          <t>Zero Fatigue</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>2019</v>
-      </c>
-      <c r="J118" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K118" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L118" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M118" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N118" s="8" t="n">
-        <v>5</v>
+        <v>2017</v>
+      </c>
+      <c r="J118" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K118" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L118" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M118" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N118" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="O118" s="6" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="P118" s="14" t="inlineStr">
         <is>
@@ -9258,12 +9262,12 @@
       </c>
       <c r="Q118" s="2" t="inlineStr">
         <is>
-          <t>Recent; commercial trajectory clearer than critical consensus</t>
+          <t>Critical darling in jazz-rap circles; broader recognition still forming</t>
         </is>
       </c>
       <c r="R118" s="2" t="inlineStr">
         <is>
-          <t>Atlanta's female trap voice. Technical skill often underestimated.</t>
+          <t>St. Louis's jazz-rap hybrid. Melodic and rhythmic sophistication.</t>
         </is>
       </c>
     </row>
@@ -9273,17 +9277,17 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>PZ</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Smino</t>
+          <t>Pusha T</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>NYC</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -9293,27 +9297,27 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>St. Louis Jazz Rap</t>
+          <t>Coke Rap Boom Bap</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Zero Fatigue</t>
+          <t>G.O.O.D.</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="J119" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K119" s="11" t="n">
-        <v>8</v>
+        <v>2002</v>
+      </c>
+      <c r="J119" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K119" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="L119" s="10" t="n">
         <v>7</v>
@@ -9327,19 +9331,15 @@
       <c r="O119" s="6" t="n">
         <v>7.4</v>
       </c>
-      <c r="P119" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q119" s="2" t="inlineStr">
-        <is>
-          <t>Critical darling in jazz-rap circles; broader recognition still forming</t>
-        </is>
-      </c>
+      <c r="P119" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q119" s="2" t="inlineStr"/>
       <c r="R119" s="2" t="inlineStr">
         <is>
-          <t>St. Louis's jazz-rap hybrid. Melodic and rhythmic sophistication.</t>
+          <t>Cocaine rap's Rembrandt. 'Daytona' — maximum density, minimum waste.</t>
         </is>
       </c>
     </row>
@@ -9349,17 +9349,17 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>PZ</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Pusha T</t>
+          <t>Tyler the Creator</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -9369,39 +9369,39 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Coke Rap Boom Bap</t>
+          <t>Odd Future/Orchestral</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>G.O.O.D.</t>
+          <t>Columbia</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>2002</v>
-      </c>
-      <c r="J120" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K120" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L120" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M120" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N120" s="10" t="n">
-        <v>7</v>
+        <v>2009</v>
+      </c>
+      <c r="J120" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K120" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L120" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M120" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="N120" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="O120" s="6" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="P120" s="7" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
       <c r="Q120" s="2" t="inlineStr"/>
       <c r="R120" s="2" t="inlineStr">
         <is>
-          <t>Cocaine rap's Rembrandt. 'Daytona' — maximum density, minimum waste.</t>
+          <t>'Igor' and 'Call Me If You Get Lost' — producer-auteur. Concept album mastery.</t>
         </is>
       </c>
     </row>
@@ -9421,17 +9421,17 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>AB2</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Tyler the Creator</t>
+          <t>Armand Hammer</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>NYC</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -9441,49 +9441,53 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Abstract</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Odd Future/Orchestral</t>
+          <t>Abstract Boom Bap</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>Columbia</t>
+          <t>Backwoodz</t>
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>2009</v>
-      </c>
-      <c r="J121" s="10" t="n">
-        <v>7</v>
+        <v>2013</v>
+      </c>
+      <c r="J121" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="K121" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L121" s="11" t="n">
-        <v>8</v>
+      <c r="L121" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="M121" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="N121" s="12" t="n">
-        <v>9</v>
+      <c r="N121" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="O121" s="6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="P121" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q121" s="2" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="P121" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q121" s="2" t="inlineStr">
+        <is>
+          <t>Critical underground darling; thin mainstream documentation</t>
+        </is>
+      </c>
       <c r="R121" s="2" t="inlineStr">
         <is>
-          <t>'Igor' and 'Call Me If You Get Lost' — producer-auteur. Concept album mastery.</t>
+          <t>billy woods + ELUCID. The most demanding abstract rap being made today.</t>
         </is>
       </c>
     </row>
@@ -9493,17 +9497,17 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>AB2</t>
+          <t>ZE</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Armand Hammer</t>
+          <t>Zack Fox</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -9518,48 +9522,48 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Abstract Boom Bap</t>
+          <t>Comedy-Abstract Rap</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Backwoodz</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>2013</v>
-      </c>
-      <c r="J122" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K122" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L122" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M122" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="N122" s="11" t="n">
-        <v>8</v>
+        <v>2020</v>
+      </c>
+      <c r="J122" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K122" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L122" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M122" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N122" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="O122" s="6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="P122" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
+        <v>6.4</v>
+      </c>
+      <c r="P122" s="15" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
         <is>
-          <t>Critical underground darling; thin mainstream documentation</t>
+          <t>Very recent; extremely limited critical record</t>
         </is>
       </c>
       <c r="R122" s="2" t="inlineStr">
         <is>
-          <t>billy woods + ELUCID. The most demanding abstract rap being made today.</t>
+          <t>Comedy-meets-rap. Formally interesting but body of work too small to score confidently.</t>
         </is>
       </c>
     </row>
@@ -9569,17 +9573,17 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>ZE</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Zack Fox</t>
+          <t>Lil Durk</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -9589,53 +9593,53 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Abstract</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Comedy-Abstract Rap</t>
+          <t>Chicago Melodic Trap</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Only the Family</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="J123" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K123" s="10" t="n">
-        <v>7</v>
+        <v>2013</v>
+      </c>
+      <c r="J123" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K123" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="L123" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="M123" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N123" s="9" t="n">
-        <v>6</v>
+      <c r="M123" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N123" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="O123" s="6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="P123" s="15" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>5.2</v>
+      </c>
+      <c r="P123" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
         <is>
-          <t>Very recent; extremely limited critical record</t>
+          <t>Commercial dominance clear; critical depth limited</t>
         </is>
       </c>
       <c r="R123" s="2" t="inlineStr">
         <is>
-          <t>Comedy-meets-rap. Formally interesting but body of work too small to score confidently.</t>
+          <t>Chicago drill's most commercially consistent voice.</t>
         </is>
       </c>
     </row>
@@ -9645,17 +9649,17 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>KS2</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Lil Durk</t>
+          <t>Kodak Black</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -9670,16 +9674,16 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Chicago Melodic Trap</t>
+          <t>Florida Trap</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Only the Family</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="J124" s="8" t="n">
         <v>5</v>
@@ -9693,12 +9697,12 @@
       <c r="M124" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N124" s="8" t="n">
+      <c r="N124" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O124" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="O124" s="6" t="n">
-        <v>5.2</v>
-      </c>
       <c r="P124" s="14" t="inlineStr">
         <is>
           <t>M</t>
@@ -9706,12 +9710,12 @@
       </c>
       <c r="Q124" s="2" t="inlineStr">
         <is>
-          <t>Commercial dominance clear; critical depth limited</t>
+          <t>Commercial success; thin critical framework; behavior clouds reception</t>
         </is>
       </c>
       <c r="R124" s="2" t="inlineStr">
         <is>
-          <t>Chicago drill's most commercially consistent voice.</t>
+          <t>Florida trap's most distinctive voice. Rough-edged regional authenticity.</t>
         </is>
       </c>
     </row>
@@ -9721,12 +9725,12 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>KS2</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Kodak Black</t>
+          <t>Rapsody</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -9741,53 +9745,49 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Florida Trap</t>
+          <t>North Carolina Soul Rap</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Jamla</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>2014</v>
-      </c>
-      <c r="J125" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K125" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L125" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M125" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N125" s="5" t="n">
-        <v>4</v>
+        <v>2010</v>
+      </c>
+      <c r="J125" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K125" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L125" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M125" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N125" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="O125" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="P125" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q125" s="2" t="inlineStr">
-        <is>
-          <t>Commercial success; thin critical framework; behavior clouds reception</t>
-        </is>
-      </c>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="P125" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q125" s="2" t="inlineStr"/>
       <c r="R125" s="2" t="inlineStr">
         <is>
-          <t>Florida trap's most distinctive voice. Rough-edged regional authenticity.</t>
+          <t>North Carolina's most complete female MC. Lyrical depth rivals any peer.</t>
         </is>
       </c>
     </row>
@@ -9797,12 +9797,12 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>MF2</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Rapsody</t>
+          <t>Mavi</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -9817,49 +9817,53 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Abstract</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>North Carolina Soul Rap</t>
+          <t>Underground Abstract</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Jamla</t>
+          <t>Secretly Canadian</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>2010</v>
-      </c>
-      <c r="J126" s="11" t="n">
-        <v>8</v>
+        <v>2019</v>
+      </c>
+      <c r="J126" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="K126" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L126" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M126" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N126" s="12" t="n">
-        <v>9</v>
+      <c r="L126" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M126" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N126" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="O126" s="6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="P126" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q126" s="2" t="inlineStr"/>
+        <v>7.2</v>
+      </c>
+      <c r="P126" s="15" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q126" s="2" t="inlineStr">
+        <is>
+          <t>Very limited critical documentation; underground following only</t>
+        </is>
+      </c>
       <c r="R126" s="2" t="inlineStr">
         <is>
-          <t>North Carolina's most complete female MC. Lyrical depth rivals any peer.</t>
+          <t>Charlotte underground. Dense introspective abstract rap. Watch this space.</t>
         </is>
       </c>
     </row>
@@ -9869,47 +9873,47 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>MF2</t>
+          <t>XP</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Mavi</t>
+          <t>Xzibit</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Abstract</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Underground Abstract</t>
+          <t>Hard West Coast</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>Secretly Canadian</t>
+          <t>Loud/Columbia</t>
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>2019</v>
+        <v>1996</v>
       </c>
       <c r="J127" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="K127" s="11" t="n">
-        <v>8</v>
+      <c r="K127" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="L127" s="10" t="n">
         <v>7</v>
@@ -9917,25 +9921,25 @@
       <c r="M127" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="N127" s="10" t="n">
-        <v>7</v>
+      <c r="N127" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="O127" s="6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="P127" s="15" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>6.8</v>
+      </c>
+      <c r="P127" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
         <is>
-          <t>Very limited critical documentation; underground following only</t>
+          <t>Well-known but limited formal critical analysis</t>
         </is>
       </c>
       <c r="R127" s="2" t="inlineStr">
         <is>
-          <t>Charlotte underground. Dense introspective abstract rap. Watch this space.</t>
+          <t>West Coast boom bap craftsman. More respected by peers than critics.</t>
         </is>
       </c>
     </row>
@@ -9945,59 +9949,59 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>XP</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Xzibit</t>
+          <t>Saweetie</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>Bay Area</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Late 90s</t>
+          <t>2020s</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Party/Pop</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Hard West Coast</t>
+          <t>Trap Pop</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Loud/Columbia</t>
+          <t>Warner</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>1996</v>
-      </c>
-      <c r="J128" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K128" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L128" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M128" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N128" s="9" t="n">
-        <v>6</v>
+        <v>2018</v>
+      </c>
+      <c r="J128" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K128" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L128" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M128" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N128" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="O128" s="6" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="P128" s="14" t="inlineStr">
         <is>
@@ -10006,12 +10010,12 @@
       </c>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>Well-known but limited formal critical analysis</t>
+          <t>Recent commercial success; limited critical depth</t>
         </is>
       </c>
       <c r="R128" s="2" t="inlineStr">
         <is>
-          <t>West Coast boom bap craftsman. More respected by peers than critics.</t>
+          <t>Bay Area trap-pop. Ice Princess persona over lyrical substance.</t>
         </is>
       </c>
     </row>
@@ -10021,17 +10025,17 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Saweetie</t>
+          <t>City Girls</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -10046,19 +10050,19 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Trap Pop</t>
+          <t>Miami Trap</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Warner</t>
+          <t>Quality Control/Motown</t>
         </is>
       </c>
       <c r="I129" s="2" t="n">
         <v>2018</v>
       </c>
-      <c r="J129" s="8" t="n">
-        <v>5</v>
+      <c r="J129" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="K129" s="8" t="n">
         <v>5</v>
@@ -10073,21 +10077,21 @@
         <v>4</v>
       </c>
       <c r="O129" s="6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P129" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
+        <v>4.6</v>
+      </c>
+      <c r="P129" s="15" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
         <is>
-          <t>Recent commercial success; limited critical depth</t>
+          <t>Limited critical record; cultural impact clearer than lyrical analysis</t>
         </is>
       </c>
       <c r="R129" s="2" t="inlineStr">
         <is>
-          <t>Bay Area trap-pop. Ice Princess persona over lyrical substance.</t>
+          <t>Miami's hedonistic party rap duo. Energy over craft.</t>
         </is>
       </c>
     </row>
@@ -10097,12 +10101,12 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>City Girls</t>
+          <t>Maxo Kream</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -10117,129 +10121,124 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>Party/Pop</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Miami Trap</t>
+          <t>Houston Narrative Trap</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Quality Control/Motown</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="J130" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K130" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L130" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="M130" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N130" s="5" t="n">
-        <v>4</v>
+        <v>2017</v>
+      </c>
+      <c r="J130" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K130" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L130" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M130" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N130" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="O130" s="6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P130" s="15" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>7.4</v>
+      </c>
+      <c r="P130" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
         <is>
-          <t>Limited critical record; cultural impact clearer than lyrical analysis</t>
+          <t>Critical acclaim in narrative rap circles; limited mainstream documentation</t>
         </is>
       </c>
       <c r="R130" s="2" t="inlineStr">
         <is>
-          <t>Miami's hedonistic party rap duo. Energy over craft.</t>
+          <t>Houston storytelling tradition continued. 'Weight of the World' deeply affecting.</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" t="n">
         <v>130</v>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>MX</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>Maxo Kream</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>Gangsta/Street</t>
-        </is>
-      </c>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t>Houston Narrative Trap</t>
-        </is>
-      </c>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>EMPIRE</t>
-        </is>
-      </c>
-      <c r="I131" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="J131" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K131" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L131" s="12" t="n">
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>The Roots</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Philly</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Golden Age</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Conscious/Lyrical</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Live-Band Boom Bap</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Geffen/MCA</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>1993</v>
+      </c>
+      <c r="J131" t="n">
+        <v>10</v>
+      </c>
+      <c r="K131" t="n">
         <v>9</v>
       </c>
-      <c r="M131" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N131" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="O131" s="6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="P131" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q131" s="2" t="inlineStr">
-        <is>
-          <t>Critical acclaim in narrative rap circles; limited mainstream documentation</t>
-        </is>
-      </c>
-      <c r="R131" s="2" t="inlineStr">
-        <is>
-          <t>Houston storytelling tradition continued. 'Weight of the World' deeply affecting.</t>
+      <c r="L131" t="n">
+        <v>8</v>
+      </c>
+      <c r="M131" t="n">
+        <v>9</v>
+      </c>
+      <c r="N131" t="n">
+        <v>8</v>
+      </c>
+      <c r="O131" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>Philadelphia's live-band institution; Black Thought's relentless technique anchors a peerless catalog.</t>
         </is>
       </c>
     </row>
@@ -10249,12 +10248,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>BS</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>The Roots</t>
+          <t>Beanie Sigel</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -10264,53 +10263,58 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Golden Age</t>
+          <t>2000s</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Live-Band Boom Bap</t>
+          <t>Soul Boom Bap</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Geffen/MCA</t>
+          <t>Roc-A-Fella</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1993</v>
+        <v>2000</v>
       </c>
       <c r="J132" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K132" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L132" t="n">
         <v>8</v>
       </c>
       <c r="M132" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N132" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O132" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>Critically respected but thinly documented outside the Roc-A-Fella context.</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>Philadelphia's live-band institution; Black Thought's relentless technique anchors a peerless catalog.</t>
+          <t>Philadelphia's hardest pen. Street narratives carried with weight and conviction.</t>
         </is>
       </c>
     </row>
@@ -10320,12 +10324,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>BS</t>
+          <t>UV</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Beanie Sigel</t>
+          <t>Lil Uzi Vert</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -10335,44 +10339,44 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Soul Boom Bap</t>
+          <t>Rage/Trap</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Roc-A-Fella</t>
+          <t>Generation Now/Atlantic</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2000</v>
+        <v>2016</v>
       </c>
       <c r="J133" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K133" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L133" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M133" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N133" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O133" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="P133" t="inlineStr">
         <is>
@@ -10381,12 +10385,12 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>Critically respected but thinly documented outside the Roc-A-Fella context.</t>
+          <t>Melodic rage star; influence on sound outweighs lyrical scholarship.</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>Philadelphia's hardest pen. Street narratives carried with weight and conviction.</t>
+          <t>Genre-bending rage pioneer. Melody and energy over lyrical density.</t>
         </is>
       </c>
     </row>
@@ -10396,12 +10400,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>UV</t>
+          <t>FW</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Lil Uzi Vert</t>
+          <t>Freeway</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -10411,58 +10415,58 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2000s</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Rage/Trap</t>
+          <t>Soul Boom Bap</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Generation Now/Atlantic</t>
+          <t>Roc-A-Fella</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2016</v>
+        <v>2003</v>
       </c>
       <c r="J134" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K134" t="n">
         <v>6</v>
       </c>
       <c r="L134" t="n">
+        <v>6</v>
+      </c>
+      <c r="M134" t="n">
+        <v>6</v>
+      </c>
+      <c r="N134" t="n">
         <v>5</v>
       </c>
-      <c r="M134" t="n">
-        <v>6</v>
-      </c>
-      <c r="N134" t="n">
-        <v>6</v>
-      </c>
       <c r="O134" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>Melodic rage star; influence on sound outweighs lyrical scholarship.</t>
+          <t>Limited critical record; respected within State Property/Roc-A-Fella circles.</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>Genre-bending rage pioneer. Melody and energy over lyrical density.</t>
+          <t>Distinctive raspy urgency and Philly grit. State Property standout.</t>
         </is>
       </c>
     </row>
@@ -10472,12 +10476,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>FW</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Freeway</t>
+          <t>Eve</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -10492,24 +10496,24 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Party/Pop</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Soul Boom Bap</t>
+          <t>Ruff Ryders</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Roc-A-Fella</t>
+          <t>Ruff Ryders/Interscope</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2003</v>
+        <v>1999</v>
       </c>
       <c r="J135" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K135" t="n">
         <v>6</v>
@@ -10524,7 +10528,7 @@
         <v>5</v>
       </c>
       <c r="O135" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="P135" t="inlineStr">
         <is>
@@ -10533,12 +10537,12 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>Limited critical record; respected within State Property/Roc-A-Fella circles.</t>
+          <t>Commercial success clearer than lyrical analysis.</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>Distinctive raspy urgency and Philly grit. State Property standout.</t>
+          <t>Ruff Ryders' First Lady. Charismatic crossover with Philly roots.</t>
         </is>
       </c>
     </row>
@@ -10548,22 +10552,22 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Eve</t>
+          <t>Da Brat</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Philly</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -10573,16 +10577,16 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Ruff Ryders</t>
+          <t>So So Def Bass</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Ruff Ryders/Interscope</t>
+          <t>So So Def</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1999</v>
+        <v>1994</v>
       </c>
       <c r="J136" t="n">
         <v>6</v>
@@ -10604,17 +10608,17 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>Commercial success clearer than lyrical analysis.</t>
+          <t>First female solo rapper to go platinum; under-analyzed lyrically.</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>Ruff Ryders' First Lady. Charismatic crossover with Philly roots.</t>
+          <t>So So Def's breakout. First female solo rapper to go platinum.</t>
         </is>
       </c>
     </row>
@@ -10624,59 +10628,59 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>TS2</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Da Brat</t>
+          <t>Too $hort</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Bay Area</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Golden Age</t>
+          <t>Old School</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Party/Pop</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>So So Def Bass</t>
+          <t>Funk/Bass</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>So So Def</t>
+          <t>Jive/Dangerous Music</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1994</v>
+        <v>1987</v>
       </c>
       <c r="J137" t="n">
         <v>6</v>
       </c>
       <c r="K137" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L137" t="n">
         <v>6</v>
       </c>
       <c r="M137" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N137" t="n">
         <v>5</v>
       </c>
       <c r="O137" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="P137" t="inlineStr">
         <is>
@@ -10685,12 +10689,12 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>First female solo rapper to go platinum; under-analyzed lyrically.</t>
+          <t>Pioneer status outweighs lyrical-craft documentation.</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>So So Def's breakout. First female solo rapper to go platinum.</t>
+          <t>Oakland pioneer and pimp-rap archetype. Influence over intricacy.</t>
         </is>
       </c>
     </row>
@@ -10700,12 +10704,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>TS2</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Too $hort</t>
+          <t>Del the Funky Homosapien</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -10715,44 +10719,44 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Old School</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Abstract</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Funk/Bass</t>
+          <t>Hieroglyphics</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Jive/Dangerous Music</t>
+          <t>Elektra/Hiero Imperium</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1987</v>
+        <v>1991</v>
       </c>
       <c r="J138" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K138" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L138" t="n">
         <v>6</v>
       </c>
       <c r="M138" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N138" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O138" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="P138" t="inlineStr">
         <is>
@@ -10761,12 +10765,12 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>Pioneer status outweighs lyrical-craft documentation.</t>
+          <t>Underground Hieroglyphics following; specialist critical attention.</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>Oakland pioneer and pimp-rap archetype. Influence over intricacy.</t>
+          <t>Hieroglyphics wordsmith. Quirky vocabulary and abstract wit.</t>
         </is>
       </c>
     </row>
@@ -10776,12 +10780,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>MD3</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Del the Funky Homosapien</t>
+          <t>Mac Dre</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -10791,58 +10795,58 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Golden Age</t>
+          <t>2000s</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Abstract</t>
+          <t>Party/Pop</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hieroglyphics</t>
+          <t>Hyphy</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Elektra/Hiero Imperium</t>
+          <t>Thizz Entertainment</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="J139" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K139" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L139" t="n">
         <v>6</v>
       </c>
       <c r="M139" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N139" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O139" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>Underground Hieroglyphics following; specialist critical attention.</t>
+          <t>Regional hyphy icon; limited national critical record.</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>Hieroglyphics wordsmith. Quirky vocabulary and abstract wit.</t>
+          <t>Hyphy movement godfather. Enduring Bay Area cult legend.</t>
         </is>
       </c>
     </row>
@@ -10852,17 +10856,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>MD3</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Mac Dre</t>
+          <t>Royce da 5'9"</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -10872,53 +10876,53 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Party/Pop</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hyphy</t>
+          <t>Detroit Boom Bap</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Thizz Entertainment</t>
+          <t>Shady/Independent</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1989</v>
+        <v>2002</v>
       </c>
       <c r="J140" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K140" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L140" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M140" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N140" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O140" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>Regional hyphy icon; limited national critical record.</t>
+          <t>Elite technician; documentation grew via Slaughterhouse and PRhyme.</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>Hyphy movement godfather. Enduring Bay Area cult legend.</t>
+          <t>Detroit technician. Slaughterhouse and PRhyme cornerstone.</t>
         </is>
       </c>
     </row>
@@ -10928,41 +10932,41 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Royce da 5'9"</t>
+          <t>Kool G Rap</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>NYC</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Detroit Boom Bap</t>
+          <t>Boom Bap</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Shady/Independent</t>
+          <t>Cold Chillin'</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2002</v>
+        <v>1989</v>
       </c>
       <c r="J141" t="n">
         <v>9</v>
@@ -10971,7 +10975,7 @@
         <v>8</v>
       </c>
       <c r="L141" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M141" t="n">
         <v>8</v>
@@ -10980,21 +10984,16 @@
         <v>7</v>
       </c>
       <c r="O141" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q141" t="inlineStr">
-        <is>
-          <t>Elite technician; documentation grew via Slaughterhouse and PRhyme.</t>
+          <t>H</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>Detroit technician. Slaughterhouse and PRhyme cornerstone.</t>
+          <t>Mafioso-rap forefather. The multisyllabic blueprint for Nas, Biggie and Jay-Z.</t>
         </is>
       </c>
     </row>
@@ -11004,12 +11003,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>RM</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Kool G Rap</t>
+          <t>Redman</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -11024,48 +11023,53 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Boom Bap</t>
+          <t>Funk Boom Bap</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Cold Chillin'</t>
+          <t>Def Jam</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1989</v>
+        <v>1992</v>
       </c>
       <c r="J142" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K142" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L142" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M142" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N142" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O142" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>Beloved and skilled; lyrical scholarship modest relative to peers.</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>Mafioso-rap forefather. The multisyllabic blueprint for Nas, Biggie and Jay-Z.</t>
+          <t>Newark's funkiest. Effortless flow with comedic menace.</t>
         </is>
       </c>
     </row>
@@ -11075,12 +11079,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>RM</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Redman</t>
+          <t>Method Man</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -11090,7 +11094,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Golden Age</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -11100,7 +11104,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Funk Boom Bap</t>
+          <t>Wu-Tang</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -11109,16 +11113,16 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="J143" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K143" t="n">
         <v>7</v>
       </c>
       <c r="L143" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M143" t="n">
         <v>7</v>
@@ -11127,7 +11131,7 @@
         <v>6</v>
       </c>
       <c r="O143" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="P143" t="inlineStr">
         <is>
@@ -11136,12 +11140,12 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>Beloved and skilled; lyrical scholarship modest relative to peers.</t>
+          <t>Scored solo; Wu-Tang charisma vs pure-lyric metrics.</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>Newark's funkiest. Effortless flow with comedic menace.</t>
+          <t>Wu-Tang's charismatic star. Gravel-voiced hooks and grit.</t>
         </is>
       </c>
     </row>
@@ -11151,12 +11155,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ME</t>
+          <t>EP</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Method Man</t>
+          <t>EPMD</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -11166,7 +11170,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Late 90s</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -11176,7 +11180,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Wu-Tang</t>
+          <t>Funk Boom Bap</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -11185,25 +11189,25 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1994</v>
+        <v>1988</v>
       </c>
       <c r="J144" t="n">
         <v>7</v>
       </c>
       <c r="K144" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L144" t="n">
         <v>6</v>
       </c>
       <c r="M144" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N144" t="n">
         <v>6</v>
       </c>
       <c r="O144" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="P144" t="inlineStr">
         <is>
@@ -11212,12 +11216,12 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>Scored solo; Wu-Tang charisma vs pure-lyric metrics.</t>
+          <t>Influential funk-rap duo; understated lyrical documentation.</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>Wu-Tang's charismatic star. Gravel-voiced hooks and grit.</t>
+          <t>Strictly Business. Laid-back funk and durable chemistry.</t>
         </is>
       </c>
     </row>
@@ -11227,59 +11231,59 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>EP</t>
+          <t>TG</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>EPMD</t>
+          <t>The Game</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Golden Age</t>
+          <t>2000s</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Funk Boom Bap</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Def Jam</t>
+          <t>Aftermath/G-Unit</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1988</v>
+        <v>2005</v>
       </c>
       <c r="J145" t="n">
         <v>7</v>
       </c>
       <c r="K145" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L145" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M145" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N145" t="n">
         <v>6</v>
       </c>
       <c r="O145" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="P145" t="inlineStr">
         <is>
@@ -11288,12 +11292,12 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>Influential funk-rap duo; understated lyrical documentation.</t>
+          <t>Commercially dominant; reference-heavy bars, mixed critical view.</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>Strictly Business. Laid-back funk and durable chemistry.</t>
+          <t>Compton revivalist. The Documentary-era West Coast resurgence.</t>
         </is>
       </c>
     </row>
@@ -11303,12 +11307,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>TG</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>The Game</t>
+          <t>Ice-T</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -11318,7 +11322,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>Old School</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -11328,34 +11332,34 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>West Coast</t>
+          <t>Electro/Funk</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Aftermath/G-Unit</t>
+          <t>Sire/Rhyme Syndicate</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2005</v>
+        <v>1987</v>
       </c>
       <c r="J146" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K146" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L146" t="n">
         <v>7</v>
       </c>
       <c r="M146" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N146" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O146" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="P146" t="inlineStr">
         <is>
@@ -11364,12 +11368,12 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>Commercially dominant; reference-heavy bars, mixed critical view.</t>
+          <t>Gangsta-rap pioneer; influence and narrative over technical metrics.</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>Compton revivalist. The Documentary-era West Coast resurgence.</t>
+          <t>Gangsta-rap originator. Street reportage before the template existed.</t>
         </is>
       </c>
     </row>
@@ -11379,12 +11383,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Ice-T</t>
+          <t>Nipsey Hussle</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -11394,44 +11398,44 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Old School</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Conscious/Street</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Electro/Funk</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Sire/Rhyme Syndicate</t>
+          <t>All Money In/Atlantic</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1987</v>
+        <v>2010</v>
       </c>
       <c r="J147" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K147" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L147" t="n">
         <v>7</v>
       </c>
       <c r="M147" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N147" t="n">
         <v>7</v>
       </c>
       <c r="O147" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="P147" t="inlineStr">
         <is>
@@ -11440,12 +11444,12 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>Gangsta-rap pioneer; influence and narrative over technical metrics.</t>
+          <t>Posthumous reappraisal ongoing; entrepreneurial legacy prominent.</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>Gangsta-rap originator. Street reportage before the template existed.</t>
+          <t>Crenshaw's marathon. Street wisdom and self-determination.</t>
         </is>
       </c>
     </row>
@@ -11455,12 +11459,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>DQ</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Nipsey Hussle</t>
+          <t>DJ Quik</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -11470,44 +11474,44 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Conscious/Street</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>West Coast</t>
+          <t>G-Funk</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>All Money In/Atlantic</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2010</v>
+        <v>1991</v>
       </c>
       <c r="J148" t="n">
         <v>7</v>
       </c>
       <c r="K148" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L148" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M148" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N148" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O148" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="P148" t="inlineStr">
         <is>
@@ -11516,86 +11520,10 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>Posthumous reappraisal ongoing; entrepreneurial legacy prominent.</t>
+          <t>Revered as a producer; underrated as a lyricist.</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
-        <is>
-          <t>Crenshaw's marathon. Street wisdom and self-determination.</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="n">
-        <v>148</v>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>DQ</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>DJ Quik</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>LA</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Golden Age</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Gangsta/Street</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>G-Funk</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Profile</t>
-        </is>
-      </c>
-      <c r="I149" t="n">
-        <v>1991</v>
-      </c>
-      <c r="J149" t="n">
-        <v>7</v>
-      </c>
-      <c r="K149" t="n">
-        <v>6</v>
-      </c>
-      <c r="L149" t="n">
-        <v>6</v>
-      </c>
-      <c r="M149" t="n">
-        <v>6</v>
-      </c>
-      <c r="N149" t="n">
-        <v>6</v>
-      </c>
-      <c r="O149" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="P149" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q149" t="inlineStr">
-        <is>
-          <t>Revered as a producer; underrated as a lyricist.</t>
-        </is>
-      </c>
-      <c r="R149" t="inlineStr">
         <is>
           <t>G-funk auteur. Producer-rapper with effortless West Coast bounce.</t>
         </is>

--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R148"/>
+  <dimension ref="A1:S148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -694,6 +694,11 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -766,6 +771,11 @@
           <t>Father of hip-hop. Innovated breakbeat DJing. His voice was the party, not the page.</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -838,6 +848,11 @@
           <t>Turntablism pioneer. Set template for social commentary rap.</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -910,6 +925,11 @@
           <t>'The Message' — first truly serious rap lyric. Dark imagery of urban decay.</t>
         </is>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -982,6 +1002,11 @@
           <t>Brought hip-hop mainstream with 'Rapper's Delight'.</t>
         </is>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -1054,6 +1079,11 @@
           <t>'Planet Rock' visionary. Pan-African ideology in party form.</t>
         </is>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -1126,6 +1156,11 @@
           <t>Def Jam's first star. Swagger as technique.</t>
         </is>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1198,6 +1233,11 @@
           <t>Merged rock and rap. Iconic minimalism.</t>
         </is>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1268,6 +1308,11 @@
       <c r="R9" s="2" t="inlineStr">
         <is>
           <t>Frenetic cultural collage. Grew into genuine experimental sophistication.</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Compound</t>
         </is>
       </c>
     </row>
@@ -1342,6 +1387,11 @@
           <t>'The Teacha.' Hip-hop philosopher-MC.</t>
         </is>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1414,6 +1464,11 @@
           <t>Maximum political rage. Bomb Squad production as sonic warfare.</t>
         </is>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1490,6 +1545,11 @@
           <t>Pioneer female MC. Battle rap legend at age 14. Foundational for women in hip-hop.</t>
         </is>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1566,6 +1626,11 @@
           <t>First solo female rapper to release a full album. Sharp, authoritative delivery.</t>
         </is>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1642,6 +1707,11 @@
           <t>Philadelphia proto-gangsta rapper. Predates N.W.A's gangsta template.</t>
         </is>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1718,6 +1788,11 @@
           <t>First rap group Grammy-nominated. Female-fronted electro-hop novelty hit.</t>
         </is>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1794,6 +1869,11 @@
           <t>Early electro-rap crossover. Bridged disco and hip-hop aesthetics.</t>
         </is>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1870,6 +1950,11 @@
           <t>Human beatbox pioneer. 'La Di Da Di' a canonical party rap text.</t>
         </is>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1942,6 +2027,11 @@
           <t>Master storyteller. Cockney-inflected delivery, vivid street fables.</t>
         </is>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -2018,6 +2108,11 @@
           <t>Storytelling peer to Slick Rick. Underrated narrative rapper.</t>
         </is>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -2090,6 +2185,11 @@
           <t>Velvet-glove delivery hiding razor-sharp multisyllabic patterns.</t>
         </is>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -2162,6 +2262,11 @@
           <t>Invented internal rhyme as default mode. The God MC.</t>
         </is>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -2234,6 +2339,11 @@
           <t>Regal feminist authority. Foundational for women in rap.</t>
         </is>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -2306,6 +2416,11 @@
           <t>Invented gangsta rap. Vérité street journalism.</t>
         </is>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -2378,6 +2493,11 @@
           <t>N.W.A's sharpest writer. Furious precision.</t>
         </is>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -2450,6 +2570,11 @@
           <t>Playful polymaths. Vast vocabulary with absurdist wit.</t>
         </is>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -2522,6 +2647,11 @@
           <t>Q-Tip's conversational genius. Jazz improvisation in verse.</t>
         </is>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -2594,6 +2724,11 @@
           <t>'Illmatic' distilled Queensbridge into literary art.</t>
         </is>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -2666,6 +2801,11 @@
           <t>Greatest natural storyteller. Cinematic scenes, effortless charisma.</t>
         </is>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -2738,6 +2878,11 @@
           <t>Nine MCs, nine styles. Martial mythology meets grim NY street.</t>
         </is>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -2810,6 +2955,11 @@
           <t>Flow as personality. Delivery transcends lyrical content.</t>
         </is>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -2882,6 +3032,11 @@
           <t>Producer-first. Lyricism secondary to sonic architecture.</t>
         </is>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -2954,6 +3109,11 @@
           <t>Acrobatic, joyful wordplay. LA's alternative answer to De La Soul.</t>
         </is>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -3026,6 +3186,11 @@
           <t>Prodigy's paranoid poetry over Havoc's glacial loops.</t>
         </is>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -3098,6 +3263,11 @@
           <t>Slang inventor. Vocabulary innovation as primary art form.</t>
         </is>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -3174,6 +3344,11 @@
           <t>Pete Rock's jazz-inflected production plus CL Smooth's introspective flows.</t>
         </is>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -3246,6 +3421,11 @@
           <t>Guru's monotone wisdom over DJ Premier's crate-dug perfection.</t>
         </is>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -3322,6 +3502,11 @@
           <t>5 Percenter theology meets Afrocentric fury. Sadat X and Grand Puba.</t>
         </is>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -3398,6 +3583,11 @@
           <t>Black nationalist imagery and Afrocentric symbolism at maximum.</t>
         </is>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -3470,6 +3660,11 @@
           <t>Punchline architect. Harlem's greatest. Wordplay density rivals anyone.</t>
         </is>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -3542,6 +3737,11 @@
           <t>Pioneered Southern horror-gangsta. Scarface's lyrical foundation.</t>
         </is>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -3618,6 +3818,11 @@
           <t>LA's jazz-rap underground. Aceyalone among the most technically gifted MCs ever.</t>
         </is>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -3694,6 +3899,11 @@
           <t>Cool jazz-rap fusion. Ladybug Mecca one of the era's sharpest female voices.</t>
         </is>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -3770,6 +3980,11 @@
           <t>Launched Busta Rhymes. Charlie Brown and Dinco D also strong voices.</t>
         </is>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -3842,6 +4057,11 @@
           <t>Hyper-kinetic delivery and flow complexity. One of the fastest MCs ever.</t>
         </is>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -3914,6 +4134,11 @@
           <t>Raw emotional intelligence. Political rage and personal vulnerability.</t>
         </is>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -3986,6 +4211,11 @@
           <t>Effortless mastery. Hustler's autobiography as album architecture.</t>
         </is>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -4058,6 +4288,11 @@
           <t>Most technically precise rapper. Internal rhyme density off the charts.</t>
         </is>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -4130,6 +4365,11 @@
           <t>Primal confessional fury. Power through raw emotional delivery.</t>
         </is>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -4202,6 +4442,11 @@
           <t>'Miseducation' — radical emotional honesty + technical precision.</t>
         </is>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -4274,6 +4519,11 @@
           <t>Flow as futurist sculpture. Rhythm manipulation over traditional lyricism.</t>
         </is>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -4346,6 +4596,11 @@
           <t>'Black on Both Sides' — blues, jazz, politics in one voice.</t>
         </is>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -4418,6 +4673,11 @@
           <t>Brooklyn's dense intellectual. Every bar packed with history.</t>
         </is>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -4490,6 +4750,11 @@
           <t>Andre 3000: genre-defying poet. Big Boi: underrated technical master.</t>
         </is>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -4562,6 +4827,11 @@
           <t>Mogul over MC. Influence is business, not bars.</t>
         </is>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -4638,6 +4908,11 @@
           <t>Pink fur and slant rhymes. Harlem's most stylistically eccentric MC.</t>
         </is>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -4714,6 +4989,11 @@
           <t>Aggressive feminine sexuality as lyrical weapon. Def Jam's answer to Lil Kim.</t>
         </is>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -4786,6 +5066,11 @@
           <t>Radical sexual candor. Graphic feminism that rewrote what women could say in rap.</t>
         </is>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -4862,6 +5147,11 @@
           <t>Cash Money's first star. New Orleans bounce meets street narrative.</t>
         </is>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -4938,6 +5228,11 @@
           <t>Battle rap legend. Technical skill occasionally undermined by ego.</t>
         </is>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -5014,6 +5309,11 @@
           <t>Philadelphia underground. Vinnie Paz's dense, conspiratorial lyricism.</t>
         </is>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -5086,6 +5386,11 @@
           <t>First Latin rapper to go platinum solo. Multisyllabic rhyme virtuoso.</t>
         </is>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -5162,6 +5467,11 @@
           <t>One of the era's most underrated lyricists. 'Doe or Die' (1995) a classic; his 'Life's a Bitch' verse is all-time.</t>
         </is>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -5234,6 +5544,11 @@
           <t>Conceptual ambition as primary engine. Each album a reinvention.</t>
         </is>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -5306,6 +5621,11 @@
           <t>Simile machine at peak. Abstract metaphor-stacking as freestyle sport.</t>
         </is>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -5378,6 +5698,11 @@
           <t>King of the South. Trap's emotional architect.</t>
         </is>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -5450,6 +5775,11 @@
           <t>Vibe and charisma over craft. Trap music's spiritual godfather.</t>
         </is>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -5522,6 +5852,11 @@
           <t>Stream-of-consciousness genius. Dense slang, vivid scene-painting.</t>
         </is>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -5594,6 +5929,11 @@
           <t>The supervillain. Labyrinths of internal rhyme no one has fully mapped.</t>
         </is>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -5666,6 +6006,11 @@
           <t>Chicago's philosopher-MC. Ernie Barnes paintings in verse form.</t>
         </is>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -5738,6 +6083,11 @@
           <t>Comic virtuosity. Punchline timing as precision instrument.</t>
         </is>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -5810,6 +6160,11 @@
           <t>Trap's motivational orator. Delivery and charisma over craft.</t>
         </is>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -5882,6 +6237,11 @@
           <t>Conceptually sui generis. 'Dumb It Down' a rebuke of simplicity.</t>
         </is>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -5954,6 +6314,11 @@
           <t>Houston's great novelist. Psychological interior in gangsta rap.</t>
         </is>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -6026,6 +6391,11 @@
           <t>NLP-verified largest unique vocabulary in rap. Dense abstract imagery.</t>
         </is>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -6102,6 +6472,11 @@
           <t>Gravelly-voiced Yonkers MC. Punchline economy and street credibility.</t>
         </is>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -6174,6 +6549,11 @@
           <t>Bulletproof charisma. Street narrative over lyrical complexity.</t>
         </is>
       </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -6250,6 +6630,11 @@
           <t>Oscar-winning Southern horror-rap. Pioneered the dark triplet flow.</t>
         </is>
       </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -6322,6 +6707,11 @@
           <t>Bun B and Pimp C. Texas's most complete rap duo.</t>
         </is>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -6398,6 +6788,11 @@
           <t>Houston's street ambassador. Chopped-and-screwed delivery as identity.</t>
         </is>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -6474,6 +6869,11 @@
           <t>LA underground legend. Freestyle Fellowship's most technically gifted MC.</t>
         </is>
       </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -6546,6 +6946,11 @@
           <t>'Only Built 4 Cuban Linx' — the Godfather Part II of rap albums.</t>
         </is>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -6618,6 +7023,11 @@
           <t>Company Flow / Run The Jewels architect. Dystopian sonic vision.</t>
         </is>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -6694,6 +7104,11 @@
           <t>Minneapolis conscious rapper. Raw emotional honesty over Ant's production.</t>
         </is>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -6770,6 +7185,11 @@
           <t>Most politically radical rapper in the genre. Conspiracy and revolution.</t>
         </is>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -6842,6 +7262,11 @@
           <t>The complete package. Every dimension at peak. Pulitzer Prize.</t>
         </is>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -6914,6 +7339,11 @@
           <t>Working-class emotional intelligence. Deep narrative craft.</t>
         </is>
       </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -6986,6 +7416,11 @@
           <t>Melody over meaning. Vocal texture as primary instrument.</t>
         </is>
       </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -7058,6 +7493,11 @@
           <t>Emotional auto-tune as confession. Vibe over lyrical architecture.</t>
         </is>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -7130,6 +7570,11 @@
           <t>Joyful complexity. Gospel cadences and Chicago love letters.</t>
         </is>
       </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -7202,6 +7647,11 @@
           <t>Compression and grief as poetics. Dense abstract imagery.</t>
         </is>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -7274,6 +7724,11 @@
           <t>Visceral urgency. Philadelphia streets in raw kinetic delivery.</t>
         </is>
       </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -7346,6 +7801,11 @@
           <t>Aesthetic as content. Flow and texture over lyrical substance.</t>
         </is>
       </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
@@ -7418,6 +7878,11 @@
           <t>Technical precision and alter-ego theatrics. 'Monster' verse.</t>
         </is>
       </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -7490,6 +7955,11 @@
           <t>Deadpan sociologist. Minimalist language doing maximum structural work.</t>
         </is>
       </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
@@ -7562,6 +8032,11 @@
           <t>Mississippi throwback futurist. Southern soul and lyrical ambition fused.</t>
         </is>
       </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -7634,6 +8109,11 @@
           <t>El-P and Killer Mike. Most politically urgent rap duo since PE.</t>
         </is>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
@@ -7706,6 +8186,11 @@
           <t>RTJ's political conscience. Atlanta's most morally serious MC.</t>
         </is>
       </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -7778,6 +8263,11 @@
           <t>Gary Indiana's finest. Technical gangsta rap with jazz-rap production.</t>
         </is>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -7850,6 +8340,11 @@
           <t>Triplet flow inventors. Cultural influence far exceeds lyrical complexity.</t>
         </is>
       </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -7926,6 +8421,11 @@
           <t>Detroit MC. Punchlines over conceptual depth. 'One Man Can Change The World'.</t>
         </is>
       </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -8002,6 +8502,11 @@
           <t>'Whack World' — 15 one-minute songs as unified concept. Wholly original.</t>
         </is>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -8074,6 +8579,11 @@
           <t>Chicago's most literary voice. Jazz cadences and political awakening.</t>
         </is>
       </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
@@ -8146,6 +8656,11 @@
           <t>'CARE FOR ME' — grief and Chicago violence as devastating concept album.</t>
         </is>
       </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -8218,6 +8733,11 @@
           <t>Detroit's avant-garde MC. Schizophrenic flows and surreal imagery.</t>
         </is>
       </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -8290,6 +8810,11 @@
           <t>Arc from frat-rap to deeply personal jazz introspection. 'Swimming' a peak.</t>
         </is>
       </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -8366,6 +8891,11 @@
           <t>Atlanta's most technically gifted rapper. 'DiCaprio 2' showed full potential.</t>
         </is>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
@@ -8438,6 +8968,11 @@
           <t>Unfiltered Bronx personality. Cultural force exceeds lyrical architecture.</t>
         </is>
       </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -8514,6 +9049,11 @@
           <t>Chicago's introspective melodic trap voice. Melancholy street memoir.</t>
         </is>
       </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
@@ -8590,6 +9130,11 @@
           <t>Emotional vulnerability over technical precision. Florida pain made universal.</t>
         </is>
       </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -8666,6 +9211,11 @@
           <t>Tampa's theatrical polymath. Technical fire meets conceptual daring.</t>
         </is>
       </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
@@ -8742,6 +9292,11 @@
           <t>Memphis energy, unfiltered personality. New Southern feminism in party form.</t>
         </is>
       </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -8818,6 +9373,11 @@
           <t>Melodic luxury trap. Vibe and aesthetic are the art.</t>
         </is>
       </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
@@ -8894,6 +9454,11 @@
           <t>Authentic street narrator. Storytelling grounded in lived experience.</t>
         </is>
       </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -8966,6 +9531,11 @@
           <t>Griselda's lyrical backbone. Buffalo street narratives with East Coast precision.</t>
         </is>
       </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
@@ -9042,6 +9612,11 @@
           <t>Migos' most lyrical member. Flow variation and delivery standout in trap context.</t>
         </is>
       </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -9118,6 +9693,11 @@
           <t>Atlanta's punk-rap hybrid. Unconventional tonal range.</t>
         </is>
       </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
@@ -9194,6 +9774,11 @@
           <t>Atlanta's female trap voice. Technical skill often underestimated.</t>
         </is>
       </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -9270,6 +9855,11 @@
           <t>St. Louis's jazz-rap hybrid. Melodic and rhythmic sophistication.</t>
         </is>
       </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
@@ -9342,6 +9932,11 @@
           <t>Cocaine rap's Rembrandt. 'Daytona' — maximum density, minimum waste.</t>
         </is>
       </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -9414,6 +10009,11 @@
           <t>'Igor' and 'Call Me If You Get Lost' — producer-auteur. Concept album mastery.</t>
         </is>
       </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
@@ -9490,6 +10090,11 @@
           <t>billy woods + ELUCID. The most demanding abstract rap being made today.</t>
         </is>
       </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
@@ -9566,6 +10171,11 @@
           <t>Comedy-meets-rap. Formally interesting but body of work too small to score confidently.</t>
         </is>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
@@ -9642,6 +10252,11 @@
           <t>Chicago drill's most commercially consistent voice.</t>
         </is>
       </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -9718,6 +10333,11 @@
           <t>Florida trap's most distinctive voice. Rough-edged regional authenticity.</t>
         </is>
       </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
@@ -9790,6 +10410,11 @@
           <t>North Carolina's most complete female MC. Lyrical depth rivals any peer.</t>
         </is>
       </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -9866,6 +10491,11 @@
           <t>Charlotte underground. Dense introspective abstract rap. Watch this space.</t>
         </is>
       </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
@@ -9942,6 +10572,11 @@
           <t>West Coast boom bap craftsman. More respected by peers than critics.</t>
         </is>
       </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
@@ -10018,6 +10653,11 @@
           <t>Bay Area trap-pop. Ice Princess persona over lyrical substance.</t>
         </is>
       </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
@@ -10094,6 +10734,11 @@
           <t>Miami's hedonistic party rap duo. Energy over craft.</t>
         </is>
       </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
@@ -10170,6 +10815,11 @@
           <t>Houston storytelling tradition continued. 'Weight of the World' deeply affecting.</t>
         </is>
       </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -10241,6 +10891,11 @@
           <t>Philadelphia's live-band institution; Black Thought's relentless technique anchors a peerless catalog.</t>
         </is>
       </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -10317,6 +10972,11 @@
           <t>Philadelphia's hardest pen. Street narratives carried with weight and conviction.</t>
         </is>
       </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -10393,6 +11053,11 @@
           <t>Genre-bending rage pioneer. Melody and energy over lyrical density.</t>
         </is>
       </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -10469,6 +11134,11 @@
           <t>Distinctive raspy urgency and Philly grit. State Property standout.</t>
         </is>
       </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -10545,6 +11215,11 @@
           <t>Ruff Ryders' First Lady. Charismatic crossover with Philly roots.</t>
         </is>
       </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -10621,6 +11296,11 @@
           <t>So So Def's breakout. First female solo rapper to go platinum.</t>
         </is>
       </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -10697,6 +11377,11 @@
           <t>Oakland pioneer and pimp-rap archetype. Influence over intricacy.</t>
         </is>
       </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -10773,6 +11458,11 @@
           <t>Hieroglyphics wordsmith. Quirky vocabulary and abstract wit.</t>
         </is>
       </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -10849,6 +11539,11 @@
           <t>Hyphy movement godfather. Enduring Bay Area cult legend.</t>
         </is>
       </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -10925,6 +11620,11 @@
           <t>Detroit technician. Slaughterhouse and PRhyme cornerstone.</t>
         </is>
       </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -10996,6 +11696,11 @@
           <t>Mafioso-rap forefather. The multisyllabic blueprint for Nas, Biggie and Jay-Z.</t>
         </is>
       </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -11072,6 +11777,11 @@
           <t>Newark's funkiest. Effortless flow with comedic menace.</t>
         </is>
       </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -11148,6 +11858,11 @@
           <t>Wu-Tang's charismatic star. Gravel-voiced hooks and grit.</t>
         </is>
       </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -11224,6 +11939,11 @@
           <t>Strictly Business. Laid-back funk and durable chemistry.</t>
         </is>
       </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -11300,6 +12020,11 @@
           <t>Compton revivalist. The Documentary-era West Coast resurgence.</t>
         </is>
       </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -11376,6 +12101,11 @@
           <t>Gangsta-rap originator. Street reportage before the template existed.</t>
         </is>
       </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -11452,6 +12182,11 @@
           <t>Crenshaw's marathon. Street wisdom and self-determination.</t>
         </is>
       </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -11526,6 +12261,11 @@
       <c r="R148" t="inlineStr">
         <is>
           <t>G-funk auteur. Producer-rapper with effortless West Coast bounce.</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>

--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -12133,7 +12133,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Conscious/Street</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">

--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -4853,7 +4853,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Late 99s</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">

--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Artist Database" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Artist Database" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Confidence Guide" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artist Database'!$A$1:$R$1</definedName>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,6 +71,9 @@
       <b val="1"/>
       <color rgb="009C0006"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="15">
@@ -157,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -203,6 +207,13 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -569,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R140"/>
+  <dimension ref="A1:S148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -683,6 +694,11 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -741,9 +757,8 @@
       <c r="N2" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O2" s="6">
-        <f>AVERAGE(J2:N2)</f>
-        <v/>
+      <c r="O2" s="6" t="n">
+        <v>3</v>
       </c>
       <c r="P2" s="7" t="inlineStr">
         <is>
@@ -754,6 +769,11 @@
       <c r="R2" s="2" t="inlineStr">
         <is>
           <t>Father of hip-hop. Innovated breakbeat DJing. His voice was the party, not the page.</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -814,9 +834,8 @@
       <c r="N3" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O3" s="6">
-        <f>AVERAGE(J3:N3)</f>
-        <v/>
+      <c r="O3" s="6" t="n">
+        <v>5.6</v>
       </c>
       <c r="P3" s="7" t="inlineStr">
         <is>
@@ -827,6 +846,11 @@
       <c r="R3" s="2" t="inlineStr">
         <is>
           <t>Turntablism pioneer. Set template for social commentary rap.</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -887,9 +911,8 @@
       <c r="N4" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O4" s="6">
-        <f>AVERAGE(J4:N4)</f>
-        <v/>
+      <c r="O4" s="6" t="n">
+        <v>7.6</v>
       </c>
       <c r="P4" s="7" t="inlineStr">
         <is>
@@ -899,7 +922,12 @@
       <c r="Q4" s="2" t="inlineStr"/>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>'The Message' redefined what rap could say.</t>
+          <t>'The Message' — first truly serious rap lyric. Dark imagery of urban decay.</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -960,9 +988,8 @@
       <c r="N5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="O5" s="6">
-        <f>AVERAGE(J5:N5)</f>
-        <v/>
+      <c r="O5" s="6" t="n">
+        <v>3.2</v>
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
@@ -972,7 +999,12 @@
       <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>First commercial rap hit.</t>
+          <t>Brought hip-hop mainstream with 'Rapper's Delight'.</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Compound</t>
         </is>
       </c>
     </row>
@@ -1033,9 +1065,8 @@
       <c r="N6" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="O6" s="6">
-        <f>AVERAGE(J6:N6)</f>
-        <v/>
+      <c r="O6" s="6" t="n">
+        <v>4.4</v>
       </c>
       <c r="P6" s="7" t="inlineStr">
         <is>
@@ -1045,7 +1076,12 @@
       <c r="Q6" s="2" t="inlineStr"/>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>Zulu Nation founder. Bridged hip-hop to electronic music.</t>
+          <t>'Planet Rock' visionary. Pan-African ideology in party form.</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -1106,9 +1142,8 @@
       <c r="N7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O7" s="6">
-        <f>AVERAGE(J7:N7)</f>
-        <v/>
+      <c r="O7" s="6" t="n">
+        <v>5.4</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1153,12 @@
       <c r="Q7" s="2" t="inlineStr"/>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>Defied rock and roll skeptics. First major Def Jam artist.</t>
+          <t>Def Jam's first star. Swagger as technique.</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -1179,9 +1219,8 @@
       <c r="N8" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O8" s="6">
-        <f>AVERAGE(J8:N8)</f>
-        <v/>
+      <c r="O8" s="6" t="n">
+        <v>5.2</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -1191,7 +1230,12 @@
       <c r="Q8" s="2" t="inlineStr"/>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>Integrated rock into rap. Made Adidas iconic.</t>
+          <t>Merged rock and rap. Iconic minimalism.</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Compound</t>
         </is>
       </c>
     </row>
@@ -1252,9 +1296,8 @@
       <c r="N9" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O9" s="6">
-        <f>AVERAGE(J9:N9)</f>
-        <v/>
+      <c r="O9" s="6" t="n">
+        <v>5.8</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -1264,7 +1307,12 @@
       <c r="Q9" s="2" t="inlineStr"/>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>Crossover kings. Made rap acceptable to white rock audiences.</t>
+          <t>Frenetic cultural collage. Grew into genuine experimental sophistication.</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Compound</t>
         </is>
       </c>
     </row>
@@ -1325,9 +1373,8 @@
       <c r="N10" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O10" s="6">
-        <f>AVERAGE(J10:N10)</f>
-        <v/>
+      <c r="O10" s="6" t="n">
+        <v>7.8</v>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
@@ -1337,7 +1384,12 @@
       <c r="Q10" s="2" t="inlineStr"/>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>The Teacha. 'South Bronx' battle classic.</t>
+          <t>'The Teacha.' Hip-hop philosopher-MC.</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -1398,9 +1450,8 @@
       <c r="N11" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="O11" s="6">
-        <f>AVERAGE(J11:N11)</f>
-        <v/>
+      <c r="O11" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
@@ -1410,7 +1461,12 @@
       <c r="Q11" s="2" t="inlineStr"/>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>Most politically explosive group in rap history.</t>
+          <t>Maximum political rage. Bomb Squad production as sonic warfare.</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Compound</t>
         </is>
       </c>
     </row>
@@ -1471,9 +1527,8 @@
       <c r="N12" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="O12" s="6">
-        <f>AVERAGE(J12:N12)</f>
-        <v/>
+      <c r="O12" s="6" t="n">
+        <v>6.2</v>
       </c>
       <c r="P12" s="14" t="inlineStr">
         <is>
@@ -1487,7 +1542,12 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>First female voice in a rap beef. Battle rap pioneer.</t>
+          <t>Pioneer female MC. Battle rap legend at age 14. Foundational for women in hip-hop.</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -1548,9 +1608,8 @@
       <c r="N13" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O13" s="6">
-        <f>AVERAGE(J13:N13)</f>
-        <v/>
+      <c r="O13" s="6" t="n">
+        <v>6.8</v>
       </c>
       <c r="P13" s="14" t="inlineStr">
         <is>
@@ -1564,7 +1623,12 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>First female rapper to release a full solo album.</t>
+          <t>First solo female rapper to release a full album. Sharp, authoritative delivery.</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1648,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Philly</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1625,9 +1689,8 @@
       <c r="N14" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="O14" s="6">
-        <f>AVERAGE(J14:N14)</f>
-        <v/>
+      <c r="O14" s="6" t="n">
+        <v>5.4</v>
       </c>
       <c r="P14" s="14" t="inlineStr">
         <is>
@@ -1641,7 +1704,12 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>Godfather of gangsta rap. Influence often unacknowledged.</t>
+          <t>Philadelphia proto-gangsta rapper. Predates N.W.A's gangsta template.</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -1702,9 +1770,8 @@
       <c r="N15" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="O15" s="6">
-        <f>AVERAGE(J15:N15)</f>
-        <v/>
+      <c r="O15" s="6" t="n">
+        <v>3.6</v>
       </c>
       <c r="P15" s="15" t="inlineStr">
         <is>
@@ -1718,7 +1785,12 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>Supersonic. Early Ruthless Records female act.</t>
+          <t>First rap group Grammy-nominated. Female-fronted electro-hop novelty hit.</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -1779,9 +1851,8 @@
       <c r="N16" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O16" s="6">
-        <f>AVERAGE(J16:N16)</f>
-        <v/>
+      <c r="O16" s="6" t="n">
+        <v>4.6</v>
       </c>
       <c r="P16" s="14" t="inlineStr">
         <is>
@@ -1795,7 +1866,12 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>Crossover R&amp;B-rap. Smooth sophistication in Old School era.</t>
+          <t>Early electro-rap crossover. Bridged disco and hip-hop aesthetics.</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -1856,9 +1932,8 @@
       <c r="N17" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O17" s="6">
-        <f>AVERAGE(J17:N17)</f>
-        <v/>
+      <c r="O17" s="6" t="n">
+        <v>5.4</v>
       </c>
       <c r="P17" s="14" t="inlineStr">
         <is>
@@ -1872,7 +1947,12 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>Human beatbox originator. 'La Di Da Di' with Slick Rick.</t>
+          <t>Human beatbox pioneer. 'La Di Da Di' a canonical party rap text.</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -1933,9 +2013,8 @@
       <c r="N18" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="O18" s="6">
-        <f>AVERAGE(J18:N18)</f>
-        <v/>
+      <c r="O18" s="6" t="n">
+        <v>7.8</v>
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
@@ -1945,7 +2024,12 @@
       <c r="Q18" s="2" t="inlineStr"/>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>Master storyteller. 'Children's Story' is a narrative benchmark.</t>
+          <t>Master storyteller. Cockney-inflected delivery, vivid street fables.</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -2006,9 +2090,8 @@
       <c r="N19" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O19" s="6">
-        <f>AVERAGE(J19:N19)</f>
-        <v/>
+      <c r="O19" s="6" t="n">
+        <v>5.8</v>
       </c>
       <c r="P19" s="15" t="inlineStr">
         <is>
@@ -2022,7 +2105,12 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>Slick Rick adjacent storyteller. Underrated narrative voice.</t>
+          <t>Storytelling peer to Slick Rick. Underrated narrative rapper.</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -2083,9 +2171,8 @@
       <c r="N20" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O20" s="6">
-        <f>AVERAGE(J20:N20)</f>
-        <v/>
+      <c r="O20" s="6" t="n">
+        <v>7.8</v>
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
@@ -2095,7 +2182,12 @@
       <c r="Q20" s="2" t="inlineStr"/>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>Smoothed battle rap into an art form. Influenced Jay-Z directly.</t>
+          <t>Velvet-glove delivery hiding razor-sharp multisyllabic patterns.</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -2156,9 +2248,8 @@
       <c r="N21" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O21" s="6">
-        <f>AVERAGE(J21:N21)</f>
-        <v/>
+      <c r="O21" s="6" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
@@ -2168,7 +2259,12 @@
       <c r="Q21" s="2" t="inlineStr"/>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>Rewired how MCs thought about flow. The God MC.</t>
+          <t>Invented internal rhyme as default mode. The God MC.</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -2229,9 +2325,8 @@
       <c r="N22" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O22" s="6">
-        <f>AVERAGE(J22:N22)</f>
-        <v/>
+      <c r="O22" s="6" t="n">
+        <v>7.6</v>
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
@@ -2241,7 +2336,12 @@
       <c r="Q22" s="2" t="inlineStr"/>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>U.N.I.T.Y. feminist anthem. First lady of hip-hop royalty.</t>
+          <t>Regal feminist authority. Foundational for women in rap.</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -2302,9 +2402,8 @@
       <c r="N23" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O23" s="6">
-        <f>AVERAGE(J23:N23)</f>
-        <v/>
+      <c r="O23" s="6" t="n">
+        <v>7.2</v>
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
@@ -2314,7 +2413,12 @@
       <c r="Q23" s="2" t="inlineStr"/>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>Straight Outta Compton. Made the coasts speak different languages.</t>
+          <t>Invented gangsta rap. Vérité street journalism.</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Compound</t>
         </is>
       </c>
     </row>
@@ -2375,9 +2479,8 @@
       <c r="N24" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O24" s="6">
-        <f>AVERAGE(J24:N24)</f>
-        <v/>
+      <c r="O24" s="6" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
@@ -2387,7 +2490,12 @@
       <c r="Q24" s="2" t="inlineStr"/>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>N.W.A pen. AmeriKKKa's Most Wanted is a lyrical high-water mark.</t>
+          <t>N.W.A's sharpest writer. Furious precision.</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -2448,9 +2556,8 @@
       <c r="N25" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O25" s="6">
-        <f>AVERAGE(J25:N25)</f>
-        <v/>
+      <c r="O25" s="6" t="n">
+        <v>7.6</v>
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
@@ -2460,7 +2567,12 @@
       <c r="Q25" s="2" t="inlineStr"/>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3 Feet High and Rising. Made sampling feel like art.</t>
+          <t>Playful polymaths. Vast vocabulary with absurdist wit.</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Compound</t>
         </is>
       </c>
     </row>
@@ -2521,9 +2633,8 @@
       <c r="N26" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O26" s="6">
-        <f>AVERAGE(J26:N26)</f>
-        <v/>
+      <c r="O26" s="6" t="n">
+        <v>8.4</v>
       </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
@@ -2533,7 +2644,12 @@
       <c r="Q26" s="2" t="inlineStr"/>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>Married jazz and hip-hop elegantly. The Low End Theory is essential.</t>
+          <t>Q-Tip's conversational genius. Jazz improvisation in verse.</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Compound</t>
         </is>
       </c>
     </row>
@@ -2594,9 +2710,8 @@
       <c r="N27" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O27" s="6">
-        <f>AVERAGE(J27:N27)</f>
-        <v/>
+      <c r="O27" s="6" t="n">
+        <v>9.4</v>
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
@@ -2606,7 +2721,12 @@
       <c r="Q27" s="2" t="inlineStr"/>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>Illmatic remains the most critically studied debut in rap.</t>
+          <t>'Illmatic' distilled Queensbridge into literary art.</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -2667,9 +2787,8 @@
       <c r="N28" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O28" s="6">
-        <f>AVERAGE(J28:N28)</f>
-        <v/>
+      <c r="O28" s="6" t="n">
+        <v>9</v>
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
@@ -2679,7 +2798,12 @@
       <c r="Q28" s="2" t="inlineStr"/>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>Lyrical density and narrative gift in equal measure.</t>
+          <t>Greatest natural storyteller. Cinematic scenes, effortless charisma.</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -2740,9 +2864,8 @@
       <c r="N29" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O29" s="6">
-        <f>AVERAGE(J29:N29)</f>
-        <v/>
+      <c r="O29" s="6" t="n">
+        <v>8.4</v>
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
@@ -2752,7 +2875,12 @@
       <c r="Q29" s="2" t="inlineStr"/>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>Enter the 36 Chambers. Martial arts mythology meets Shaolin New York.</t>
+          <t>Nine MCs, nine styles. Martial mythology meets grim NY street.</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Compound</t>
         </is>
       </c>
     </row>
@@ -2813,9 +2941,8 @@
       <c r="N30" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O30" s="6">
-        <f>AVERAGE(J30:N30)</f>
-        <v/>
+      <c r="O30" s="6" t="n">
+        <v>6.6</v>
       </c>
       <c r="P30" s="7" t="inlineStr">
         <is>
@@ -2825,7 +2952,12 @@
       <c r="Q30" s="2" t="inlineStr"/>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>Iconic delivery over Dre's G-Funk. Doggystyle defined an era.</t>
+          <t>Flow as personality. Delivery transcends lyrical content.</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -2886,9 +3018,8 @@
       <c r="N31" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O31" s="6">
-        <f>AVERAGE(J31:N31)</f>
-        <v/>
+      <c r="O31" s="6" t="n">
+        <v>5.6</v>
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
@@ -2898,7 +3029,12 @@
       <c r="Q31" s="2" t="inlineStr"/>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>G-Funk architect. The Chronic changed West Coast sound globally.</t>
+          <t>Producer-first. Lyricism secondary to sonic architecture.</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -2959,9 +3095,8 @@
       <c r="N32" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="O32" s="6">
-        <f>AVERAGE(J32:N32)</f>
-        <v/>
+      <c r="O32" s="6" t="n">
+        <v>7.2</v>
       </c>
       <c r="P32" s="7" t="inlineStr">
         <is>
@@ -2971,7 +3106,12 @@
       <c r="Q32" s="2" t="inlineStr"/>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>Bizarre Ride II. Quirky alternative to gangsta dominance.</t>
+          <t>Acrobatic, joyful wordplay. LA's alternative answer to De La Soul.</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Compound</t>
         </is>
       </c>
     </row>
@@ -3032,9 +3172,8 @@
       <c r="N33" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O33" s="6">
-        <f>AVERAGE(J33:N33)</f>
-        <v/>
+      <c r="O33" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
@@ -3044,7 +3183,12 @@
       <c r="Q33" s="2" t="inlineStr"/>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>The Infamous is peak Queens gothic menace.</t>
+          <t>Prodigy's paranoid poetry over Havoc's glacial loops.</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Compound</t>
         </is>
       </c>
     </row>
@@ -3105,9 +3249,8 @@
       <c r="N34" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O34" s="6">
-        <f>AVERAGE(J34:N34)</f>
-        <v/>
+      <c r="O34" s="6" t="n">
+        <v>6.8</v>
       </c>
       <c r="P34" s="7" t="inlineStr">
         <is>
@@ -3117,7 +3260,12 @@
       <c r="Q34" s="2" t="inlineStr"/>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>Dictionary of Bay slang. Slanguistics pioneer.</t>
+          <t>Slang inventor. Vocabulary innovation as primary art form.</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -3178,9 +3326,8 @@
       <c r="N35" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O35" s="6">
-        <f>AVERAGE(J35:N35)</f>
-        <v/>
+      <c r="O35" s="6" t="n">
+        <v>7.4</v>
       </c>
       <c r="P35" s="14" t="inlineStr">
         <is>
@@ -3194,7 +3341,12 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>Mecca and the Soul Brother. CL Smooth's introspection over Pete's soul.</t>
+          <t>Pete Rock's jazz-inflected production plus CL Smooth's introspective flows.</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Compound</t>
         </is>
       </c>
     </row>
@@ -3255,9 +3407,8 @@
       <c r="N36" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O36" s="6">
-        <f>AVERAGE(J36:N36)</f>
-        <v/>
+      <c r="O36" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="P36" s="7" t="inlineStr">
         <is>
@@ -3267,7 +3418,12 @@
       <c r="Q36" s="2" t="inlineStr"/>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>Guru's flat-affect wisdom over Primo's chopped jazz. Step In the Arena.</t>
+          <t>Guru's monotone wisdom over DJ Premier's crate-dug perfection.</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Compound</t>
         </is>
       </c>
     </row>
@@ -3328,9 +3484,8 @@
       <c r="N37" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O37" s="6">
-        <f>AVERAGE(J37:N37)</f>
-        <v/>
+      <c r="O37" s="6" t="n">
+        <v>7.2</v>
       </c>
       <c r="P37" s="14" t="inlineStr">
         <is>
@@ -3344,7 +3499,12 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>5% Nation theology in hip-hop. One for All is a conscious landmark.</t>
+          <t>5 Percenter theology meets Afrocentric fury. Sadat X and Grand Puba.</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Compound</t>
         </is>
       </c>
     </row>
@@ -3405,9 +3565,8 @@
       <c r="N38" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O38" s="6">
-        <f>AVERAGE(J38:N38)</f>
-        <v/>
+      <c r="O38" s="6" t="n">
+        <v>7</v>
       </c>
       <c r="P38" s="14" t="inlineStr">
         <is>
@@ -3421,7 +3580,12 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>To the East Blackwards. Black nationalist aesthetics in full bloom.</t>
+          <t>Black nationalist imagery and Afrocentric symbolism at maximum.</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Compound</t>
         </is>
       </c>
     </row>
@@ -3482,9 +3646,8 @@
       <c r="N39" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O39" s="6">
-        <f>AVERAGE(J39:N39)</f>
-        <v/>
+      <c r="O39" s="6" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3657,12 @@
       <c r="Q39" s="2" t="inlineStr"/>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>Punchline king. Lifestylez ov da Poor &amp; Dangerous is criminally slept on.</t>
+          <t>Punchline architect. Harlem's greatest. Wordplay density rivals anyone.</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -3555,9 +3723,8 @@
       <c r="N40" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O40" s="6">
-        <f>AVERAGE(J40:N40)</f>
-        <v/>
+      <c r="O40" s="6" t="n">
+        <v>7.4</v>
       </c>
       <c r="P40" s="7" t="inlineStr">
         <is>
@@ -3567,7 +3734,12 @@
       <c r="Q40" s="2" t="inlineStr"/>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>My Mind Playing Tricks on Me. Southern rap's dark psychological turn.</t>
+          <t>Pioneered Southern horror-gangsta. Scarface's lyrical foundation.</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Compound</t>
         </is>
       </c>
     </row>
@@ -3607,7 +3779,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Acacia</t>
+          <t>Sun Music</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
@@ -3628,9 +3800,8 @@
       <c r="N41" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O41" s="6">
-        <f>AVERAGE(J41:N41)</f>
-        <v/>
+      <c r="O41" s="6" t="n">
+        <v>7.8</v>
       </c>
       <c r="P41" s="14" t="inlineStr">
         <is>
@@ -3644,7 +3815,12 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>Innercity Griots. Improvised lyricism from the Good Life Café scene.</t>
+          <t>LA's jazz-rap underground. Aceyalone among the most technically gifted MCs ever.</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Compound</t>
         </is>
       </c>
     </row>
@@ -3705,9 +3881,8 @@
       <c r="N42" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O42" s="6">
-        <f>AVERAGE(J42:N42)</f>
-        <v/>
+      <c r="O42" s="6" t="n">
+        <v>7</v>
       </c>
       <c r="P42" s="14" t="inlineStr">
         <is>
@@ -3721,7 +3896,12 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>Reachin' (A New Refutation of Time and Space). Bohemian cool jazz.</t>
+          <t>Cool jazz-rap fusion. Ladybug Mecca one of the era's sharpest female voices.</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Compound</t>
         </is>
       </c>
     </row>
@@ -3782,9 +3962,8 @@
       <c r="N43" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O43" s="6">
-        <f>AVERAGE(J43:N43)</f>
-        <v/>
+      <c r="O43" s="6" t="n">
+        <v>7.4</v>
       </c>
       <c r="P43" s="14" t="inlineStr">
         <is>
@@ -3798,7 +3977,12 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>A Future Without a Past. Busta Rhymes's stage before his solo explosions.</t>
+          <t>Launched Busta Rhymes. Charlie Brown and Dinco D also strong voices.</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Compound</t>
         </is>
       </c>
     </row>
@@ -3859,9 +4043,8 @@
       <c r="N44" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O44" s="6">
-        <f>AVERAGE(J44:N44)</f>
-        <v/>
+      <c r="O44" s="6" t="n">
+        <v>7.8</v>
       </c>
       <c r="P44" s="7" t="inlineStr">
         <is>
@@ -3871,7 +4054,12 @@
       <c r="Q44" s="2" t="inlineStr"/>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>Hyperkinetic flow and energy. The Coming announced a superstar.</t>
+          <t>Hyper-kinetic delivery and flow complexity. One of the fastest MCs ever.</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -3932,9 +4120,8 @@
       <c r="N45" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O45" s="6">
-        <f>AVERAGE(J45:N45)</f>
-        <v/>
+      <c r="O45" s="6" t="n">
+        <v>8.4</v>
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
@@ -3944,7 +4131,12 @@
       <c r="Q45" s="2" t="inlineStr"/>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>Me Against the World / All Eyez on Me. Embodied generational pain.</t>
+          <t>Raw emotional intelligence. Political rage and personal vulnerability.</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -4005,9 +4197,8 @@
       <c r="N46" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O46" s="6">
-        <f>AVERAGE(J46:N46)</f>
-        <v/>
+      <c r="O46" s="6" t="n">
+        <v>8.6</v>
       </c>
       <c r="P46" s="7" t="inlineStr">
         <is>
@@ -4017,7 +4208,12 @@
       <c r="Q46" s="2" t="inlineStr"/>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>Reasonable Doubt to Blueprint. Business and artistry in concert.</t>
+          <t>Effortless mastery. Hustler's autobiography as album architecture.</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -4078,9 +4274,8 @@
       <c r="N47" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O47" s="6">
-        <f>AVERAGE(J47:N47)</f>
-        <v/>
+      <c r="O47" s="6" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
@@ -4090,7 +4285,12 @@
       <c r="Q47" s="2" t="inlineStr"/>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>Slim Shady LP. Technical rhyme density unchallenged in any era.</t>
+          <t>Most technically precise rapper. Internal rhyme density off the charts.</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -4151,9 +4351,8 @@
       <c r="N48" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="O48" s="6">
-        <f>AVERAGE(J48:N48)</f>
-        <v/>
+      <c r="O48" s="6" t="n">
+        <v>6.2</v>
       </c>
       <c r="P48" s="7" t="inlineStr">
         <is>
@@ -4163,7 +4362,12 @@
       <c r="Q48" s="2" t="inlineStr"/>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>Barking aggression as spiritual crisis. It's Dark and Hell Is Hot.</t>
+          <t>Primal confessional fury. Power through raw emotional delivery.</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -4224,9 +4428,8 @@
       <c r="N49" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O49" s="6">
-        <f>AVERAGE(J49:N49)</f>
-        <v/>
+      <c r="O49" s="6" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
@@ -4236,7 +4439,12 @@
       <c r="Q49" s="2" t="inlineStr"/>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>Miseducation is the high point of rap-soul fusion.</t>
+          <t>'Miseducation' — radical emotional honesty + technical precision.</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -4297,9 +4505,8 @@
       <c r="N50" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O50" s="6">
-        <f>AVERAGE(J50:N50)</f>
-        <v/>
+      <c r="O50" s="6" t="n">
+        <v>7.2</v>
       </c>
       <c r="P50" s="7" t="inlineStr">
         <is>
@@ -4309,7 +4516,12 @@
       <c r="Q50" s="2" t="inlineStr"/>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>Supa Dupa Fly. Avant-garde Southern vision over Timbaland.</t>
+          <t>Flow as futurist sculpture. Rhythm manipulation over traditional lyricism.</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -4370,9 +4582,8 @@
       <c r="N51" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O51" s="6">
-        <f>AVERAGE(J51:N51)</f>
-        <v/>
+      <c r="O51" s="6" t="n">
+        <v>8.6</v>
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
@@ -4382,7 +4593,12 @@
       <c r="Q51" s="2" t="inlineStr"/>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>Black on Both Sides. Renaissance man MC.</t>
+          <t>'Black on Both Sides' — blues, jazz, politics in one voice.</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -4443,9 +4659,8 @@
       <c r="N52" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O52" s="6">
-        <f>AVERAGE(J52:N52)</f>
-        <v/>
+      <c r="O52" s="6" t="n">
+        <v>8.4</v>
       </c>
       <c r="P52" s="7" t="inlineStr">
         <is>
@@ -4455,7 +4670,12 @@
       <c r="Q52" s="2" t="inlineStr"/>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>Reflection Eternal. Wordy, dense, deeply political.</t>
+          <t>Brooklyn's dense intellectual. Every bar packed with history.</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -4516,9 +4736,8 @@
       <c r="N53" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O53" s="6">
-        <f>AVERAGE(J53:N53)</f>
-        <v/>
+      <c r="O53" s="6" t="n">
+        <v>8.6</v>
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
@@ -4528,7 +4747,12 @@
       <c r="Q53" s="2" t="inlineStr"/>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>Aquemini. Andre 3000 is a singular artistic voice.</t>
+          <t>Andre 3000: genre-defying poet. Big Boi: underrated technical master.</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Compound</t>
         </is>
       </c>
     </row>
@@ -4589,9 +4813,8 @@
       <c r="N54" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O54" s="6">
-        <f>AVERAGE(J54:N54)</f>
-        <v/>
+      <c r="O54" s="6" t="n">
+        <v>3.8</v>
       </c>
       <c r="P54" s="7" t="inlineStr">
         <is>
@@ -4601,7 +4824,12 @@
       <c r="Q54" s="2" t="inlineStr"/>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>Ghetto D. Cash Money architect. Business over lyricism.</t>
+          <t>Mogul over MC. Influence is business, not bars.</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -4662,9 +4890,8 @@
       <c r="N55" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="O55" s="6">
-        <f>AVERAGE(J55:N55)</f>
-        <v/>
+      <c r="O55" s="6" t="n">
+        <v>7</v>
       </c>
       <c r="P55" s="14" t="inlineStr">
         <is>
@@ -4678,7 +4905,12 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>Come Home with Me. Pink fur and oblique rap logic.</t>
+          <t>Pink fur and slant rhymes. Harlem's most stylistically eccentric MC.</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -4739,9 +4971,8 @@
       <c r="N56" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="O56" s="6">
-        <f>AVERAGE(J56:N56)</f>
-        <v/>
+      <c r="O56" s="6" t="n">
+        <v>6.8</v>
       </c>
       <c r="P56" s="14" t="inlineStr">
         <is>
@@ -4755,7 +4986,12 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>Ill Na Na. Mafioso rap via the female gaze.</t>
+          <t>Aggressive feminine sexuality as lyrical weapon. Def Jam's answer to Lil Kim.</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -4816,9 +5052,8 @@
       <c r="N57" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="O57" s="6">
-        <f>AVERAGE(J57:N57)</f>
-        <v/>
+      <c r="O57" s="6" t="n">
+        <v>7</v>
       </c>
       <c r="P57" s="7" t="inlineStr">
         <is>
@@ -4828,7 +5063,12 @@
       <c r="Q57" s="2" t="inlineStr"/>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>Hard Core. Explicit female sexuality as power and disruption.</t>
+          <t>Radical sexual candor. Graphic feminism that rewrote what women could say in rap.</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -4853,7 +5093,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Late 99s</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -4889,9 +5129,8 @@
       <c r="N58" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O58" s="6">
-        <f>AVERAGE(J58:N58)</f>
-        <v/>
+      <c r="O58" s="6" t="n">
+        <v>5.8</v>
       </c>
       <c r="P58" s="14" t="inlineStr">
         <is>
@@ -4905,7 +5144,12 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>400 Degreez. Cash Money's breakout moment.</t>
+          <t>Cash Money's first star. New Orleans bounce meets street narrative.</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -4966,9 +5210,8 @@
       <c r="N59" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O59" s="6">
-        <f>AVERAGE(J59:N59)</f>
-        <v/>
+      <c r="O59" s="6" t="n">
+        <v>7</v>
       </c>
       <c r="P59" s="14" t="inlineStr">
         <is>
@@ -4982,7 +5225,12 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>Syllable count obsessive. Battle loss to LL never fully recovered from.</t>
+          <t>Battle rap legend. Technical skill occasionally undermined by ego.</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5250,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>Philly</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -5043,9 +5291,8 @@
       <c r="N60" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O60" s="6">
-        <f>AVERAGE(J60:N60)</f>
-        <v/>
+      <c r="O60" s="6" t="n">
+        <v>7.4</v>
       </c>
       <c r="P60" s="15" t="inlineStr">
         <is>
@@ -5059,7 +5306,12 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>Violent by Design. Horror-core meets political paranoia underground.</t>
+          <t>Philadelphia underground. Vinnie Paz's dense, conspiratorial lyricism.</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -5120,9 +5372,8 @@
       <c r="N61" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O61" s="6">
-        <f>AVERAGE(J61:N61)</f>
-        <v/>
+      <c r="O61" s="6" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
@@ -5132,7 +5383,12 @@
       <c r="Q61" s="2" t="inlineStr"/>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>Capital Punishment. First Latino rapper to go platinum solo.</t>
+          <t>First Latin rapper to go platinum solo. Multisyllabic rhyme virtuoso.</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -5142,12 +5398,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Nas feat. AZ</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -5193,9 +5449,8 @@
       <c r="N62" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O62" s="6">
-        <f>AVERAGE(J62:N62)</f>
-        <v/>
+      <c r="O62" s="6" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="P62" s="14" t="inlineStr">
         <is>
@@ -5204,12 +5459,17 @@
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>AZ's solo career less documented than Nas; scored as AZ</t>
+          <t>Solo career less documented than Nas; scored on his own body of work.</t>
         </is>
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>Life's a Bitch collab. AZ's verse is among the finest in rap history.</t>
+          <t>One of the era's most underrated lyricists. 'Doe or Die' (1995) a classic; his 'Life's a Bitch' verse is all-time.</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -5270,9 +5530,8 @@
       <c r="N63" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="O63" s="6">
-        <f>AVERAGE(J63:N63)</f>
-        <v/>
+      <c r="O63" s="6" t="n">
+        <v>8.4</v>
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
@@ -5282,7 +5541,12 @@
       <c r="Q63" s="2" t="inlineStr"/>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>College Dropout to 808s. Artistic ambition reshapes each era.</t>
+          <t>Conceptual ambition as primary engine. Each album a reinvention.</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -5343,9 +5607,8 @@
       <c r="N64" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O64" s="6">
-        <f>AVERAGE(J64:N64)</f>
-        <v/>
+      <c r="O64" s="6" t="n">
+        <v>8.4</v>
       </c>
       <c r="P64" s="7" t="inlineStr">
         <is>
@@ -5355,7 +5618,12 @@
       <c r="Q64" s="2" t="inlineStr"/>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>Tha Carter III. Mixtape era Wayne is the definition of peak lyricism.</t>
+          <t>Simile machine at peak. Abstract metaphor-stacking as freestyle sport.</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -5416,9 +5684,8 @@
       <c r="N65" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O65" s="6">
-        <f>AVERAGE(J65:N65)</f>
-        <v/>
+      <c r="O65" s="6" t="n">
+        <v>7.2</v>
       </c>
       <c r="P65" s="7" t="inlineStr">
         <is>
@@ -5428,7 +5695,12 @@
       <c r="Q65" s="2" t="inlineStr"/>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>King. Claimed the ATL throne and the trap blueprint.</t>
+          <t>King of the South. Trap's emotional architect.</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -5489,9 +5761,8 @@
       <c r="N66" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="O66" s="6">
-        <f>AVERAGE(J66:N66)</f>
-        <v/>
+      <c r="O66" s="6" t="n">
+        <v>4.8</v>
       </c>
       <c r="P66" s="7" t="inlineStr">
         <is>
@@ -5501,7 +5772,12 @@
       <c r="Q66" s="2" t="inlineStr"/>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>Trap God. Prolific mixtape movement godfather.</t>
+          <t>Vibe and charisma over craft. Trap music's spiritual godfather.</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -5562,9 +5838,8 @@
       <c r="N67" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O67" s="6">
-        <f>AVERAGE(J67:N67)</f>
-        <v/>
+      <c r="O67" s="6" t="n">
+        <v>8.4</v>
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
@@ -5574,7 +5849,12 @@
       <c r="Q67" s="2" t="inlineStr"/>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>Supreme Clientele. Dense, dazzling, associative.</t>
+          <t>Stream-of-consciousness genius. Dense slang, vivid scene-painting.</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -5635,9 +5915,8 @@
       <c r="N68" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O68" s="6">
-        <f>AVERAGE(J68:N68)</f>
-        <v/>
+      <c r="O68" s="6" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="P68" s="7" t="inlineStr">
         <is>
@@ -5647,7 +5926,12 @@
       <c r="Q68" s="2" t="inlineStr"/>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>Madvillainy. The mask, the myth, the syllable wizardry.</t>
+          <t>The supervillain. Labyrinths of internal rhyme no one has fully mapped.</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -5708,9 +5992,8 @@
       <c r="N69" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O69" s="6">
-        <f>AVERAGE(J69:N69)</f>
-        <v/>
+      <c r="O69" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
@@ -5720,7 +6003,12 @@
       <c r="Q69" s="2" t="inlineStr"/>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>Be. Elevated conscious rap into mainstream Grammy territory.</t>
+          <t>Chicago's philosopher-MC. Ernie Barnes paintings in verse form.</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -5781,9 +6069,8 @@
       <c r="N70" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O70" s="6">
-        <f>AVERAGE(J70:N70)</f>
-        <v/>
+      <c r="O70" s="6" t="n">
+        <v>6.6</v>
       </c>
       <c r="P70" s="7" t="inlineStr">
         <is>
@@ -5793,7 +6080,12 @@
       <c r="Q70" s="2" t="inlineStr"/>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>Word of Mouf. Playful Southern rapping with genuine lyrical edge.</t>
+          <t>Comic virtuosity. Punchline timing as precision instrument.</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -5854,9 +6146,8 @@
       <c r="N71" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="O71" s="6">
-        <f>AVERAGE(J71:N71)</f>
-        <v/>
+      <c r="O71" s="6" t="n">
+        <v>5.4</v>
       </c>
       <c r="P71" s="7" t="inlineStr">
         <is>
@@ -5866,7 +6157,12 @@
       <c r="Q71" s="2" t="inlineStr"/>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>Let's Get It: Thug Motivation 101. Trap's motivational speaker.</t>
+          <t>Trap's motivational orator. Delivery and charisma over craft.</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -5927,9 +6223,8 @@
       <c r="N72" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="O72" s="6">
-        <f>AVERAGE(J72:N72)</f>
-        <v/>
+      <c r="O72" s="6" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="P72" s="7" t="inlineStr">
         <is>
@@ -5939,7 +6234,12 @@
       <c r="Q72" s="2" t="inlineStr"/>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>Food &amp; Liquor. Skate kid from Chicago with dictionary flow.</t>
+          <t>Conceptually sui generis. 'Dumb It Down' a rebuke of simplicity.</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -6000,9 +6300,8 @@
       <c r="N73" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O73" s="6">
-        <f>AVERAGE(J73:N73)</f>
-        <v/>
+      <c r="O73" s="6" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
@@ -6012,7 +6311,12 @@
       <c r="Q73" s="2" t="inlineStr"/>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>The World Is Yours. Southern rap's great novelist.</t>
+          <t>Houston's great novelist. Psychological interior in gangsta rap.</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -6073,9 +6377,8 @@
       <c r="N74" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O74" s="6">
-        <f>AVERAGE(J74:N74)</f>
-        <v/>
+      <c r="O74" s="6" t="n">
+        <v>8.4</v>
       </c>
       <c r="P74" s="7" t="inlineStr">
         <is>
@@ -6085,7 +6388,12 @@
       <c r="Q74" s="2" t="inlineStr"/>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>None Shall Pass. Largest vocabulary in measured rap.</t>
+          <t>NLP-verified largest unique vocabulary in rap. Dense abstract imagery.</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6403,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>JE</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Ghostface / Fishscale era</t>
+          <t>Jadakiss</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -6115,40 +6423,39 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Wu-Tang/Soul</t>
+          <t>East Coast Grit</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Def Jam</t>
+          <t>Ruff Ryders</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>2006</v>
-      </c>
-      <c r="J75" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="K75" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L75" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M75" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="N75" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="O75" s="6">
-        <f>AVERAGE(J75:N75)</f>
-        <v/>
+        <v>2001</v>
+      </c>
+      <c r="J75" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="K75" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L75" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M75" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N75" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="O75" s="6" t="n">
+        <v>7.2</v>
       </c>
       <c r="P75" s="14" t="inlineStr">
         <is>
@@ -6157,12 +6464,17 @@
       </c>
       <c r="Q75" s="2" t="inlineStr">
         <is>
-          <t>Scored specifically for Fishscale-era peak; earlier work variable</t>
+          <t>Well-regarded but limited scholarly analysis</t>
         </is>
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>Fishscale is Ghostface at peak: cinematic, dense, unmatched.</t>
+          <t>Gravelly-voiced Yonkers MC. Punchline economy and street credibility.</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -6172,12 +6484,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>JE</t>
+          <t>FK2</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Jadakiss</t>
+          <t>50 Cent</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -6197,49 +6509,49 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>East Coast Grit</t>
+          <t>G-Unit Boom Bap</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Ruff Ryders</t>
+          <t>Shady/Aftermath</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>2001</v>
-      </c>
-      <c r="J76" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K76" s="10" t="n">
-        <v>7</v>
+        <v>2003</v>
+      </c>
+      <c r="J76" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K76" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="L76" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="M76" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N76" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="O76" s="6">
-        <f>AVERAGE(J76:N76)</f>
-        <v/>
-      </c>
-      <c r="P76" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q76" s="2" t="inlineStr">
-        <is>
-          <t>Well-regarded but limited scholarly analysis</t>
-        </is>
-      </c>
+      <c r="M76" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N76" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="O76" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="P76" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>Why? punchline king. LOX member whose grimace became iconic.</t>
+          <t>Bulletproof charisma. Street narrative over lyrical complexity.</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -6249,17 +6561,17 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>FK2</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>50 Cent</t>
+          <t>Three 6 Mafia</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -6274,25 +6586,25 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>G-Unit Boom Bap</t>
+          <t>Memphis Horrorcore</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Shady/Aftermath</t>
+          <t>Hypnotize Minds</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>2003</v>
-      </c>
-      <c r="J77" s="9" t="n">
-        <v>6</v>
+        <v>1995</v>
+      </c>
+      <c r="J77" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="K77" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="L77" s="10" t="n">
-        <v>7</v>
+      <c r="L77" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="M77" s="9" t="n">
         <v>6</v>
@@ -6300,19 +6612,27 @@
       <c r="N77" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O77" s="6">
-        <f>AVERAGE(J77:N77)</f>
-        <v/>
-      </c>
-      <c r="P77" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="O77" s="6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="P77" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>Oscar win elevated profile; lyrical analysis limited</t>
+        </is>
+      </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>Get Rich or Die Tryin'. Commercial domination built on street cred.</t>
+          <t>Oscar-winning Southern horror-rap. Pioneered the dark triplet flow.</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>Compound</t>
         </is>
       </c>
     </row>
@@ -6322,12 +6642,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>UG</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Three 6 Mafia</t>
+          <t>UGK</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -6347,49 +6667,49 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Memphis Horrorcore</t>
+          <t>Texas Funk Rap</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Sony</t>
+          <t>Jive</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>1995</v>
-      </c>
-      <c r="J78" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K78" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L78" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M78" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N78" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="O78" s="6">
-        <f>AVERAGE(J78:N78)</f>
-        <v/>
-      </c>
-      <c r="P78" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q78" s="2" t="inlineStr">
-        <is>
-          <t>Oscar win elevated profile; lyrical analysis limited</t>
-        </is>
-      </c>
+        <v>1992</v>
+      </c>
+      <c r="J78" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K78" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L78" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M78" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N78" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="O78" s="6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="P78" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>Tear da Club Up. Memphis horrorcore before trap existed.</t>
+          <t>Bun B and Pimp C. Texas's most complete rap duo.</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>Compound</t>
         </is>
       </c>
     </row>
@@ -6399,12 +6719,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>TL2</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>UGK</t>
+          <t>Trae Tha Truth</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -6424,45 +6744,53 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Texas Funk Rap</t>
+          <t>Houston Chopped</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Jive</t>
+          <t>Asylum</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>1992</v>
-      </c>
-      <c r="J79" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K79" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L79" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M79" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N79" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="O79" s="6">
-        <f>AVERAGE(J79:N79)</f>
-        <v/>
-      </c>
-      <c r="P79" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q79" s="2" t="inlineStr"/>
+        <v>2003</v>
+      </c>
+      <c r="J79" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K79" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L79" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M79" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N79" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="O79" s="6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="P79" s="15" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>Regional significance; limited national critical record</t>
+        </is>
+      </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>Ridin' Dirty. Bun B and Pimp C: Southern rap's purist duo.</t>
+          <t>Houston's street ambassador. Chopped-and-screwed delivery as identity.</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -6472,17 +6800,17 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>TL2</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Trae Tha Truth</t>
+          <t>Aceyalone</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -6492,54 +6820,58 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Abstract</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Houston Chopped</t>
+          <t>LA Free Jazz Rap</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Asylum</t>
+          <t>Project Blowed</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>2003</v>
-      </c>
-      <c r="J80" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K80" s="10" t="n">
-        <v>7</v>
+        <v>1993</v>
+      </c>
+      <c r="J80" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K80" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="L80" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="M80" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N80" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="O80" s="6">
-        <f>AVERAGE(J80:N80)</f>
-        <v/>
-      </c>
-      <c r="P80" s="15" t="inlineStr">
-        <is>
-          <t>L</t>
+      <c r="M80" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N80" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="O80" s="6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="P80" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>Regional significance; limited national critical record</t>
+          <t>Highly regarded in underground circles; thin mainstream documentation</t>
         </is>
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>Restless. Houston street reporting with slow, heavy flow.</t>
+          <t>LA underground legend. Freestyle Fellowship's most technically gifted MC.</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -6549,17 +6881,17 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>RA2</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Aceyalone</t>
+          <t>Raekwon</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>NYC</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -6569,54 +6901,54 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Abstract</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>LA Free Jazz Rap</t>
+          <t>Wu-Tang/Mafioso</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Project Blowed</t>
+          <t>Loud</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="J81" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="K81" s="12" t="n">
+      <c r="K81" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L81" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L81" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="M81" s="11" t="n">
         <v>8</v>
       </c>
       <c r="N81" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="O81" s="6">
-        <f>AVERAGE(J81:N81)</f>
-        <v/>
-      </c>
-      <c r="P81" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q81" s="2" t="inlineStr">
-        <is>
-          <t>Highly regarded in underground circles; thin mainstream documentation</t>
-        </is>
-      </c>
+      <c r="O81" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="P81" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>All Balls Don't Bounce. Project Blowed's academic underground MC.</t>
+          <t>'Only Built 4 Cuban Linx' — the Godfather Part II of rap albums.</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -6626,12 +6958,12 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>RA2</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Raekwon</t>
+          <t>El-P</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -6646,40 +6978,39 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Wu-Tang/Mafioso</t>
+          <t>Industrial Boom Bap</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Loud</t>
+          <t>Def Jux</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>1995</v>
+        <v>2002</v>
       </c>
       <c r="J82" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="K82" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L82" s="12" t="n">
+      <c r="K82" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="M82" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N82" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="O82" s="6">
-        <f>AVERAGE(J82:N82)</f>
-        <v/>
+      <c r="L82" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M82" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="N82" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="O82" s="6" t="n">
+        <v>8.4</v>
       </c>
       <c r="P82" s="7" t="inlineStr">
         <is>
@@ -6689,7 +7020,12 @@
       <c r="Q82" s="2" t="inlineStr"/>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>Only Built 4 Cuban Linx. Mafioso rap as cinematic epic.</t>
+          <t>Company Flow / Run The Jewels architect. Dystopian sonic vision.</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -6699,17 +7035,17 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>BU</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>El-P</t>
+          <t>Brother Ali</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -6719,50 +7055,58 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Industrial Boom Bap</t>
+          <t>Boom Bap/Soul</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Def Jux</t>
+          <t>Rhymesayers</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>2002</v>
-      </c>
-      <c r="J83" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K83" s="12" t="n">
-        <v>9</v>
+        <v>2000</v>
+      </c>
+      <c r="J83" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K83" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="L83" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="M83" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="N83" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="O83" s="6">
-        <f>AVERAGE(J83:N83)</f>
-        <v/>
-      </c>
-      <c r="P83" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="M83" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N83" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="O83" s="6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="P83" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>Well-regarded in conscious rap; limited broader academic attention</t>
+        </is>
+      </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
-          <t>Fantastic Damage. Dystopian industrial rap from the Def Jux era.</t>
+          <t>Minneapolis conscious rapper. Raw emotional honesty over Ant's production.</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -6772,17 +7116,17 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>BU</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Brother Ali</t>
+          <t>Immortal Technique</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>NYC</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -6792,21 +7136,21 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Political</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Boom Bap/Soul</t>
+          <t>Underground Agit-Rap</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Rhymesayers</t>
+          <t>Viper</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="J84" s="10" t="n">
         <v>7</v>
@@ -6820,12 +7164,11 @@
       <c r="M84" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="N84" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="O84" s="6">
-        <f>AVERAGE(J84:N84)</f>
-        <v/>
+      <c r="N84" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="O84" s="6" t="n">
+        <v>7.6</v>
       </c>
       <c r="P84" s="14" t="inlineStr">
         <is>
@@ -6834,12 +7177,17 @@
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>Well-regarded in conscious rap; limited broader academic attention</t>
+          <t>Heavy political reputation; thin formal lyrical analysis</t>
         </is>
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>Shadows on the Sun. Minneapolis underground social conscience.</t>
+          <t>Most politically radical rapper in the genre. Conspiracy and revolution.</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -6849,74 +7197,74 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>KL</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Immortal Technique</t>
+          <t>Kendrick Lamar</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Political</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Underground Agit-Rap</t>
+          <t>Compton Concept</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Viper</t>
+          <t>Top Dawg</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>2001</v>
-      </c>
-      <c r="J85" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K85" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L85" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M85" s="10" t="n">
-        <v>7</v>
+        <v>2011</v>
+      </c>
+      <c r="J85" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="K85" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="L85" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="M85" s="13" t="n">
+        <v>10</v>
       </c>
       <c r="N85" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="O85" s="6">
-        <f>AVERAGE(J85:N85)</f>
-        <v/>
-      </c>
-      <c r="P85" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q85" s="2" t="inlineStr">
-        <is>
-          <t>Heavy political reputation; thin formal lyrical analysis</t>
-        </is>
-      </c>
+      <c r="O85" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="P85" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
       <c r="R85" s="2" t="inlineStr">
         <is>
-          <t>Revolutionary Vol. 2. Conspiracy rap with genuine rhetorical force.</t>
+          <t>The complete package. Every dimension at peak. Pulitzer Prize.</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -6926,17 +7274,17 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>KL</t>
+          <t>JC</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Kendrick Lamar</t>
+          <t>J. Cole</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -6951,35 +7299,34 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Compton Concept</t>
+          <t>Soulful Boom Bap</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Top Dawg</t>
+          <t>Dreamville</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
         <v>2011</v>
       </c>
-      <c r="J86" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="K86" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="L86" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="M86" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="N86" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="O86" s="6">
-        <f>AVERAGE(J86:N86)</f>
-        <v/>
+      <c r="J86" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K86" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L86" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M86" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N86" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="O86" s="6" t="n">
+        <v>8.4</v>
       </c>
       <c r="P86" s="7" t="inlineStr">
         <is>
@@ -6989,7 +7336,12 @@
       <c r="Q86" s="2" t="inlineStr"/>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>good kid m.A.A.d city / TPAB. The most complete MC since Nas.</t>
+          <t>Working-class emotional intelligence. Deep narrative craft.</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -6999,17 +7351,17 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>YT</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Drake</t>
+          <t>Young Thug</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -7019,40 +7371,39 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Party/Pop</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Melodic Rap</t>
+          <t>Melodic Trap</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>OVO/Young Money</t>
+          <t>300 Entertainment</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>2006</v>
-      </c>
-      <c r="J87" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K87" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L87" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M87" s="10" t="n">
-        <v>7</v>
+        <v>2011</v>
+      </c>
+      <c r="J87" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K87" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M87" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="N87" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O87" s="6">
-        <f>AVERAGE(J87:N87)</f>
-        <v/>
+      <c r="O87" s="6" t="n">
+        <v>5.2</v>
       </c>
       <c r="P87" s="7" t="inlineStr">
         <is>
@@ -7062,7 +7413,12 @@
       <c r="Q87" s="2" t="inlineStr"/>
       <c r="R87" s="2" t="inlineStr">
         <is>
-          <t>Take Care. Emotional rap at massive commercial scale.</t>
+          <t>Melody over meaning. Vocal texture as primary instrument.</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -7072,12 +7428,12 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>JC</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>J. Cole</t>
+          <t>Future</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -7092,40 +7448,39 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Trap/Drill</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Soulful Boom Bap</t>
+          <t>Auto-Tune Trap</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Dreamville</t>
+          <t>A1/Epic</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>2011</v>
-      </c>
-      <c r="J88" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K88" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L88" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M88" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N88" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="O88" s="6">
-        <f>AVERAGE(J88:N88)</f>
-        <v/>
+        <v>2012</v>
+      </c>
+      <c r="J88" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K88" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L88" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M88" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N88" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="O88" s="6" t="n">
+        <v>5.2</v>
       </c>
       <c r="P88" s="7" t="inlineStr">
         <is>
@@ -7135,7 +7490,12 @@
       <c r="Q88" s="2" t="inlineStr"/>
       <c r="R88" s="2" t="inlineStr">
         <is>
-          <t>2014 Forest Hills Drive. Self-produced introspection at scale.</t>
+          <t>Emotional auto-tune as confession. Vibe over lyrical architecture.</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -7145,17 +7505,17 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>YT</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Young Thug</t>
+          <t>Chance the Rapper</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -7165,40 +7525,39 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Melodic Trap</t>
+          <t>Chicago Gospel Rap</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>300 Entertainment</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>2011</v>
-      </c>
-      <c r="J89" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K89" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L89" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M89" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N89" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="O89" s="6">
-        <f>AVERAGE(J89:N89)</f>
-        <v/>
+        <v>2013</v>
+      </c>
+      <c r="J89" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K89" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L89" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M89" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N89" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="O89" s="6" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="P89" s="7" t="inlineStr">
         <is>
@@ -7208,7 +7567,12 @@
       <c r="Q89" s="2" t="inlineStr"/>
       <c r="R89" s="2" t="inlineStr">
         <is>
-          <t>Barter 6. Recontextualized flow as melodic instrument.</t>
+          <t>Joyful complexity. Gospel cadences and Chicago love letters.</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -7218,17 +7582,17 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Future</t>
+          <t>Earl Sweatshirt</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -7238,40 +7602,39 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Trap/Drill</t>
+          <t>Abstract</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Auto-Tune Trap</t>
+          <t>Odd Future/Boom Bap</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>A1/Epic</t>
+          <t>Tan Cressida</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>2012</v>
-      </c>
-      <c r="J90" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K90" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L90" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="M90" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N90" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="O90" s="6">
-        <f>AVERAGE(J90:N90)</f>
-        <v/>
+        <v>2010</v>
+      </c>
+      <c r="J90" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K90" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L90" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M90" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="N90" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="O90" s="6" t="n">
+        <v>8.4</v>
       </c>
       <c r="P90" s="7" t="inlineStr">
         <is>
@@ -7281,7 +7644,12 @@
       <c r="Q90" s="2" t="inlineStr"/>
       <c r="R90" s="2" t="inlineStr">
         <is>
-          <t>DS2. Emotional ambivalence as trap subgenre.</t>
+          <t>Compression and grief as poetics. Dense abstract imagery.</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -7291,17 +7659,17 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>MM</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Chance the Rapper</t>
+          <t>Meek Mill</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>Philly</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -7311,40 +7679,39 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Chicago Gospel Rap</t>
+          <t>Philly Trap</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Maybach Music</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>2013</v>
-      </c>
-      <c r="J91" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K91" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L91" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M91" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N91" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="O91" s="6">
-        <f>AVERAGE(J91:N91)</f>
-        <v/>
+        <v>2012</v>
+      </c>
+      <c r="J91" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K91" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L91" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M91" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N91" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="O91" s="6" t="n">
+        <v>6.2</v>
       </c>
       <c r="P91" s="7" t="inlineStr">
         <is>
@@ -7354,7 +7721,12 @@
       <c r="Q91" s="2" t="inlineStr"/>
       <c r="R91" s="2" t="inlineStr">
         <is>
-          <t>Coloring Book. Gospel rap from Chicago's south side.</t>
+          <t>Visceral urgency. Philadelphia streets in raw kinetic delivery.</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -7364,17 +7736,17 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Earl Sweatshirt</t>
+          <t>A$AP Rocky</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>NYC</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -7384,40 +7756,39 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Abstract</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Odd Future/Boom Bap</t>
+          <t>Cloud Rap/Fashion</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Tan Cressida</t>
+          <t>A$AP/RCA</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>2010</v>
-      </c>
-      <c r="J92" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="K92" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L92" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M92" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="N92" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="O92" s="6">
-        <f>AVERAGE(J92:N92)</f>
-        <v/>
+        <v>2011</v>
+      </c>
+      <c r="J92" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K92" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L92" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M92" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N92" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="O92" s="6" t="n">
+        <v>6</v>
       </c>
       <c r="P92" s="7" t="inlineStr">
         <is>
@@ -7427,7 +7798,12 @@
       <c r="Q92" s="2" t="inlineStr"/>
       <c r="R92" s="2" t="inlineStr">
         <is>
-          <t>I Don't Like Shit. Dense, interior, self-lacerating.</t>
+          <t>Aesthetic as content. Flow and texture over lyrical substance.</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -7437,17 +7813,17 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>MM</t>
+          <t>NM</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Meek Mill</t>
+          <t>Nicki Minaj</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>NYC</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -7457,40 +7833,39 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Philly Trap</t>
+          <t>Pop Rap/Dancehall</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Maybach Music</t>
+          <t>Young Money</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>2012</v>
-      </c>
-      <c r="J93" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K93" s="9" t="n">
-        <v>6</v>
+        <v>2010</v>
+      </c>
+      <c r="J93" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K93" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="L93" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="M93" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N93" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="O93" s="6">
-        <f>AVERAGE(J93:N93)</f>
-        <v/>
+      <c r="M93" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N93" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="O93" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="P93" s="7" t="inlineStr">
         <is>
@@ -7500,7 +7875,12 @@
       <c r="Q93" s="2" t="inlineStr"/>
       <c r="R93" s="2" t="inlineStr">
         <is>
-          <t>Dreams and Nightmares. Philly grit at arena scale.</t>
+          <t>Technical precision and alter-ego theatrics. 'Monster' verse.</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -7510,17 +7890,17 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>A$AP Rocky</t>
+          <t>Vince Staples</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -7530,40 +7910,39 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Political</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Cloud Rap/Fashion</t>
+          <t>West Coast Minimalism</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>A$AP/RCA</t>
+          <t>Def Jam</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>2011</v>
-      </c>
-      <c r="J94" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K94" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L94" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="M94" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N94" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="O94" s="6">
-        <f>AVERAGE(J94:N94)</f>
-        <v/>
+        <v>2012</v>
+      </c>
+      <c r="J94" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K94" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L94" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M94" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N94" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="O94" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="P94" s="7" t="inlineStr">
         <is>
@@ -7573,7 +7952,12 @@
       <c r="Q94" s="2" t="inlineStr"/>
       <c r="R94" s="2" t="inlineStr">
         <is>
-          <t>Long.Live.ASAP. Harlem avant-garde aesthetics in rap form.</t>
+          <t>Deadpan sociologist. Minimalist language doing maximum structural work.</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -7583,17 +7967,17 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>NM</t>
+          <t>BK2</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Nicki Minaj</t>
+          <t>Big K.R.I.T.</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -7608,35 +7992,34 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Pop Rap/Dancehall</t>
+          <t>Mississippi Soul Rap</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Young Money</t>
+          <t>Def Jam</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
         <v>2010</v>
       </c>
-      <c r="J95" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="K95" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L95" s="10" t="n">
-        <v>7</v>
+      <c r="J95" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K95" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L95" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="M95" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="N95" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="O95" s="6">
-        <f>AVERAGE(J95:N95)</f>
-        <v/>
+      <c r="N95" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="O95" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="P95" s="7" t="inlineStr">
         <is>
@@ -7646,7 +8029,12 @@
       <c r="Q95" s="2" t="inlineStr"/>
       <c r="R95" s="2" t="inlineStr">
         <is>
-          <t>Pink Friday. Technical bars meet pop domination.</t>
+          <t>Mississippi throwback futurist. Southern soul and lyrical ambition fused.</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -7656,17 +8044,17 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Vince Staples</t>
+          <t>Run The Jewels</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -7681,35 +8069,34 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>West Coast Minimalism</t>
+          <t>Industrial Boom Bap</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Def Jam</t>
+          <t>Mass Appeal</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>2012</v>
-      </c>
-      <c r="J96" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K96" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L96" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M96" s="11" t="n">
-        <v>8</v>
+        <v>2013</v>
+      </c>
+      <c r="J96" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K96" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L96" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M96" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="N96" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="O96" s="6">
-        <f>AVERAGE(J96:N96)</f>
-        <v/>
+      <c r="O96" s="6" t="n">
+        <v>8.4</v>
       </c>
       <c r="P96" s="7" t="inlineStr">
         <is>
@@ -7719,7 +8106,12 @@
       <c r="Q96" s="2" t="inlineStr"/>
       <c r="R96" s="2" t="inlineStr">
         <is>
-          <t>Summertime '06. Long Beach noir, economical and bleak.</t>
+          <t>El-P and Killer Mike. Most politically urgent rap duo since PE.</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>Compound</t>
         </is>
       </c>
     </row>
@@ -7729,12 +8121,12 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>BK2</t>
+          <t>KM</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Big K.R.I.T.</t>
+          <t>Killer Mike</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -7749,21 +8141,21 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Political</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Mississippi Soul Rap</t>
+          <t>Atlanta Boom Bap</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Def Jam</t>
+          <t>SMC Recordings</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>2010</v>
+        <v>2003</v>
       </c>
       <c r="J97" s="11" t="n">
         <v>8</v>
@@ -7777,12 +8169,11 @@
       <c r="M97" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="N97" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="O97" s="6">
-        <f>AVERAGE(J97:N97)</f>
-        <v/>
+      <c r="N97" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="O97" s="6" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="P97" s="7" t="inlineStr">
         <is>
@@ -7792,7 +8183,12 @@
       <c r="Q97" s="2" t="inlineStr"/>
       <c r="R97" s="2" t="inlineStr">
         <is>
-          <t>Live from the Underground. Southern rap's self-produced soul heir.</t>
+          <t>RTJ's political conscience. Atlanta's most morally serious MC.</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -7802,12 +8198,12 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Run The Jewels</t>
+          <t>Freddie Gibbs</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -7822,40 +8218,39 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Political</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Industrial Boom Bap</t>
+          <t>Gangsta Boom Bap</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Mass Appeal</t>
+          <t>ESGN</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>2013</v>
+        <v>2004</v>
       </c>
       <c r="J98" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="K98" s="12" t="n">
+      <c r="K98" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L98" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L98" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M98" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="N98" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="O98" s="6">
-        <f>AVERAGE(J98:N98)</f>
-        <v/>
+      <c r="M98" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N98" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="O98" s="6" t="n">
+        <v>7.8</v>
       </c>
       <c r="P98" s="7" t="inlineStr">
         <is>
@@ -7865,7 +8260,12 @@
       <c r="Q98" s="2" t="inlineStr"/>
       <c r="R98" s="2" t="inlineStr">
         <is>
-          <t>RTJ2. El-P + Killer Mike = relentless political rap.</t>
+          <t>Gary Indiana's finest. Technical gangsta rap with jazz-rap production.</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -7875,12 +8275,12 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>KM</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Killer Mike</t>
+          <t>Migos</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -7895,40 +8295,39 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Political</t>
+          <t>Trap/Drill</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Boom Bap</t>
+          <t>Atlanta Triplet Trap</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>SMC Recordings</t>
+          <t>Quality Control</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>2003</v>
-      </c>
-      <c r="J99" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K99" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L99" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M99" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N99" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="O99" s="6">
-        <f>AVERAGE(J99:N99)</f>
-        <v/>
+        <v>2013</v>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M99" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N99" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O99" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="P99" s="7" t="inlineStr">
         <is>
@@ -7938,7 +8337,12 @@
       <c r="Q99" s="2" t="inlineStr"/>
       <c r="R99" s="2" t="inlineStr">
         <is>
-          <t>R.A.P. Music. Atlanta social critique at its angriest best.</t>
+          <t>Triplet flow inventors. Cultural influence far exceeds lyrical complexity.</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>Compound</t>
         </is>
       </c>
     </row>
@@ -7948,17 +8352,17 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>BI2</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Iggy Azalea</t>
+          <t>Big Sean</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -7973,45 +8377,53 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Southern Trap Pop</t>
+          <t>Detroit Pop Rap</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Grand Hustle</t>
+          <t>G.O.O.D.</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>2014</v>
-      </c>
-      <c r="J100" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K100" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="L100" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M100" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="N100" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="O100" s="6">
-        <f>AVERAGE(J100:N100)</f>
-        <v/>
-      </c>
-      <c r="P100" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q100" s="2" t="inlineStr"/>
+        <v>2011</v>
+      </c>
+      <c r="J100" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K100" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L100" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M100" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N100" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="O100" s="6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="P100" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>Commercial success; critical reception mixed; thin formal analysis</t>
+        </is>
+      </c>
       <c r="R100" s="2" t="inlineStr">
         <is>
-          <t>Fancy. Commercial peak; authenticity debates dominated reception.</t>
+          <t>Detroit MC. Punchlines over conceptual depth. 'One Man Can Change The World'.</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -8021,17 +8433,17 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Freddie Gibbs</t>
+          <t>Tierra Whack</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>Philly</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -8041,50 +8453,58 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Gangsta Boom Bap</t>
+          <t>Experimental Pop Rap</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>ESGN</t>
+          <t>Interscope</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>2004</v>
-      </c>
-      <c r="J101" s="11" t="n">
-        <v>8</v>
+        <v>2018</v>
+      </c>
+      <c r="J101" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="K101" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L101" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M101" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N101" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="O101" s="6">
-        <f>AVERAGE(J101:N101)</f>
-        <v/>
-      </c>
-      <c r="P101" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="L101" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M101" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N101" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="O101" s="6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="P101" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>Breakout 2018; critical buzz high but career short; scoring may shift</t>
+        </is>
+      </c>
       <c r="R101" s="2" t="inlineStr">
         <is>
-          <t>Piñata. Madlib collab reinvented his career and the genre.</t>
+          <t>'Whack World' — 15 one-minute songs as unified concept. Wholly original.</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -8094,17 +8514,17 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Migos</t>
+          <t>Noname</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -8114,40 +8534,39 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Trap/Drill</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Triplet Trap</t>
+          <t>Chicago Jazz Rap</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>2013</v>
-      </c>
-      <c r="J102" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K102" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="L102" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M102" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N102" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="O102" s="6">
-        <f>AVERAGE(J102:N102)</f>
-        <v/>
+        <v>2016</v>
+      </c>
+      <c r="J102" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K102" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L102" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M102" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N102" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="O102" s="6" t="n">
+        <v>8.4</v>
       </c>
       <c r="P102" s="7" t="inlineStr">
         <is>
@@ -8157,7 +8576,12 @@
       <c r="Q102" s="2" t="inlineStr"/>
       <c r="R102" s="2" t="inlineStr">
         <is>
-          <t>Culture. Triplet flow codified an era; lyricism secondary.</t>
+          <t>Chicago's most literary voice. Jazz cadences and political awakening.</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -8167,12 +8591,12 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>BI2</t>
+          <t>SZ</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Big Sean</t>
+          <t>Saba</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -8187,54 +8611,54 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Party/Pop</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Detroit Pop Rap</t>
+          <t>Chicago Boom Bap</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>G.O.O.D.</t>
+          <t>Pivot Gang</t>
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>2011</v>
-      </c>
-      <c r="J103" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K103" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L103" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M103" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N103" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="O103" s="6">
-        <f>AVERAGE(J103:N103)</f>
-        <v/>
-      </c>
-      <c r="P103" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q103" s="2" t="inlineStr">
-        <is>
-          <t>Commercial success; critical reception mixed; thin formal analysis</t>
-        </is>
-      </c>
+        <v>2014</v>
+      </c>
+      <c r="J103" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K103" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L103" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M103" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N103" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="O103" s="6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="P103" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
       <c r="R103" s="2" t="inlineStr">
         <is>
-          <t>I Decided. Catchy rap with occasional lyrical ambition.</t>
+          <t>'CARE FOR ME' — grief and Chicago violence as devastating concept album.</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -8244,17 +8668,17 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Tierra Whack</t>
+          <t>Danny Brown</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -8269,49 +8693,49 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Experimental Pop Rap</t>
+          <t>Detroit Noise Rap</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Interscope</t>
+          <t>Fool's Gold</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="J104" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K104" s="11" t="n">
-        <v>8</v>
+        <v>2010</v>
+      </c>
+      <c r="J104" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K104" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="L104" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="M104" s="11" t="n">
-        <v>8</v>
+      <c r="M104" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="N104" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O104" s="6">
-        <f>AVERAGE(J104:N104)</f>
-        <v/>
-      </c>
-      <c r="P104" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q104" s="2" t="inlineStr">
-        <is>
-          <t>Breakout 2018; critical buzz high but career short; scoring may shift</t>
-        </is>
-      </c>
+      <c r="O104" s="6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="P104" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
       <c r="R104" s="2" t="inlineStr">
         <is>
-          <t>Whack World. 15 one-minute songs as conceptual art project.</t>
+          <t>Detroit's avant-garde MC. Schizophrenic flows and surreal imagery.</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -8321,12 +8745,12 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Noname</t>
+          <t>Mac Miller</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -8346,35 +8770,34 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Chicago Jazz Rap</t>
+          <t>Pittsburgh Soul Rap</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Rostrum</t>
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="J105" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K105" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L105" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M105" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N105" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="O105" s="6">
-        <f>AVERAGE(J105:N105)</f>
-        <v/>
+        <v>2010</v>
+      </c>
+      <c r="J105" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K105" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L105" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M105" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N105" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="O105" s="6" t="n">
+        <v>7.4</v>
       </c>
       <c r="P105" s="7" t="inlineStr">
         <is>
@@ -8384,7 +8807,12 @@
       <c r="Q105" s="2" t="inlineStr"/>
       <c r="R105" s="2" t="inlineStr">
         <is>
-          <t>Room 25. Quiet devastation over jazz loops.</t>
+          <t>Arc from frat-rap to deeply personal jazz introspection. 'Swimming' a peak.</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -8394,17 +8822,17 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>SZ</t>
+          <t>JD2</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Saba</t>
+          <t>JID</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -8419,25 +8847,25 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Chicago Boom Bap</t>
+          <t>Atlanta Jazz Rap</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Pivot Gang</t>
+          <t>Dreamville</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>2014</v>
-      </c>
-      <c r="J106" s="11" t="n">
-        <v>8</v>
+        <v>2017</v>
+      </c>
+      <c r="J106" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="K106" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L106" s="12" t="n">
-        <v>9</v>
+      <c r="L106" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="M106" s="11" t="n">
         <v>8</v>
@@ -8445,19 +8873,27 @@
       <c r="N106" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="O106" s="6">
-        <f>AVERAGE(J106:N106)</f>
-        <v/>
-      </c>
-      <c r="P106" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="O106" s="6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="P106" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr">
+        <is>
+          <t>Late-decade emergence; critical acclaim building; may rescore upward</t>
+        </is>
+      </c>
       <c r="R106" s="2" t="inlineStr">
         <is>
-          <t>CARE FOR ME. Grief album as Chicago hip-hop masterpiece.</t>
+          <t>Atlanta's most technically gifted rapper. 'DiCaprio 2' showed full potential.</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -8467,17 +8903,17 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Danny Brown</t>
+          <t>Cardi B</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>NYC</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -8487,40 +8923,39 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Party/Pop</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Detroit Noise Rap</t>
+          <t>Bronx Trap Pop</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Fool's Gold</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>2010</v>
-      </c>
-      <c r="J107" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K107" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L107" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M107" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="N107" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="O107" s="6">
-        <f>AVERAGE(J107:N107)</f>
-        <v/>
+        <v>2018</v>
+      </c>
+      <c r="J107" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K107" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L107" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M107" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N107" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O107" s="6" t="n">
+        <v>5.6</v>
       </c>
       <c r="P107" s="7" t="inlineStr">
         <is>
@@ -8530,7 +8965,12 @@
       <c r="Q107" s="2" t="inlineStr"/>
       <c r="R107" s="2" t="inlineStr">
         <is>
-          <t>Atrocity Exhibition. Detroit's answer to post-punk sonic chaos.</t>
+          <t>Unfiltered Bronx personality. Cultural force exceeds lyrical architecture.</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -8540,12 +8980,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Mac Miller</t>
+          <t>Polo G</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -8555,55 +8995,63 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Pittsburgh Soul Rap</t>
+          <t>Chicago Melodic Trap</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Rostrum</t>
+          <t>Columbia</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>2010</v>
+        <v>2019</v>
       </c>
       <c r="J108" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="K108" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L108" s="10" t="n">
-        <v>7</v>
+      <c r="K108" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L108" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="M108" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="N108" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="O108" s="6">
-        <f>AVERAGE(J108:N108)</f>
-        <v/>
-      </c>
-      <c r="P108" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q108" s="2" t="inlineStr"/>
+      <c r="N108" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="O108" s="6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="P108" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>Recent emergence; trajectory still forming</t>
+        </is>
+      </c>
       <c r="R108" s="2" t="inlineStr">
         <is>
-          <t>Swimming. Self-medication turned into heartbreaking art.</t>
+          <t>Chicago's introspective melodic trap voice. Melancholy street memoir.</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -8613,12 +9061,12 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>JD2</t>
+          <t>RW</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>J.I.D</t>
+          <t>Rod Wave</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -8628,45 +9076,44 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Jazz Rap</t>
+          <t>Florida Soul Trap</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Dreamville</t>
+          <t>Alamo</t>
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="J109" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="K109" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L109" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M109" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N109" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="O109" s="6">
-        <f>AVERAGE(J109:N109)</f>
-        <v/>
+        <v>2019</v>
+      </c>
+      <c r="J109" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K109" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L109" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M109" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N109" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="O109" s="6" t="n">
+        <v>5.6</v>
       </c>
       <c r="P109" s="14" t="inlineStr">
         <is>
@@ -8675,12 +9122,17 @@
       </c>
       <c r="Q109" s="2" t="inlineStr">
         <is>
-          <t>Late-decade emergence; critical acclaim building; may rescore upward</t>
+          <t>Recent; critical consensus not yet settled</t>
         </is>
       </c>
       <c r="R109" s="2" t="inlineStr">
         <is>
-          <t>DiCaprio 2. Switchable flow at a pace few can match.</t>
+          <t>Emotional vulnerability over technical precision. Florida pain made universal.</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -8690,70 +9142,78 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Cardi B</t>
+          <t>Doechii</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Party/Pop</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Bronx Trap Pop</t>
+          <t>Tampa Art Rap</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Capitol</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="J110" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K110" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L110" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M110" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N110" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="O110" s="6">
-        <f>AVERAGE(J110:N110)</f>
-        <v/>
-      </c>
-      <c r="P110" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q110" s="2" t="inlineStr"/>
+        <v>2021</v>
+      </c>
+      <c r="J110" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K110" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L110" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M110" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N110" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="O110" s="6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="P110" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q110" s="2" t="inlineStr">
+        <is>
+          <t>Breakout recent; scoring may shift upward as body of work grows</t>
+        </is>
+      </c>
       <c r="R110" s="2" t="inlineStr">
         <is>
-          <t>Invasion of Privacy. Bronx bravado at Grammys level.</t>
+          <t>Tampa's theatrical polymath. Technical fire meets conceptual daring.</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -8763,17 +9223,17 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>GG2</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Polo G</t>
+          <t>GloRilla</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -8783,54 +9243,58 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Party/Pop</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Chicago Melodic Trap</t>
+          <t>Memphis Trap</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Columbia</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>2019</v>
-      </c>
-      <c r="J111" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K111" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L111" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M111" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N111" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="O111" s="6">
-        <f>AVERAGE(J111:N111)</f>
-        <v/>
-      </c>
-      <c r="P111" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
+        <v>2022</v>
+      </c>
+      <c r="J111" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K111" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L111" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M111" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N111" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O111" s="6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P111" s="15" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
         <is>
-          <t>Recent emergence; trajectory still forming</t>
+          <t>Very recent; limited critical record; commercial impact clear</t>
         </is>
       </c>
       <c r="R111" s="2" t="inlineStr">
         <is>
-          <t>Pop Out. Melancholy Chicago trap with genuine lyrical care.</t>
+          <t>Memphis energy, unfiltered personality. New Southern feminism in party form.</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -8840,12 +9304,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>GN</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Rod Wave</t>
+          <t>Gunna</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -8860,40 +9324,39 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Trap/Drill</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Florida Soul Trap</t>
+          <t>Atlanta Melodic Trap</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Alamo</t>
+          <t>Young Stoner Life</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>2019</v>
-      </c>
-      <c r="J112" s="8" t="n">
-        <v>5</v>
+        <v>2018</v>
+      </c>
+      <c r="J112" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="K112" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="L112" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M112" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N112" s="8" t="n">
+      <c r="L112" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M112" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O112" s="6">
-        <f>AVERAGE(J112:N112)</f>
-        <v/>
+      <c r="N112" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O112" s="6" t="n">
+        <v>4.2</v>
       </c>
       <c r="P112" s="14" t="inlineStr">
         <is>
@@ -8902,12 +9365,17 @@
       </c>
       <c r="Q112" s="2" t="inlineStr">
         <is>
-          <t>Recent; critical consensus not yet settled</t>
+          <t>Significant commercial presence; thin critical analysis</t>
         </is>
       </c>
       <c r="R112" s="2" t="inlineStr">
         <is>
-          <t>SoulFly. Florida's emotional trap meets gospel music.</t>
+          <t>Melodic luxury trap. Vibe and aesthetic are the art.</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -8917,12 +9385,12 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Doechii</t>
+          <t>Lil Baby</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -8937,40 +9405,39 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Tampa Art Rap</t>
+          <t>Atlanta Slime Trap</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Capitol</t>
+          <t>Quality Control</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>2021</v>
-      </c>
-      <c r="J113" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K113" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L113" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M113" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N113" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="O113" s="6">
-        <f>AVERAGE(J113:N113)</f>
-        <v/>
+        <v>2017</v>
+      </c>
+      <c r="J113" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K113" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L113" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M113" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N113" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="O113" s="6" t="n">
+        <v>5.2</v>
       </c>
       <c r="P113" s="14" t="inlineStr">
         <is>
@@ -8979,12 +9446,17 @@
       </c>
       <c r="Q113" s="2" t="inlineStr">
         <is>
-          <t>Breakout recent; scoring may shift upward as body of work grows</t>
+          <t>Recent; commercial dominance clear; critical depth forming</t>
         </is>
       </c>
       <c r="R113" s="2" t="inlineStr">
         <is>
-          <t>Alligator Bites Never Heal. Tampa avant-garde challenging rap norms.</t>
+          <t>Authentic street narrator. Storytelling grounded in lived experience.</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -8994,17 +9466,17 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>GG2</t>
+          <t>BT</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>GloRilla</t>
+          <t>Benny the Butcher</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>NYC</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -9014,54 +9486,54 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Party/Pop</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Memphis Trap</t>
+          <t>Buffalo Boom Bap</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>Griselda</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>2022</v>
-      </c>
-      <c r="J114" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K114" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L114" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="M114" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N114" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="O114" s="6">
-        <f>AVERAGE(J114:N114)</f>
-        <v/>
-      </c>
-      <c r="P114" s="15" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="Q114" s="2" t="inlineStr">
-        <is>
-          <t>Very recent; limited critical record; commercial impact clear</t>
-        </is>
-      </c>
+        <v>2012</v>
+      </c>
+      <c r="J114" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K114" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L114" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M114" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N114" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="O114" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="P114" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q114" s="2" t="inlineStr"/>
       <c r="R114" s="2" t="inlineStr">
         <is>
-          <t>FNF. Memphis energy with instant cultural resonance.</t>
+          <t>Griselda's lyrical backbone. Buffalo street narratives with East Coast precision.</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -9071,12 +9543,12 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>GN</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Gunna</t>
+          <t>Offset</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -9096,36 +9568,35 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Melodic Trap</t>
+          <t>Migos Solo Trap</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Young Stoner Life</t>
+          <t>Quality Control</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="J115" s="5" t="n">
-        <v>4</v>
+        <v>2017</v>
+      </c>
+      <c r="J115" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="K115" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="L115" s="5" t="n">
+      <c r="L115" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M115" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N115" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="M115" s="8" t="n">
+      <c r="O115" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="N115" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="O115" s="6">
-        <f>AVERAGE(J115:N115)</f>
-        <v/>
-      </c>
       <c r="P115" s="14" t="inlineStr">
         <is>
           <t>M</t>
@@ -9133,12 +9604,17 @@
       </c>
       <c r="Q115" s="2" t="inlineStr">
         <is>
-          <t>Significant commercial presence; thin critical analysis</t>
+          <t>Solo career emerging post-Migos; scoring tentative</t>
         </is>
       </c>
       <c r="R115" s="2" t="inlineStr">
         <is>
-          <t>DS4EVER. Melodic trap comfort zone never pushed.</t>
+          <t>Migos' most lyrical member. Flow variation and delivery standout in trap context.</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9624,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Lil Baby</t>
+          <t>Kenny Mason</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -9168,54 +9644,58 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Slime Trap</t>
+          <t>Atlanta Punk Rap</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>RCA Records</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="J116" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K116" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L116" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M116" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N116" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="O116" s="6">
-        <f>AVERAGE(J116:N116)</f>
-        <v/>
-      </c>
-      <c r="P116" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
+        <v>2019</v>
+      </c>
+      <c r="J116" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K116" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L116" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M116" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N116" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="O116" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="P116" s="15" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
         <is>
-          <t>Recent; commercial dominance clear; critical depth forming</t>
+          <t>Limited documentation; critical buzz building in underground circles</t>
         </is>
       </c>
       <c r="R116" s="2" t="inlineStr">
         <is>
-          <t>My Turn. Effortless commercial dominance; artistry developing.</t>
+          <t>Atlanta's punk-rap hybrid. Unconventional tonal range.</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -9225,17 +9705,17 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Benny the Butcher</t>
+          <t>Latto</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -9250,45 +9730,53 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Buffalo Boom Bap</t>
+          <t>Atlanta Female Trap</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Griselda</t>
+          <t>RCA</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>2012</v>
-      </c>
-      <c r="J117" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K117" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L117" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M117" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N117" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="O117" s="6">
-        <f>AVERAGE(J117:N117)</f>
-        <v/>
-      </c>
-      <c r="P117" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q117" s="2" t="inlineStr"/>
+        <v>2019</v>
+      </c>
+      <c r="J117" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K117" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L117" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M117" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N117" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="O117" s="6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="P117" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q117" s="2" t="inlineStr">
+        <is>
+          <t>Recent; commercial trajectory clearer than critical consensus</t>
+        </is>
+      </c>
       <c r="R117" s="2" t="inlineStr">
         <is>
-          <t>Burden of Proof. Griselda's street pulpit.</t>
+          <t>Atlanta's female trap voice. Technical skill often underestimated.</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -9298,17 +9786,17 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>SR</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Stormzy</t>
+          <t>Smino</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -9318,50 +9806,58 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Political</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>UK Grime/Gospel</t>
+          <t>St. Louis Jazz Rap</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>#Merky</t>
+          <t>Zero Fatigue</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="J118" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="K118" s="10" t="n">
-        <v>7</v>
+      <c r="K118" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="L118" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="M118" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N118" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="O118" s="6">
-        <f>AVERAGE(J118:N118)</f>
-        <v/>
-      </c>
-      <c r="P118" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q118" s="2" t="inlineStr"/>
+      <c r="M118" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N118" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="O118" s="6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="P118" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q118" s="2" t="inlineStr">
+        <is>
+          <t>Critical darling in jazz-rap circles; broader recognition still forming</t>
+        </is>
+      </c>
       <c r="R118" s="2" t="inlineStr">
         <is>
-          <t>Heavy Is the Head. UK grime at Glastonbury scale.</t>
+          <t>St. Louis's jazz-rap hybrid. Melodic and rhythmic sophistication.</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -9371,17 +9867,17 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>PZ</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Bad Bunny</t>
+          <t>Pusha T</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>NYC</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -9391,54 +9887,54 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Party/Pop</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Reggaeton/Latin Trap</t>
+          <t>Coke Rap Boom Bap</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Rimas</t>
+          <t>G.O.O.D.</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="J119" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K119" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L119" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M119" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N119" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="O119" s="6">
-        <f>AVERAGE(J119:N119)</f>
-        <v/>
-      </c>
-      <c r="P119" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q119" s="2" t="inlineStr">
-        <is>
-          <t>Massive influence on global rap; Spanish-language scoring requires different critical frame</t>
-        </is>
-      </c>
+        <v>2002</v>
+      </c>
+      <c r="J119" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K119" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L119" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M119" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N119" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="O119" s="6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="P119" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q119" s="2" t="inlineStr"/>
       <c r="R119" s="2" t="inlineStr">
         <is>
-          <t>Un Verano Sin Ti. Latin trap global domination.</t>
+          <t>Cocaine rap's Rembrandt. 'Daytona' — maximum density, minimum waste.</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -9448,17 +9944,17 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>JB</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>J Balvin</t>
+          <t>Tyler the Creator</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -9468,54 +9964,54 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Party/Pop</t>
+          <t>Experimental</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Reggaeton</t>
+          <t>Odd Future/Orchestral</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Capitol</t>
+          <t>Columbia</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>2007</v>
-      </c>
-      <c r="J120" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K120" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L120" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M120" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N120" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="O120" s="6">
-        <f>AVERAGE(J120:N120)</f>
-        <v/>
-      </c>
-      <c r="P120" s="15" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="Q120" s="2" t="inlineStr">
-        <is>
-          <t>Minimal lyrical critical record; scored on available Spanish-language criticism</t>
-        </is>
-      </c>
+        <v>2009</v>
+      </c>
+      <c r="J120" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K120" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L120" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M120" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="N120" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="O120" s="6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="P120" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q120" s="2" t="inlineStr"/>
       <c r="R120" s="2" t="inlineStr">
         <is>
-          <t>Colores. Reggaeton popstar with rap adjacency.</t>
+          <t>'Igor' and 'Call Me If You Get Lost' — producer-auteur. Concept album mastery.</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -9525,17 +10021,17 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>OM</t>
+          <t>AB2</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Offset</t>
+          <t>Armand Hammer</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>NYC</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -9545,40 +10041,39 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Trap/Drill</t>
+          <t>Abstract</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Migos Solo Trap</t>
+          <t>Abstract Boom Bap</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>Quality Control</t>
+          <t>Backwoodz</t>
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="J121" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K121" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L121" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="M121" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N121" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="O121" s="6">
-        <f>AVERAGE(J121:N121)</f>
-        <v/>
+        <v>2013</v>
+      </c>
+      <c r="J121" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K121" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L121" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M121" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="N121" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="O121" s="6" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="P121" s="14" t="inlineStr">
         <is>
@@ -9587,12 +10082,17 @@
       </c>
       <c r="Q121" s="2" t="inlineStr">
         <is>
-          <t>Solo career emerging post-Migos; scoring tentative</t>
+          <t>Critical underground darling; thin mainstream documentation</t>
         </is>
       </c>
       <c r="R121" s="2" t="inlineStr">
         <is>
-          <t>Set It Off. Post-Migos identity search ongoing.</t>
+          <t>billy woods + ELUCID. The most demanding abstract rap being made today.</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -9602,12 +10102,12 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>ZE</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Kenny Mason</t>
+          <t>Zack Fox</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -9622,12 +10122,12 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Abstract</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Punk Rap</t>
+          <t>Comedy-Abstract Rap</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -9636,26 +10136,25 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>2019</v>
-      </c>
-      <c r="J122" s="10" t="n">
-        <v>7</v>
+        <v>2020</v>
+      </c>
+      <c r="J122" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="K122" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="L122" s="10" t="n">
-        <v>7</v>
+      <c r="L122" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="M122" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="N122" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="O122" s="6">
-        <f>AVERAGE(J122:N122)</f>
-        <v/>
+      <c r="N122" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="O122" s="6" t="n">
+        <v>6.4</v>
       </c>
       <c r="P122" s="15" t="inlineStr">
         <is>
@@ -9664,12 +10163,17 @@
       </c>
       <c r="Q122" s="2" t="inlineStr">
         <is>
-          <t>Limited documentation; critical buzz building in underground circles</t>
+          <t>Very recent; extremely limited critical record</t>
         </is>
       </c>
       <c r="R122" s="2" t="inlineStr">
         <is>
-          <t>Angelic Hoodrat. Atlanta experimental underground at its weirdest.</t>
+          <t>Comedy-meets-rap. Formally interesting but body of work too small to score confidently.</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -9679,17 +10183,17 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Latto</t>
+          <t>Lil Durk</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -9704,35 +10208,34 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Female Trap</t>
+          <t>Chicago Melodic Trap</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>RCA</t>
+          <t>Only the Family</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>2019</v>
-      </c>
-      <c r="J123" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K123" s="9" t="n">
-        <v>6</v>
+        <v>2013</v>
+      </c>
+      <c r="J123" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K123" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="L123" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="M123" s="9" t="n">
-        <v>6</v>
+      <c r="M123" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="N123" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="O123" s="6">
-        <f>AVERAGE(J123:N123)</f>
-        <v/>
+      <c r="O123" s="6" t="n">
+        <v>5.2</v>
       </c>
       <c r="P123" s="14" t="inlineStr">
         <is>
@@ -9741,12 +10244,17 @@
       </c>
       <c r="Q123" s="2" t="inlineStr">
         <is>
-          <t>Recent; commercial trajectory clearer than critical consensus</t>
+          <t>Commercial dominance clear; critical depth limited</t>
         </is>
       </c>
       <c r="R123" s="2" t="inlineStr">
         <is>
-          <t>777. Southern female rap following Cardi and Nicki's path.</t>
+          <t>Chicago drill's most commercially consistent voice.</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -9756,17 +10264,17 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>SR</t>
+          <t>KS2</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Smino</t>
+          <t>Kodak Black</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -9776,40 +10284,39 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>St. Louis Jazz Rap</t>
+          <t>Florida Trap</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Zero Fatigue</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="J124" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K124" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L124" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M124" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N124" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="O124" s="6">
-        <f>AVERAGE(J124:N124)</f>
-        <v/>
+        <v>2014</v>
+      </c>
+      <c r="J124" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K124" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L124" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M124" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N124" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O124" s="6" t="n">
+        <v>5</v>
       </c>
       <c r="P124" s="14" t="inlineStr">
         <is>
@@ -9818,12 +10325,17 @@
       </c>
       <c r="Q124" s="2" t="inlineStr">
         <is>
-          <t>Critical darling in jazz-rap circles; broader recognition still forming</t>
+          <t>Commercial success; thin critical framework; behavior clouds reception</t>
         </is>
       </c>
       <c r="R124" s="2" t="inlineStr">
         <is>
-          <t>blkswn. Jazz-rap from St. Louis with melodic depth.</t>
+          <t>Florida trap's most distinctive voice. Rough-edged regional authenticity.</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -9833,17 +10345,17 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>PZ</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Pusha T</t>
+          <t>Rapsody</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -9853,40 +10365,39 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Coke Rap Boom Bap</t>
+          <t>North Carolina Soul Rap</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>G.O.O.D.</t>
+          <t>Jamla</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>2002</v>
+        <v>2010</v>
       </c>
       <c r="J125" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="K125" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L125" s="10" t="n">
-        <v>7</v>
+      <c r="K125" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L125" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="M125" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="N125" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="O125" s="6">
-        <f>AVERAGE(J125:N125)</f>
-        <v/>
+      <c r="N125" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="O125" s="6" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="P125" s="7" t="inlineStr">
         <is>
@@ -9896,7 +10407,12 @@
       <c r="Q125" s="2" t="inlineStr"/>
       <c r="R125" s="2" t="inlineStr">
         <is>
-          <t>It's Almost Dry. Coke rap as high art. Pharrell and Kanye dual production.</t>
+          <t>North Carolina's most complete female MC. Lyrical depth rivals any peer.</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -9906,12 +10422,12 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>JS</t>
+          <t>MF2</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>JID</t>
+          <t>Mavi</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -9926,54 +10442,58 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Abstract</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Atlanta Technical Rap</t>
+          <t>Underground Abstract</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Dreamville</t>
+          <t>Secretly Canadian</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="J126" s="12" t="n">
-        <v>9</v>
+        <v>2019</v>
+      </c>
+      <c r="J126" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="K126" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L126" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M126" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N126" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="O126" s="6">
-        <f>AVERAGE(J126:N126)</f>
-        <v/>
-      </c>
-      <c r="P126" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
+      <c r="L126" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M126" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N126" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="O126" s="6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="P126" s="15" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t>Recent; scoring likely conservative; upward trajectory clear</t>
+          <t>Very limited critical documentation; underground following only</t>
         </is>
       </c>
       <c r="R126" s="2" t="inlineStr">
         <is>
-          <t>The Never Story / Pandemonium!. Technical rapper escaping Atlanta tropes.</t>
+          <t>Charlotte underground. Dense introspective abstract rap. Watch this space.</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -9983,12 +10503,12 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>XP</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Tyler the Creator</t>
+          <t>Xzibit</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -9998,55 +10518,63 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Odd Future/Orchestral</t>
+          <t>Hard West Coast</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>Columbia</t>
+          <t>Loud/Columbia</t>
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>2009</v>
+        <v>1996</v>
       </c>
       <c r="J127" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="K127" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L127" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M127" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="N127" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="O127" s="6">
-        <f>AVERAGE(J127:N127)</f>
-        <v/>
-      </c>
-      <c r="P127" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q127" s="2" t="inlineStr"/>
+      <c r="K127" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L127" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M127" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N127" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="O127" s="6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="P127" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q127" s="2" t="inlineStr">
+        <is>
+          <t>Well-known but limited formal critical analysis</t>
+        </is>
+      </c>
       <c r="R127" s="2" t="inlineStr">
         <is>
-          <t>Igor / Call Me If You Get Lost. Conceptual album art as rap.</t>
+          <t>West Coast boom bap craftsman. More respected by peers than critics.</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -10056,17 +10584,17 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>AB2</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Armand Hammer</t>
+          <t>Saweetie</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>Bay Area</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -10076,40 +10604,39 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Abstract</t>
+          <t>Party/Pop</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Abstract Boom Bap</t>
+          <t>Trap Pop</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Backwoodz</t>
+          <t>Warner</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>2012</v>
-      </c>
-      <c r="J128" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K128" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L128" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M128" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="N128" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="O128" s="6">
-        <f>AVERAGE(J128:N128)</f>
-        <v/>
+        <v>2018</v>
+      </c>
+      <c r="J128" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K128" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L128" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M128" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N128" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O128" s="6" t="n">
+        <v>4.8</v>
       </c>
       <c r="P128" s="14" t="inlineStr">
         <is>
@@ -10118,12 +10645,17 @@
       </c>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>Critical underground darling; thin mainstream documentation</t>
+          <t>Recent commercial success; limited critical depth</t>
         </is>
       </c>
       <c r="R128" s="2" t="inlineStr">
         <is>
-          <t>Haram. billy woods + ELUCID: dense, allusive, uncompromising.</t>
+          <t>Bay Area trap-pop. Ice Princess persona over lyrical substance.</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -10133,17 +10665,17 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>ZE</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Zach Fox</t>
+          <t>City Girls</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -10153,40 +10685,39 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>Abstract</t>
+          <t>Party/Pop</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Comedy-Abstract Rap</t>
+          <t>Miami Trap</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Quality Control/Motown</t>
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="J129" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K129" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L129" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M129" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N129" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="O129" s="6">
-        <f>AVERAGE(J129:N129)</f>
-        <v/>
+        <v>2018</v>
+      </c>
+      <c r="J129" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K129" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L129" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M129" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N129" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O129" s="6" t="n">
+        <v>4.6</v>
       </c>
       <c r="P129" s="15" t="inlineStr">
         <is>
@@ -10195,12 +10726,17 @@
       </c>
       <c r="Q129" s="2" t="inlineStr">
         <is>
-          <t>Very recent; extremely limited critical record</t>
+          <t>Limited critical record; cultural impact clearer than lyrical analysis</t>
         </is>
       </c>
       <c r="R129" s="2" t="inlineStr">
         <is>
-          <t>Bussin. Internet-native absurdist rapper with genuine lyrical wit.</t>
+          <t>Miami's hedonistic party rap duo. Energy over craft.</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>Compound</t>
         </is>
       </c>
     </row>
@@ -10210,12 +10746,12 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Lil Durk</t>
+          <t>Maxo Kream</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -10235,815 +10771,1501 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Chicago Melodic Trap</t>
+          <t>Houston Narrative Trap</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Only the Family</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>2013</v>
-      </c>
-      <c r="J130" s="8" t="n">
+        <v>2017</v>
+      </c>
+      <c r="J130" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K130" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L130" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M130" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N130" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="O130" s="6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="P130" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q130" s="2" t="inlineStr">
+        <is>
+          <t>Critical acclaim in narrative rap circles; limited mainstream documentation</t>
+        </is>
+      </c>
+      <c r="R130" s="2" t="inlineStr">
+        <is>
+          <t>Houston storytelling tradition continued. 'Weight of the World' deeply affecting.</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>The Roots</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Philly</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Golden Age</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Conscious/Lyrical</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Live-Band Boom Bap</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Geffen/MCA</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>1993</v>
+      </c>
+      <c r="J131" t="n">
+        <v>10</v>
+      </c>
+      <c r="K131" t="n">
+        <v>9</v>
+      </c>
+      <c r="L131" t="n">
+        <v>8</v>
+      </c>
+      <c r="M131" t="n">
+        <v>9</v>
+      </c>
+      <c r="N131" t="n">
+        <v>8</v>
+      </c>
+      <c r="O131" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>Philadelphia's live-band institution; Black Thought's relentless technique anchors a peerless catalog.</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Beanie Sigel</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Philly</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Gangsta/Street</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Soul Boom Bap</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Roc-A-Fella</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J132" t="n">
+        <v>8</v>
+      </c>
+      <c r="K132" t="n">
+        <v>7</v>
+      </c>
+      <c r="L132" t="n">
+        <v>8</v>
+      </c>
+      <c r="M132" t="n">
+        <v>7</v>
+      </c>
+      <c r="N132" t="n">
+        <v>7</v>
+      </c>
+      <c r="O132" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>Critically respected but thinly documented outside the Roc-A-Fella context.</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>Philadelphia's hardest pen. Street narratives carried with weight and conviction.</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>UV</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Lil Uzi Vert</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Philly</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Rage/Trap</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Generation Now/Atlantic</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>2016</v>
+      </c>
+      <c r="J133" t="n">
+        <v>6</v>
+      </c>
+      <c r="K133" t="n">
+        <v>6</v>
+      </c>
+      <c r="L133" t="n">
         <v>5</v>
       </c>
-      <c r="K130" s="8" t="n">
+      <c r="M133" t="n">
+        <v>6</v>
+      </c>
+      <c r="N133" t="n">
+        <v>6</v>
+      </c>
+      <c r="O133" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>Melodic rage star; influence on sound outweighs lyrical scholarship.</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>Genre-bending rage pioneer. Melody and energy over lyrical density.</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>FW</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Freeway</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Philly</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Gangsta/Street</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Soul Boom Bap</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Roc-A-Fella</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>2003</v>
+      </c>
+      <c r="J134" t="n">
+        <v>7</v>
+      </c>
+      <c r="K134" t="n">
+        <v>6</v>
+      </c>
+      <c r="L134" t="n">
+        <v>6</v>
+      </c>
+      <c r="M134" t="n">
+        <v>6</v>
+      </c>
+      <c r="N134" t="n">
         <v>5</v>
       </c>
-      <c r="L130" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M130" s="8" t="n">
+      <c r="O134" t="n">
+        <v>6</v>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>Limited critical record; respected within State Property/Roc-A-Fella circles.</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>Distinctive raspy urgency and Philly grit. State Property standout.</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Eve</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Philly</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Party/Pop</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Ruff Ryders</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Ruff Ryders/Interscope</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>1999</v>
+      </c>
+      <c r="J135" t="n">
+        <v>6</v>
+      </c>
+      <c r="K135" t="n">
+        <v>6</v>
+      </c>
+      <c r="L135" t="n">
+        <v>6</v>
+      </c>
+      <c r="M135" t="n">
+        <v>6</v>
+      </c>
+      <c r="N135" t="n">
         <v>5</v>
       </c>
-      <c r="N130" s="8" t="n">
+      <c r="O135" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>Commercial success clearer than lyrical analysis.</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>Ruff Ryders' First Lady. Charismatic crossover with Philly roots.</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Da Brat</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Golden Age</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Party/Pop</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>So So Def Bass</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>So So Def</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>1994</v>
+      </c>
+      <c r="J136" t="n">
+        <v>6</v>
+      </c>
+      <c r="K136" t="n">
+        <v>6</v>
+      </c>
+      <c r="L136" t="n">
+        <v>6</v>
+      </c>
+      <c r="M136" t="n">
+        <v>6</v>
+      </c>
+      <c r="N136" t="n">
         <v>5</v>
       </c>
-      <c r="O130" s="6">
-        <f>AVERAGE(J130:N130)</f>
-        <v/>
-      </c>
-      <c r="P130" s="14" t="inlineStr">
+      <c r="O136" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="P136" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="Q130" s="2" t="inlineStr">
-        <is>
-          <t>Commercial dominance clear; critical depth limited</t>
-        </is>
-      </c>
-      <c r="R130" s="2" t="inlineStr">
-        <is>
-          <t>The Voice. Chicago melodic trap emotional authenticity at scale.</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="n">
-        <v>130</v>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>KS2</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>Kodak Black</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>First female solo rapper to go platinum; under-analyzed lyrically.</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>So So Def's breakout. First female solo rapper to go platinum.</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>TS2</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Too $hort</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Old School</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
         <is>
           <t>Gangsta/Street</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t>Florida Trap</t>
-        </is>
-      </c>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>Atlantic</t>
-        </is>
-      </c>
-      <c r="I131" s="2" t="n">
-        <v>2014</v>
-      </c>
-      <c r="J131" s="8" t="n">
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Funk/Bass</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Jive/Dangerous Music</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>1987</v>
+      </c>
+      <c r="J137" t="n">
+        <v>6</v>
+      </c>
+      <c r="K137" t="n">
         <v>5</v>
       </c>
-      <c r="K131" s="8" t="n">
+      <c r="L137" t="n">
+        <v>6</v>
+      </c>
+      <c r="M137" t="n">
         <v>5</v>
       </c>
-      <c r="L131" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M131" s="8" t="n">
+      <c r="N137" t="n">
         <v>5</v>
       </c>
-      <c r="N131" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="O131" s="6">
-        <f>AVERAGE(J131:N131)</f>
-        <v/>
-      </c>
-      <c r="P131" s="14" t="inlineStr">
+      <c r="O137" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="P137" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="Q131" s="2" t="inlineStr">
-        <is>
-          <t>Commercial success; thin critical framework; behavior clouds reception</t>
-        </is>
-      </c>
-      <c r="R131" s="2" t="inlineStr">
-        <is>
-          <t>Project Baby. Florida trap originality clouded by off-mic controversies.</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="n">
-        <v>131</v>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>LA2</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>Lana (Kali Uchis rap)</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>Experimental</t>
-        </is>
-      </c>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>R&amp;B/Latin Rap Hybrid</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>Virgin</t>
-        </is>
-      </c>
-      <c r="I132" s="2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="J132" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K132" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L132" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M132" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N132" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="O132" s="6">
-        <f>AVERAGE(J132:N132)</f>
-        <v/>
-      </c>
-      <c r="P132" s="15" t="inlineStr">
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>Pioneer status outweighs lyrical-craft documentation.</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>Oakland pioneer and pimp-rap archetype. Influence over intricacy.</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Del the Funky Homosapien</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Golden Age</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Hieroglyphics</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Elektra/Hiero Imperium</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>1991</v>
+      </c>
+      <c r="J138" t="n">
+        <v>7</v>
+      </c>
+      <c r="K138" t="n">
+        <v>8</v>
+      </c>
+      <c r="L138" t="n">
+        <v>6</v>
+      </c>
+      <c r="M138" t="n">
+        <v>7</v>
+      </c>
+      <c r="N138" t="n">
+        <v>7</v>
+      </c>
+      <c r="O138" t="n">
+        <v>7</v>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>Underground Hieroglyphics following; specialist critical attention.</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>Hieroglyphics wordsmith. Quirky vocabulary and abstract wit.</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>MD3</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Mac Dre</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Party/Pop</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Hyphy</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Thizz Entertainment</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J139" t="n">
+        <v>6</v>
+      </c>
+      <c r="K139" t="n">
+        <v>6</v>
+      </c>
+      <c r="L139" t="n">
+        <v>6</v>
+      </c>
+      <c r="M139" t="n">
+        <v>5</v>
+      </c>
+      <c r="N139" t="n">
+        <v>5</v>
+      </c>
+      <c r="O139" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="P139" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="Q132" s="2" t="inlineStr">
-        <is>
-          <t>Primarily R&amp;B artist; rap output limited and under-analyzed</t>
-        </is>
-      </c>
-      <c r="R132" s="2" t="inlineStr">
-        <is>
-          <t>Por Vida. Colombian-American bilingual artistry; rap adjacent.</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="n">
-        <v>132</v>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>RC</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>Rapsody</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="E133" s="2" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>Regional hyphy icon; limited national critical record.</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>Hyphy movement godfather. Enduring Bay Area cult legend.</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Royce da 5'9"</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
         <is>
           <t>Conscious/Lyrical</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
-        <is>
-          <t>North Carolina Soul Rap</t>
-        </is>
-      </c>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t>Jamla</t>
-        </is>
-      </c>
-      <c r="I133" s="2" t="n">
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Detroit Boom Bap</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Shady/Independent</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>2002</v>
+      </c>
+      <c r="J140" t="n">
+        <v>9</v>
+      </c>
+      <c r="K140" t="n">
+        <v>8</v>
+      </c>
+      <c r="L140" t="n">
+        <v>7</v>
+      </c>
+      <c r="M140" t="n">
+        <v>8</v>
+      </c>
+      <c r="N140" t="n">
+        <v>7</v>
+      </c>
+      <c r="O140" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>Elite technician; documentation grew via Slaughterhouse and PRhyme.</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>Detroit technician. Slaughterhouse and PRhyme cornerstone.</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Kool G Rap</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Golden Age</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Gangsta/Street</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Boom Bap</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Cold Chillin'</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J141" t="n">
+        <v>9</v>
+      </c>
+      <c r="K141" t="n">
+        <v>8</v>
+      </c>
+      <c r="L141" t="n">
+        <v>9</v>
+      </c>
+      <c r="M141" t="n">
+        <v>8</v>
+      </c>
+      <c r="N141" t="n">
+        <v>7</v>
+      </c>
+      <c r="O141" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>Mafioso-rap forefather. The multisyllabic blueprint for Nas, Biggie and Jay-Z.</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>RM</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Redman</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Golden Age</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Conscious/Lyrical</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Funk Boom Bap</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Def Jam</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>1992</v>
+      </c>
+      <c r="J142" t="n">
+        <v>8</v>
+      </c>
+      <c r="K142" t="n">
+        <v>7</v>
+      </c>
+      <c r="L142" t="n">
+        <v>7</v>
+      </c>
+      <c r="M142" t="n">
+        <v>7</v>
+      </c>
+      <c r="N142" t="n">
+        <v>6</v>
+      </c>
+      <c r="O142" t="n">
+        <v>7</v>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>Beloved and skilled; lyrical scholarship modest relative to peers.</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>Newark's funkiest. Effortless flow with comedic menace.</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Method Man</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Late 90s</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Conscious/Lyrical</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Wu-Tang</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Def Jam</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>1994</v>
+      </c>
+      <c r="J143" t="n">
+        <v>7</v>
+      </c>
+      <c r="K143" t="n">
+        <v>7</v>
+      </c>
+      <c r="L143" t="n">
+        <v>6</v>
+      </c>
+      <c r="M143" t="n">
+        <v>7</v>
+      </c>
+      <c r="N143" t="n">
+        <v>6</v>
+      </c>
+      <c r="O143" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>Scored solo; Wu-Tang charisma vs pure-lyric metrics.</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>Wu-Tang's charismatic star. Gravel-voiced hooks and grit.</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>EP</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>EPMD</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Golden Age</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Conscious/Lyrical</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Funk Boom Bap</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Def Jam</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>1988</v>
+      </c>
+      <c r="J144" t="n">
+        <v>7</v>
+      </c>
+      <c r="K144" t="n">
+        <v>6</v>
+      </c>
+      <c r="L144" t="n">
+        <v>6</v>
+      </c>
+      <c r="M144" t="n">
+        <v>6</v>
+      </c>
+      <c r="N144" t="n">
+        <v>6</v>
+      </c>
+      <c r="O144" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>Influential funk-rap duo; understated lyrical documentation.</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>Strictly Business. Laid-back funk and durable chemistry.</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>TG</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>The Game</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Gangsta/Street</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>West Coast</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Aftermath/G-Unit</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>2005</v>
+      </c>
+      <c r="J145" t="n">
+        <v>7</v>
+      </c>
+      <c r="K145" t="n">
+        <v>7</v>
+      </c>
+      <c r="L145" t="n">
+        <v>7</v>
+      </c>
+      <c r="M145" t="n">
+        <v>7</v>
+      </c>
+      <c r="N145" t="n">
+        <v>6</v>
+      </c>
+      <c r="O145" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>Commercially dominant; reference-heavy bars, mixed critical view.</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>Compton revivalist. The Documentary-era West Coast resurgence.</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Ice-T</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Old School</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Gangsta/Street</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Electro/Funk</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Sire/Rhyme Syndicate</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>1987</v>
+      </c>
+      <c r="J146" t="n">
+        <v>6</v>
+      </c>
+      <c r="K146" t="n">
+        <v>6</v>
+      </c>
+      <c r="L146" t="n">
+        <v>7</v>
+      </c>
+      <c r="M146" t="n">
+        <v>6</v>
+      </c>
+      <c r="N146" t="n">
+        <v>7</v>
+      </c>
+      <c r="O146" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>Gangsta-rap pioneer; influence and narrative over technical metrics.</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>Gangsta-rap originator. Street reportage before the template existed.</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Nipsey Hussle</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Conscious/Lyrical</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>West Coast</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>All Money In/Atlantic</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
         <v>2010</v>
       </c>
-      <c r="J133" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K133" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L133" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M133" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N133" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="O133" s="6">
-        <f>AVERAGE(J133:N133)</f>
-        <v/>
-      </c>
-      <c r="P133" s="7" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q133" s="2" t="inlineStr"/>
-      <c r="R133" s="2" t="inlineStr">
-        <is>
-          <t>Eve. Named every track after a Black woman. Precision and purpose.</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="n">
-        <v>133</v>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>NG</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>Noname (Ghetto Sage)</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>Midwest</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="inlineStr">
-        <is>
-          <t>Political</t>
-        </is>
-      </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>Political Jazz Rap</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>Independent</t>
-        </is>
-      </c>
-      <c r="I134" s="2" t="n">
-        <v>2019</v>
-      </c>
-      <c r="J134" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K134" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L134" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M134" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N134" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="O134" s="6">
-        <f>AVERAGE(J134:N134)</f>
-        <v/>
-      </c>
-      <c r="P134" s="14" t="inlineStr">
+      <c r="J147" t="n">
+        <v>7</v>
+      </c>
+      <c r="K147" t="n">
+        <v>7</v>
+      </c>
+      <c r="L147" t="n">
+        <v>7</v>
+      </c>
+      <c r="M147" t="n">
+        <v>7</v>
+      </c>
+      <c r="N147" t="n">
+        <v>7</v>
+      </c>
+      <c r="O147" t="n">
+        <v>7</v>
+      </c>
+      <c r="P147" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="Q134" s="2" t="inlineStr">
-        <is>
-          <t>Political evolution post-Room 25; scoring for this phase specifically</t>
-        </is>
-      </c>
-      <c r="R134" s="2" t="inlineStr">
-        <is>
-          <t>Factory Baby. Post-Room 25 political radicalization era.</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="n">
-        <v>134</v>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>MF2</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>Mavi</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
-      <c r="F135" s="2" t="inlineStr">
-        <is>
-          <t>Abstract</t>
-        </is>
-      </c>
-      <c r="G135" s="2" t="inlineStr">
-        <is>
-          <t>Underground Abstract</t>
-        </is>
-      </c>
-      <c r="H135" s="2" t="inlineStr">
-        <is>
-          <t>Mutant Academy</t>
-        </is>
-      </c>
-      <c r="I135" s="2" t="n">
-        <v>2019</v>
-      </c>
-      <c r="J135" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K135" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L135" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M135" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N135" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="O135" s="6">
-        <f>AVERAGE(J135:N135)</f>
-        <v/>
-      </c>
-      <c r="P135" s="15" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="Q135" s="2" t="inlineStr">
-        <is>
-          <t>Very limited critical documentation; underground following only</t>
-        </is>
-      </c>
-      <c r="R135" s="2" t="inlineStr">
-        <is>
-          <t>Let the Sun Talk. Introspective underground debut with cultish following.</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="n">
-        <v>135</v>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>XP</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>Xzibit</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>Posthumous reappraisal ongoing; entrepreneurial legacy prominent.</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>Crenshaw's marathon. Street wisdom and self-determination.</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>DQ</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>DJ Quik</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
         <is>
           <t>LA</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>2000s</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Golden Age</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
         <is>
           <t>Gangsta/Street</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t>Hard West Coast</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>Loud/Columbia</t>
-        </is>
-      </c>
-      <c r="I136" s="2" t="n">
-        <v>1996</v>
-      </c>
-      <c r="J136" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K136" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L136" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M136" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N136" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="O136" s="6">
-        <f>AVERAGE(J136:N136)</f>
-        <v/>
-      </c>
-      <c r="P136" s="14" t="inlineStr">
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>G-Funk</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>1991</v>
+      </c>
+      <c r="J148" t="n">
+        <v>7</v>
+      </c>
+      <c r="K148" t="n">
+        <v>6</v>
+      </c>
+      <c r="L148" t="n">
+        <v>6</v>
+      </c>
+      <c r="M148" t="n">
+        <v>6</v>
+      </c>
+      <c r="N148" t="n">
+        <v>6</v>
+      </c>
+      <c r="O148" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="P148" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="Q136" s="2" t="inlineStr">
-        <is>
-          <t>Well-known but limited formal critical analysis</t>
-        </is>
-      </c>
-      <c r="R136" s="2" t="inlineStr">
-        <is>
-          <t>At the Speed of Life. West Coast boom bap craftsman.</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="n">
-        <v>136</v>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>Saweetie</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>LA</t>
-        </is>
-      </c>
-      <c r="E137" s="2" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="inlineStr">
-        <is>
-          <t>Party/Pop</t>
-        </is>
-      </c>
-      <c r="G137" s="2" t="inlineStr">
-        <is>
-          <t>Trap Pop</t>
-        </is>
-      </c>
-      <c r="H137" s="2" t="inlineStr">
-        <is>
-          <t>Warner</t>
-        </is>
-      </c>
-      <c r="I137" s="2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="J137" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K137" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L137" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="M137" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N137" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="O137" s="6">
-        <f>AVERAGE(J137:N137)</f>
-        <v/>
-      </c>
-      <c r="P137" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q137" s="2" t="inlineStr">
-        <is>
-          <t>Recent commercial success; limited critical depth</t>
-        </is>
-      </c>
-      <c r="R137" s="2" t="inlineStr">
-        <is>
-          <t>Pretty Summer Playlist. Bay Area trap-pop aesthetic.</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="n">
-        <v>137</v>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>CI</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>City Girls</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr">
-        <is>
-          <t>Party/Pop</t>
-        </is>
-      </c>
-      <c r="G138" s="2" t="inlineStr">
-        <is>
-          <t>Miami Trap</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>Quality Control/Motown</t>
-        </is>
-      </c>
-      <c r="I138" s="2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="J138" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K138" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L138" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="M138" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N138" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="O138" s="6">
-        <f>AVERAGE(J138:N138)</f>
-        <v/>
-      </c>
-      <c r="P138" s="15" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="Q138" s="2" t="inlineStr">
-        <is>
-          <t>Limited critical record; cultural impact clearer than lyrical analysis</t>
-        </is>
-      </c>
-      <c r="R138" s="2" t="inlineStr">
-        <is>
-          <t>Period. Miami hedonistic party rap duo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="n">
-        <v>138</v>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>MX</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>Maxo Kream</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="E139" s="2" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>Gangsta/Street</t>
-        </is>
-      </c>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t>Houston Narrative Trap</t>
-        </is>
-      </c>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t>EMPIRE</t>
-        </is>
-      </c>
-      <c r="I139" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="J139" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K139" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L139" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M139" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N139" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="O139" s="6">
-        <f>AVERAGE(J139:N139)</f>
-        <v/>
-      </c>
-      <c r="P139" s="14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="Q139" s="2" t="inlineStr">
-        <is>
-          <t>Critical acclaim in narrative rap circles; limited mainstream documentation</t>
-        </is>
-      </c>
-      <c r="R139" s="2" t="inlineStr">
-        <is>
-          <t>Weight of the World. Houston storytelling tradition continued.</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="n">
-        <v>139</v>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>YN</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>Yvonne (Yaya Bey)</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>NYC</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t>2020s</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>Experimental</t>
-        </is>
-      </c>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t>Neo-Soul Jazz Rap</t>
-        </is>
-      </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>Independent</t>
-        </is>
-      </c>
-      <c r="I140" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="J140" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K140" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L140" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M140" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N140" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="O140" s="6">
-        <f>AVERAGE(J140:N140)</f>
-        <v/>
-      </c>
-      <c r="P140" s="15" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="Q140" s="2" t="inlineStr">
-        <is>
-          <t>Very recent and limited documentation; genre straddles rap and R&amp;B</t>
-        </is>
-      </c>
-      <c r="R140" s="2" t="inlineStr">
-        <is>
-          <t>Brooklyn experimental R&amp;B-rap hybrid. Underrecognized artistic depth.</t>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>Revered as a producer; underrated as a lyricist.</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>G-funk auteur. Producer-rapper with effortless West Coast bounce.</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>Element</t>
         </is>
       </c>
     </row>
@@ -11051,4 +12273,161 @@
   <autoFilter ref="A1:R1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>Scoring Confidence Flag Guide</t>
+        </is>
+      </c>
+      <c r="C1" s="17" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Flag</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+      <c r="C2" s="18" t="inlineStr">
+        <is>
+          <t>Criteria for assignment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>H — High</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Extensive critical record</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>Artist has: (1) sustained critical and/or academic attention, (2) multiple long-form critical analyses of their lyrical craft, (3) consistent reception across multiple sources, (4) enough body of work that scores are stable across albums. Examples: Rakim, Nas, Eminem, Kendrick, Biggie, Jay-Z.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>M — Medium</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Moderate documentation</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>Artist meets 1–2 of the High criteria but not all. May be: historically significant but under-analyzed (e.g. MC Lyte), recently emergent with promising but incomplete body of work (e.g. J.I.D, Doechii), subject to contested or shifting critical reception, or significant in regional/underground circles without mainstream scholarly attention. Scores should be treated as provisional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>L — Low</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Thin or contested record</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>Artist has: limited formal critical analysis, very recent emergence (insufficient time for consensus), scores that rely heavily on a single source or thin evidence base, reception clouded by non-lyrical controversy, or requires critical frameworks not well-developed in English-language sources (e.g. Latin rap, non-English artists). Scores marked L should be treated as initial estimates requiring verification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" s="17" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>METHODOLOGICAL NOTES</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Scoring basis</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>Critical consensus synthesis</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>All scores are derived from synthesis of published music criticism, academic hip-hop scholarship (Bradley, Chang, Kajikawa, Rabaka), and documented critical consensus. They are NOT computational — no NLP analysis was run. Aesop Rock is used as the Vocab Breadth=10 anchor based on published NLP studies of unique vocabulary in rap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Known biases</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Prestige / gender / language</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>The dataset over-represents: critically acclaimed artists vs commercially dominant ones; male artists (correcting); Golden Age NYC; English-language rap. Latin, African, and non-Anglophone rap are significantly underrepresented and scores for international artists should be treated with extra caution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Recommended verification</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>For each L- and M-flagged artist</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>Cross-reference against: RateYourMusic critical consensus scores, Pitchfork / The Wire artist discography reviews, academic sources via Google Scholar ('artist name' + 'lyricism' or 'hip-hop'), genre-specific publications (The Source, XXL retrospectives, Passion of the Weiss).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Artist Database" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Confidence Guide" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Data Dictionary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Artist Database'!$A$1:$R$1</definedName>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,6 +75,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="15">
@@ -161,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -215,6 +220,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1790,7 +1796,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>Element</t>
+          <t>Compound</t>
         </is>
       </c>
     </row>
@@ -12430,4 +12436,658 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B1" s="19" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="19" t="inlineStr">
+        <is>
+          <t>Allowed values / range</t>
+        </is>
+      </c>
+      <c r="D1" s="19" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="E1" s="19" t="inlineStr">
+        <is>
+          <t>Source / method</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>1–999</t>
+        </is>
+      </c>
+      <c r="D2" s="17" t="inlineStr">
+        <is>
+          <t>Display identifier for the tile. Not a true atomic number — ordering is historical accident of data entry, not a property of the artist.</t>
+        </is>
+      </c>
+      <c r="E2" s="17" t="inlineStr">
+        <is>
+          <t>Assigned at entry; display-only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>Text (≤4 chars)</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>Unique per act</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>Periodic-table-style abbreviation shown on the tile (e.g. Kd = Kendrick Lamar).</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>Assigned at entry; must be unique.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Artist Name</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>Canonical performing name of the act, web-verified spelling.</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>Verified against artist's official releases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>NYC, Philly, LA, South, Midwest, Bay Area</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>US scene the act is professionally rooted in. Assigned by label home / scene affiliation, NOT city of birth (e.g. Da Brat = South via So So Def, though born in Chicago).</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>Methods decision, documented 2026-06. International/UK acts are outside the sampling frame.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>Era</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>Old School, Golden Age, Late 90s, 2000s, 2010s, 2020s</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>The period of the act's defining run (peak prominence), not strictly debut year — debut years overlap era boundaries by design.</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>Judgment call from critical consensus on when the act's defining work landed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>Style</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Party/Pop, Political, Conscious/Lyrical, Gangsta/Street, Abstract, Jazz-Rap, Experimental, Trap/Drill</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Primary lyrical style. One value per act (dominant mode, not exhaustive description). Conscious/Street was merged into Conscious/Lyrical.</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>Assigned from critical consensus descriptions of the act's catalog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>Production Style</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Free text</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>Short descriptor of the act's characteristic production sound. Descriptive only; not used in scoring.</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>Entered from critical/press descriptions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Free text</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>Label most associated with the act's defining run (also anchors Region). Web-verified for L/M-confidence acts.</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>Verified against release credits and music-press coverage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>Debut Year</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>1973–present</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>Year of first commercial release (single or album).</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>Discographies; may precede assigned Era.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>Rhyme Density</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>1–10</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>CONSTRUCT: Frequency and complexity of rhyme — internal rhyme, multisyllabic chains, rhymes per bar, scheme inventiveness. Anchor: Rakim = 10 (pioneered internal/multisyllabic rhyme as standard practice).</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>Critical consensus synthesis (see Scoring basis). Not computed by NLP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>Vocab Breadth</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>1–10</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>CONSTRUCT: Lexical diversity — range of unique words and registers deployed across the catalog. Anchor: Aesop Rock = 10, based on published NLP studies of unique-word counts in rap.</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>Critical consensus synthesis, anchored to published NLP vocabulary studies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>Storytelling</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>1–10</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>CONSTRUCT: Narrative construction — character, plot, perspective shifts, and arc sustained within songs and across albums. Anchor: Scarface = 10; Slick Rick exemplary.</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>Critical consensus synthesis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Metaphor/Imagery</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>1–10</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>CONSTRUCT: Density and originality of figurative language — extended metaphor, vivid concrete imagery, double meanings.</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>Critical consensus synthesis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>Conceptual Depth</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>1–10</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>CONSTRUCT: Thematic ambition and coherence — album-level concepts, social/philosophical substance, sustained ideas. Anchor: Kendrick Lamar = 10; 10 is reserved for album-length conceptual execution at the highest tier.</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>Critical consensus synthesis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>Composite Score</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>Decimal (1 dp)</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>1.0–10.0</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>Unweighted mean of the five dimension scores. Serves as the 'atomic number' on the tile. Teaching point: equal weighting is itself a methods decision.</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>Computed: mean of 5 dimensions, rounded to 1 decimal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>H, M, L</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>How much to trust the scores for this act, based on depth of the critical record. Full criteria on the Confidence Guide sheet.</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>Rubric on Confidence Guide sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>Confidence Note</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>Free text</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>Why an act is M or L — what evidence is thin or contested. Blank for most H acts.</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>Entered at scoring time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Free text</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>One-to-two sentence profile shown in the tile modal.</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>Written from critical/press coverage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Element, Compound</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>Element = solo artist; Compound = group/crew (rendered in the separate Compounds table). An artist may appear as both a group member and an Element when they have a substantial solo career (e.g. Method Man, Ghostface Killah).</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>Methods decision, documented 2026-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="n"/>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="17" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>SAMPLING FRAME &amp; SCOPE RULES</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>Population</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>US-based hip-hop acts with a national critical record, 1973–present.</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="n"/>
+      <c r="D23" s="17" t="n"/>
+      <c r="E23" s="17" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>Inclusion</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>US-born or US-scene-based acts affiliated with a US label/scene during their defining run.</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="17" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>Exclusion</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>International and UK acts (scope decision to keep the frame tractable); acts without national critical coverage (survivorship limitation, documented).</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>Unit of analysis</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>The act (solo artist or group). Groups are Compounds; solo careers are Elements; both may appear.</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>Known frame biases</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>Over-represents critical acclaim, NYC, Golden Age, and men. See Confidence Guide sheet for the full bias table.</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S148"/>
+  <dimension ref="A1:T148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -705,6 +705,11 @@
           <t>Type</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -782,6 +787,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -859,6 +869,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -936,6 +951,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -1013,6 +1033,11 @@
           <t>Compound</t>
         </is>
       </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -1090,6 +1115,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -1167,6 +1197,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1244,6 +1279,11 @@
           <t>Compound</t>
         </is>
       </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1319,6 +1359,11 @@
       <c r="S9" t="inlineStr">
         <is>
           <t>Compound</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1398,6 +1443,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1475,6 +1525,11 @@
           <t>Compound</t>
         </is>
       </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1556,6 +1611,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1637,6 +1697,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1718,6 +1783,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1799,6 +1869,11 @@
           <t>Compound</t>
         </is>
       </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1880,6 +1955,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1961,6 +2041,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -2038,6 +2123,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -2119,6 +2209,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -2196,6 +2291,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -2255,7 +2355,7 @@
         <v>8</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.8</v>
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
@@ -2271,6 +2371,11 @@
       <c r="S21" t="inlineStr">
         <is>
           <t>Element</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2350,6 +2455,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -2427,6 +2537,11 @@
           <t>Compound</t>
         </is>
       </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -2486,7 +2601,7 @@
         <v>8</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.2</v>
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
@@ -2502,6 +2617,11 @@
       <c r="S24" t="inlineStr">
         <is>
           <t>Element</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2581,6 +2701,11 @@
           <t>Compound</t>
         </is>
       </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -2658,6 +2783,11 @@
           <t>Compound</t>
         </is>
       </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -2735,6 +2865,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -2812,6 +2947,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -2889,6 +3029,11 @@
           <t>Compound</t>
         </is>
       </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -2966,6 +3111,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -3043,6 +3193,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -3120,6 +3275,11 @@
           <t>Compound</t>
         </is>
       </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -3197,6 +3357,11 @@
           <t>Compound</t>
         </is>
       </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -3274,6 +3439,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -3355,6 +3525,11 @@
           <t>Compound</t>
         </is>
       </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -3432,6 +3607,11 @@
           <t>Compound</t>
         </is>
       </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -3513,6 +3693,11 @@
           <t>Compound</t>
         </is>
       </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -3594,6 +3779,11 @@
           <t>Compound</t>
         </is>
       </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -3653,7 +3843,7 @@
         <v>7</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.2</v>
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
@@ -3669,6 +3859,11 @@
       <c r="S39" t="inlineStr">
         <is>
           <t>Element</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3748,6 +3943,11 @@
           <t>Compound</t>
         </is>
       </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -3829,6 +4029,11 @@
           <t>Compound</t>
         </is>
       </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -3910,6 +4115,11 @@
           <t>Compound</t>
         </is>
       </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -3991,6 +4201,11 @@
           <t>Compound</t>
         </is>
       </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -4068,6 +4283,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -4145,6 +4365,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -4222,6 +4447,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -4281,7 +4511,7 @@
         <v>8</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.2</v>
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
@@ -4297,6 +4527,11 @@
       <c r="S47" t="inlineStr">
         <is>
           <t>Element</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4376,6 +4611,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -4435,7 +4675,7 @@
         <v>9</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.8</v>
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
@@ -4451,6 +4691,11 @@
       <c r="S49" t="inlineStr">
         <is>
           <t>Element</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -4530,6 +4775,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -4607,6 +4857,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -4684,6 +4939,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -4761,6 +5021,11 @@
           <t>Compound</t>
         </is>
       </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -4838,6 +5103,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -4919,6 +5189,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -5000,6 +5275,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -5077,6 +5357,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -5158,6 +5443,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -5239,6 +5529,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -5320,6 +5615,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -5379,7 +5679,7 @@
         <v>7</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.2</v>
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
@@ -5395,6 +5695,11 @@
       <c r="S61" t="inlineStr">
         <is>
           <t>Element</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5456,7 +5761,7 @@
         <v>8</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.2</v>
       </c>
       <c r="P62" s="14" t="inlineStr">
         <is>
@@ -5476,6 +5781,11 @@
       <c r="S62" t="inlineStr">
         <is>
           <t>Element</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5555,6 +5865,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -5632,6 +5947,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -5709,6 +6029,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -5786,6 +6111,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -5863,6 +6193,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -5922,7 +6257,7 @@
         <v>8</v>
       </c>
       <c r="O68" s="6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.2</v>
       </c>
       <c r="P68" s="7" t="inlineStr">
         <is>
@@ -5938,6 +6273,11 @@
       <c r="S68" t="inlineStr">
         <is>
           <t>Element</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -6017,6 +6357,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -6094,6 +6439,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -6171,6 +6521,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -6230,7 +6585,7 @@
         <v>10</v>
       </c>
       <c r="O72" s="6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.8</v>
       </c>
       <c r="P72" s="7" t="inlineStr">
         <is>
@@ -6246,6 +6601,11 @@
       <c r="S72" t="inlineStr">
         <is>
           <t>Element</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -6307,7 +6667,7 @@
         <v>8</v>
       </c>
       <c r="O73" s="6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.2</v>
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
@@ -6323,6 +6683,11 @@
       <c r="S73" t="inlineStr">
         <is>
           <t>Element</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -6402,6 +6767,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -6483,6 +6853,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -6560,6 +6935,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -6641,6 +7021,11 @@
           <t>Compound</t>
         </is>
       </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -6718,6 +7103,11 @@
           <t>Compound</t>
         </is>
       </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -6799,6 +7189,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -6880,6 +7275,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -6957,6 +7357,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -7034,6 +7439,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -7115,6 +7525,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -7196,6 +7611,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -7273,6 +7693,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -7350,6 +7775,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -7427,6 +7857,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -7504,6 +7939,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -7563,7 +8003,7 @@
         <v>9</v>
       </c>
       <c r="O89" s="6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.2</v>
       </c>
       <c r="P89" s="7" t="inlineStr">
         <is>
@@ -7579,6 +8019,11 @@
       <c r="S89" t="inlineStr">
         <is>
           <t>Element</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -7658,6 +8103,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -7735,6 +8185,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -7812,6 +8267,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
@@ -7889,6 +8349,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -7966,6 +8431,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
@@ -8043,6 +8513,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -8120,6 +8595,11 @@
           <t>Compound</t>
         </is>
       </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
@@ -8179,7 +8659,7 @@
         <v>9</v>
       </c>
       <c r="O97" s="6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.2</v>
       </c>
       <c r="P97" s="7" t="inlineStr">
         <is>
@@ -8195,6 +8675,11 @@
       <c r="S97" t="inlineStr">
         <is>
           <t>Element</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -8274,6 +8759,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -8351,6 +8841,11 @@
           <t>Compound</t>
         </is>
       </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -8432,6 +8927,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -8513,6 +9013,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -8590,6 +9095,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
@@ -8649,7 +9159,7 @@
         <v>8</v>
       </c>
       <c r="O103" s="6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.2</v>
       </c>
       <c r="P103" s="7" t="inlineStr">
         <is>
@@ -8665,6 +9175,11 @@
       <c r="S103" t="inlineStr">
         <is>
           <t>Element</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -8726,7 +9241,7 @@
         <v>8</v>
       </c>
       <c r="O104" s="6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.2</v>
       </c>
       <c r="P104" s="7" t="inlineStr">
         <is>
@@ -8742,6 +9257,11 @@
       <c r="S104" t="inlineStr">
         <is>
           <t>Element</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -8821,6 +9341,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -8880,7 +9405,7 @@
         <v>8</v>
       </c>
       <c r="O106" s="6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.2</v>
       </c>
       <c r="P106" s="14" t="inlineStr">
         <is>
@@ -8900,6 +9425,11 @@
       <c r="S106" t="inlineStr">
         <is>
           <t>Element</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -8979,6 +9509,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -9060,6 +9595,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
@@ -9141,6 +9681,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -9200,7 +9745,7 @@
         <v>9</v>
       </c>
       <c r="O110" s="6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.2</v>
       </c>
       <c r="P110" s="14" t="inlineStr">
         <is>
@@ -9220,6 +9765,11 @@
       <c r="S110" t="inlineStr">
         <is>
           <t>Element</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -9303,6 +9853,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -9384,6 +9939,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
@@ -9465,6 +10025,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -9542,6 +10107,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
@@ -9623,6 +10193,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -9704,6 +10279,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
@@ -9785,6 +10365,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -9866,6 +10451,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
@@ -9943,6 +10533,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -10020,6 +10615,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
@@ -10079,7 +10679,7 @@
         <v>8</v>
       </c>
       <c r="O121" s="6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.2</v>
       </c>
       <c r="P121" s="14" t="inlineStr">
         <is>
@@ -10099,6 +10699,11 @@
       <c r="S121" t="inlineStr">
         <is>
           <t>Element</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -10182,6 +10787,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
@@ -10263,6 +10873,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -10344,6 +10959,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
@@ -10403,7 +11023,7 @@
         <v>9</v>
       </c>
       <c r="O125" s="6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.2</v>
       </c>
       <c r="P125" s="7" t="inlineStr">
         <is>
@@ -10419,6 +11039,11 @@
       <c r="S125" t="inlineStr">
         <is>
           <t>Element</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -10502,6 +11127,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
@@ -10583,6 +11213,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
@@ -10664,6 +11299,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
@@ -10745,6 +11385,11 @@
           <t>Compound</t>
         </is>
       </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
@@ -10826,6 +11471,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -10885,7 +11535,7 @@
         <v>8</v>
       </c>
       <c r="O131" t="n">
-        <v>8.800000000000001</v>
+        <v>8.8</v>
       </c>
       <c r="P131" t="inlineStr">
         <is>
@@ -10900,6 +11550,11 @@
       <c r="S131" t="inlineStr">
         <is>
           <t>Compound</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -10983,6 +11638,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -11064,6 +11724,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -11145,6 +11810,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -11226,6 +11896,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -11307,6 +11982,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -11388,6 +12068,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -11469,6 +12154,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -11550,6 +12240,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -11631,6 +12326,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -11690,7 +12390,7 @@
         <v>7</v>
       </c>
       <c r="O141" t="n">
-        <v>8.199999999999999</v>
+        <v>8.2</v>
       </c>
       <c r="P141" t="inlineStr">
         <is>
@@ -11705,6 +12405,11 @@
       <c r="S141" t="inlineStr">
         <is>
           <t>Element</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -11788,6 +12493,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -11869,6 +12579,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -11950,6 +12665,11 @@
           <t>Compound</t>
         </is>
       </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -12031,6 +12751,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -12112,6 +12837,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -12193,6 +12923,11 @@
           <t>Element</t>
         </is>
       </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -12272,6 +13007,11 @@
       <c r="S148" t="inlineStr">
         <is>
           <t>Element</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -12444,7 +13184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12995,18 +13735,34 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="n"/>
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="17" t="n"/>
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>Male, Female, Mixed</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>Gender of the act as publicly identified. Mixed = group with members of more than one gender. Drives the dashboard’s gender-representation chart.</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>Public record; entered at data entry.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>SAMPLING FRAME &amp; SCOPE RULES</t>
-        </is>
-      </c>
+      <c r="A22" s="17" t="n"/>
       <c r="B22" s="17" t="n"/>
       <c r="C22" s="17" t="n"/>
       <c r="D22" s="17" t="n"/>
@@ -13015,14 +13771,10 @@
     <row r="23">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>Population</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>US-based hip-hop acts with a national critical record, 1973–present.</t>
-        </is>
-      </c>
+          <t>SAMPLING FRAME &amp; SCOPE RULES</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n"/>
       <c r="C23" s="17" t="n"/>
       <c r="D23" s="17" t="n"/>
       <c r="E23" s="17" t="n"/>
@@ -13030,12 +13782,12 @@
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>Inclusion</t>
+          <t>Population</t>
         </is>
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>US-born or US-scene-based acts affiliated with a US label/scene during their defining run.</t>
+          <t>US-based hip-hop acts with a national critical record, 1973–present.</t>
         </is>
       </c>
       <c r="C24" s="17" t="n"/>
@@ -13045,12 +13797,12 @@
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>Exclusion</t>
+          <t>Inclusion</t>
         </is>
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>International and UK acts (scope decision to keep the frame tractable); acts without national critical coverage (survivorship limitation, documented).</t>
+          <t>US-born or US-scene-based acts affiliated with a US label/scene during their defining run.</t>
         </is>
       </c>
       <c r="C25" s="17" t="n"/>
@@ -13060,12 +13812,12 @@
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>Unit of analysis</t>
+          <t>Exclusion</t>
         </is>
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>The act (solo artist or group). Groups are Compounds; solo careers are Elements; both may appear.</t>
+          <t>International and UK acts (scope decision to keep the frame tractable); acts without national critical coverage (survivorship limitation, documented).</t>
         </is>
       </c>
       <c r="C26" s="17" t="n"/>
@@ -13075,17 +13827,32 @@
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>Known frame biases</t>
+          <t>Unit of analysis</t>
         </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>Over-represents critical acclaim, NYC, Golden Age, and men. See Confidence Guide sheet for the full bias table.</t>
+          <t>The act (solo artist or group). Groups are Compounds; solo careers are Elements; both may appear.</t>
         </is>
       </c>
       <c r="C27" s="17" t="n"/>
       <c r="D27" s="17" t="n"/>
       <c r="E27" s="17" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>Known frame biases</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>Over-represents critical acclaim, NYC, Golden Age, and men. See Confidence Guide sheet for the full bias table.</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T148"/>
+  <dimension ref="A1:T164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -13015,6 +13015,1378 @@
         </is>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Salt-N-Pepa</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Golden Age</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Party/Pop</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>New Jack/Pop Rap</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Next Plateau</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>1985</v>
+      </c>
+      <c r="J149" t="n">
+        <v>5</v>
+      </c>
+      <c r="K149" t="n">
+        <v>5</v>
+      </c>
+      <c r="L149" t="n">
+        <v>5</v>
+      </c>
+      <c r="M149" t="n">
+        <v>5</v>
+      </c>
+      <c r="N149" t="n">
+        <v>6</v>
+      </c>
+      <c r="O149" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>Extensively covered historically; close lyrical analysis thinner than cultural impact</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>Best-selling female rap act of their era. Sex-positive anthems that moved the mainstream.</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Megan Thee Stallion</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Party/Pop</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Houston Trap</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>1501 Certified/300</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>2016</v>
+      </c>
+      <c r="J150" t="n">
+        <v>7</v>
+      </c>
+      <c r="K150" t="n">
+        <v>6</v>
+      </c>
+      <c r="L150" t="n">
+        <v>5</v>
+      </c>
+      <c r="M150" t="n">
+        <v>7</v>
+      </c>
+      <c r="N150" t="n">
+        <v>5</v>
+      </c>
+      <c r="O150" t="n">
+        <v>6</v>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>Recent; awards and commercial dominance clear; long-form lyrical analysis still accumulating</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>Houston hot-girl anthems built on genuine freestyle technique. Grammy Best New Artist.</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>YY</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Yo-Yo</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Golden Age</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Conscious/Lyrical</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>West Coast Funk</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>East West</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>1991</v>
+      </c>
+      <c r="J151" t="n">
+        <v>6</v>
+      </c>
+      <c r="K151" t="n">
+        <v>6</v>
+      </c>
+      <c r="L151" t="n">
+        <v>6</v>
+      </c>
+      <c r="M151" t="n">
+        <v>5</v>
+      </c>
+      <c r="N151" t="n">
+        <v>7</v>
+      </c>
+      <c r="O151" t="n">
+        <v>6</v>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>Cited in histories of women in rap; limited close lyrical analysis</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>Ice Cube protégée and IBWC founder. Feminist counterpoint inside gangsta-era LA.</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>BH</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Bahamadia</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Philly</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Late 90s</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Conscious/Lyrical</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Jazz Boom Bap</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Chrysalis/EMI</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>1995</v>
+      </c>
+      <c r="J152" t="n">
+        <v>8</v>
+      </c>
+      <c r="K152" t="n">
+        <v>8</v>
+      </c>
+      <c r="L152" t="n">
+        <v>6</v>
+      </c>
+      <c r="M152" t="n">
+        <v>7</v>
+      </c>
+      <c r="N152" t="n">
+        <v>7</v>
+      </c>
+      <c r="O152" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>Revered in underground and DJ circles; scant mainstream scholarship</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>Philly's smoothest technician. Kollage a cult classic of low-key precision flow.</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Jean Grae</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Conscious/Lyrical</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Underground Boom Bap</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Blacksmith</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>2002</v>
+      </c>
+      <c r="J153" t="n">
+        <v>8</v>
+      </c>
+      <c r="K153" t="n">
+        <v>8</v>
+      </c>
+      <c r="L153" t="n">
+        <v>7</v>
+      </c>
+      <c r="M153" t="n">
+        <v>8</v>
+      </c>
+      <c r="N153" t="n">
+        <v>7</v>
+      </c>
+      <c r="O153" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>Peer-acclaimed technician; coverage concentrated in underground press</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>Punchline surgeon and satirist. One of underground New York's most complete pens.</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Trina</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Party/Pop</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Miami Bass/Trap</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Slip-n-Slide</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>1998</v>
+      </c>
+      <c r="J154" t="n">
+        <v>5</v>
+      </c>
+      <c r="K154" t="n">
+        <v>5</v>
+      </c>
+      <c r="L154" t="n">
+        <v>4</v>
+      </c>
+      <c r="M154" t="n">
+        <v>5</v>
+      </c>
+      <c r="N154" t="n">
+        <v>4</v>
+      </c>
+      <c r="O154" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>Commercial longevity clear; almost no formal lyrical analysis</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>Miami mainstay. Two decades of unapologetic Southern raunch rap and resilience.</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Mia X</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Late 90s</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Gangsta/Street</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>No Limit Bounce</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>No Limit</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>1995</v>
+      </c>
+      <c r="J155" t="n">
+        <v>6</v>
+      </c>
+      <c r="K155" t="n">
+        <v>5</v>
+      </c>
+      <c r="L155" t="n">
+        <v>7</v>
+      </c>
+      <c r="M155" t="n">
+        <v>5</v>
+      </c>
+      <c r="N155" t="n">
+        <v>5</v>
+      </c>
+      <c r="O155" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>No Limit's first lady; regional significance with minimal national critical record</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>No Limit's first female star. New Orleans street matriarch with real narrative weight.</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>BTH</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Bone Thugs-N-Harmony</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Late 90s</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Gangsta/Street</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Melodic Midwest G-Funk</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Ruthless</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>1994</v>
+      </c>
+      <c r="J156" t="n">
+        <v>9</v>
+      </c>
+      <c r="K156" t="n">
+        <v>6</v>
+      </c>
+      <c r="L156" t="n">
+        <v>7</v>
+      </c>
+      <c r="M156" t="n">
+        <v>6</v>
+      </c>
+      <c r="N156" t="n">
+        <v>7</v>
+      </c>
+      <c r="O156" t="n">
+        <v>7</v>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr"/>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>Cleveland's melodic-speed innovators. Harmonized double-time no one has replicated.</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>8B</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>8Ball &amp; MJG</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Late 90s</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Gangsta/Street</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Memphis Funk</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Suave House</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>1993</v>
+      </c>
+      <c r="J157" t="n">
+        <v>7</v>
+      </c>
+      <c r="K157" t="n">
+        <v>6</v>
+      </c>
+      <c r="L157" t="n">
+        <v>8</v>
+      </c>
+      <c r="M157" t="n">
+        <v>6</v>
+      </c>
+      <c r="N157" t="n">
+        <v>6</v>
+      </c>
+      <c r="O157" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>Well-cited in Southern rap histories; close analysis thinner</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>Memphis's founding duo. Country-fried pimp narratives that drew the South's blueprint.</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>SM</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Souls of Mischief</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Golden Age</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Jazz-Rap</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Hieroglyphics Jazz Sample</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Jive</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>1993</v>
+      </c>
+      <c r="J158" t="n">
+        <v>8</v>
+      </c>
+      <c r="K158" t="n">
+        <v>8</v>
+      </c>
+      <c r="L158" t="n">
+        <v>6</v>
+      </c>
+      <c r="M158" t="n">
+        <v>7</v>
+      </c>
+      <c r="N158" t="n">
+        <v>7</v>
+      </c>
+      <c r="O158" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>'93 til Infinity canonical; group-level scholarship thinner than the single's fame</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>Hieroglyphics' teenage virtuosos. '93 til Infinity is the Bay's jazz-rap landmark.</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Twista</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Gangsta/Street</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Chicago Chopper/Soul</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Atlantic</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>1992</v>
+      </c>
+      <c r="J159" t="n">
+        <v>9</v>
+      </c>
+      <c r="K159" t="n">
+        <v>6</v>
+      </c>
+      <c r="L159" t="n">
+        <v>6</v>
+      </c>
+      <c r="M159" t="n">
+        <v>6</v>
+      </c>
+      <c r="N159" t="n">
+        <v>5</v>
+      </c>
+      <c r="O159" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>Speed technique widely celebrated; substantive analysis of the writing thinner</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>Chicago chopper pioneer. Once Guinness-fastest; precision at absurd tempo.</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>T9</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Tech N9ne</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Strange Music Horrorcore</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Strange Music</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>1999</v>
+      </c>
+      <c r="J160" t="n">
+        <v>9</v>
+      </c>
+      <c r="K160" t="n">
+        <v>7</v>
+      </c>
+      <c r="L160" t="n">
+        <v>6</v>
+      </c>
+      <c r="M160" t="n">
+        <v>6</v>
+      </c>
+      <c r="N160" t="n">
+        <v>6</v>
+      </c>
+      <c r="O160" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>Independent institution; peer-revered technique with little academic attention</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>Kansas City's independent empire. Chopper virtuosity meets horrorcore theatricality.</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Nelly</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Party/Pop</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>St. Louis Pop Rap</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Universal</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J161" t="n">
+        <v>5</v>
+      </c>
+      <c r="K161" t="n">
+        <v>5</v>
+      </c>
+      <c r="L161" t="n">
+        <v>5</v>
+      </c>
+      <c r="M161" t="n">
+        <v>5</v>
+      </c>
+      <c r="N161" t="n">
+        <v>4</v>
+      </c>
+      <c r="O161" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>Diamond-selling; critical framework mostly dismissive — a prestige-bias test case</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>St. Louis's melodic hitmaker. Country Grammar went diamond; craft chronically under-analyzed.</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Chief Keef</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Trap/Drill</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Chicago Drill</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Glory Boyz/Interscope</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>2012</v>
+      </c>
+      <c r="J162" t="n">
+        <v>4</v>
+      </c>
+      <c r="K162" t="n">
+        <v>4</v>
+      </c>
+      <c r="L162" t="n">
+        <v>4</v>
+      </c>
+      <c r="M162" t="n">
+        <v>5</v>
+      </c>
+      <c r="N162" t="n">
+        <v>5</v>
+      </c>
+      <c r="O162" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>Drill progenitor; reappraisal ongoing — influence far exceeds documented analysis</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>Drill's teenage architect. A Chicago sound that reshaped a decade of rap worldwide.</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>ROC</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Roc Marciano</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Gangsta/Street</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Drumless Loop Minimalism</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Marci Enterprises</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J163" t="n">
+        <v>8</v>
+      </c>
+      <c r="K163" t="n">
+        <v>8</v>
+      </c>
+      <c r="L163" t="n">
+        <v>7</v>
+      </c>
+      <c r="M163" t="n">
+        <v>9</v>
+      </c>
+      <c r="N163" t="n">
+        <v>7</v>
+      </c>
+      <c r="O163" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>Underground canon (Marcberg, Reloaded); specialist-press documentation only</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>Rebuilt New York minimalism. Slang-dense mafioso poetry; the modern underground's blueprint.</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>DZ</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Denzel Curry</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Florida Punk Trap</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Loma Vista</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>2013</v>
+      </c>
+      <c r="J164" t="n">
+        <v>8</v>
+      </c>
+      <c r="K164" t="n">
+        <v>7</v>
+      </c>
+      <c r="L164" t="n">
+        <v>6</v>
+      </c>
+      <c r="M164" t="n">
+        <v>7</v>
+      </c>
+      <c r="N164" t="n">
+        <v>8</v>
+      </c>
+      <c r="O164" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>Strong critical reception; scholarship still forming for the late-2010s class</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>Carol City shape-shifter. TA13OO fused punk energy with conceptual architecture.</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:R1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T164"/>
+  <dimension ref="A1:U164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -710,6 +710,11 @@
           <t>Gender</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Scene</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -727,7 +732,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -790,6 +795,11 @@
       <c r="T2" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -809,7 +819,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -872,6 +882,11 @@
       <c r="T3" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -891,7 +906,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -954,6 +969,11 @@
       <c r="T4" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -973,7 +993,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1036,6 +1056,11 @@
       <c r="T5" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1080,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1118,6 +1143,11 @@
       <c r="T6" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1167,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1202,6 +1232,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1219,7 +1254,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1284,6 +1319,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1301,7 +1341,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1364,6 +1404,11 @@
       <c r="T9" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1428,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1446,6 +1491,11 @@
       <c r="T10" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1515,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1528,6 +1578,11 @@
       <c r="T11" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1602,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1614,6 +1669,11 @@
       <c r="T12" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1693,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1700,6 +1760,11 @@
       <c r="T13" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1784,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Philly</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1786,6 +1851,11 @@
       <c r="T14" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Philly</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1875,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1872,6 +1942,11 @@
       <c r="T15" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1966,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1958,6 +2033,11 @@
       <c r="T16" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -1977,7 +2057,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2044,6 +2124,11 @@
       <c r="T17" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2148,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2126,6 +2211,11 @@
       <c r="T18" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2235,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2212,6 +2302,11 @@
       <c r="T19" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2326,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2294,6 +2389,11 @@
       <c r="T20" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -2313,7 +2413,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2376,6 +2476,11 @@
       <c r="T21" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2500,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2458,6 +2563,11 @@
       <c r="T22" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -2477,7 +2587,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2540,6 +2650,11 @@
       <c r="T23" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2674,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2622,6 +2737,11 @@
       <c r="T24" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2761,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -2704,6 +2824,11 @@
       <c r="T25" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -2723,7 +2848,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2786,6 +2911,11 @@
       <c r="T26" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2935,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2868,6 +2998,11 @@
       <c r="T27" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -2887,7 +3022,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2950,6 +3085,11 @@
       <c r="T28" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -2969,7 +3109,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3032,6 +3172,11 @@
       <c r="T29" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3196,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3114,6 +3259,11 @@
       <c r="T30" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3283,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3196,6 +3346,11 @@
       <c r="T31" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3370,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3278,6 +3433,11 @@
       <c r="T32" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3457,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -3360,6 +3520,11 @@
       <c r="T33" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -3379,7 +3544,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -3442,6 +3607,11 @@
       <c r="T34" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3631,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -3528,6 +3698,11 @@
       <c r="T35" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -3547,7 +3722,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -3610,6 +3785,11 @@
       <c r="T36" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3809,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -3696,6 +3876,11 @@
       <c r="T37" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3900,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -3782,6 +3967,11 @@
       <c r="T38" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3991,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -3864,6 +4054,11 @@
       <c r="T39" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -3948,6 +4143,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -3965,7 +4165,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4032,6 +4232,11 @@
       <c r="T41" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4256,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -4118,6 +4323,11 @@
       <c r="T42" t="inlineStr">
         <is>
           <t>Mixed</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -4137,7 +4347,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -4204,6 +4414,11 @@
       <c r="T43" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4438,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -4286,6 +4501,11 @@
       <c r="T44" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4525,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -4368,6 +4588,11 @@
       <c r="T45" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -4387,7 +4612,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -4450,6 +4675,11 @@
       <c r="T46" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -4534,6 +4764,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -4551,7 +4786,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -4614,6 +4849,11 @@
       <c r="T48" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -4633,7 +4873,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -4696,6 +4936,11 @@
       <c r="T49" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -4780,6 +5025,11 @@
           <t>Female</t>
         </is>
       </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -4797,7 +5047,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -4860,6 +5110,11 @@
       <c r="T51" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -4879,7 +5134,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -4942,6 +5197,11 @@
       <c r="T52" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -5026,6 +5286,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -5108,6 +5373,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -5125,7 +5395,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -5192,6 +5462,11 @@
       <c r="T55" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -5211,7 +5486,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -5278,6 +5553,11 @@
       <c r="T56" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -5297,7 +5577,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -5360,6 +5640,11 @@
       <c r="T57" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -5448,6 +5733,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -5465,7 +5755,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -5532,6 +5822,11 @@
       <c r="T59" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5846,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Philly</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -5618,6 +5913,11 @@
       <c r="T60" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Philly</t>
         </is>
       </c>
     </row>
@@ -5637,7 +5937,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -5700,6 +6000,11 @@
       <c r="T61" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -5719,7 +6024,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -5786,6 +6091,11 @@
       <c r="T62" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -5870,6 +6180,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -5952,6 +6267,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -6034,6 +6354,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -6116,6 +6441,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -6133,7 +6463,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -6196,6 +6526,11 @@
       <c r="T67" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6550,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -6278,6 +6613,11 @@
       <c r="T68" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -6362,6 +6702,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -6444,6 +6789,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -6526,6 +6876,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -6608,6 +6963,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -6690,6 +7050,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -6707,7 +7072,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -6770,6 +7135,11 @@
       <c r="T74" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -6789,7 +7159,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -6856,6 +7226,11 @@
       <c r="T75" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -6875,7 +7250,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -6938,6 +7313,11 @@
       <c r="T76" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -7026,6 +7406,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -7108,6 +7493,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -7194,6 +7584,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -7211,7 +7606,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -7278,6 +7673,11 @@
       <c r="T80" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7697,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -7360,6 +7760,11 @@
       <c r="T81" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7784,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -7442,6 +7847,11 @@
       <c r="T82" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -7530,6 +7940,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -7547,7 +7962,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -7614,6 +8029,11 @@
       <c r="T84" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -7633,7 +8053,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -7696,6 +8116,11 @@
       <c r="T85" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -7780,6 +8205,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -7862,6 +8292,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -7944,6 +8379,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -8026,6 +8466,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -8043,7 +8488,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -8106,6 +8551,11 @@
       <c r="T90" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -8125,7 +8575,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Philly</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -8188,6 +8638,11 @@
       <c r="T91" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Philly</t>
         </is>
       </c>
     </row>
@@ -8207,7 +8662,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -8270,6 +8725,11 @@
       <c r="T92" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -8289,7 +8749,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -8352,6 +8812,11 @@
       <c r="T93" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -8371,7 +8836,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -8434,6 +8899,11 @@
       <c r="T94" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -8518,6 +8988,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -8600,6 +9075,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
@@ -8682,6 +9162,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -8764,6 +9249,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -8846,6 +9336,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -8932,6 +9427,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -8949,7 +9449,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Philly</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -9016,6 +9516,11 @@
       <c r="T101" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Philly</t>
         </is>
       </c>
     </row>
@@ -9100,6 +9605,11 @@
           <t>Female</t>
         </is>
       </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
@@ -9182,6 +9692,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -9264,6 +9779,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -9346,6 +9866,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -9432,6 +9957,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
@@ -9449,7 +9979,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -9512,6 +10042,11 @@
       <c r="T107" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -9600,6 +10135,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
@@ -9686,6 +10226,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -9772,6 +10317,11 @@
           <t>Female</t>
         </is>
       </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
@@ -9858,6 +10408,11 @@
           <t>Female</t>
         </is>
       </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -9944,6 +10499,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
@@ -10030,6 +10590,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -10047,7 +10612,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -10110,6 +10675,11 @@
       <c r="T114" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -10198,6 +10768,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -10284,6 +10859,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
@@ -10370,6 +10950,11 @@
           <t>Female</t>
         </is>
       </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -10456,6 +11041,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
@@ -10473,7 +11063,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -10536,6 +11126,11 @@
       <c r="T119" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -10555,7 +11150,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -10618,6 +11213,11 @@
       <c r="T120" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -10637,7 +11237,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -10704,6 +11304,11 @@
       <c r="T121" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -10792,6 +11397,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
@@ -10878,6 +11488,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -10964,6 +11579,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
@@ -11046,6 +11666,11 @@
           <t>Female</t>
         </is>
       </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -11132,6 +11757,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
@@ -11149,7 +11779,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -11216,6 +11846,11 @@
       <c r="T127" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -11235,7 +11870,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -11302,6 +11937,11 @@
       <c r="T128" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
         </is>
       </c>
     </row>
@@ -11390,6 +12030,11 @@
           <t>Female</t>
         </is>
       </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
@@ -11476,6 +12121,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -11493,7 +12143,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Philly</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -11555,6 +12205,11 @@
       <c r="T131" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Philly</t>
         </is>
       </c>
     </row>
@@ -11574,7 +12229,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Philly</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -11641,6 +12296,11 @@
       <c r="T132" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Philly</t>
         </is>
       </c>
     </row>
@@ -11660,7 +12320,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Philly</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -11727,6 +12387,11 @@
       <c r="T133" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Philly</t>
         </is>
       </c>
     </row>
@@ -11746,7 +12411,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Philly</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -11813,6 +12478,11 @@
       <c r="T134" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Philly</t>
         </is>
       </c>
     </row>
@@ -11832,7 +12502,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Philly</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -11899,6 +12569,11 @@
       <c r="T135" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Philly</t>
         </is>
       </c>
     </row>
@@ -11987,6 +12662,11 @@
           <t>Female</t>
         </is>
       </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -12004,7 +12684,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12071,6 +12751,11 @@
       <c r="T137" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
         </is>
       </c>
     </row>
@@ -12090,7 +12775,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12157,6 +12842,11 @@
       <c r="T138" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
         </is>
       </c>
     </row>
@@ -12176,7 +12866,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12243,6 +12933,11 @@
       <c r="T139" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
         </is>
       </c>
     </row>
@@ -12331,6 +13026,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -12348,7 +13048,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12410,6 +13110,11 @@
       <c r="T141" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -12429,7 +13134,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12496,6 +13201,11 @@
       <c r="T142" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -12515,7 +13225,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -12582,6 +13292,11 @@
       <c r="T143" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -12601,7 +13316,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -12668,6 +13383,11 @@
       <c r="T144" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -12687,7 +13407,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -12754,6 +13474,11 @@
       <c r="T145" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -12773,7 +13498,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -12840,6 +13565,11 @@
       <c r="T146" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -12859,7 +13589,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -12926,6 +13656,11 @@
       <c r="T147" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -12945,7 +13680,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13012,6 +13747,11 @@
       <c r="T148" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -13031,7 +13771,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13098,6 +13838,11 @@
       <c r="T149" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -13186,6 +13931,11 @@
           <t>Female</t>
         </is>
       </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -13203,7 +13953,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13270,6 +14020,11 @@
       <c r="T151" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -13289,7 +14044,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Philly</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13356,6 +14111,11 @@
       <c r="T152" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Philly</t>
         </is>
       </c>
     </row>
@@ -13375,7 +14135,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13442,6 +14202,11 @@
       <c r="T153" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -13530,6 +14295,11 @@
           <t>Female</t>
         </is>
       </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -13616,6 +14386,11 @@
           <t>Female</t>
         </is>
       </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -13698,6 +14473,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -13784,6 +14564,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -13801,7 +14586,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -13868,6 +14653,11 @@
       <c r="T158" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
         </is>
       </c>
     </row>
@@ -13956,6 +14746,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -14042,6 +14837,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -14128,6 +14928,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -14214,6 +15019,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -14231,7 +15041,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14298,6 +15108,11 @@
       <c r="T163" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -14384,6 +15199,11 @@
       <c r="T164" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>South</t>
         </is>
       </c>
     </row>
@@ -14556,7 +15376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14687,17 +15507,17 @@
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>NYC, Philly, LA, South, Midwest, Bay Area</t>
+          <t>East Coast, West Coast, South, Midwest</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>US scene the act is professionally rooted in. Assigned by label home / scene affiliation, NOT city of birth (e.g. Da Brat = South via So So Def, though born in Chicago).</t>
+          <t>Coast-level region: East Coast = NYC + Philly scenes; West Coast = LA + Bay Area; South and Midwest map 1:1. Used by the dashboard charts and the periodic table’s shape glyph.</t>
         </is>
       </c>
       <c r="E5" s="17" t="inlineStr">
         <is>
-          <t>Methods decision, documented 2026-06. International/UK acts are outside the sampling frame.</t>
+          <t>Derived from Scene; coast rollup documented 2026-07.</t>
         </is>
       </c>
     </row>
@@ -15134,18 +15954,34 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="n"/>
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="17" t="n"/>
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>Scene</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>NYC, Philly, LA, South, Midwest, Bay Area</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>US scene the act is professionally rooted in — label home and scene affiliation during the defining run, NOT city of birth (e.g. Da Brat = South via So So Def, though born in Chicago). Finer-grained than Region; preserved when Region was rolled up to coasts.</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>Methods decision, documented 2026-06.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
-        <is>
-          <t>SAMPLING FRAME &amp; SCOPE RULES</t>
-        </is>
-      </c>
+      <c r="A23" s="17" t="n"/>
       <c r="B23" s="17" t="n"/>
       <c r="C23" s="17" t="n"/>
       <c r="D23" s="17" t="n"/>
@@ -15154,14 +15990,10 @@
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>Population</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>US-based hip-hop acts with a national critical record, 1973–present.</t>
-        </is>
-      </c>
+          <t>SAMPLING FRAME &amp; SCOPE RULES</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n"/>
       <c r="C24" s="17" t="n"/>
       <c r="D24" s="17" t="n"/>
       <c r="E24" s="17" t="n"/>
@@ -15169,12 +16001,12 @@
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>Inclusion</t>
+          <t>Population</t>
         </is>
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>US-born or US-scene-based acts affiliated with a US label/scene during their defining run.</t>
+          <t>US-based hip-hop acts with a national critical record, 1973–present.</t>
         </is>
       </c>
       <c r="C25" s="17" t="n"/>
@@ -15184,12 +16016,12 @@
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>Exclusion</t>
+          <t>Inclusion</t>
         </is>
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>International and UK acts (scope decision to keep the frame tractable); acts without national critical coverage (survivorship limitation, documented).</t>
+          <t>US-born or US-scene-based acts affiliated with a US label/scene during their defining run.</t>
         </is>
       </c>
       <c r="C26" s="17" t="n"/>
@@ -15199,12 +16031,12 @@
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>Unit of analysis</t>
+          <t>Exclusion</t>
         </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>The act (solo artist or group). Groups are Compounds; solo careers are Elements; both may appear.</t>
+          <t>International and UK acts (scope decision to keep the frame tractable); acts without national critical coverage (survivorship limitation, documented).</t>
         </is>
       </c>
       <c r="C27" s="17" t="n"/>
@@ -15214,17 +16046,32 @@
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>Known frame biases</t>
+          <t>Unit of analysis</t>
         </is>
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>Over-represents critical acclaim, NYC, Golden Age, and men. See Confidence Guide sheet for the full bias table.</t>
+          <t>The act (solo artist or group). Groups are Compounds; solo careers are Elements; both may appear.</t>
         </is>
       </c>
       <c r="C28" s="17" t="n"/>
       <c r="D28" s="17" t="n"/>
       <c r="E28" s="17" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>Known frame biases</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>Over-represents critical acclaim, NYC, Golden Age, and men. See Confidence Guide sheet for the full bias table.</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U164"/>
+  <dimension ref="A1:U174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Element</t>
+          <t>Compound</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -11298,7 +11298,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>Element</t>
+          <t>Compound</t>
         </is>
       </c>
       <c r="T121" t="inlineStr">
@@ -15204,6 +15204,908 @@
       <c r="U164" t="inlineStr">
         <is>
           <t>South</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>FG</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>The Fugees</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>East Coast</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Late 90s</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Conscious/Lyrical</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Neo-Soul Boom Bap</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Ruffhouse</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>1994</v>
+      </c>
+      <c r="J165" t="n">
+        <v>7</v>
+      </c>
+      <c r="K165" t="n">
+        <v>8</v>
+      </c>
+      <c r="L165" t="n">
+        <v>8</v>
+      </c>
+      <c r="M165" t="n">
+        <v>8</v>
+      </c>
+      <c r="N165" t="n">
+        <v>8</v>
+      </c>
+      <c r="O165" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr"/>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>The Score — three voices, one landmark. Refugee soul meets New York boom bap.</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Goodie Mob</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Late 90s</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Conscious/Lyrical</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Dungeon Family Funk</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>LaFace</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>1995</v>
+      </c>
+      <c r="J166" t="n">
+        <v>6</v>
+      </c>
+      <c r="K166" t="n">
+        <v>7</v>
+      </c>
+      <c r="L166" t="n">
+        <v>7</v>
+      </c>
+      <c r="M166" t="n">
+        <v>6</v>
+      </c>
+      <c r="N166" t="n">
+        <v>8</v>
+      </c>
+      <c r="O166" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>Well-cited in Southern rap histories; less close analysis than OutKast</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>Soul Food coined the Dirty South. The Dungeon Family's spiritual conscience.</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Company Flow</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>East Coast</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Late 90s</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Industrial Boom Bap</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Rawkus</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>1996</v>
+      </c>
+      <c r="J167" t="n">
+        <v>8</v>
+      </c>
+      <c r="K167" t="n">
+        <v>9</v>
+      </c>
+      <c r="L167" t="n">
+        <v>6</v>
+      </c>
+      <c r="M167" t="n">
+        <v>8</v>
+      </c>
+      <c r="N167" t="n">
+        <v>8</v>
+      </c>
+      <c r="O167" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>Underground canon; specialist-press documentation only</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>Funcrusher Plus — independent rap's blueprint. Dense, abrasive, uncompromising.</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Clipse</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Gangsta/Street</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Neptunes Minimalism</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Star Trak</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>2002</v>
+      </c>
+      <c r="J168" t="n">
+        <v>8</v>
+      </c>
+      <c r="K168" t="n">
+        <v>8</v>
+      </c>
+      <c r="L168" t="n">
+        <v>8</v>
+      </c>
+      <c r="M168" t="n">
+        <v>9</v>
+      </c>
+      <c r="N168" t="n">
+        <v>7</v>
+      </c>
+      <c r="O168" t="n">
+        <v>8</v>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr"/>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>Hell Hath No Fury — coke rap's cold masterpiece over Neptunes minimalism.</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>dead prez</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>East Coast</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Political</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Militant Boom Bap</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Loud</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J169" t="n">
+        <v>6</v>
+      </c>
+      <c r="K169" t="n">
+        <v>7</v>
+      </c>
+      <c r="L169" t="n">
+        <v>6</v>
+      </c>
+      <c r="M169" t="n">
+        <v>6</v>
+      </c>
+      <c r="N169" t="n">
+        <v>9</v>
+      </c>
+      <c r="O169" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>Politically canonical; formal lyrical analysis thinner</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>Let's Get Free — revolutionary program set to rap. 'Hip-Hop' still detonates.</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>LB2</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Little Brother</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Conscious/Lyrical</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>9th Wonder Soul</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>ABB/Atlantic</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>2003</v>
+      </c>
+      <c r="J170" t="n">
+        <v>7</v>
+      </c>
+      <c r="K170" t="n">
+        <v>7</v>
+      </c>
+      <c r="L170" t="n">
+        <v>8</v>
+      </c>
+      <c r="M170" t="n">
+        <v>7</v>
+      </c>
+      <c r="N170" t="n">
+        <v>8</v>
+      </c>
+      <c r="O170" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>Critically beloved; scholarship modest relative to reputation</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>The Listening and The Minstrel Show — North Carolina soul-rap satire and craft.</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Atmosphere</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Conscious/Lyrical</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Ant Soul Loops</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Rhymesayers</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>1997</v>
+      </c>
+      <c r="J171" t="n">
+        <v>7</v>
+      </c>
+      <c r="K171" t="n">
+        <v>7</v>
+      </c>
+      <c r="L171" t="n">
+        <v>8</v>
+      </c>
+      <c r="M171" t="n">
+        <v>7</v>
+      </c>
+      <c r="N171" t="n">
+        <v>7</v>
+      </c>
+      <c r="O171" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>Independent institution; underground-press documentation</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>Slug and Ant. Minneapolis confessional rap that built an independent empire.</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>BL</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Blackalicious</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>West Coast</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Conscious/Lyrical</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Quannum Funk</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Quannum/MCA</t>
+        </is>
+      </c>
+      <c r="I172" t="n">
+        <v>1994</v>
+      </c>
+      <c r="J172" t="n">
+        <v>9</v>
+      </c>
+      <c r="K172" t="n">
+        <v>9</v>
+      </c>
+      <c r="L172" t="n">
+        <v>6</v>
+      </c>
+      <c r="M172" t="n">
+        <v>7</v>
+      </c>
+      <c r="N172" t="n">
+        <v>7</v>
+      </c>
+      <c r="O172" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>Gift of Gab peer-revered; limited mainstream scholarship</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>Gift of Gab's tongue-twisting virtuosity over Chief Xcel. Alphabet Aerobics tier.</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>BP</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Brockhampton</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>West Coast</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>DIY Pop Rap</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Question Everything/RCA</t>
+        </is>
+      </c>
+      <c r="I173" t="n">
+        <v>2016</v>
+      </c>
+      <c r="J173" t="n">
+        <v>6</v>
+      </c>
+      <c r="K173" t="n">
+        <v>7</v>
+      </c>
+      <c r="L173" t="n">
+        <v>6</v>
+      </c>
+      <c r="M173" t="n">
+        <v>7</v>
+      </c>
+      <c r="N173" t="n">
+        <v>8</v>
+      </c>
+      <c r="O173" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>Recent; heavy press coverage, little formal analysis</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>The Saturation trilogy in one year. The streaming era's self-made boy band.</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Griselda</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>East Coast</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Gangsta/Street</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Drumless Boom Bap</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Griselda/Shady</t>
+        </is>
+      </c>
+      <c r="I174" t="n">
+        <v>2016</v>
+      </c>
+      <c r="J174" t="n">
+        <v>8</v>
+      </c>
+      <c r="K174" t="n">
+        <v>8</v>
+      </c>
+      <c r="L174" t="n">
+        <v>8</v>
+      </c>
+      <c r="M174" t="n">
+        <v>8</v>
+      </c>
+      <c r="N174" t="n">
+        <v>7</v>
+      </c>
+      <c r="O174" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>Crew output vast and recent; critical framework still consolidating</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>Buffalo's family business. WWCD made drumless grit the sound of underground NY.</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>

--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T164"/>
+  <dimension ref="A1:U174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -710,6 +710,11 @@
           <t>Gender</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Scene</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -727,7 +732,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -790,6 +795,11 @@
       <c r="T2" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -809,7 +819,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -872,6 +882,11 @@
       <c r="T3" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -891,7 +906,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -954,6 +969,11 @@
       <c r="T4" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -973,7 +993,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1036,6 +1056,11 @@
       <c r="T5" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1080,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1118,6 +1143,11 @@
       <c r="T6" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1167,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1202,6 +1232,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1219,7 +1254,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1284,6 +1319,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1301,7 +1341,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1364,6 +1404,11 @@
       <c r="T9" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1428,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1446,6 +1491,11 @@
       <c r="T10" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1515,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1528,6 +1578,11 @@
       <c r="T11" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1602,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1614,6 +1669,11 @@
       <c r="T12" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1693,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1700,6 +1760,11 @@
       <c r="T13" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1784,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Philly</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1786,6 +1851,11 @@
       <c r="T14" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Philly</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1875,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1872,6 +1942,11 @@
       <c r="T15" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1966,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1952,12 +2027,17 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Element</t>
+          <t>Compound</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -1977,7 +2057,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2044,6 +2124,11 @@
       <c r="T17" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2148,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2126,6 +2211,11 @@
       <c r="T18" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2235,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2212,6 +2302,11 @@
       <c r="T19" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2326,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2294,6 +2389,11 @@
       <c r="T20" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -2313,7 +2413,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2376,6 +2476,11 @@
       <c r="T21" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2500,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2458,6 +2563,11 @@
       <c r="T22" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -2477,7 +2587,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2540,6 +2650,11 @@
       <c r="T23" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2674,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2622,6 +2737,11 @@
       <c r="T24" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2761,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -2704,6 +2824,11 @@
       <c r="T25" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -2723,7 +2848,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2786,6 +2911,11 @@
       <c r="T26" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2935,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2868,6 +2998,11 @@
       <c r="T27" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -2887,7 +3022,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2950,6 +3085,11 @@
       <c r="T28" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -2969,7 +3109,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3032,6 +3172,11 @@
       <c r="T29" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3196,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3114,6 +3259,11 @@
       <c r="T30" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3283,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3196,6 +3346,11 @@
       <c r="T31" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3370,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3278,6 +3433,11 @@
       <c r="T32" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3457,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -3360,6 +3520,11 @@
       <c r="T33" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -3379,7 +3544,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -3442,6 +3607,11 @@
       <c r="T34" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3631,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -3528,6 +3698,11 @@
       <c r="T35" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -3547,7 +3722,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -3610,6 +3785,11 @@
       <c r="T36" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3809,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -3696,6 +3876,11 @@
       <c r="T37" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3900,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -3782,6 +3967,11 @@
       <c r="T38" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3991,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -3864,6 +4054,11 @@
       <c r="T39" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -3948,6 +4143,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -3965,7 +4165,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4032,6 +4232,11 @@
       <c r="T41" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4256,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -4118,6 +4323,11 @@
       <c r="T42" t="inlineStr">
         <is>
           <t>Mixed</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -4137,7 +4347,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -4204,6 +4414,11 @@
       <c r="T43" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4438,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -4286,6 +4501,11 @@
       <c r="T44" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4525,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -4368,6 +4588,11 @@
       <c r="T45" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -4387,7 +4612,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -4450,6 +4675,11 @@
       <c r="T46" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -4534,6 +4764,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -4551,7 +4786,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -4614,6 +4849,11 @@
       <c r="T48" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -4633,7 +4873,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -4696,6 +4936,11 @@
       <c r="T49" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -4780,6 +5025,11 @@
           <t>Female</t>
         </is>
       </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -4797,7 +5047,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -4860,6 +5110,11 @@
       <c r="T51" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -4879,7 +5134,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -4942,6 +5197,11 @@
       <c r="T52" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -5026,6 +5286,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -5108,6 +5373,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -5125,7 +5395,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -5192,6 +5462,11 @@
       <c r="T55" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -5211,7 +5486,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -5278,6 +5553,11 @@
       <c r="T56" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -5297,7 +5577,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -5360,6 +5640,11 @@
       <c r="T57" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -5448,6 +5733,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -5465,7 +5755,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -5532,6 +5822,11 @@
       <c r="T59" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5846,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Philly</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -5618,6 +5913,11 @@
       <c r="T60" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Philly</t>
         </is>
       </c>
     </row>
@@ -5637,7 +5937,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -5700,6 +6000,11 @@
       <c r="T61" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -5719,7 +6024,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -5786,6 +6091,11 @@
       <c r="T62" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -5870,6 +6180,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -5952,6 +6267,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -6034,6 +6354,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -6116,6 +6441,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -6133,7 +6463,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -6196,6 +6526,11 @@
       <c r="T67" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6550,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -6278,6 +6613,11 @@
       <c r="T68" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -6362,6 +6702,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -6444,6 +6789,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -6526,6 +6876,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -6608,6 +6963,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -6690,6 +7050,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -6707,7 +7072,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -6770,6 +7135,11 @@
       <c r="T74" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -6789,7 +7159,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -6856,6 +7226,11 @@
       <c r="T75" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -6875,7 +7250,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -6938,6 +7313,11 @@
       <c r="T76" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -7026,6 +7406,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -7108,6 +7493,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -7194,6 +7584,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -7211,7 +7606,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -7278,6 +7673,11 @@
       <c r="T80" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7697,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -7360,6 +7760,11 @@
       <c r="T81" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7784,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -7442,6 +7847,11 @@
       <c r="T82" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -7530,6 +7940,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -7547,7 +7962,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -7614,6 +8029,11 @@
       <c r="T84" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -7633,7 +8053,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -7696,6 +8116,11 @@
       <c r="T85" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -7780,6 +8205,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -7862,6 +8292,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -7944,6 +8379,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -8026,6 +8466,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -8043,7 +8488,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -8106,6 +8551,11 @@
       <c r="T90" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -8125,7 +8575,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Philly</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -8188,6 +8638,11 @@
       <c r="T91" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Philly</t>
         </is>
       </c>
     </row>
@@ -8207,7 +8662,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -8270,6 +8725,11 @@
       <c r="T92" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -8289,7 +8749,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -8352,6 +8812,11 @@
       <c r="T93" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -8371,7 +8836,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -8434,6 +8899,11 @@
       <c r="T94" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -8518,6 +8988,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -8600,6 +9075,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
@@ -8682,6 +9162,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -8764,6 +9249,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -8846,6 +9336,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -8932,6 +9427,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -8949,7 +9449,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Philly</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -9016,6 +9516,11 @@
       <c r="T101" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Philly</t>
         </is>
       </c>
     </row>
@@ -9100,6 +9605,11 @@
           <t>Female</t>
         </is>
       </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
@@ -9182,6 +9692,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -9264,6 +9779,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -9346,6 +9866,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -9432,6 +9957,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
@@ -9449,7 +9979,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -9512,6 +10042,11 @@
       <c r="T107" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -9600,6 +10135,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
@@ -9686,6 +10226,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -9772,6 +10317,11 @@
           <t>Female</t>
         </is>
       </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
@@ -9858,6 +10408,11 @@
           <t>Female</t>
         </is>
       </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -9944,6 +10499,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
@@ -10030,6 +10590,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -10047,7 +10612,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -10110,6 +10675,11 @@
       <c r="T114" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -10198,6 +10768,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -10284,6 +10859,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
@@ -10370,6 +10950,11 @@
           <t>Female</t>
         </is>
       </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -10456,6 +11041,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
@@ -10473,7 +11063,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -10536,6 +11126,11 @@
       <c r="T119" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -10555,7 +11150,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -10618,6 +11213,11 @@
       <c r="T120" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -10637,7 +11237,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -10698,12 +11298,17 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>Element</t>
+          <t>Compound</t>
         </is>
       </c>
       <c r="T121" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -10792,6 +11397,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
@@ -10878,6 +11488,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -10964,6 +11579,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
@@ -11046,6 +11666,11 @@
           <t>Female</t>
         </is>
       </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -11132,6 +11757,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
@@ -11149,7 +11779,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -11216,6 +11846,11 @@
       <c r="T127" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -11235,7 +11870,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -11302,6 +11937,11 @@
       <c r="T128" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
         </is>
       </c>
     </row>
@@ -11390,6 +12030,11 @@
           <t>Female</t>
         </is>
       </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
@@ -11476,6 +12121,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -11493,7 +12143,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Philly</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -11555,6 +12205,11 @@
       <c r="T131" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Philly</t>
         </is>
       </c>
     </row>
@@ -11574,7 +12229,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Philly</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -11641,6 +12296,11 @@
       <c r="T132" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Philly</t>
         </is>
       </c>
     </row>
@@ -11660,7 +12320,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Philly</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -11727,6 +12387,11 @@
       <c r="T133" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Philly</t>
         </is>
       </c>
     </row>
@@ -11746,7 +12411,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Philly</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -11813,6 +12478,11 @@
       <c r="T134" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Philly</t>
         </is>
       </c>
     </row>
@@ -11832,7 +12502,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Philly</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -11899,6 +12569,11 @@
       <c r="T135" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Philly</t>
         </is>
       </c>
     </row>
@@ -11987,6 +12662,11 @@
           <t>Female</t>
         </is>
       </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -12004,7 +12684,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12071,6 +12751,11 @@
       <c r="T137" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
         </is>
       </c>
     </row>
@@ -12090,7 +12775,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12157,6 +12842,11 @@
       <c r="T138" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
         </is>
       </c>
     </row>
@@ -12176,7 +12866,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12243,6 +12933,11 @@
       <c r="T139" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
         </is>
       </c>
     </row>
@@ -12331,6 +13026,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -12348,7 +13048,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12410,6 +13110,11 @@
       <c r="T141" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -12429,7 +13134,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -12496,6 +13201,11 @@
       <c r="T142" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -12515,7 +13225,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -12582,6 +13292,11 @@
       <c r="T143" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -12601,7 +13316,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -12668,6 +13383,11 @@
       <c r="T144" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -12687,7 +13407,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -12754,6 +13474,11 @@
       <c r="T145" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -12773,7 +13498,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -12840,6 +13565,11 @@
       <c r="T146" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -12859,7 +13589,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -12926,6 +13656,11 @@
       <c r="T147" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -12945,7 +13680,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13012,6 +13747,11 @@
       <c r="T148" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -13031,7 +13771,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13098,6 +13838,11 @@
       <c r="T149" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -13186,6 +13931,11 @@
           <t>Female</t>
         </is>
       </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -13203,7 +13953,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13270,6 +14020,11 @@
       <c r="T151" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -13289,7 +14044,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Philly</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13356,6 +14111,11 @@
       <c r="T152" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Philly</t>
         </is>
       </c>
     </row>
@@ -13375,7 +14135,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13442,6 +14202,11 @@
       <c r="T153" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -13530,6 +14295,11 @@
           <t>Female</t>
         </is>
       </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -13616,6 +14386,11 @@
           <t>Female</t>
         </is>
       </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -13698,6 +14473,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -13784,6 +14564,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -13801,7 +14586,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Bay Area</t>
+          <t>West Coast</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -13868,6 +14653,11 @@
       <c r="T158" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
         </is>
       </c>
     </row>
@@ -13956,6 +14746,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -14042,6 +14837,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -14128,6 +14928,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -14214,6 +15019,11 @@
           <t>Male</t>
         </is>
       </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -14231,7 +15041,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NYC</t>
+          <t>East Coast</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14298,6 +15108,11 @@
       <c r="T163" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -14384,6 +15199,913 @@
       <c r="T164" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>FG</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>The Fugees</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>East Coast</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Late 90s</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Conscious/Lyrical</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Neo-Soul Boom Bap</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Ruffhouse</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>1994</v>
+      </c>
+      <c r="J165" t="n">
+        <v>7</v>
+      </c>
+      <c r="K165" t="n">
+        <v>8</v>
+      </c>
+      <c r="L165" t="n">
+        <v>8</v>
+      </c>
+      <c r="M165" t="n">
+        <v>8</v>
+      </c>
+      <c r="N165" t="n">
+        <v>8</v>
+      </c>
+      <c r="O165" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr"/>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>The Score — three voices, one landmark. Refugee soul meets New York boom bap.</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Goodie Mob</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Late 90s</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Conscious/Lyrical</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Dungeon Family Funk</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>LaFace</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>1995</v>
+      </c>
+      <c r="J166" t="n">
+        <v>6</v>
+      </c>
+      <c r="K166" t="n">
+        <v>7</v>
+      </c>
+      <c r="L166" t="n">
+        <v>7</v>
+      </c>
+      <c r="M166" t="n">
+        <v>6</v>
+      </c>
+      <c r="N166" t="n">
+        <v>8</v>
+      </c>
+      <c r="O166" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>Well-cited in Southern rap histories; less close analysis than OutKast</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>Soul Food coined the Dirty South. The Dungeon Family's spiritual conscience.</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Company Flow</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>East Coast</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Late 90s</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Industrial Boom Bap</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Rawkus</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>1996</v>
+      </c>
+      <c r="J167" t="n">
+        <v>8</v>
+      </c>
+      <c r="K167" t="n">
+        <v>9</v>
+      </c>
+      <c r="L167" t="n">
+        <v>6</v>
+      </c>
+      <c r="M167" t="n">
+        <v>8</v>
+      </c>
+      <c r="N167" t="n">
+        <v>8</v>
+      </c>
+      <c r="O167" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>Underground canon; specialist-press documentation only</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>Funcrusher Plus — independent rap's blueprint. Dense, abrasive, uncompromising.</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Clipse</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Gangsta/Street</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Neptunes Minimalism</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Star Trak</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>2002</v>
+      </c>
+      <c r="J168" t="n">
+        <v>8</v>
+      </c>
+      <c r="K168" t="n">
+        <v>8</v>
+      </c>
+      <c r="L168" t="n">
+        <v>8</v>
+      </c>
+      <c r="M168" t="n">
+        <v>9</v>
+      </c>
+      <c r="N168" t="n">
+        <v>7</v>
+      </c>
+      <c r="O168" t="n">
+        <v>8</v>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr"/>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>Hell Hath No Fury — coke rap's cold masterpiece over Neptunes minimalism.</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>dead prez</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>East Coast</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Political</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Militant Boom Bap</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Loud</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J169" t="n">
+        <v>6</v>
+      </c>
+      <c r="K169" t="n">
+        <v>7</v>
+      </c>
+      <c r="L169" t="n">
+        <v>6</v>
+      </c>
+      <c r="M169" t="n">
+        <v>6</v>
+      </c>
+      <c r="N169" t="n">
+        <v>9</v>
+      </c>
+      <c r="O169" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>Politically canonical; formal lyrical analysis thinner</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>Let's Get Free — revolutionary program set to rap. 'Hip-Hop' still detonates.</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>LB2</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Little Brother</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Conscious/Lyrical</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>9th Wonder Soul</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>ABB/Atlantic</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>2003</v>
+      </c>
+      <c r="J170" t="n">
+        <v>7</v>
+      </c>
+      <c r="K170" t="n">
+        <v>7</v>
+      </c>
+      <c r="L170" t="n">
+        <v>8</v>
+      </c>
+      <c r="M170" t="n">
+        <v>7</v>
+      </c>
+      <c r="N170" t="n">
+        <v>8</v>
+      </c>
+      <c r="O170" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>Critically beloved; scholarship modest relative to reputation</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>The Listening and The Minstrel Show — North Carolina soul-rap satire and craft.</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Atmosphere</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Conscious/Lyrical</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Ant Soul Loops</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Rhymesayers</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>1997</v>
+      </c>
+      <c r="J171" t="n">
+        <v>7</v>
+      </c>
+      <c r="K171" t="n">
+        <v>7</v>
+      </c>
+      <c r="L171" t="n">
+        <v>8</v>
+      </c>
+      <c r="M171" t="n">
+        <v>7</v>
+      </c>
+      <c r="N171" t="n">
+        <v>7</v>
+      </c>
+      <c r="O171" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>Independent institution; underground-press documentation</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>Slug and Ant. Minneapolis confessional rap that built an independent empire.</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>BL</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Blackalicious</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>West Coast</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Conscious/Lyrical</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Quannum Funk</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Quannum/MCA</t>
+        </is>
+      </c>
+      <c r="I172" t="n">
+        <v>1994</v>
+      </c>
+      <c r="J172" t="n">
+        <v>9</v>
+      </c>
+      <c r="K172" t="n">
+        <v>9</v>
+      </c>
+      <c r="L172" t="n">
+        <v>6</v>
+      </c>
+      <c r="M172" t="n">
+        <v>7</v>
+      </c>
+      <c r="N172" t="n">
+        <v>7</v>
+      </c>
+      <c r="O172" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>Gift of Gab peer-revered; limited mainstream scholarship</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>Gift of Gab's tongue-twisting virtuosity over Chief Xcel. Alphabet Aerobics tier.</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>BP</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Brockhampton</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>West Coast</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>DIY Pop Rap</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Question Everything/RCA</t>
+        </is>
+      </c>
+      <c r="I173" t="n">
+        <v>2016</v>
+      </c>
+      <c r="J173" t="n">
+        <v>6</v>
+      </c>
+      <c r="K173" t="n">
+        <v>7</v>
+      </c>
+      <c r="L173" t="n">
+        <v>6</v>
+      </c>
+      <c r="M173" t="n">
+        <v>7</v>
+      </c>
+      <c r="N173" t="n">
+        <v>8</v>
+      </c>
+      <c r="O173" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>Recent; heavy press coverage, little formal analysis</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>The Saturation trilogy in one year. The streaming era's self-made boy band.</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Griselda</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>East Coast</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Gangsta/Street</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Drumless Boom Bap</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Griselda/Shady</t>
+        </is>
+      </c>
+      <c r="I174" t="n">
+        <v>2016</v>
+      </c>
+      <c r="J174" t="n">
+        <v>8</v>
+      </c>
+      <c r="K174" t="n">
+        <v>8</v>
+      </c>
+      <c r="L174" t="n">
+        <v>8</v>
+      </c>
+      <c r="M174" t="n">
+        <v>8</v>
+      </c>
+      <c r="N174" t="n">
+        <v>7</v>
+      </c>
+      <c r="O174" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>Crew output vast and recent; critical framework still consolidating</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>Buffalo's family business. WWCD made drumless grit the sound of underground NY.</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>NYC</t>
         </is>
       </c>
     </row>
@@ -14556,7 +16278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14687,17 +16409,17 @@
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>NYC, Philly, LA, South, Midwest, Bay Area</t>
+          <t>East Coast, West Coast, South, Midwest</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>US scene the act is professionally rooted in. Assigned by label home / scene affiliation, NOT city of birth (e.g. Da Brat = South via So So Def, though born in Chicago).</t>
+          <t>Coast-level region: East Coast = NYC + Philly scenes; West Coast = LA + Bay Area; South and Midwest map 1:1. Used by the dashboard charts and the periodic table’s shape glyph.</t>
         </is>
       </c>
       <c r="E5" s="17" t="inlineStr">
         <is>
-          <t>Methods decision, documented 2026-06. International/UK acts are outside the sampling frame.</t>
+          <t>Derived from Scene; coast rollup documented 2026-07.</t>
         </is>
       </c>
     </row>
@@ -15134,18 +16856,34 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="n"/>
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="17" t="n"/>
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>Scene</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>Categorical</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>NYC, Philly, LA, South, Midwest, Bay Area</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>US scene the act is professionally rooted in — label home and scene affiliation during the defining run, NOT city of birth (e.g. Da Brat = South via So So Def, though born in Chicago). Finer-grained than Region; preserved when Region was rolled up to coasts.</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>Methods decision, documented 2026-06.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
-        <is>
-          <t>SAMPLING FRAME &amp; SCOPE RULES</t>
-        </is>
-      </c>
+      <c r="A23" s="17" t="n"/>
       <c r="B23" s="17" t="n"/>
       <c r="C23" s="17" t="n"/>
       <c r="D23" s="17" t="n"/>
@@ -15154,14 +16892,10 @@
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>Population</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>US-based hip-hop acts with a national critical record, 1973–present.</t>
-        </is>
-      </c>
+          <t>SAMPLING FRAME &amp; SCOPE RULES</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n"/>
       <c r="C24" s="17" t="n"/>
       <c r="D24" s="17" t="n"/>
       <c r="E24" s="17" t="n"/>
@@ -15169,12 +16903,12 @@
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>Inclusion</t>
+          <t>Population</t>
         </is>
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>US-born or US-scene-based acts affiliated with a US label/scene during their defining run.</t>
+          <t>US-based hip-hop acts with a national critical record, 1973–present.</t>
         </is>
       </c>
       <c r="C25" s="17" t="n"/>
@@ -15184,12 +16918,12 @@
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>Exclusion</t>
+          <t>Inclusion</t>
         </is>
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>International and UK acts (scope decision to keep the frame tractable); acts without national critical coverage (survivorship limitation, documented).</t>
+          <t>US-born or US-scene-based acts affiliated with a US label/scene during their defining run.</t>
         </is>
       </c>
       <c r="C26" s="17" t="n"/>
@@ -15199,12 +16933,12 @@
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>Unit of analysis</t>
+          <t>Exclusion</t>
         </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>The act (solo artist or group). Groups are Compounds; solo careers are Elements; both may appear.</t>
+          <t>International and UK acts (scope decision to keep the frame tractable); acts without national critical coverage (survivorship limitation, documented).</t>
         </is>
       </c>
       <c r="C27" s="17" t="n"/>
@@ -15214,17 +16948,32 @@
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>Known frame biases</t>
+          <t>Unit of analysis</t>
         </is>
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>Over-represents critical acclaim, NYC, Golden Age, and men. See Confidence Guide sheet for the full bias table.</t>
+          <t>The act (solo artist or group). Groups are Compounds; solo careers are Elements; both may appear.</t>
         </is>
       </c>
       <c r="C28" s="17" t="n"/>
       <c r="D28" s="17" t="n"/>
       <c r="E28" s="17" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>Known frame biases</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>Over-represents critical acclaim, NYC, Golden Age, and men. See Confidence Guide sheet for the full bias table.</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -819,6 +819,16 @@
           <t>Scene</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Signature Work</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Active Through</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="14" t="n">
@@ -906,6 +916,9 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="W2" t="n">
+        <v>1977</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
@@ -993,6 +1006,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>The Adventures of Grandmaster Flash on the Wheels of Steel (1981)</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>2009</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
@@ -1078,6 +1099,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>The Message (1982)</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>1989</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
@@ -1165,6 +1194,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Rapper's Delight (1979)</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>1985</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
@@ -1252,6 +1289,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Planet Rock (1982)</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>1991</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
@@ -1339,6 +1384,11 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Mama Said Knock You Out (1990)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="n">
@@ -1426,6 +1476,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Raising Hell (1986)</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>2002</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
@@ -1512,6 +1570,14 @@
         <is>
           <t>NYC</t>
         </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Paul's Boutique (1989)</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>2012</v>
       </c>
     </row>
     <row r="10">
@@ -1600,6 +1666,11 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Criminal Minded (1987)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="n">
@@ -1687,6 +1758,11 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>It Takes a Nation of Millions to Hold Us Back (1988)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="n">
@@ -1778,6 +1854,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Roxanne's Revenge (1984)</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>1992</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="n">
@@ -1869,6 +1953,11 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lyte as a Rock (1988)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="n">
@@ -1960,6 +2049,14 @@
           <t>Philly</t>
         </is>
       </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>P.S.K. What Does It Mean? (1985)</t>
+        </is>
+      </c>
+      <c r="W14" t="n">
+        <v>2000</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="n">
@@ -2051,6 +2148,14 @@
           <t>LA</t>
         </is>
       </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Supersonic (1988)</t>
+        </is>
+      </c>
+      <c r="W15" t="n">
+        <v>1992</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="n">
@@ -2142,6 +2247,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Escape (1984)</t>
+        </is>
+      </c>
+      <c r="W16" t="n">
+        <v>1996</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="n">
@@ -2233,6 +2346,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>The Show / La Di Da Di (1985)</t>
+        </is>
+      </c>
+      <c r="W17" t="n">
+        <v>1995</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="n">
@@ -2320,6 +2441,11 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>The Great Adventures of Slick Rick (1988)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="n">
@@ -2411,6 +2537,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dana Dane with Fame (1987)</t>
+        </is>
+      </c>
+      <c r="W19" t="n">
+        <v>1995</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="14" t="n">
@@ -2498,6 +2632,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Long Live the Kane (1988)</t>
+        </is>
+      </c>
+      <c r="W20" t="n">
+        <v>1998</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="n">
@@ -2585,6 +2727,11 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Paid in Full (1987)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="14" t="n">
@@ -2672,6 +2819,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>All Hail the Queen (1989)</t>
+        </is>
+      </c>
+      <c r="W22" t="n">
+        <v>1998</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="n">
@@ -2759,6 +2914,14 @@
           <t>LA</t>
         </is>
       </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Straight Outta Compton (1988)</t>
+        </is>
+      </c>
+      <c r="W23" t="n">
+        <v>1991</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="14" t="n">
@@ -2846,6 +3009,11 @@
           <t>LA</t>
         </is>
       </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>AmeriKKKa's Most Wanted (1990)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="n">
@@ -2933,6 +3101,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>3 Feet High and Rising (1989)</t>
+        </is>
+      </c>
+      <c r="W25" t="n">
+        <v>2016</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="n">
@@ -3020,6 +3196,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>The Low End Theory (1991)</t>
+        </is>
+      </c>
+      <c r="W26" t="n">
+        <v>2016</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="n">
@@ -3107,6 +3291,11 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Illmatic (1994)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="n">
@@ -3194,6 +3383,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ready to Die (1994)</t>
+        </is>
+      </c>
+      <c r="W28" t="n">
+        <v>1997</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="n">
@@ -3281,6 +3478,11 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Enter the Wu-Tang (36 Chambers) (1993)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="n">
@@ -3368,6 +3570,11 @@
           <t>LA</t>
         </is>
       </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Doggystyle (1993)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="n">
@@ -3455,6 +3662,11 @@
           <t>LA</t>
         </is>
       </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>The Chronic (1992)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="n">
@@ -3542,6 +3754,14 @@
           <t>LA</t>
         </is>
       </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Bizarre Ride II the Pharcyde (1992)</t>
+        </is>
+      </c>
+      <c r="W32" t="n">
+        <v>2004</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="14" t="n">
@@ -3629,6 +3849,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>The Infamous (1995)</t>
+        </is>
+      </c>
+      <c r="W33" t="n">
+        <v>2017</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="14" t="n">
@@ -3716,6 +3944,11 @@
           <t>Bay Area</t>
         </is>
       </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>In a Major Way (1995)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="14" t="n">
@@ -3807,6 +4040,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Mecca and the Soul Brother (1992)</t>
+        </is>
+      </c>
+      <c r="W35" t="n">
+        <v>1995</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="n">
@@ -3894,6 +4135,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Moment of Truth (1998)</t>
+        </is>
+      </c>
+      <c r="W36" t="n">
+        <v>2003</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="n">
@@ -3985,6 +4234,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>One for All (1990)</t>
+        </is>
+      </c>
+      <c r="W37" t="n">
+        <v>2007</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="n">
@@ -4076,6 +4333,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>To the East, Blackwards (1990)</t>
+        </is>
+      </c>
+      <c r="W38" t="n">
+        <v>2007</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="n">
@@ -4163,6 +4428,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Lifestylez ov da Poor &amp; Dangerous (1995)</t>
+        </is>
+      </c>
+      <c r="W39" t="n">
+        <v>1999</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="n">
@@ -4250,6 +4523,14 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>We Can't Be Stopped (1991)</t>
+        </is>
+      </c>
+      <c r="W40" t="n">
+        <v>2005</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="n">
@@ -4341,6 +4622,14 @@
           <t>LA</t>
         </is>
       </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Innercity Griots (1993)</t>
+        </is>
+      </c>
+      <c r="W41" t="n">
+        <v>2011</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="14" t="n">
@@ -4432,6 +4721,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Reachin' (A New Refutation of Time and Space) (1993)</t>
+        </is>
+      </c>
+      <c r="W42" t="n">
+        <v>1995</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="n">
@@ -4523,6 +4820,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>A Future Without a Past... (1991)</t>
+        </is>
+      </c>
+      <c r="W43" t="n">
+        <v>1994</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="14" t="n">
@@ -4610,6 +4915,11 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>When Disaster Strikes... (1997)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="14" t="n">
@@ -4697,6 +5007,14 @@
           <t>LA</t>
         </is>
       </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>All Eyez on Me (1996)</t>
+        </is>
+      </c>
+      <c r="W45" t="n">
+        <v>1996</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="14" t="n">
@@ -4784,6 +5102,11 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>The Blueprint (2001)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="14" t="n">
@@ -4871,6 +5194,11 @@
           <t>Midwest</t>
         </is>
       </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>The Marshall Mathers LP (2000)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="14" t="n">
@@ -4958,6 +5286,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>It's Dark and Hell Is Hot (1998)</t>
+        </is>
+      </c>
+      <c r="W48" t="n">
+        <v>2021</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="14" t="n">
@@ -5043,6 +5379,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>The Miseducation of Lauryn Hill (1998)</t>
+        </is>
+      </c>
+      <c r="W49" t="n">
+        <v>2002</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="14" t="n">
@@ -5130,6 +5474,11 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Supa Dupa Fly (1997)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="14" t="n">
@@ -5215,6 +5564,11 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Black on Both Sides (1999)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="14" t="n">
@@ -5302,6 +5656,11 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Quality (2002)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="14" t="n">
@@ -5389,6 +5748,14 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Aquemini (1998)</t>
+        </is>
+      </c>
+      <c r="W53" t="n">
+        <v>2006</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="14" t="n">
@@ -5476,6 +5843,14 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ghetto D (1997)</t>
+        </is>
+      </c>
+      <c r="W54" t="n">
+        <v>2005</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="14" t="n">
@@ -5567,6 +5942,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Purple Haze (2004)</t>
+        </is>
+      </c>
+      <c r="W55" t="n">
+        <v>2019</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="14" t="n">
@@ -5658,6 +6041,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ill Na Na (1996)</t>
+        </is>
+      </c>
+      <c r="W56" t="n">
+        <v>2008</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="14" t="n">
@@ -5745,6 +6136,11 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Hard Core (1996)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="14" t="n">
@@ -5836,6 +6232,14 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>400 Degreez (1998)</t>
+        </is>
+      </c>
+      <c r="W58" t="n">
+        <v>2019</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="14" t="n">
@@ -5927,6 +6331,11 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Can-I-Bus (1998)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="14" t="n">
@@ -6018,6 +6427,11 @@
           <t>Philly</t>
         </is>
       </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Violent by Design (2000)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="14" t="n">
@@ -6105,6 +6519,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Capital Punishment (1998)</t>
+        </is>
+      </c>
+      <c r="W61" t="n">
+        <v>2000</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="14" t="n">
@@ -6196,6 +6618,11 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Doe or Die (1995)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="14" t="n">
@@ -6283,6 +6710,11 @@
           <t>Midwest</t>
         </is>
       </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>My Beautiful Dark Twisted Fantasy (2010)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="14" t="n">
@@ -6370,6 +6802,11 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Tha Carter III (2008)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="14" t="n">
@@ -6457,6 +6894,11 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Trap Muzik (2003)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="14" t="n">
@@ -6544,6 +6986,11 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>The State vs. Radric Davis (2009)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="14" t="n">
@@ -6631,6 +7078,11 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Supreme Clientele (2000)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="14" t="n">
@@ -6718,6 +7170,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Madvillainy (2004)</t>
+        </is>
+      </c>
+      <c r="W68" t="n">
+        <v>2020</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="14" t="n">
@@ -6805,6 +7265,11 @@
           <t>Midwest</t>
         </is>
       </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Be (2005)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="14" t="n">
@@ -6892,6 +7357,14 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Word of Mouf (2001)</t>
+        </is>
+      </c>
+      <c r="W70" t="n">
+        <v>2015</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="14" t="n">
@@ -6979,6 +7452,11 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Let's Get It: Thug Motivation 101 (2005)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="14" t="n">
@@ -7066,6 +7544,11 @@
           <t>Midwest</t>
         </is>
       </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>The Cool (2007)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="14" t="n">
@@ -7153,6 +7636,14 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>The Diary (1994)</t>
+        </is>
+      </c>
+      <c r="W73" t="n">
+        <v>2015</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="14" t="n">
@@ -7240,6 +7731,11 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Labor Days (2001)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="14" t="n">
@@ -7331,6 +7827,11 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Kiss of Death (2004)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="14" t="n">
@@ -7418,6 +7919,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Get Rich or Die Tryin' (2003)</t>
+        </is>
+      </c>
+      <c r="W76" t="n">
+        <v>2014</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="14" t="n">
@@ -7509,6 +8018,14 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Mystic Stylez (1995)</t>
+        </is>
+      </c>
+      <c r="W77" t="n">
+        <v>2008</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="14" t="n">
@@ -7596,6 +8113,14 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Ridin' Dirty (1996)</t>
+        </is>
+      </c>
+      <c r="W78" t="n">
+        <v>2007</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="14" t="n">
@@ -7687,6 +8212,11 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Restless (2006)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="14" t="n">
@@ -7778,6 +8308,11 @@
           <t>LA</t>
         </is>
       </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>All Balls Don't Bounce (1995)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="14" t="n">
@@ -7863,6 +8398,11 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Only Built 4 Cuban Linx… (1995)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="14" t="n">
@@ -7950,6 +8490,11 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Fantastic Damage (2002)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="14" t="n">
@@ -8041,6 +8586,11 @@
           <t>Midwest</t>
         </is>
       </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Shadows on the Sun (2003)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="14" t="n">
@@ -8132,6 +8682,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Revolutionary Vol. 2 (2003)</t>
+        </is>
+      </c>
+      <c r="W84" t="n">
+        <v>2011</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="14" t="n">
@@ -8219,6 +8777,11 @@
           <t>LA</t>
         </is>
       </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>To Pimp a Butterfly (2015)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="14" t="n">
@@ -8306,6 +8869,11 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>2014 Forest Hills Drive (2014)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="14" t="n">
@@ -8393,6 +8961,11 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jeffery (2016)</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="14" t="n">
@@ -8480,6 +9053,11 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>DS2 (2015)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="14" t="n">
@@ -8567,6 +9145,11 @@
           <t>Midwest</t>
         </is>
       </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Acid Rap (2013)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="14" t="n">
@@ -8654,6 +9237,11 @@
           <t>LA</t>
         </is>
       </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Some Rap Songs (2018)</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="14" t="n">
@@ -8741,6 +9329,11 @@
           <t>Philly</t>
         </is>
       </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dreams and Nightmares (2012)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="14" t="n">
@@ -8828,6 +9421,11 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Long. Live. A$AP (2013)</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="14" t="n">
@@ -8915,6 +9513,11 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Pink Friday (2010)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="14" t="n">
@@ -9002,6 +9605,11 @@
           <t>LA</t>
         </is>
       </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Summertime '06 (2015)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="14" t="n">
@@ -9089,6 +9697,11 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>4eva Is a Mighty Long Time (2017)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="14" t="n">
@@ -9176,6 +9789,11 @@
           <t>Midwest</t>
         </is>
       </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Run the Jewels 2 (2014)</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="14" t="n">
@@ -9263,6 +9881,11 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>R.A.P. Music (2012)</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="n">
@@ -9350,6 +9973,11 @@
           <t>Midwest</t>
         </is>
       </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Piñata (2014)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="14" t="n">
@@ -9437,6 +10065,14 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Culture (2017)</t>
+        </is>
+      </c>
+      <c r="W99" t="n">
+        <v>2022</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="n">
@@ -9528,6 +10164,11 @@
           <t>Midwest</t>
         </is>
       </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dark Sky Paradise (2015)</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="14" t="n">
@@ -9617,6 +10258,11 @@
           <t>Philly</t>
         </is>
       </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Whack World (2018)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="n">
@@ -9704,6 +10350,11 @@
           <t>Midwest</t>
         </is>
       </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Room 25 (2018)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="14" t="n">
@@ -9789,6 +10440,11 @@
           <t>Midwest</t>
         </is>
       </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>CARE FOR ME (2018)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="n">
@@ -9876,6 +10532,11 @@
           <t>Midwest</t>
         </is>
       </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Atrocity Exhibition (2016)</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="14" t="n">
@@ -9963,6 +10624,14 @@
           <t>Midwest</t>
         </is>
       </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Swimming (2018)</t>
+        </is>
+      </c>
+      <c r="W105" t="n">
+        <v>2018</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="14" t="n">
@@ -10054,6 +10723,11 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>The Forever Story (2022)</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="14" t="n">
@@ -10141,6 +10815,11 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Invasion of Privacy (2018)</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="14" t="n">
@@ -10232,6 +10911,11 @@
           <t>Midwest</t>
         </is>
       </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Hall of Fame (2021)</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="14" t="n">
@@ -10323,6 +11007,11 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>SoulFly (2021)</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="14" t="n">
@@ -10414,6 +11103,11 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Alligator Bites Never Heal (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="14" t="n">
@@ -10505,6 +11199,11 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>GLORIOUS (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="14" t="n">
@@ -10596,6 +11295,11 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>WUNNA (2020)</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="14" t="n">
@@ -10687,6 +11391,11 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>My Turn (2020)</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="14" t="n">
@@ -10774,6 +11483,11 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Tana Talk 3 (2018)</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="14" t="n">
@@ -10865,6 +11579,11 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Father of 4 (2019)</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="14" t="n">
@@ -10956,6 +11675,11 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Angelic Hoodrat (2020)</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="14" t="n">
@@ -11047,6 +11771,11 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>777 (2022)</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="14" t="n">
@@ -11138,6 +11867,11 @@
           <t>Midwest</t>
         </is>
       </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>blkswn (2017)</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="14" t="n">
@@ -11223,6 +11957,11 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Daytona (2018)</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="14" t="n">
@@ -11308,6 +12047,11 @@
           <t>LA</t>
         </is>
       </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Igor (2019)</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="14" t="n">
@@ -11399,6 +12143,11 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Haram (2021)</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="14" t="n">
@@ -11490,6 +12239,11 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>shut the fuck up talking to me (2021)</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="14" t="n">
@@ -11581,6 +12335,11 @@
           <t>Midwest</t>
         </is>
       </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>The Voice (2020)</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="14" t="n">
@@ -11672,6 +12431,11 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Painting Pictures (2017)</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="14" t="n">
@@ -11759,6 +12523,11 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Laila's Wisdom (2017)</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="14" t="n">
@@ -11850,6 +12619,11 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Let the Sun Talk (2019)</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="14" t="n">
@@ -11941,6 +12715,11 @@
           <t>LA</t>
         </is>
       </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>40 Dayz &amp; 40 Nightz (1998)</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="14" t="n">
@@ -12032,6 +12811,11 @@
           <t>Bay Area</t>
         </is>
       </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>My Type (2019)</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="14" t="n">
@@ -12123,6 +12907,14 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Girl Code (2018)</t>
+        </is>
+      </c>
+      <c r="W129" t="n">
+        <v>2023</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="14" t="n">
@@ -12214,6 +13006,11 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Weight of the World (2021)</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -12300,6 +13097,11 @@
           <t>Philly</t>
         </is>
       </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Things Fall Apart (1999)</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -12391,6 +13193,14 @@
           <t>Philly</t>
         </is>
       </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>The Truth (2000)</t>
+        </is>
+      </c>
+      <c r="W132" t="n">
+        <v>2012</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -12482,6 +13292,11 @@
           <t>Philly</t>
         </is>
       </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Eternal Atake (2020)</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -12573,6 +13388,14 @@
           <t>Philly</t>
         </is>
       </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Philadelphia Freeway (2003)</t>
+        </is>
+      </c>
+      <c r="W134" t="n">
+        <v>2018</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -12664,6 +13487,14 @@
           <t>Philly</t>
         </is>
       </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Let There Be Eve... Ruff Ryders' First Lady (1999)</t>
+        </is>
+      </c>
+      <c r="W135" t="n">
+        <v>2013</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -12755,6 +13586,14 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Funkdafied (1994)</t>
+        </is>
+      </c>
+      <c r="W136" t="n">
+        <v>2003</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -12846,6 +13685,11 @@
           <t>Bay Area</t>
         </is>
       </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Life Is... Too Short (1988)</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -12937,6 +13781,11 @@
           <t>Bay Area</t>
         </is>
       </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>I Wish My Brother George Was Here (1991)</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -13028,6 +13877,14 @@
           <t>Bay Area</t>
         </is>
       </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Ronald Dregan: Dreganomics (2004)</t>
+        </is>
+      </c>
+      <c r="W139" t="n">
+        <v>2004</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -13119,6 +13976,11 @@
           <t>Midwest</t>
         </is>
       </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Book of Ryan (2018)</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -13205,6 +14067,11 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Live and Let Die (1992)</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -13296,6 +14163,11 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Muddy Waters (1996)</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -13387,6 +14259,11 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Tical (1994)</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -13478,6 +14355,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Strictly Business (1988)</t>
+        </is>
+      </c>
+      <c r="W144" t="n">
+        <v>2008</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -13569,6 +14454,11 @@
           <t>LA</t>
         </is>
       </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>The Documentary (2005)</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -13660,6 +14550,14 @@
           <t>LA</t>
         </is>
       </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>O.G. Original Gangster (1991)</t>
+        </is>
+      </c>
+      <c r="W146" t="n">
+        <v>2006</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -13751,6 +14649,14 @@
           <t>LA</t>
         </is>
       </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Victory Lap (2018)</t>
+        </is>
+      </c>
+      <c r="W147" t="n">
+        <v>2019</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -13842,6 +14748,14 @@
           <t>LA</t>
         </is>
       </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Quik Is the Name (1991)</t>
+        </is>
+      </c>
+      <c r="W148" t="n">
+        <v>2017</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -13933,6 +14847,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Very Necessary (1993)</t>
+        </is>
+      </c>
+      <c r="W149" t="n">
+        <v>1997</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -14024,6 +14946,11 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Good News (2020)</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -14115,6 +15042,14 @@
           <t>LA</t>
         </is>
       </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Make Way for the Motherlode (1991)</t>
+        </is>
+      </c>
+      <c r="W151" t="n">
+        <v>1996</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -14206,6 +15141,11 @@
           <t>Philly</t>
         </is>
       </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Kollage (1996)</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -14297,6 +15237,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Jeanius (2008)</t>
+        </is>
+      </c>
+      <c r="W153" t="n">
+        <v>2018</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -14388,6 +15336,14 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Da Baddest Bitch (2000)</t>
+        </is>
+      </c>
+      <c r="W154" t="n">
+        <v>2019</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -14479,6 +15435,14 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Unlady Like (1997)</t>
+        </is>
+      </c>
+      <c r="W155" t="n">
+        <v>1998</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -14566,6 +15530,14 @@
           <t>Midwest</t>
         </is>
       </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>E. 1999 Eternal (1995)</t>
+        </is>
+      </c>
+      <c r="W156" t="n">
+        <v>2017</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -14657,6 +15629,14 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>On Top of the World (1995)</t>
+        </is>
+      </c>
+      <c r="W157" t="n">
+        <v>2010</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -14748,6 +15728,14 @@
           <t>Bay Area</t>
         </is>
       </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>93 'til Infinity (1993)</t>
+        </is>
+      </c>
+      <c r="W158" t="n">
+        <v>2014</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -14839,6 +15827,11 @@
           <t>Midwest</t>
         </is>
       </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Kamikaze (2004)</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -14930,6 +15923,11 @@
           <t>Midwest</t>
         </is>
       </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>All 6's and 7's (2011)</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -15019,6 +16017,11 @@
           <t>Midwest</t>
         </is>
       </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Country Grammar (2000)</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -15108,6 +16111,11 @@
           <t>Midwest</t>
         </is>
       </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Finally Rich (2012)</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -15199,6 +16207,11 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Reloaded (2012)</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -15290,6 +16303,11 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>TA13OO (2018)</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -15375,6 +16393,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>The Score (1996)</t>
+        </is>
+      </c>
+      <c r="W165" t="n">
+        <v>1997</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -15466,6 +16492,11 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Soul Food (1995)</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -15555,6 +16586,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Funcrusher Plus (1997)</t>
+        </is>
+      </c>
+      <c r="W167" t="n">
+        <v>2000</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -15640,6 +16679,11 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Hell Hath No Fury (2006)</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -15729,6 +16773,14 @@
           <t>NYC</t>
         </is>
       </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Let's Get Free (2000)</t>
+        </is>
+      </c>
+      <c r="W169" t="n">
+        <v>2012</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -15818,6 +16870,14 @@
           <t>South</t>
         </is>
       </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>The Minstrel Show (2005)</t>
+        </is>
+      </c>
+      <c r="W170" t="n">
+        <v>2019</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -15909,6 +16969,11 @@
           <t>Midwest</t>
         </is>
       </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>God Loves Ugly (2002)</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -16000,6 +17065,14 @@
           <t>Bay Area</t>
         </is>
       </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>Blazing Arrow (2002)</t>
+        </is>
+      </c>
+      <c r="W172" t="n">
+        <v>2021</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -16091,6 +17164,14 @@
           <t>LA</t>
         </is>
       </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>Saturation II (2017)</t>
+        </is>
+      </c>
+      <c r="W173" t="n">
+        <v>2022</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -16180,6 +17261,11 @@
       <c r="U174" t="inlineStr">
         <is>
           <t>NYC</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>WWCD (2019)</t>
         </is>
       </c>
     </row>
@@ -16931,34 +18017,62 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>Signature Work</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>"Title (Year)"; blank if none recorded</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>The act’s consensus defining release: an album, or a single for acts that predate albums. One per act; blank only where no recorded signature work exists (e.g. Kool Herc).</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>Critical consensus synthesis; entered 2026-07.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>SAMPLING FRAME &amp; SCOPE RULES</t>
-        </is>
-      </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>Active Through</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>1977–present; blank = still active</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>Last year of new primary-catalog output (death, disbandment, or final album). With Debut Year, gives the active span shown on the tile modal.</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>Discographies; judgment call for gradual fade-outs.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>Population</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>US-based hip-hop acts with a national critical record, 1973–present.</t>
-        </is>
-      </c>
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
       <c r="C25" s="17"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
@@ -16966,14 +18080,10 @@
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>Inclusion</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>US-born or US-scene-based acts affiliated with a US label/scene during their defining run.</t>
-        </is>
-      </c>
+          <t>SAMPLING FRAME &amp; SCOPE RULES</t>
+        </is>
+      </c>
+      <c r="B26" s="17"/>
       <c r="C26" s="17"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
@@ -16981,12 +18091,12 @@
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>Exclusion</t>
+          <t>Population</t>
         </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>International and UK acts (scope decision to keep the frame tractable); acts without national critical coverage (survivorship limitation, documented).</t>
+          <t>US-based hip-hop acts with a national critical record, 1973–present.</t>
         </is>
       </c>
       <c r="C27" s="17"/>
@@ -16996,12 +18106,12 @@
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>Unit of analysis</t>
+          <t>Inclusion</t>
         </is>
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>The act (solo artist or group). Groups are Compounds; solo careers are Elements; both may appear.</t>
+          <t>US-born or US-scene-based acts affiliated with a US label/scene during their defining run.</t>
         </is>
       </c>
       <c r="C28" s="17"/>
@@ -17011,17 +18121,47 @@
     <row r="29">
       <c r="A29" s="18" t="inlineStr">
         <is>
-          <t>Known frame biases</t>
+          <t>Exclusion</t>
         </is>
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>Over-represents critical acclaim, NYC, Golden Age, and men. See Confidence Guide sheet for the full bias table.</t>
+          <t>International and UK acts (scope decision to keep the frame tractable); acts without national critical coverage (survivorship limitation, documented).</t>
         </is>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>Unit of analysis</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>The act (solo artist or group). Groups are Compounds; solo careers are Elements; both may appear.</t>
+        </is>
+      </c>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>Known frame biases</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>Over-represents critical acclaim, NYC, Golden Age, and men. See Confidence Guide sheet for the full bias table.</t>
+        </is>
+      </c>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -829,6 +829,11 @@
           <t>Active Through</t>
         </is>
       </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="14" t="n">
@@ -919,6 +924,9 @@
       <c r="W2" t="n">
         <v>1977</v>
       </c>
+      <c r="X2" t="n">
+        <v>1955</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
@@ -1014,6 +1022,9 @@
       <c r="W3" t="n">
         <v>2009</v>
       </c>
+      <c r="X3" t="n">
+        <v>1958</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="n">
@@ -1107,6 +1118,9 @@
       <c r="W4" t="n">
         <v>1989</v>
       </c>
+      <c r="X4" t="n">
+        <v>1961</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
@@ -1297,6 +1311,9 @@
       <c r="W6" t="n">
         <v>1991</v>
       </c>
+      <c r="X6" t="n">
+        <v>1957</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
@@ -1389,6 +1406,9 @@
           <t>Mama Said Knock You Out (1990)</t>
         </is>
       </c>
+      <c r="X7" t="n">
+        <v>1968</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="n">
@@ -1671,6 +1691,9 @@
           <t>Criminal Minded (1987)</t>
         </is>
       </c>
+      <c r="X10" t="n">
+        <v>1965</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="n">
@@ -1862,6 +1885,9 @@
       <c r="W12" t="n">
         <v>1992</v>
       </c>
+      <c r="X12" t="n">
+        <v>1969</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="n">
@@ -1958,6 +1984,9 @@
           <t>Lyte as a Rock (1988)</t>
         </is>
       </c>
+      <c r="X13" t="n">
+        <v>1970</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="n">
@@ -2057,6 +2086,9 @@
       <c r="W14" t="n">
         <v>2000</v>
       </c>
+      <c r="X14" t="n">
+        <v>1962</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="n">
@@ -2354,6 +2386,9 @@
       <c r="W17" t="n">
         <v>1995</v>
       </c>
+      <c r="X17" t="n">
+        <v>1966</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="n">
@@ -2446,6 +2481,9 @@
           <t>The Great Adventures of Slick Rick (1988)</t>
         </is>
       </c>
+      <c r="X18" t="n">
+        <v>1965</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="n">
@@ -2545,6 +2583,9 @@
       <c r="W19" t="n">
         <v>1995</v>
       </c>
+      <c r="X19" t="n">
+        <v>1965</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="14" t="n">
@@ -2640,6 +2681,9 @@
       <c r="W20" t="n">
         <v>1998</v>
       </c>
+      <c r="X20" t="n">
+        <v>1968</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="n">
@@ -2732,6 +2776,9 @@
           <t>Paid in Full (1987)</t>
         </is>
       </c>
+      <c r="X21" t="n">
+        <v>1968</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="14" t="n">
@@ -2827,6 +2874,9 @@
       <c r="W22" t="n">
         <v>1998</v>
       </c>
+      <c r="X22" t="n">
+        <v>1970</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="n">
@@ -3014,6 +3064,9 @@
           <t>AmeriKKKa's Most Wanted (1990)</t>
         </is>
       </c>
+      <c r="X24" t="n">
+        <v>1969</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="n">
@@ -3296,6 +3349,9 @@
           <t>Illmatic (1994)</t>
         </is>
       </c>
+      <c r="X27" t="n">
+        <v>1973</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="n">
@@ -3391,6 +3447,9 @@
       <c r="W28" t="n">
         <v>1997</v>
       </c>
+      <c r="X28" t="n">
+        <v>1972</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="n">
@@ -3575,6 +3634,9 @@
           <t>Doggystyle (1993)</t>
         </is>
       </c>
+      <c r="X30" t="n">
+        <v>1971</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="n">
@@ -3667,6 +3729,9 @@
           <t>The Chronic (1992)</t>
         </is>
       </c>
+      <c r="X31" t="n">
+        <v>1965</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="n">
@@ -3949,6 +4014,9 @@
           <t>In a Major Way (1995)</t>
         </is>
       </c>
+      <c r="X34" t="n">
+        <v>1967</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="14" t="n">
@@ -4436,6 +4504,9 @@
       <c r="W39" t="n">
         <v>1999</v>
       </c>
+      <c r="X39" t="n">
+        <v>1974</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="n">
@@ -4920,6 +4991,9 @@
           <t>When Disaster Strikes... (1997)</t>
         </is>
       </c>
+      <c r="X44" t="n">
+        <v>1972</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="14" t="n">
@@ -5015,6 +5089,9 @@
       <c r="W45" t="n">
         <v>1996</v>
       </c>
+      <c r="X45" t="n">
+        <v>1971</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="14" t="n">
@@ -5107,6 +5184,9 @@
           <t>The Blueprint (2001)</t>
         </is>
       </c>
+      <c r="X46" t="n">
+        <v>1969</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="14" t="n">
@@ -5199,6 +5279,9 @@
           <t>The Marshall Mathers LP (2000)</t>
         </is>
       </c>
+      <c r="X47" t="n">
+        <v>1972</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="14" t="n">
@@ -5294,6 +5377,9 @@
       <c r="W48" t="n">
         <v>2021</v>
       </c>
+      <c r="X48" t="n">
+        <v>1970</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="14" t="n">
@@ -5387,6 +5473,9 @@
       <c r="W49" t="n">
         <v>2002</v>
       </c>
+      <c r="X49" t="n">
+        <v>1975</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="14" t="n">
@@ -5479,6 +5568,9 @@
           <t>Supa Dupa Fly (1997)</t>
         </is>
       </c>
+      <c r="X50" t="n">
+        <v>1971</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="14" t="n">
@@ -5569,6 +5661,9 @@
           <t>Black on Both Sides (1999)</t>
         </is>
       </c>
+      <c r="X51" t="n">
+        <v>1973</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="14" t="n">
@@ -5661,6 +5756,9 @@
           <t>Quality (2002)</t>
         </is>
       </c>
+      <c r="X52" t="n">
+        <v>1975</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="14" t="n">
@@ -5851,6 +5949,9 @@
       <c r="W54" t="n">
         <v>2005</v>
       </c>
+      <c r="X54" t="n">
+        <v>1970</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="14" t="n">
@@ -5950,6 +6051,9 @@
       <c r="W55" t="n">
         <v>2019</v>
       </c>
+      <c r="X55" t="n">
+        <v>1976</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="14" t="n">
@@ -6049,6 +6153,9 @@
       <c r="W56" t="n">
         <v>2008</v>
       </c>
+      <c r="X56" t="n">
+        <v>1978</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="14" t="n">
@@ -6141,6 +6248,9 @@
           <t>Hard Core (1996)</t>
         </is>
       </c>
+      <c r="X57" t="n">
+        <v>1974</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="14" t="n">
@@ -6240,6 +6350,9 @@
       <c r="W58" t="n">
         <v>2019</v>
       </c>
+      <c r="X58" t="n">
+        <v>1975</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="14" t="n">
@@ -6336,6 +6449,9 @@
           <t>Can-I-Bus (1998)</t>
         </is>
       </c>
+      <c r="X59" t="n">
+        <v>1974</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="14" t="n">
@@ -6432,6 +6548,9 @@
           <t>Violent by Design (2000)</t>
         </is>
       </c>
+      <c r="X60" t="n">
+        <v>1977</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="14" t="n">
@@ -6527,6 +6646,9 @@
       <c r="W61" t="n">
         <v>2000</v>
       </c>
+      <c r="X61" t="n">
+        <v>1971</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="14" t="n">
@@ -6623,6 +6745,9 @@
           <t>Doe or Die (1995)</t>
         </is>
       </c>
+      <c r="X62" t="n">
+        <v>1972</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="14" t="n">
@@ -6715,6 +6840,9 @@
           <t>My Beautiful Dark Twisted Fantasy (2010)</t>
         </is>
       </c>
+      <c r="X63" t="n">
+        <v>1977</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="14" t="n">
@@ -6807,6 +6935,9 @@
           <t>Tha Carter III (2008)</t>
         </is>
       </c>
+      <c r="X64" t="n">
+        <v>1982</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="14" t="n">
@@ -6899,6 +7030,9 @@
           <t>Trap Muzik (2003)</t>
         </is>
       </c>
+      <c r="X65" t="n">
+        <v>1980</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="14" t="n">
@@ -6991,6 +7125,9 @@
           <t>The State vs. Radric Davis (2009)</t>
         </is>
       </c>
+      <c r="X66" t="n">
+        <v>1980</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="14" t="n">
@@ -7083,6 +7220,9 @@
           <t>Supreme Clientele (2000)</t>
         </is>
       </c>
+      <c r="X67" t="n">
+        <v>1970</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="14" t="n">
@@ -7178,6 +7318,9 @@
       <c r="W68" t="n">
         <v>2020</v>
       </c>
+      <c r="X68" t="n">
+        <v>1971</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="14" t="n">
@@ -7270,6 +7413,9 @@
           <t>Be (2005)</t>
         </is>
       </c>
+      <c r="X69" t="n">
+        <v>1972</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="14" t="n">
@@ -7365,6 +7511,9 @@
       <c r="W70" t="n">
         <v>2015</v>
       </c>
+      <c r="X70" t="n">
+        <v>1977</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="14" t="n">
@@ -7457,6 +7606,9 @@
           <t>Let's Get It: Thug Motivation 101 (2005)</t>
         </is>
       </c>
+      <c r="X71" t="n">
+        <v>1977</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="14" t="n">
@@ -7549,6 +7701,9 @@
           <t>The Cool (2007)</t>
         </is>
       </c>
+      <c r="X72" t="n">
+        <v>1982</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="14" t="n">
@@ -7644,6 +7799,9 @@
       <c r="W73" t="n">
         <v>2015</v>
       </c>
+      <c r="X73" t="n">
+        <v>1970</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="14" t="n">
@@ -7736,6 +7894,9 @@
           <t>Labor Days (2001)</t>
         </is>
       </c>
+      <c r="X74" t="n">
+        <v>1976</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="14" t="n">
@@ -7832,6 +7993,9 @@
           <t>Kiss of Death (2004)</t>
         </is>
       </c>
+      <c r="X75" t="n">
+        <v>1975</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="14" t="n">
@@ -7927,6 +8091,9 @@
       <c r="W76" t="n">
         <v>2014</v>
       </c>
+      <c r="X76" t="n">
+        <v>1975</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="14" t="n">
@@ -8217,6 +8384,9 @@
           <t>Restless (2006)</t>
         </is>
       </c>
+      <c r="X79" t="n">
+        <v>1980</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="14" t="n">
@@ -8313,6 +8483,9 @@
           <t>All Balls Don't Bounce (1995)</t>
         </is>
       </c>
+      <c r="X80" t="n">
+        <v>1970</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="14" t="n">
@@ -8403,6 +8576,9 @@
           <t>Only Built 4 Cuban Linx… (1995)</t>
         </is>
       </c>
+      <c r="X81" t="n">
+        <v>1970</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="14" t="n">
@@ -8495,6 +8671,9 @@
           <t>Fantastic Damage (2002)</t>
         </is>
       </c>
+      <c r="X82" t="n">
+        <v>1975</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="14" t="n">
@@ -8591,6 +8770,9 @@
           <t>Shadows on the Sun (2003)</t>
         </is>
       </c>
+      <c r="X83" t="n">
+        <v>1977</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="14" t="n">
@@ -8690,6 +8872,9 @@
       <c r="W84" t="n">
         <v>2011</v>
       </c>
+      <c r="X84" t="n">
+        <v>1978</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="14" t="n">
@@ -8782,6 +8967,9 @@
           <t>To Pimp a Butterfly (2015)</t>
         </is>
       </c>
+      <c r="X85" t="n">
+        <v>1987</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="14" t="n">
@@ -8874,6 +9062,9 @@
           <t>2014 Forest Hills Drive (2014)</t>
         </is>
       </c>
+      <c r="X86" t="n">
+        <v>1985</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="14" t="n">
@@ -8966,6 +9157,9 @@
           <t>Jeffery (2016)</t>
         </is>
       </c>
+      <c r="X87" t="n">
+        <v>1991</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="14" t="n">
@@ -9058,6 +9252,9 @@
           <t>DS2 (2015)</t>
         </is>
       </c>
+      <c r="X88" t="n">
+        <v>1983</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="14" t="n">
@@ -9150,6 +9347,9 @@
           <t>Acid Rap (2013)</t>
         </is>
       </c>
+      <c r="X89" t="n">
+        <v>1993</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="14" t="n">
@@ -9242,6 +9442,9 @@
           <t>Some Rap Songs (2018)</t>
         </is>
       </c>
+      <c r="X90" t="n">
+        <v>1994</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="14" t="n">
@@ -9334,6 +9537,9 @@
           <t>Dreams and Nightmares (2012)</t>
         </is>
       </c>
+      <c r="X91" t="n">
+        <v>1987</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="14" t="n">
@@ -9426,6 +9632,9 @@
           <t>Long. Live. A$AP (2013)</t>
         </is>
       </c>
+      <c r="X92" t="n">
+        <v>1988</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="14" t="n">
@@ -9518,6 +9727,9 @@
           <t>Pink Friday (2010)</t>
         </is>
       </c>
+      <c r="X93" t="n">
+        <v>1982</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="14" t="n">
@@ -9610,6 +9822,9 @@
           <t>Summertime '06 (2015)</t>
         </is>
       </c>
+      <c r="X94" t="n">
+        <v>1993</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="14" t="n">
@@ -9702,6 +9917,9 @@
           <t>4eva Is a Mighty Long Time (2017)</t>
         </is>
       </c>
+      <c r="X95" t="n">
+        <v>1986</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="14" t="n">
@@ -9886,6 +10104,9 @@
           <t>R.A.P. Music (2012)</t>
         </is>
       </c>
+      <c r="X97" t="n">
+        <v>1975</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="n">
@@ -9978,6 +10199,9 @@
           <t>Piñata (2014)</t>
         </is>
       </c>
+      <c r="X98" t="n">
+        <v>1982</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="14" t="n">
@@ -10169,6 +10393,9 @@
           <t>Dark Sky Paradise (2015)</t>
         </is>
       </c>
+      <c r="X100" t="n">
+        <v>1988</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="14" t="n">
@@ -10263,6 +10490,9 @@
           <t>Whack World (2018)</t>
         </is>
       </c>
+      <c r="X101" t="n">
+        <v>1995</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="n">
@@ -10355,6 +10585,9 @@
           <t>Room 25 (2018)</t>
         </is>
       </c>
+      <c r="X102" t="n">
+        <v>1991</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="14" t="n">
@@ -10445,6 +10678,9 @@
           <t>CARE FOR ME (2018)</t>
         </is>
       </c>
+      <c r="X103" t="n">
+        <v>1994</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="n">
@@ -10537,6 +10773,9 @@
           <t>Atrocity Exhibition (2016)</t>
         </is>
       </c>
+      <c r="X104" t="n">
+        <v>1981</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="14" t="n">
@@ -10632,6 +10871,9 @@
       <c r="W105" t="n">
         <v>2018</v>
       </c>
+      <c r="X105" t="n">
+        <v>1992</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="14" t="n">
@@ -10728,6 +10970,9 @@
           <t>The Forever Story (2022)</t>
         </is>
       </c>
+      <c r="X106" t="n">
+        <v>1990</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="14" t="n">
@@ -10820,6 +11065,9 @@
           <t>Invasion of Privacy (2018)</t>
         </is>
       </c>
+      <c r="X107" t="n">
+        <v>1992</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="14" t="n">
@@ -10916,6 +11164,9 @@
           <t>Hall of Fame (2021)</t>
         </is>
       </c>
+      <c r="X108" t="n">
+        <v>1999</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="14" t="n">
@@ -11012,6 +11263,9 @@
           <t>SoulFly (2021)</t>
         </is>
       </c>
+      <c r="X109" t="n">
+        <v>1999</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="14" t="n">
@@ -11108,6 +11362,9 @@
           <t>Alligator Bites Never Heal (2024)</t>
         </is>
       </c>
+      <c r="X110" t="n">
+        <v>1998</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="14" t="n">
@@ -11204,6 +11461,9 @@
           <t>GLORIOUS (2024)</t>
         </is>
       </c>
+      <c r="X111" t="n">
+        <v>1999</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="14" t="n">
@@ -11300,6 +11560,9 @@
           <t>WUNNA (2020)</t>
         </is>
       </c>
+      <c r="X112" t="n">
+        <v>1993</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="14" t="n">
@@ -11396,6 +11659,9 @@
           <t>My Turn (2020)</t>
         </is>
       </c>
+      <c r="X113" t="n">
+        <v>1994</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="14" t="n">
@@ -11488,6 +11754,9 @@
           <t>Tana Talk 3 (2018)</t>
         </is>
       </c>
+      <c r="X114" t="n">
+        <v>1984</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="14" t="n">
@@ -11584,6 +11853,9 @@
           <t>Father of 4 (2019)</t>
         </is>
       </c>
+      <c r="X115" t="n">
+        <v>1991</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="14" t="n">
@@ -11680,6 +11952,9 @@
           <t>Angelic Hoodrat (2020)</t>
         </is>
       </c>
+      <c r="X116" t="n">
+        <v>1994</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="14" t="n">
@@ -11776,6 +12051,9 @@
           <t>777 (2022)</t>
         </is>
       </c>
+      <c r="X117" t="n">
+        <v>1998</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="14" t="n">
@@ -11872,6 +12150,9 @@
           <t>blkswn (2017)</t>
         </is>
       </c>
+      <c r="X118" t="n">
+        <v>1991</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="14" t="n">
@@ -11962,6 +12243,9 @@
           <t>Daytona (2018)</t>
         </is>
       </c>
+      <c r="X119" t="n">
+        <v>1977</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="14" t="n">
@@ -12052,6 +12336,9 @@
           <t>Igor (2019)</t>
         </is>
       </c>
+      <c r="X120" t="n">
+        <v>1991</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="14" t="n">
@@ -12244,6 +12531,9 @@
           <t>shut the fuck up talking to me (2021)</t>
         </is>
       </c>
+      <c r="X122" t="n">
+        <v>1990</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="14" t="n">
@@ -12340,6 +12630,9 @@
           <t>The Voice (2020)</t>
         </is>
       </c>
+      <c r="X123" t="n">
+        <v>1992</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="14" t="n">
@@ -12436,6 +12729,9 @@
           <t>Painting Pictures (2017)</t>
         </is>
       </c>
+      <c r="X124" t="n">
+        <v>1997</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="14" t="n">
@@ -12528,6 +12824,9 @@
           <t>Laila's Wisdom (2017)</t>
         </is>
       </c>
+      <c r="X125" t="n">
+        <v>1983</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="14" t="n">
@@ -12624,6 +12923,9 @@
           <t>Let the Sun Talk (2019)</t>
         </is>
       </c>
+      <c r="X126" t="n">
+        <v>1999</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="14" t="n">
@@ -12720,6 +13022,9 @@
           <t>40 Dayz &amp; 40 Nightz (1998)</t>
         </is>
       </c>
+      <c r="X127" t="n">
+        <v>1974</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="14" t="n">
@@ -12816,6 +13121,9 @@
           <t>My Type (2019)</t>
         </is>
       </c>
+      <c r="X128" t="n">
+        <v>1993</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="14" t="n">
@@ -13011,6 +13319,9 @@
           <t>Weight of the World (2021)</t>
         </is>
       </c>
+      <c r="X130" t="n">
+        <v>1990</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13201,6 +13512,9 @@
       <c r="W132" t="n">
         <v>2012</v>
       </c>
+      <c r="X132" t="n">
+        <v>1974</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13297,6 +13611,9 @@
           <t>Eternal Atake (2020)</t>
         </is>
       </c>
+      <c r="X133" t="n">
+        <v>1994</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13396,6 +13713,9 @@
       <c r="W134" t="n">
         <v>2018</v>
       </c>
+      <c r="X134" t="n">
+        <v>1978</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13495,6 +13815,9 @@
       <c r="W135" t="n">
         <v>2013</v>
       </c>
+      <c r="X135" t="n">
+        <v>1978</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -13594,6 +13917,9 @@
       <c r="W136" t="n">
         <v>2003</v>
       </c>
+      <c r="X136" t="n">
+        <v>1974</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -13690,6 +14016,9 @@
           <t>Life Is... Too Short (1988)</t>
         </is>
       </c>
+      <c r="X137" t="n">
+        <v>1966</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -13786,6 +14115,9 @@
           <t>I Wish My Brother George Was Here (1991)</t>
         </is>
       </c>
+      <c r="X138" t="n">
+        <v>1972</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -13885,6 +14217,9 @@
       <c r="W139" t="n">
         <v>2004</v>
       </c>
+      <c r="X139" t="n">
+        <v>1970</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -13981,6 +14316,9 @@
           <t>Book of Ryan (2018)</t>
         </is>
       </c>
+      <c r="X140" t="n">
+        <v>1977</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14072,6 +14410,9 @@
           <t>Live and Let Die (1992)</t>
         </is>
       </c>
+      <c r="X141" t="n">
+        <v>1968</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14168,6 +14509,9 @@
           <t>Muddy Waters (1996)</t>
         </is>
       </c>
+      <c r="X142" t="n">
+        <v>1970</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14264,6 +14608,9 @@
           <t>Tical (1994)</t>
         </is>
       </c>
+      <c r="X143" t="n">
+        <v>1971</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14459,6 +14806,9 @@
           <t>The Documentary (2005)</t>
         </is>
       </c>
+      <c r="X145" t="n">
+        <v>1979</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -14558,6 +14908,9 @@
       <c r="W146" t="n">
         <v>2006</v>
       </c>
+      <c r="X146" t="n">
+        <v>1958</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -14657,6 +15010,9 @@
       <c r="W147" t="n">
         <v>2019</v>
       </c>
+      <c r="X147" t="n">
+        <v>1985</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -14756,6 +15112,9 @@
       <c r="W148" t="n">
         <v>2017</v>
       </c>
+      <c r="X148" t="n">
+        <v>1970</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -14951,6 +15310,9 @@
           <t>Good News (2020)</t>
         </is>
       </c>
+      <c r="X150" t="n">
+        <v>1995</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15050,6 +15412,9 @@
       <c r="W151" t="n">
         <v>1996</v>
       </c>
+      <c r="X151" t="n">
+        <v>1971</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15146,6 +15511,9 @@
           <t>Kollage (1996)</t>
         </is>
       </c>
+      <c r="X152" t="n">
+        <v>1966</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15245,6 +15613,9 @@
       <c r="W153" t="n">
         <v>2018</v>
       </c>
+      <c r="X153" t="n">
+        <v>1976</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15344,6 +15715,9 @@
       <c r="W154" t="n">
         <v>2019</v>
       </c>
+      <c r="X154" t="n">
+        <v>1974</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -15443,6 +15817,9 @@
       <c r="W155" t="n">
         <v>1998</v>
       </c>
+      <c r="X155" t="n">
+        <v>1970</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -15832,6 +16209,9 @@
           <t>Kamikaze (2004)</t>
         </is>
       </c>
+      <c r="X159" t="n">
+        <v>1973</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -15928,6 +16308,9 @@
           <t>All 6's and 7's (2011)</t>
         </is>
       </c>
+      <c r="X160" t="n">
+        <v>1971</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16022,6 +16405,9 @@
           <t>Country Grammar (2000)</t>
         </is>
       </c>
+      <c r="X161" t="n">
+        <v>1974</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16116,6 +16502,9 @@
           <t>Finally Rich (2012)</t>
         </is>
       </c>
+      <c r="X162" t="n">
+        <v>1995</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16212,6 +16601,9 @@
           <t>Reloaded (2012)</t>
         </is>
       </c>
+      <c r="X163" t="n">
+        <v>1978</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16307,6 +16699,9 @@
         <is>
           <t>TA13OO (2018)</t>
         </is>
+      </c>
+      <c r="X164" t="n">
+        <v>1995</v>
       </c>
     </row>
     <row r="165">
@@ -18071,18 +18466,34 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>1955–present; Elements only (blank for Compounds)</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>Birth year of the solo artist, for age-at-debut and age-at-signature-work analysis. Group members vary in age, so Compounds are left blank.</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>Public record (documented dates of birth).</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>SAMPLING FRAME &amp; SCOPE RULES</t>
-        </is>
-      </c>
+      <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
       <c r="D26" s="17"/>
@@ -18091,14 +18502,10 @@
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>Population</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>US-based hip-hop acts with a national critical record, 1973–present.</t>
-        </is>
-      </c>
+          <t>SAMPLING FRAME &amp; SCOPE RULES</t>
+        </is>
+      </c>
+      <c r="B27" s="17"/>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
@@ -18106,12 +18513,12 @@
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>Inclusion</t>
+          <t>Population</t>
         </is>
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>US-born or US-scene-based acts affiliated with a US label/scene during their defining run.</t>
+          <t>US-based hip-hop acts with a national critical record, 1973–present.</t>
         </is>
       </c>
       <c r="C28" s="17"/>
@@ -18121,12 +18528,12 @@
     <row r="29">
       <c r="A29" s="18" t="inlineStr">
         <is>
-          <t>Exclusion</t>
+          <t>Inclusion</t>
         </is>
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>International and UK acts (scope decision to keep the frame tractable); acts without national critical coverage (survivorship limitation, documented).</t>
+          <t>US-born or US-scene-based acts affiliated with a US label/scene during their defining run.</t>
         </is>
       </c>
       <c r="C29" s="17"/>
@@ -18136,12 +18543,12 @@
     <row r="30">
       <c r="A30" s="18" t="inlineStr">
         <is>
-          <t>Unit of analysis</t>
+          <t>Exclusion</t>
         </is>
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>The act (solo artist or group). Groups are Compounds; solo careers are Elements; both may appear.</t>
+          <t>International and UK acts (scope decision to keep the frame tractable); acts without national critical coverage (survivorship limitation, documented).</t>
         </is>
       </c>
       <c r="C30" s="17"/>
@@ -18151,17 +18558,32 @@
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>Known frame biases</t>
+          <t>Unit of analysis</t>
         </is>
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>Over-represents critical acclaim, NYC, Golden Age, and men. See Confidence Guide sheet for the full bias table.</t>
+          <t>The act (solo artist or group). Groups are Compounds; solo careers are Elements; both may appear.</t>
         </is>
       </c>
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>Known frame biases</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>Over-represents critical acclaim, NYC, Golden Age, and men. See Confidence Guide sheet for the full bias table.</t>
+        </is>
+      </c>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -1336,7 +1336,7 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Old School</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Old School</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Old School</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Old School</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Old School</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Old School</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Old School</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Old School</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>Old School</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>Golden Age</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F33" s="14" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>Golden Age</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>Golden Age</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>Golden Age</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F39" s="14" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>Golden Age</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>Late 90s</t>
+          <t>2000s</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>Late 90s</t>
+          <t>2000s</t>
         </is>
       </c>
       <c r="F47" s="14" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>Late 90s</t>
+          <t>2000s</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>Late 90s</t>
+          <t>2000s</t>
         </is>
       </c>
       <c r="F55" s="14" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>Late 90s</t>
+          <t>2000s</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F63" s="14" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F73" s="14" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F77" s="14" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="E81" s="14" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F81" s="14" t="inlineStr">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
       <c r="F106" s="14" t="inlineStr">
@@ -11684,7 +11684,7 @@
       </c>
       <c r="E114" s="14" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F114" s="14" t="inlineStr">
@@ -11779,7 +11779,7 @@
       </c>
       <c r="E115" s="14" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F115" s="14" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="E118" s="14" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F118" s="14" t="inlineStr">
@@ -12175,7 +12175,7 @@
       </c>
       <c r="E119" s="14" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F119" s="14" t="inlineStr">
@@ -12268,7 +12268,7 @@
       </c>
       <c r="E120" s="14" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F120" s="14" t="inlineStr">
@@ -12655,7 +12655,7 @@
       </c>
       <c r="E124" s="14" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F124" s="14" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="E125" s="14" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F125" s="14" t="inlineStr">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="E126" s="14" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F126" s="14" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="E128" s="14" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F128" s="14" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="E129" s="14" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F129" s="14" t="inlineStr">
@@ -13344,7 +13344,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Golden Age</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -13738,7 +13738,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -13942,7 +13942,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Old School</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -14435,7 +14435,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Golden Age</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -14534,7 +14534,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Late 90s</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -14831,7 +14831,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Old School</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -16234,7 +16234,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -17589,7 +17589,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -17981,15 +17981,17 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>Old School, Golden Age, Late 90s, 2000s, 2010s, 2020s</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>16</v>
+          <t>Old School (through 1985), Golden Age (1986-1994), Late 90s (1995-1999), 2000s (2000-2009), 2010s (2010-2019), 2020s (2020 on)</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>The era bracket containing the year of the act's Signature Work (the year the defining work landed). Acts with no signature work on record (only Kool Herc) use Debut Year instead.</t>
+        </is>
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t>Judgment call from critical consensus on when the act's defining work landed.</t>
+          <t>Derived from the Signature Work column, so it is auditable: recompute the bracket from the signature year and it must match. The judgment call lives in the Signature Work pick, not in Era.</t>
         </is>
       </c>
     </row>

--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -5686,7 +5686,7 @@
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>Quality (2002)</t>
+          <t>Mos Def &amp; Talib Kweli Are Black Star (1998)</t>
         </is>
       </c>
       <c r="X52" t="n">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>Element</t>
+          <t>Compound</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
@@ -6547,9 +6547,6 @@
         <is>
           <t>Violent by Design (2000)</t>
         </is>
-      </c>
-      <c r="X60" t="n">
-        <v>1977</v>
       </c>
     </row>
     <row r="61">
@@ -7343,7 +7340,7 @@
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F69" s="14" t="inlineStr">
@@ -7410,7 +7407,7 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>Be (2005)</t>
+          <t>Resurrection (1994)</t>
         </is>
       </c>
       <c r="X69" t="n">
@@ -7698,7 +7695,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>The Cool (2007)</t>
+          <t>Lupe Fiasco's Food &amp; Liquor (2006)</t>
         </is>
       </c>
       <c r="X72" t="n">
@@ -9629,7 +9626,7 @@
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>Long. Live. A$AP (2013)</t>
+          <t>Live. Love. A$AP (2011)</t>
         </is>
       </c>
       <c r="X92" t="n">
@@ -11090,7 +11087,7 @@
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F108" s="14" t="inlineStr">
@@ -11161,7 +11158,7 @@
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>Hall of Fame (2021)</t>
+          <t>Die a Legend (2019)</t>
         </is>
       </c>
       <c r="X108" t="n">
@@ -11260,7 +11257,7 @@
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>SoulFly (2021)</t>
+          <t>Pray 4 Love (2020)</t>
         </is>
       </c>
       <c r="X109" t="n">
@@ -13537,7 +13534,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -13608,7 +13605,7 @@
       </c>
       <c r="V133" t="inlineStr">
         <is>
-          <t>Eternal Atake (2020)</t>
+          <t>Luv Is Rage 2 (2017)</t>
         </is>
       </c>
       <c r="X133" t="n">
@@ -14041,7 +14038,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Golden Age</t>
+          <t>2000s</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -14112,7 +14109,7 @@
       </c>
       <c r="V138" t="inlineStr">
         <is>
-          <t>I Wish My Brother George Was Here (1991)</t>
+          <t>Deltron 3030 (2000)</t>
         </is>
       </c>
       <c r="X138" t="n">
@@ -15208,7 +15205,7 @@
       </c>
       <c r="V149" t="inlineStr">
         <is>
-          <t>Very Necessary (1993)</t>
+          <t>Hot, Cool &amp; Vicious (1986)</t>
         </is>
       </c>
       <c r="W149" t="n">
@@ -16135,7 +16132,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -16206,7 +16203,7 @@
       </c>
       <c r="V159" t="inlineStr">
         <is>
-          <t>Kamikaze (2004)</t>
+          <t>Adrenaline Rush (1997)</t>
         </is>
       </c>
       <c r="X159" t="n">
@@ -18426,17 +18423,17 @@
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>"Title (Year)"; blank if none recorded</t>
+          <t>"Title (Year)"; year = original release year; blank if none recorded</t>
         </is>
       </c>
       <c r="D23" s="17" t="inlineStr">
         <is>
-          <t>The act’s consensus defining release: an album, or a single for acts that predate albums. One per act; blank only where no recorded signature work exists (e.g. Kool Herc).</t>
+          <t>The act's defining release, picked by procedure. Candidate pool: full-length studio projects from the act's own catalog (canonical mixtapes count; a single only for acts that predate albums or never made one; no compilations, live albums, or guest spots; releases by a side group count only when that group has no row of its own). Pick the release most consistently named the act's essential work across the verification sources; genuine splits are resolved by maintainer call and logged in the worklist. One per act; blank only where none exists (Kool Herc).</t>
         </is>
       </c>
       <c r="E23" s="17" t="inlineStr">
         <is>
-          <t>Critical consensus synthesis; entered 2026-07.</t>
+          <t>Consensus read from critic retrospectives and rating aggregates (the Confidence Guide verification sources). Splits and their resolutions are logged in the worklist. Era derives from this column's year.</t>
         </is>
       </c>
     </row>

--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -1336,7 +1336,7 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Old School</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Old School</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Old School</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Old School</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Old School</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Old School</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Old School</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Old School</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>Old School</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>Golden Age</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F33" s="14" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>Golden Age</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>Golden Age</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>Golden Age</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F39" s="14" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>Golden Age</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>Late 90s</t>
+          <t>2000s</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>Late 90s</t>
+          <t>2000s</t>
         </is>
       </c>
       <c r="F47" s="14" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>Quality (2002)</t>
+          <t>Mos Def &amp; Talib Kweli Are Black Star (1998)</t>
         </is>
       </c>
       <c r="X52" t="n">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>Late 90s</t>
+          <t>2000s</t>
         </is>
       </c>
       <c r="F55" s="14" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>Late 90s</t>
+          <t>2000s</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>Element</t>
+          <t>Compound</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
@@ -6547,9 +6547,6 @@
         <is>
           <t>Violent by Design (2000)</t>
         </is>
-      </c>
-      <c r="X60" t="n">
-        <v>1977</v>
       </c>
     </row>
     <row r="61">
@@ -6770,7 +6767,7 @@
       </c>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F63" s="14" t="inlineStr">
@@ -7343,7 +7340,7 @@
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F69" s="14" t="inlineStr">
@@ -7410,7 +7407,7 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>Be (2005)</t>
+          <t>Resurrection (1994)</t>
         </is>
       </c>
       <c r="X69" t="n">
@@ -7698,7 +7695,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>The Cool (2007)</t>
+          <t>Lupe Fiasco's Food &amp; Liquor (2006)</t>
         </is>
       </c>
       <c r="X72" t="n">
@@ -7726,7 +7723,7 @@
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F73" s="14" t="inlineStr">
@@ -8116,7 +8113,7 @@
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F77" s="14" t="inlineStr">
@@ -8215,7 +8212,7 @@
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
@@ -8409,7 +8406,7 @@
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
@@ -8508,7 +8505,7 @@
       </c>
       <c r="E81" s="14" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F81" s="14" t="inlineStr">
@@ -9629,7 +9626,7 @@
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>Long. Live. A$AP (2013)</t>
+          <t>Live. Love. A$AP (2011)</t>
         </is>
       </c>
       <c r="X92" t="n">
@@ -10896,7 +10893,7 @@
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>2010s</t>
+          <t>2020s</t>
         </is>
       </c>
       <c r="F106" s="14" t="inlineStr">
@@ -11090,7 +11087,7 @@
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F108" s="14" t="inlineStr">
@@ -11161,7 +11158,7 @@
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>Hall of Fame (2021)</t>
+          <t>Die a Legend (2019)</t>
         </is>
       </c>
       <c r="X108" t="n">
@@ -11260,7 +11257,7 @@
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>SoulFly (2021)</t>
+          <t>Pray 4 Love (2020)</t>
         </is>
       </c>
       <c r="X109" t="n">
@@ -11684,7 +11681,7 @@
       </c>
       <c r="E114" s="14" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F114" s="14" t="inlineStr">
@@ -11779,7 +11776,7 @@
       </c>
       <c r="E115" s="14" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F115" s="14" t="inlineStr">
@@ -12076,7 +12073,7 @@
       </c>
       <c r="E118" s="14" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F118" s="14" t="inlineStr">
@@ -12175,7 +12172,7 @@
       </c>
       <c r="E119" s="14" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F119" s="14" t="inlineStr">
@@ -12268,7 +12265,7 @@
       </c>
       <c r="E120" s="14" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F120" s="14" t="inlineStr">
@@ -12655,7 +12652,7 @@
       </c>
       <c r="E124" s="14" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F124" s="14" t="inlineStr">
@@ -12754,7 +12751,7 @@
       </c>
       <c r="E125" s="14" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F125" s="14" t="inlineStr">
@@ -12849,7 +12846,7 @@
       </c>
       <c r="E126" s="14" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F126" s="14" t="inlineStr">
@@ -13047,7 +13044,7 @@
       </c>
       <c r="E128" s="14" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F128" s="14" t="inlineStr">
@@ -13146,7 +13143,7 @@
       </c>
       <c r="E129" s="14" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F129" s="14" t="inlineStr">
@@ -13344,7 +13341,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Golden Age</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -13608,7 +13605,7 @@
       </c>
       <c r="V133" t="inlineStr">
         <is>
-          <t>Eternal Atake (2020)</t>
+          <t>Luv Is Rage 2 (2017)</t>
         </is>
       </c>
       <c r="X133" t="n">
@@ -13738,7 +13735,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -13942,7 +13939,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Old School</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -14041,7 +14038,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Golden Age</t>
+          <t>2000s</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -14112,7 +14109,7 @@
       </c>
       <c r="V138" t="inlineStr">
         <is>
-          <t>I Wish My Brother George Was Here (1991)</t>
+          <t>Deltron 3030 (2000)</t>
         </is>
       </c>
       <c r="X138" t="n">
@@ -14242,7 +14239,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -14435,7 +14432,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Golden Age</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -14534,7 +14531,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Late 90s</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -14831,7 +14828,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Old School</t>
+          <t>Golden Age</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -15208,7 +15205,7 @@
       </c>
       <c r="V149" t="inlineStr">
         <is>
-          <t>Very Necessary (1993)</t>
+          <t>Hot, Cool &amp; Vicious (1986)</t>
         </is>
       </c>
       <c r="W149" t="n">
@@ -16135,7 +16132,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>Late 90s</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -16206,7 +16203,7 @@
       </c>
       <c r="V159" t="inlineStr">
         <is>
-          <t>Kamikaze (2004)</t>
+          <t>Adrenaline Rush (1997)</t>
         </is>
       </c>
       <c r="X159" t="n">
@@ -16234,7 +16231,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -17589,7 +17586,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2020s</t>
+          <t>2010s</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -17981,15 +17978,17 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>Old School, Golden Age, Late 90s, 2000s, 2010s, 2020s</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>16</v>
+          <t>Old School (through 1985), Golden Age (1986-1994), Late 90s (1995-1999), 2000s (2000-2009), 2010s (2010-2019), 2020s (2020 on)</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>The era bracket containing the year of the act's Signature Work (the year the defining work landed). Acts with no signature work on record (only Kool Herc) use Debut Year instead.</t>
+        </is>
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t>Judgment call from critical consensus on when the act's defining work landed.</t>
+          <t>Derived from the Signature Work column, so it is auditable: recompute the bracket from the signature year and it must match. The judgment call lives in the Signature Work pick, not in Era.</t>
         </is>
       </c>
     </row>
@@ -18424,17 +18423,17 @@
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>"Title (Year)"; blank if none recorded</t>
+          <t>"Title (Year)"; year = original release year; blank if none recorded</t>
         </is>
       </c>
       <c r="D23" s="17" t="inlineStr">
         <is>
-          <t>The act’s consensus defining release: an album, or a single for acts that predate albums. One per act; blank only where no recorded signature work exists (e.g. Kool Herc).</t>
+          <t>The act's defining release, picked by procedure. Candidate pool: full-length studio projects from the act's own catalog (canonical mixtapes count; a single only for acts that predate albums or never made one; no compilations, live albums, or guest spots; releases by a side group count only when that group has no row of its own). Pick the release most consistently named the act's essential work across the verification sources; genuine splits are resolved by maintainer call and logged in the worklist. One per act; blank only where none exists (Kool Herc).</t>
         </is>
       </c>
       <c r="E23" s="17" t="inlineStr">
         <is>
-          <t>Critical consensus synthesis; entered 2026-07.</t>
+          <t>Consensus read from critic retrospectives and rating aggregates (the Confidence Guide verification sources). Splits and their resolutions are logged in the worklist. Era derives from this column's year.</t>
         </is>
       </c>
     </row>

--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -11191,7 +11191,7 @@
       </c>
       <c r="F109" s="14" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Trap/Drill</t>
         </is>
       </c>
       <c r="G109" s="14" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="R118" s="14" t="inlineStr">
         <is>
-          <t>St. Louis's jazz-rap hybrid. Melodic and rhythmic sophistication.</t>
+          <t>St. Louis's soul-rap hybrid. Melodic and rhythmic sophistication.</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
@@ -18010,12 +18010,12 @@
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>Primary lyrical style. One value per act (dominant mode, not exhaustive description). Conscious/Street was merged into Conscious/Lyrical.</t>
+          <t>Primary style of the act's defining run: one value per act, the dominant mode rather than an exhaustive description. Each value is defined in the STYLE TAXONOMY block below. Conscious/Street was merged into Conscious/Lyrical.</t>
         </is>
       </c>
       <c r="E7" s="17" t="inlineStr">
         <is>
-          <t>Assigned from critical consensus descriptions of the act's catalog.</t>
+          <t>Assigned from critical consensus descriptions of the act's catalog; see the taxonomy block for definitions, anchor acts, and the Abstract vs Experimental tiebreak.</t>
         </is>
       </c>
     </row>
@@ -18584,6 +18584,114 @@
       <c r="D32" s="17"/>
       <c r="E32" s="17"/>
     </row>
+    <row r="33">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>STYLE TAXONOMY</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>One value per act: the dominant mode of the defining run, judged from critical descriptions. Tiebreak: if the strangeness lives in the words it is Abstract; if it lives in the sound or form it is Experimental.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>Party/Pop</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>Crowd-first rap: hooks, humor, dance, and radio crossover are the dominant mode; the room matters more than the page. Anchor: Salt-N-Pepa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>Political</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>An explicit political program or protest organizes the catalog; the message is the mode, not an occasional topic. Anchor: Public Enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>Conscious/Lyrical</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>Craft-and-substance writing: introspection, social observation, and technical pen as the dominant mode. Absorbs the former Conscious/Street label. Anchor: Nas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>Gangsta/Street</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>Street narrative and persona as the primary subject: reportage, hustling economics, survival stakes. Anchor: N.W.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>Pen-first left field: oblique, allusive, nonlinear writing; the strangeness lives in the language itself. Anchor: MF DOOM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>Jazz-Rap</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>The early-90s jazz-sample movement: live-jazz textures, conversational flow, bohemian scene ties. A scene-and-era label; later jazz-inflected acts take their dominant mode instead. Anchor: A Tribe Called Quest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>Form-first left field: production, song structure, or vocal approach breaks convention even when the writing is conventional. Anchor: Missy Elliott.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>Trap/Drill</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>The trap and drill sound family: 808-driven production with melodic, chanted, or sung delivery; cadence and vibe carry more than lyric density. Anchor: Future.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -18091,7 +18091,7 @@
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t>Year of first commercial release (single or album).</t>
+          <t>Year of first commercial release under the act's own billing (single or album); guest appearances do not count.</t>
         </is>
       </c>
       <c r="E10" s="17" t="inlineStr">
@@ -18191,8 +18191,10 @@
           <t>1–10</t>
         </is>
       </c>
-      <c r="D14" s="17" t="s">
-        <v>20</v>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>CONSTRUCT: Density and originality of figurative language (extended metaphor, vivid concrete imagery, double meanings). Anchor: Lil Wayne = 10 (simile machine; metaphor-stacking as his defining critical reputation).</t>
+        </is>
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
@@ -18295,8 +18297,10 @@
           <t>Free text</t>
         </is>
       </c>
-      <c r="D18" s="17" t="s">
-        <v>22</v>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>Why an act is M or L: what evidence is thin or disputed. Required for every M and L act; blank for most H acts.</t>
+        </is>
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
@@ -18349,7 +18353,7 @@
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
-          <t>Element = solo artist; Compound = group/crew (rendered in the separate Compounds table). An artist may appear as both a group member and an Element when they have a substantial solo career (e.g. Method Man, Ghostface Killah).</t>
+          <t>Element = solo artist; Compound = group/crew (rendered in the separate Compounds table). Duos and trios are Compounds, including MC+producer duos (Gang Starr, Atmosphere, Jedi Mind Tricks). An artist may appear as both a group member and an Element when they have a substantial solo career (e.g. Method Man, Ghostface Killah).</t>
         </is>
       </c>
       <c r="E20" s="17" t="inlineStr">

--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -834,6 +834,11 @@
           <t>Birth Year</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Member Of</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="14" t="n">
@@ -3067,6 +3072,11 @@
       <c r="X24" t="n">
         <v>1969</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>N.W.A</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="n">
@@ -3732,6 +3742,11 @@
       <c r="X31" t="n">
         <v>1965</v>
       </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>N.W.A</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="n">
@@ -4994,6 +5009,11 @@
       <c r="X44" t="n">
         <v>1972</v>
       </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>Leaders of the New School</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="14" t="n">
@@ -5476,6 +5496,11 @@
       <c r="X49" t="n">
         <v>1975</v>
       </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>The Fugees</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="14" t="n">
@@ -7220,6 +7245,11 @@
       <c r="X67" t="n">
         <v>1970</v>
       </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>Wu-Tang Clan</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="14" t="n">
@@ -7799,6 +7829,11 @@
       <c r="X73" t="n">
         <v>1970</v>
       </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>The Geto Boys</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="14" t="n">
@@ -8483,6 +8518,11 @@
       <c r="X80" t="n">
         <v>1970</v>
       </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>Freestyle Fellowship</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="14" t="n">
@@ -8576,6 +8616,11 @@
       <c r="X81" t="n">
         <v>1970</v>
       </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>Wu-Tang Clan</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="14" t="n">
@@ -8671,6 +8716,11 @@
       <c r="X82" t="n">
         <v>1975</v>
       </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>Company Flow; Run The Jewels</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="14" t="n">
@@ -10104,6 +10154,11 @@
       <c r="X97" t="n">
         <v>1975</v>
       </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>Run The Jewels</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="n">
@@ -11754,6 +11809,11 @@
       <c r="X114" t="n">
         <v>1984</v>
       </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>Griselda</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="14" t="n">
@@ -11853,6 +11913,11 @@
       <c r="X115" t="n">
         <v>1991</v>
       </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>Migos</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="14" t="n">
@@ -12243,6 +12308,11 @@
       <c r="X119" t="n">
         <v>1977</v>
       </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>Clipse</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="14" t="n">
@@ -14608,6 +14678,11 @@
       <c r="X143" t="n">
         <v>1971</v>
       </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>Wu-Tang Clan</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -17659,6 +17734,1407 @@
         <is>
           <t>WWCD (2019)</t>
         </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Pop Smoke</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>East Coast</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Trap/Drill</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Brooklyn Drill</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Victor Victor/Republic</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>2019</v>
+      </c>
+      <c r="J175" t="n">
+        <v>4</v>
+      </c>
+      <c r="K175" t="n">
+        <v>4</v>
+      </c>
+      <c r="L175" t="n">
+        <v>4</v>
+      </c>
+      <c r="M175" t="n">
+        <v>4</v>
+      </c>
+      <c r="N175" t="n">
+        <v>3</v>
+      </c>
+      <c r="O175" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>Two-year career; drill canon status clear, lyrical record thin</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>Brooklyn drill's breakout voice. The growl remade New York in two years.</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>Meet the Woo 2 (2020)</t>
+        </is>
+      </c>
+      <c r="W175" t="n">
+        <v>2020</v>
+      </c>
+      <c r="X175" t="n">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>KV</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>King Von</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Gangsta/Street</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Chicago Drill</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Only the Family/Empire</t>
+        </is>
+      </c>
+      <c r="I176" t="n">
+        <v>2018</v>
+      </c>
+      <c r="J176" t="n">
+        <v>5</v>
+      </c>
+      <c r="K176" t="n">
+        <v>4</v>
+      </c>
+      <c r="L176" t="n">
+        <v>7</v>
+      </c>
+      <c r="M176" t="n">
+        <v>4</v>
+      </c>
+      <c r="N176" t="n">
+        <v>4</v>
+      </c>
+      <c r="O176" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>Catalog cut short at two years; storytelling consensus strong</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>Drill's dead-eyed narrator. Crime stories told with reporter detail.</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>Welcome to O'Block (2020)</t>
+        </is>
+      </c>
+      <c r="W176" t="n">
+        <v>2020</v>
+      </c>
+      <c r="X176" t="n">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>21 Savage</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Trap/Drill</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Atlanta Trap</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Slaughter Gang/Epic</t>
+        </is>
+      </c>
+      <c r="I177" t="n">
+        <v>2015</v>
+      </c>
+      <c r="J177" t="n">
+        <v>5</v>
+      </c>
+      <c r="K177" t="n">
+        <v>4</v>
+      </c>
+      <c r="L177" t="n">
+        <v>5</v>
+      </c>
+      <c r="M177" t="n">
+        <v>5</v>
+      </c>
+      <c r="N177" t="n">
+        <v>5</v>
+      </c>
+      <c r="O177" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>Deadpan menace refined into economy. Atlanta trap's quiet professional.</t>
+        </is>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>Savage Mode II (2020)</t>
+        </is>
+      </c>
+      <c r="X177" t="n">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>YD</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Young Dolph</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Trap/Drill</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Memphis Trap</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Paper Route Empire</t>
+        </is>
+      </c>
+      <c r="I178" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J178" t="n">
+        <v>5</v>
+      </c>
+      <c r="K178" t="n">
+        <v>4</v>
+      </c>
+      <c r="L178" t="n">
+        <v>5</v>
+      </c>
+      <c r="M178" t="n">
+        <v>6</v>
+      </c>
+      <c r="N178" t="n">
+        <v>4</v>
+      </c>
+      <c r="O178" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>Independent catalog; critical retrospectives grew after his death</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>Memphis independence made flesh. Owned his masters, minted his heirs.</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>King of Memphis (2016)</t>
+        </is>
+      </c>
+      <c r="W178" t="n">
+        <v>2021</v>
+      </c>
+      <c r="X178" t="n">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Playboi Carti</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Rage/Punk Trap</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>AWGE/Interscope</t>
+        </is>
+      </c>
+      <c r="I179" t="n">
+        <v>2015</v>
+      </c>
+      <c r="J179" t="n">
+        <v>3</v>
+      </c>
+      <c r="K179" t="n">
+        <v>2</v>
+      </c>
+      <c r="L179" t="n">
+        <v>2</v>
+      </c>
+      <c r="M179" t="n">
+        <v>3</v>
+      </c>
+      <c r="N179" t="n">
+        <v>5</v>
+      </c>
+      <c r="O179" t="n">
+        <v>3</v>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>Reception splits on minimalism as craft or absence; sources conflict on birth year (1995 vs 1996)</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>Vocal texture as the whole language. Rage's architect, anti-lyricist by design.</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>Whole Lotta Red (2020)</t>
+        </is>
+      </c>
+      <c r="X179" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>SX</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Sexyy Red</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Trap/Drill</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>St. Louis Trap</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Open Shift/gamma</t>
+        </is>
+      </c>
+      <c r="I180" t="n">
+        <v>2018</v>
+      </c>
+      <c r="J180" t="n">
+        <v>4</v>
+      </c>
+      <c r="K180" t="n">
+        <v>3</v>
+      </c>
+      <c r="L180" t="n">
+        <v>4</v>
+      </c>
+      <c r="M180" t="n">
+        <v>4</v>
+      </c>
+      <c r="N180" t="n">
+        <v>3</v>
+      </c>
+      <c r="O180" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>Very recent; critical writing thin, cultural footprint large</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>St. Louis raunch as folk art. Zero filter, total conviction.</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>Hood Hottest Princess (2023)</t>
+        </is>
+      </c>
+      <c r="X180" t="n">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Ice Spice</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>East Coast</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Trap/Drill</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Bronx Drill</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>10K Projects/Capitol</t>
+        </is>
+      </c>
+      <c r="I181" t="n">
+        <v>2021</v>
+      </c>
+      <c r="J181" t="n">
+        <v>4</v>
+      </c>
+      <c r="K181" t="n">
+        <v>3</v>
+      </c>
+      <c r="L181" t="n">
+        <v>3</v>
+      </c>
+      <c r="M181" t="n">
+        <v>4</v>
+      </c>
+      <c r="N181" t="n">
+        <v>3</v>
+      </c>
+      <c r="O181" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>Breakout very recent; defining work is an EP the signature rule excludes (ruling logged in codebook)</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>Bronx drill gone bubblegum. The whisper that ate 2023.</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>Y2K! (2024)</t>
+        </is>
+      </c>
+      <c r="X181" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>FM</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Flo Milli</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Party/Pop</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Playful Pop Trap</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>'94 Sounds/RCA</t>
+        </is>
+      </c>
+      <c r="I182" t="n">
+        <v>2018</v>
+      </c>
+      <c r="J182" t="n">
+        <v>6</v>
+      </c>
+      <c r="K182" t="n">
+        <v>4</v>
+      </c>
+      <c r="L182" t="n">
+        <v>4</v>
+      </c>
+      <c r="M182" t="n">
+        <v>6</v>
+      </c>
+      <c r="N182" t="n">
+        <v>4</v>
+      </c>
+      <c r="O182" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>Acclaimed debut tape; the longer arc is still forming</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>Bratty precision out of Mobile. Cheerleader cadence, killer instinct.</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>Ho, Why Is You Here? (2020)</t>
+        </is>
+      </c>
+      <c r="X182" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>DOJ</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Doja Cat</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>West Coast</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Party/Pop</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Pop-Rap/Funk</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Kemosabe/RCA</t>
+        </is>
+      </c>
+      <c r="I183" t="n">
+        <v>2014</v>
+      </c>
+      <c r="J183" t="n">
+        <v>6</v>
+      </c>
+      <c r="K183" t="n">
+        <v>5</v>
+      </c>
+      <c r="L183" t="n">
+        <v>3</v>
+      </c>
+      <c r="M183" t="n">
+        <v>5</v>
+      </c>
+      <c r="N183" t="n">
+        <v>4</v>
+      </c>
+      <c r="O183" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>Critical record centers pop craft; rap-focused analysis thinner</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>Internet-native shapeshifter. Pop instinct carried by real rap technique.</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>Planet Her (2021)</t>
+        </is>
+      </c>
+      <c r="X183" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>BFR</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Babyface Ray</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>2020s</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Gangsta/Street</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Detroit Wave</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Wavy Gang/Empire</t>
+        </is>
+      </c>
+      <c r="I184" t="n">
+        <v>2015</v>
+      </c>
+      <c r="J184" t="n">
+        <v>4</v>
+      </c>
+      <c r="K184" t="n">
+        <v>4</v>
+      </c>
+      <c r="L184" t="n">
+        <v>5</v>
+      </c>
+      <c r="M184" t="n">
+        <v>5</v>
+      </c>
+      <c r="N184" t="n">
+        <v>4</v>
+      </c>
+      <c r="O184" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>Detroit scene figurehead; national critical attention arrived only in the 2020s</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>Detroit's unbothered dean. Effortless cool over off-kilter keys.</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>FACE (2022)</t>
+        </is>
+      </c>
+      <c r="X184" t="n">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Rah Digga</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>East Coast</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>2000s</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Conscious/Lyrical</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Flipmode Boom Bap</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Flipmode/Elektra</t>
+        </is>
+      </c>
+      <c r="I185" t="n">
+        <v>1999</v>
+      </c>
+      <c r="J185" t="n">
+        <v>7</v>
+      </c>
+      <c r="K185" t="n">
+        <v>6</v>
+      </c>
+      <c r="L185" t="n">
+        <v>5</v>
+      </c>
+      <c r="M185" t="n">
+        <v>6</v>
+      </c>
+      <c r="N185" t="n">
+        <v>6</v>
+      </c>
+      <c r="O185" t="n">
+        <v>6</v>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>One classic album; the catalog thins after it</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>Flipmode's First Lady. Bar for bar with any man in the cipher.</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>Dirty Harriet (2000)</t>
+        </is>
+      </c>
+      <c r="W185" t="n">
+        <v>2010</v>
+      </c>
+      <c r="X185" t="n">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>GB2</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Gangsta Boo</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Late 90s</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Gangsta/Street</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Memphis Horrorcore</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Hypnotize Minds</t>
+        </is>
+      </c>
+      <c r="I186" t="n">
+        <v>1998</v>
+      </c>
+      <c r="J186" t="n">
+        <v>6</v>
+      </c>
+      <c r="K186" t="n">
+        <v>4</v>
+      </c>
+      <c r="L186" t="n">
+        <v>5</v>
+      </c>
+      <c r="M186" t="n">
+        <v>5</v>
+      </c>
+      <c r="N186" t="n">
+        <v>4</v>
+      </c>
+      <c r="O186" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>Memphis pioneer; serious critical reappraisal came late</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>The Devil's Daughter. Memphis menace with a technician's tongue.</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>Enquiring Minds (1998)</t>
+        </is>
+      </c>
+      <c r="W186" t="n">
+        <v>2023</v>
+      </c>
+      <c r="X186" t="n">
+        <v>1979</v>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>Three 6 Mafia</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>YM</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Young M.A</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>East Coast</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Gangsta/Street</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Brooklyn Street</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>M.A Music</t>
+        </is>
+      </c>
+      <c r="I187" t="n">
+        <v>2016</v>
+      </c>
+      <c r="J187" t="n">
+        <v>6</v>
+      </c>
+      <c r="K187" t="n">
+        <v>4</v>
+      </c>
+      <c r="L187" t="n">
+        <v>5</v>
+      </c>
+      <c r="M187" t="n">
+        <v>5</v>
+      </c>
+      <c r="N187" t="n">
+        <v>4</v>
+      </c>
+      <c r="O187" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>One studio album; freestyle pedigree outruns the album record</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>East New York, no persona. Punchlines with dead-eye delivery.</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>Herstory in the Making (2019)</t>
+        </is>
+      </c>
+      <c r="X187" t="n">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>KA</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Kamaiyah</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>West Coast</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>2010s</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Party/Pop</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>G-Funk Revival</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>4Hunnid/Interscope</t>
+        </is>
+      </c>
+      <c r="I188" t="n">
+        <v>2015</v>
+      </c>
+      <c r="J188" t="n">
+        <v>4</v>
+      </c>
+      <c r="K188" t="n">
+        <v>3</v>
+      </c>
+      <c r="L188" t="n">
+        <v>4</v>
+      </c>
+      <c r="M188" t="n">
+        <v>5</v>
+      </c>
+      <c r="N188" t="n">
+        <v>4</v>
+      </c>
+      <c r="O188" t="n">
+        <v>4</v>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>One beloved tape; momentum stalled in label limbo</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>Oakland sunshine in a 90s wrapper. Joy as a flex.</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>Bay Area</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>A Good Night in the Ghetto (2016)</t>
+        </is>
+      </c>
+      <c r="X188" t="n">
+        <v>1992</v>
       </c>
     </row>
   </sheetData>
@@ -18496,18 +19972,34 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>Member Of</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>Compound names from this table; blank = no in-table group</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>The Compound(s) the Element belongs to when the group also has a row of its own: the table's bonds. Recorded only when both sides have a tile, so blank means no bond here, not no group history. Multiple bonds are separated with a semicolon (El-P: Company Flow; Run The Jewels).</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>Group membership per the public record. Stored on the Element side only; the table derives each Compound's member list from this column at render time.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="inlineStr">
-        <is>
-          <t>SAMPLING FRAME &amp; SCOPE RULES</t>
-        </is>
-      </c>
+      <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
@@ -18516,14 +20008,10 @@
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>Population</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>US-based hip-hop acts with a national critical record, 1973–present.</t>
-        </is>
-      </c>
+          <t>SAMPLING FRAME &amp; SCOPE RULES</t>
+        </is>
+      </c>
+      <c r="B28" s="17"/>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
@@ -18531,12 +20019,12 @@
     <row r="29">
       <c r="A29" s="18" t="inlineStr">
         <is>
-          <t>Inclusion</t>
+          <t>Population</t>
         </is>
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>US-born or US-scene-based acts affiliated with a US label/scene during their defining run.</t>
+          <t>US-based hip-hop acts with a national critical record, 1973–present.</t>
         </is>
       </c>
       <c r="C29" s="17"/>
@@ -18546,12 +20034,12 @@
     <row r="30">
       <c r="A30" s="18" t="inlineStr">
         <is>
-          <t>Exclusion</t>
+          <t>Inclusion</t>
         </is>
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>International and UK acts (scope decision to keep the frame tractable); acts without national critical coverage (survivorship limitation, documented).</t>
+          <t>US-born or US-scene-based acts affiliated with a US label/scene during their defining run.</t>
         </is>
       </c>
       <c r="C30" s="17"/>
@@ -18561,12 +20049,12 @@
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>Unit of analysis</t>
+          <t>Exclusion</t>
         </is>
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>The act (solo artist or group). Groups are Compounds; solo careers are Elements; both may appear.</t>
+          <t>International and UK acts (scope decision to keep the frame tractable); acts without national critical coverage (survivorship limitation, documented).</t>
         </is>
       </c>
       <c r="C31" s="17"/>
@@ -18576,12 +20064,12 @@
     <row r="32">
       <c r="A32" s="18" t="inlineStr">
         <is>
-          <t>Known frame biases</t>
+          <t>Unit of analysis</t>
         </is>
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>Over-represents critical acclaim, NYC, Golden Age, and men. See Confidence Guide sheet for the full bias table.</t>
+          <t>The act (solo artist or group). Groups are Compounds; solo careers are Elements; both may appear.</t>
         </is>
       </c>
       <c r="C32" s="17"/>
@@ -18591,106 +20079,121 @@
     <row r="33">
       <c r="A33" s="18" t="inlineStr">
         <is>
-          <t>STYLE TAXONOMY</t>
+          <t>Known frame biases</t>
         </is>
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>One value per act: the dominant mode of the defining run, judged from critical descriptions. Tiebreak: if the strangeness lives in the words it is Abstract; if it lives in the sound or form it is Experimental.</t>
-        </is>
-      </c>
+          <t>Over-represents critical acclaim, NYC, Golden Age, and men. See Confidence Guide sheet for the full bias table.</t>
+        </is>
+      </c>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
     </row>
     <row r="34">
       <c r="A34" s="18" t="inlineStr">
         <is>
-          <t>Party/Pop</t>
+          <t>STYLE TAXONOMY</t>
         </is>
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>Crowd-first rap: hooks, humor, dance, and radio crossover are the dominant mode; the room matters more than the page. Anchor: Salt-N-Pepa.</t>
+          <t>One value per act: the dominant mode of the defining run, judged from critical descriptions. Tiebreak: if the strangeness lives in the words it is Abstract; if it lives in the sound or form it is Experimental.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="18" t="inlineStr">
         <is>
-          <t>Political</t>
+          <t>Party/Pop</t>
         </is>
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>An explicit political program or protest organizes the catalog; the message is the mode, not an occasional topic. Anchor: Public Enemy.</t>
+          <t>Crowd-first rap: hooks, humor, dance, and radio crossover are the dominant mode; the room matters more than the page. Anchor: Salt-N-Pepa.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="18" t="inlineStr">
         <is>
-          <t>Conscious/Lyrical</t>
+          <t>Political</t>
         </is>
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>Craft-and-substance writing: introspection, social observation, and technical pen as the dominant mode. Absorbs the former Conscious/Street label. Anchor: Nas.</t>
+          <t>An explicit political program or protest organizes the catalog; the message is the mode, not an occasional topic. Anchor: Public Enemy.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="18" t="inlineStr">
         <is>
-          <t>Gangsta/Street</t>
+          <t>Conscious/Lyrical</t>
         </is>
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>Street narrative and persona as the primary subject: reportage, hustling economics, survival stakes. Anchor: N.W.A.</t>
+          <t>Craft-and-substance writing: introspection, social observation, and technical pen as the dominant mode. Absorbs the former Conscious/Street label. Anchor: Nas.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="18" t="inlineStr">
         <is>
-          <t>Abstract</t>
+          <t>Gangsta/Street</t>
         </is>
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>Pen-first left field: oblique, allusive, nonlinear writing; the strangeness lives in the language itself. Anchor: MF DOOM.</t>
+          <t>Street narrative and persona as the primary subject: reportage, hustling economics, survival stakes. Anchor: N.W.A.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>Jazz-Rap</t>
+          <t>Abstract</t>
         </is>
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>The early-90s jazz-sample movement: live-jazz textures, conversational flow, bohemian scene ties. A scene-and-era label; later jazz-inflected acts take their dominant mode instead. Anchor: A Tribe Called Quest.</t>
+          <t>Pen-first left field: oblique, allusive, nonlinear writing; the strangeness lives in the language itself. Anchor: MF DOOM.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="18" t="inlineStr">
         <is>
-          <t>Experimental</t>
+          <t>Jazz-Rap</t>
         </is>
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>Form-first left field: production, song structure, or vocal approach breaks convention even when the writing is conventional. Anchor: Missy Elliott.</t>
+          <t>The early-90s jazz-sample movement: live-jazz textures, conversational flow, bohemian scene ties. A scene-and-era label; later jazz-inflected acts take their dominant mode instead. Anchor: A Tribe Called Quest.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="18" t="inlineStr">
         <is>
+          <t>Experimental</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>Form-first left field: production, song structure, or vocal approach breaks convention even when the writing is conventional. Anchor: Missy Elliott.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="18" t="inlineStr">
+        <is>
           <t>Trap/Drill</t>
         </is>
       </c>
-      <c r="B41" s="17" t="inlineStr">
+      <c r="B42" s="17" t="inlineStr">
         <is>
           <t>The trap and drill sound family: 808-driven production with melodic, chanted, or sung delivery; cadence and vibe carry more than lyric density. Anchor: Future.</t>
         </is>

--- a/hiphop/data/hiphop_artists.xlsx
+++ b/hiphop/data/hiphop_artists.xlsx
@@ -20199,6 +20199,85 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="17"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="17"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>SCORING LADDERS</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>One ladder per dimension: the top anchor, calibration rungs from this table, and a defined floor. A score is a placement: the rung the act sits nearest, between rungs when the record says between. Rungs name acts whose stored score equals the rung, so the ladder stays honest as scores change. The floor is defined but unoccupied: the sampling frame requires a national critical record, which excludes the construct's true bottom by design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="17" t="inlineStr">
+        <is>
+          <t>Rhyme Density</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t>10 Rakim (anchor) · 8 Jay-Z · 6 LL Cool J · 4 Migos · 1 = spoken cadence with no worked rhyme scheme</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="17" t="inlineStr">
+        <is>
+          <t>Vocab Breadth</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="inlineStr">
+        <is>
+          <t>10 Aesop Rock (anchor) · 8 Busta Rhymes · 6 50 Cent · 4 21 Savage · 1 = a small stock vocabulary, reused catalog-wide</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="17" t="inlineStr">
+        <is>
+          <t>Storytelling</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="inlineStr">
+        <is>
+          <t>10 Scarface (anchor) · 8 OutKast · 6 Ludacris · 4 Young Thug · 1 = no narrative construction anywhere in the catalog</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="17" t="inlineStr">
+        <is>
+          <t>Metaphor/Imagery</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="inlineStr">
+        <is>
+          <t>10 Lil Wayne (anchor) · 8 Nicki Minaj · 6 Future · 4 Pop Smoke · 1 = entirely literal writing</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="17" t="inlineStr">
+        <is>
+          <t>Conceptual Depth</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>10 Kendrick Lamar (anchor) · 8 Biggie · 6 DMX · 4 Gucci Mane · 1 = no sustained idea across any project</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
